--- a/pc.xlsx
+++ b/pc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D71DD05-6815-4B94-B707-DBA381E2ED70}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FFBB936C-775F-4998-8C51-BB0EBC58EB72}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="110">
   <si>
     <t>Cod. producto</t>
   </si>
@@ -130,37 +130,55 @@
     <t>Bomba P50 Engranaje 2.1/2" Eje Z14 Trompa 5"x4" Giro Derecho S1.1/2"-P1.1/4" 200L</t>
   </si>
   <si>
+    <t>FILT-10MZ10</t>
+  </si>
+  <si>
+    <t>ELEMENTO FILTRO HIDRAULICO 10MIC SPIN-ON LARGO 10"</t>
+  </si>
+  <si>
+    <t>SOL - 2030</t>
+  </si>
+  <si>
+    <t>FILT-MZ10</t>
+  </si>
+  <si>
+    <t>ELEMENTO FILTRO HIDRAULICO 10MIC SPIN-ON LARGO 7"</t>
+  </si>
+  <si>
     <t>RETEN-6002</t>
   </si>
   <si>
-    <t>SOL - 2030</t>
-  </si>
-  <si>
-    <t>FILT-10MZ10</t>
-  </si>
-  <si>
-    <t>ELEMENTO FILTRO HIDRAULICO 10MIC SPIN-ON LARGO 10"</t>
-  </si>
-  <si>
-    <t>FILT-MZ10</t>
-  </si>
-  <si>
-    <t>ELEMENTO FILTRO HIDRAULICO 10MIC SPIN-ON LARGO 7"</t>
-  </si>
-  <si>
-    <t>HTX-24-16P</t>
-  </si>
-  <si>
-    <t>ADAP RECTO DOBLE MF JIC 1.7/8" X 1.5/16" UNF</t>
+    <t>HTX-24-20P</t>
+  </si>
+  <si>
+    <t>ADAP RECTO DOBLE MF JIC 1.7/8" X 1.5/8" UNF</t>
   </si>
   <si>
     <t>SOL - 2032</t>
   </si>
   <si>
-    <t>HTX-24-20P</t>
-  </si>
-  <si>
-    <t>ADAP RECTO DOBLE MF JIC 1.7/8" X 1.5/8" UNF</t>
+    <t>10643-16-12P</t>
+  </si>
+  <si>
+    <t>TERMINAL HG JIC 1 5/16"  X MANGUERA 3/4"</t>
+  </si>
+  <si>
+    <t>SOL - 2033</t>
+  </si>
+  <si>
+    <t>CD Buenos Aires</t>
+  </si>
+  <si>
+    <t>1JC77-16-16P</t>
+  </si>
+  <si>
+    <t>TERMINAL RECTO HG 1.7/16" AS PLANO X MANGUERA R15 1"</t>
+  </si>
+  <si>
+    <t>1JC77-20-20P</t>
+  </si>
+  <si>
+    <t>TERMINAL RECTO HG 1.11/16" AS PLANO X MANGUERA R15 1.1/4"</t>
   </si>
   <si>
     <t>JK-06P</t>
@@ -169,28 +187,37 @@
     <t>MANGUERA JACK HOSE 3/8</t>
   </si>
   <si>
-    <t>SOL - 2033</t>
-  </si>
-  <si>
-    <t>CD Buenos Aires</t>
-  </si>
-  <si>
-    <t>10643-16-12P</t>
-  </si>
-  <si>
-    <t>TERMINAL HG JIC 1 5/16"  X MANGUERA 3/4"</t>
-  </si>
-  <si>
-    <t>1JC77-16-16P</t>
-  </si>
-  <si>
-    <t>TERMINAL RECTO HG 1.7/16" AS PLANO X MANGUERA R15 1"</t>
-  </si>
-  <si>
-    <t>1JC77-20-20P</t>
-  </si>
-  <si>
-    <t>TERMINAL RECTO HG 1.11/16" AS PLANO X MANGUERA R15 1.1/4"</t>
+    <t>ANV 38 NPT F</t>
+  </si>
+  <si>
+    <t>ACOPLE RAPIDO HEMBRA C/ROSCA HEMBRA DE 3/8" NPT FASTER</t>
+  </si>
+  <si>
+    <t>SOL - 2034</t>
+  </si>
+  <si>
+    <t>ANV 38 NPT M</t>
+  </si>
+  <si>
+    <t>ACOPLE RAPIDO MACHO C/ROSCA HEMBRA DE 3/8" NPT FASTER</t>
+  </si>
+  <si>
+    <t>FFH20 114NPT F</t>
+  </si>
+  <si>
+    <t>ACOPLE FRENTE PLANO 1.1/4" HEMBRA CON ROSCA HEMBRA DE 1.1/4" NPT</t>
+  </si>
+  <si>
+    <t>FFH20 114NPT M</t>
+  </si>
+  <si>
+    <t>ACOPLE FRENTE PLANO 1.1/4" MACHO CON ROSCA HEMBRA DE 1.1/4" NPT</t>
+  </si>
+  <si>
+    <t>T2F2</t>
+  </si>
+  <si>
+    <t>ACOPLE RAPIDO NIPLE 1/4" X HEMBRA 1/4" NPT 10.000PSI</t>
   </si>
   <si>
     <t>2TM2</t>
@@ -199,39 +226,6 @@
     <t>ACOPLE RAPIDO CUPLA 1/4" X MACHO 1/4" NPT 10.000PSI</t>
   </si>
   <si>
-    <t>SOL - 2034</t>
-  </si>
-  <si>
-    <t>ANV 38 NPT F</t>
-  </si>
-  <si>
-    <t>ACOPLE RAPIDO HEMBRA C/ROSCA HEMBRA DE 3/8" NPT FASTER</t>
-  </si>
-  <si>
-    <t>ANV 38 NPT M</t>
-  </si>
-  <si>
-    <t>ACOPLE RAPIDO MACHO C/ROSCA HEMBRA DE 3/8" NPT FASTER</t>
-  </si>
-  <si>
-    <t>T2F2</t>
-  </si>
-  <si>
-    <t>ACOPLE RAPIDO NIPLE 1/4" X HEMBRA 1/4" NPT 10.000PSI</t>
-  </si>
-  <si>
-    <t>FFH20 114NPT F</t>
-  </si>
-  <si>
-    <t>ACOPLE FRENTE PLANO 1.1/4" HEMBRA CON ROSCA HEMBRA DE 1.1/4" NPT</t>
-  </si>
-  <si>
-    <t>FFH20 114NPT M</t>
-  </si>
-  <si>
-    <t>ACOPLE FRENTE PLANO 1.1/4" MACHO CON ROSCA HEMBRA DE 1.1/4" NPT</t>
-  </si>
-  <si>
     <t>F5OG-10-1/2P</t>
   </si>
   <si>
@@ -241,12 +235,6 @@
     <t>SOL - 2035</t>
   </si>
   <si>
-    <t>F5OX-06-08P</t>
-  </si>
-  <si>
-    <t>ADAP MF 9/16" AS JIC 37° X MF 3/4" AS ORING</t>
-  </si>
-  <si>
     <t>HTX-20-16P</t>
   </si>
   <si>
@@ -292,82 +280,76 @@
     <t>00884</t>
   </si>
   <si>
-    <t>FSE10-1/2</t>
-  </si>
-  <si>
-    <t>CONECTOR CODO 90° AIRE P/TECALAN DE 10MM X MF 1/2" NPT</t>
-  </si>
-  <si>
-    <t>SOL - 2112</t>
+    <t>HERR Y CENTRALES HCAS</t>
+  </si>
+  <si>
+    <t>HERRAMIENTAS Y CENTRALES HIDRAULICAS - GENERICO</t>
+  </si>
+  <si>
+    <t>SOL - 2139</t>
+  </si>
+  <si>
+    <t>00903</t>
   </si>
   <si>
     <t>2026-05</t>
   </si>
   <si>
-    <t>FUE-12</t>
-  </si>
-  <si>
-    <t>CONECTOR RECTO EMPALME AIRE P/TECALAN DE 12MM</t>
-  </si>
-  <si>
-    <t>313-2812-000P</t>
-  </si>
-  <si>
-    <t>JUEGO ENGRANAJE P50 DE 1 1/4"</t>
-  </si>
-  <si>
-    <t>SOL - 2124</t>
-  </si>
-  <si>
-    <t>00895</t>
-  </si>
-  <si>
-    <t>313-8212-100</t>
-  </si>
-  <si>
-    <t>CUERPO P50 PARA ENGRANAJE DE 1 1/4"</t>
-  </si>
-  <si>
-    <t>CV INSUMOS TALLER</t>
-  </si>
-  <si>
-    <t>Insumos - Materiales Taller</t>
-  </si>
-  <si>
-    <t>SOL - 2125</t>
-  </si>
-  <si>
-    <t>00896</t>
-  </si>
-  <si>
-    <t>CF200-10CS</t>
-  </si>
-  <si>
-    <t>CAMISA PARA PRENSAR BAJA PRESION 2" DIAM INT 67.00 MM - 20 BAR</t>
-  </si>
-  <si>
-    <t>SOL - 2129</t>
-  </si>
-  <si>
-    <t>CF300-10CS</t>
-  </si>
-  <si>
-    <t>CAMISA PARA PRENSAR BAJA PRESION 3" DIAM INT 94.00 MM - 15 BAR</t>
-  </si>
-  <si>
-    <t>CF400-10CS</t>
-  </si>
-  <si>
-    <t>CAMISA PARA PRENSAR BAJA PRESION 4" DIAM INT 120.7 MM - 10 BAR</t>
-  </si>
-  <si>
-    <t>391-2883-119P</t>
-  </si>
-  <si>
-    <t>RETEN M-30 P/EJE ENTERIZO</t>
-  </si>
-  <si>
-    <t>SOL - 2131</t>
+    <t>SOL - 2140</t>
+  </si>
+  <si>
+    <t>00904</t>
+  </si>
+  <si>
+    <t>SOL - 2141</t>
+  </si>
+  <si>
+    <t>00905</t>
+  </si>
+  <si>
+    <t>FILTRO HIDRAULICO</t>
+  </si>
+  <si>
+    <t>FILTRO HIDRAULICO - GENERICO</t>
+  </si>
+  <si>
+    <t>SOL - 2142</t>
+  </si>
+  <si>
+    <t>00906</t>
+  </si>
+  <si>
+    <t>76581002</t>
+  </si>
+  <si>
+    <t>MANG. DE PVC CON ESPIRAL DE ACERO ASP/EXP GRADO ALIMENT.RAUSPIRAFLEX M 50 MM</t>
+  </si>
+  <si>
+    <t>SOL - 2143</t>
+  </si>
+  <si>
+    <t>710308065</t>
+  </si>
+  <si>
+    <t>TERMINAL RECTO HG JIC 9/16" UNF X MANGUERA 1/4" G25170-0406 4G-6FJX</t>
+  </si>
+  <si>
+    <t>FT 257/5-14</t>
+  </si>
+  <si>
+    <t>VALVULA AGUJA UNIDIRECCIONAL 1/4" - 350 BAR 15 LT</t>
+  </si>
+  <si>
+    <t>SOL - 2145</t>
+  </si>
+  <si>
+    <t>00816</t>
+  </si>
+  <si>
+    <t>HIDROIL SRL</t>
+  </si>
+  <si>
+    <t>Deposito</t>
   </si>
 </sst>
 </file>
@@ -719,7 +701,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R40"/>
+  <dimension ref="A1:R37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
@@ -1063,16 +1045,16 @@
         <v>36</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
         <v>21</v>
       </c>
       <c r="E7">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
         <v>21</v>
@@ -1081,7 +1063,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="I7" t="s">
         <v>22</v>
@@ -1116,19 +1098,19 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" t="s">
         <v>38</v>
       </c>
-      <c r="B8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" t="s">
-        <v>37</v>
-      </c>
       <c r="D8" t="s">
         <v>21</v>
       </c>
       <c r="E8">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F8" t="s">
         <v>21</v>
@@ -1137,7 +1119,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I8" t="s">
         <v>22</v>
@@ -1172,19 +1154,19 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B9" t="s">
         <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
         <v>21</v>
       </c>
       <c r="E9">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F9" t="s">
         <v>21</v>
@@ -1193,7 +1175,7 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I9" t="s">
         <v>22</v>
@@ -1290,13 +1272,13 @@
         <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s">
         <v>21</v>
       </c>
       <c r="E11">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F11" t="s">
         <v>21</v>
@@ -1305,7 +1287,7 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I11" t="s">
         <v>22</v>
@@ -1320,7 +1302,7 @@
         <v>25</v>
       </c>
       <c r="M11" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="N11" t="s">
         <v>21</v>
@@ -1340,19 +1322,19 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" t="s">
         <v>47</v>
       </c>
-      <c r="B12" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" t="s">
-        <v>49</v>
-      </c>
       <c r="D12" t="s">
         <v>21</v>
       </c>
       <c r="E12">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="F12" t="s">
         <v>21</v>
@@ -1361,7 +1343,7 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="I12" t="s">
         <v>22</v>
@@ -1376,7 +1358,7 @@
         <v>25</v>
       </c>
       <c r="M12" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N12" t="s">
         <v>21</v>
@@ -1402,13 +1384,13 @@
         <v>52</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
         <v>21</v>
       </c>
       <c r="E13">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F13" t="s">
         <v>21</v>
@@ -1417,7 +1399,7 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="I13" t="s">
         <v>22</v>
@@ -1432,7 +1414,7 @@
         <v>25</v>
       </c>
       <c r="M13" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N13" t="s">
         <v>21</v>
@@ -1458,13 +1440,13 @@
         <v>54</v>
       </c>
       <c r="C14" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D14" t="s">
         <v>21</v>
       </c>
       <c r="E14">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="F14" t="s">
         <v>21</v>
@@ -1473,7 +1455,7 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="I14" t="s">
         <v>22</v>
@@ -1488,7 +1470,7 @@
         <v>25</v>
       </c>
       <c r="M14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N14" t="s">
         <v>21</v>
@@ -1514,13 +1496,13 @@
         <v>56</v>
       </c>
       <c r="C15" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="D15" t="s">
         <v>21</v>
       </c>
       <c r="E15">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="F15" t="s">
         <v>21</v>
@@ -1529,7 +1511,7 @@
         <v>0</v>
       </c>
       <c r="H15">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="I15" t="s">
         <v>22</v>
@@ -1544,7 +1526,7 @@
         <v>25</v>
       </c>
       <c r="M15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N15" t="s">
         <v>21</v>
@@ -1564,19 +1546,19 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" t="s">
         <v>57</v>
       </c>
-      <c r="B16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C16" t="s">
-        <v>59</v>
-      </c>
       <c r="D16" t="s">
         <v>21</v>
       </c>
       <c r="E16">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="F16" t="s">
         <v>21</v>
@@ -1585,7 +1567,7 @@
         <v>0</v>
       </c>
       <c r="H16">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="I16" t="s">
         <v>22</v>
@@ -1600,7 +1582,7 @@
         <v>25</v>
       </c>
       <c r="M16" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N16" t="s">
         <v>21</v>
@@ -1626,13 +1608,13 @@
         <v>61</v>
       </c>
       <c r="C17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D17" t="s">
         <v>21</v>
       </c>
       <c r="E17">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F17" t="s">
         <v>21</v>
@@ -1641,7 +1623,7 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="I17" t="s">
         <v>22</v>
@@ -1656,7 +1638,7 @@
         <v>25</v>
       </c>
       <c r="M17" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N17" t="s">
         <v>21</v>
@@ -1682,13 +1664,13 @@
         <v>63</v>
       </c>
       <c r="C18" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D18" t="s">
         <v>21</v>
       </c>
       <c r="E18">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F18" t="s">
         <v>21</v>
@@ -1697,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="H18">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I18" t="s">
         <v>22</v>
@@ -1712,7 +1694,7 @@
         <v>25</v>
       </c>
       <c r="M18" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N18" t="s">
         <v>21</v>
@@ -1738,7 +1720,7 @@
         <v>65</v>
       </c>
       <c r="C19" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D19" t="s">
         <v>21</v>
@@ -1768,7 +1750,7 @@
         <v>25</v>
       </c>
       <c r="M19" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N19" t="s">
         <v>21</v>
@@ -1794,13 +1776,13 @@
         <v>67</v>
       </c>
       <c r="C20" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D20" t="s">
         <v>21</v>
       </c>
       <c r="E20">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="F20" t="s">
         <v>21</v>
@@ -1809,7 +1791,7 @@
         <v>0</v>
       </c>
       <c r="H20">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="I20" t="s">
         <v>22</v>
@@ -1824,7 +1806,7 @@
         <v>25</v>
       </c>
       <c r="M20" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N20" t="s">
         <v>21</v>
@@ -1850,13 +1832,13 @@
         <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="D21" t="s">
         <v>21</v>
       </c>
       <c r="E21">
-        <v>300</v>
+        <v>10</v>
       </c>
       <c r="F21" t="s">
         <v>21</v>
@@ -1865,7 +1847,7 @@
         <v>0</v>
       </c>
       <c r="H21">
-        <v>300</v>
+        <v>10</v>
       </c>
       <c r="I21" t="s">
         <v>22</v>
@@ -1880,7 +1862,7 @@
         <v>25</v>
       </c>
       <c r="M21" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N21" t="s">
         <v>21</v>
@@ -1900,19 +1882,19 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>71</v>
+      </c>
+      <c r="B22" t="s">
+        <v>72</v>
+      </c>
+      <c r="C22" t="s">
         <v>70</v>
       </c>
-      <c r="B22" t="s">
-        <v>71</v>
-      </c>
-      <c r="C22" t="s">
-        <v>72</v>
-      </c>
       <c r="D22" t="s">
         <v>21</v>
       </c>
       <c r="E22">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F22" t="s">
         <v>21</v>
@@ -1921,7 +1903,7 @@
         <v>0</v>
       </c>
       <c r="H22">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I22" t="s">
         <v>22</v>
@@ -1936,7 +1918,7 @@
         <v>25</v>
       </c>
       <c r="M22" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N22" t="s">
         <v>21</v>
@@ -1962,13 +1944,13 @@
         <v>74</v>
       </c>
       <c r="C23" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D23" t="s">
         <v>21</v>
       </c>
       <c r="E23">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F23" t="s">
         <v>21</v>
@@ -1977,7 +1959,7 @@
         <v>0</v>
       </c>
       <c r="H23">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="I23" t="s">
         <v>22</v>
@@ -1992,7 +1974,7 @@
         <v>25</v>
       </c>
       <c r="M23" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N23" t="s">
         <v>21</v>
@@ -2012,19 +1994,19 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24" t="s">
+        <v>74</v>
+      </c>
+      <c r="C24" t="s">
         <v>75</v>
       </c>
-      <c r="B24" t="s">
-        <v>76</v>
-      </c>
-      <c r="C24" t="s">
-        <v>72</v>
-      </c>
       <c r="D24" t="s">
         <v>21</v>
       </c>
       <c r="E24">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F24" t="s">
         <v>21</v>
@@ -2033,7 +2015,7 @@
         <v>0</v>
       </c>
       <c r="H24">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="I24" t="s">
         <v>22</v>
@@ -2048,7 +2030,7 @@
         <v>25</v>
       </c>
       <c r="M24" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N24" t="s">
         <v>21</v>
@@ -2068,13 +2050,13 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B25" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C25" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D25" t="s">
         <v>21</v>
@@ -2104,7 +2086,7 @@
         <v>25</v>
       </c>
       <c r="M25" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N25" t="s">
         <v>21</v>
@@ -2124,19 +2106,19 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B26" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C26" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D26" t="s">
         <v>21</v>
       </c>
       <c r="E26">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F26" t="s">
         <v>21</v>
@@ -2145,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="H26">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I26" t="s">
         <v>22</v>
@@ -2160,7 +2142,7 @@
         <v>25</v>
       </c>
       <c r="M26" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N26" t="s">
         <v>21</v>
@@ -2180,19 +2162,19 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B27" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C27" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D27" t="s">
         <v>21</v>
       </c>
       <c r="E27">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F27" t="s">
         <v>21</v>
@@ -2201,7 +2183,7 @@
         <v>0</v>
       </c>
       <c r="H27">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I27" t="s">
         <v>22</v>
@@ -2216,7 +2198,7 @@
         <v>25</v>
       </c>
       <c r="M27" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N27" t="s">
         <v>21</v>
@@ -2236,19 +2218,19 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B28" t="s">
         <v>77</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>78</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>79</v>
       </c>
-      <c r="D28" t="s">
-        <v>21</v>
-      </c>
       <c r="E28">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="F28" t="s">
         <v>21</v>
@@ -2257,7 +2239,7 @@
         <v>0</v>
       </c>
       <c r="H28">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I28" t="s">
         <v>22</v>
@@ -2266,13 +2248,13 @@
         <v>23</v>
       </c>
       <c r="K28" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="L28" t="s">
         <v>25</v>
       </c>
       <c r="M28" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="N28" t="s">
         <v>21</v>
@@ -2292,19 +2274,19 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B29" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C29" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D29" t="s">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="E29">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="F29" t="s">
         <v>21</v>
@@ -2313,7 +2295,7 @@
         <v>0</v>
       </c>
       <c r="H29">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I29" t="s">
         <v>22</v>
@@ -2322,13 +2304,13 @@
         <v>23</v>
       </c>
       <c r="K29" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="L29" t="s">
         <v>25</v>
       </c>
       <c r="M29" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="N29" t="s">
         <v>21</v>
@@ -2348,43 +2330,43 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>86</v>
+      </c>
+      <c r="B30" t="s">
+        <v>87</v>
+      </c>
+      <c r="C30" t="s">
+        <v>88</v>
+      </c>
+      <c r="D30" t="s">
+        <v>89</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30" t="s">
+        <v>21</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="I30" t="s">
+        <v>22</v>
+      </c>
+      <c r="J30" t="s">
+        <v>90</v>
+      </c>
+      <c r="K30" t="s">
         <v>80</v>
       </c>
-      <c r="B30" t="s">
+      <c r="L30" t="s">
+        <v>25</v>
+      </c>
+      <c r="M30" t="s">
         <v>81</v>
-      </c>
-      <c r="C30" t="s">
-        <v>82</v>
-      </c>
-      <c r="D30" t="s">
-        <v>83</v>
-      </c>
-      <c r="E30">
-        <v>90</v>
-      </c>
-      <c r="F30" t="s">
-        <v>21</v>
-      </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
-      <c r="H30">
-        <v>30</v>
-      </c>
-      <c r="I30" t="s">
-        <v>22</v>
-      </c>
-      <c r="J30" t="s">
-        <v>23</v>
-      </c>
-      <c r="K30" t="s">
-        <v>84</v>
-      </c>
-      <c r="L30" t="s">
-        <v>25</v>
-      </c>
-      <c r="M30" t="s">
-        <v>85</v>
       </c>
       <c r="N30" t="s">
         <v>21</v>
@@ -2410,37 +2392,37 @@
         <v>87</v>
       </c>
       <c r="C31" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D31" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E31">
+        <v>1</v>
+      </c>
+      <c r="F31" t="s">
+        <v>21</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>1</v>
+      </c>
+      <c r="I31" t="s">
+        <v>22</v>
+      </c>
+      <c r="J31" t="s">
         <v>90</v>
       </c>
-      <c r="F31" t="s">
-        <v>21</v>
-      </c>
-      <c r="G31">
-        <v>0</v>
-      </c>
-      <c r="H31">
-        <v>30</v>
-      </c>
-      <c r="I31" t="s">
-        <v>22</v>
-      </c>
-      <c r="J31" t="s">
-        <v>23</v>
-      </c>
       <c r="K31" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="L31" t="s">
         <v>25</v>
       </c>
       <c r="M31" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="N31" t="s">
         <v>21</v>
@@ -2460,43 +2442,43 @@
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>86</v>
+      </c>
+      <c r="B32" t="s">
+        <v>87</v>
+      </c>
+      <c r="C32" t="s">
+        <v>93</v>
+      </c>
+      <c r="D32" t="s">
+        <v>94</v>
+      </c>
+      <c r="E32">
+        <v>1</v>
+      </c>
+      <c r="F32" t="s">
+        <v>21</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>1</v>
+      </c>
+      <c r="I32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J32" t="s">
         <v>90</v>
       </c>
-      <c r="B32" t="s">
-        <v>91</v>
-      </c>
-      <c r="C32" t="s">
-        <v>92</v>
-      </c>
-      <c r="D32" t="s">
-        <v>21</v>
-      </c>
-      <c r="E32">
-        <v>50</v>
-      </c>
-      <c r="F32" t="s">
-        <v>21</v>
-      </c>
-      <c r="G32">
-        <v>0</v>
-      </c>
-      <c r="H32">
-        <v>50</v>
-      </c>
-      <c r="I32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J32" t="s">
-        <v>93</v>
-      </c>
       <c r="K32" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="L32" t="s">
         <v>25</v>
       </c>
       <c r="M32" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="N32" t="s">
         <v>21</v>
@@ -2516,19 +2498,19 @@
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B33" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C33" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D33" t="s">
-        <v>21</v>
+        <v>98</v>
       </c>
       <c r="E33">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="F33" t="s">
         <v>21</v>
@@ -2537,22 +2519,22 @@
         <v>0</v>
       </c>
       <c r="H33">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="I33" t="s">
         <v>22</v>
       </c>
       <c r="J33" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="K33" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="L33" t="s">
         <v>25</v>
       </c>
       <c r="M33" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="N33" t="s">
         <v>21</v>
@@ -2572,19 +2554,19 @@
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B34" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C34" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D34" t="s">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="E34">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="F34" t="s">
         <v>21</v>
@@ -2593,22 +2575,22 @@
         <v>0</v>
       </c>
       <c r="H34">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="I34" t="s">
         <v>22</v>
       </c>
       <c r="J34" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="K34" t="s">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="L34" t="s">
         <v>25</v>
       </c>
       <c r="M34" t="s">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="N34" t="s">
         <v>21</v>
@@ -2628,19 +2610,19 @@
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B35" t="s">
+        <v>103</v>
+      </c>
+      <c r="C35" t="s">
         <v>101</v>
       </c>
-      <c r="C35" t="s">
-        <v>98</v>
-      </c>
       <c r="D35" t="s">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="E35">
-        <v>6</v>
+        <v>500</v>
       </c>
       <c r="F35" t="s">
         <v>21</v>
@@ -2649,22 +2631,22 @@
         <v>0</v>
       </c>
       <c r="H35">
-        <v>5</v>
+        <v>500</v>
       </c>
       <c r="I35" t="s">
         <v>22</v>
       </c>
       <c r="J35" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="K35" t="s">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="L35" t="s">
         <v>25</v>
       </c>
       <c r="M35" t="s">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="N35" t="s">
         <v>21</v>
@@ -2684,19 +2666,19 @@
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>102</v>
+        <v>45</v>
       </c>
       <c r="B36" t="s">
-        <v>103</v>
+        <v>46</v>
       </c>
       <c r="C36" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D36" t="s">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="E36">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="F36" t="s">
         <v>21</v>
@@ -2705,22 +2687,22 @@
         <v>0</v>
       </c>
       <c r="H36">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="I36" t="s">
         <v>22</v>
       </c>
       <c r="J36" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="K36" t="s">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="L36" t="s">
         <v>25</v>
       </c>
       <c r="M36" t="s">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="N36" t="s">
         <v>21</v>
@@ -2740,43 +2722,43 @@
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>104</v>
+      </c>
+      <c r="B37" t="s">
+        <v>105</v>
+      </c>
+      <c r="C37" t="s">
         <v>106</v>
       </c>
-      <c r="B37" t="s">
+      <c r="D37" t="s">
         <v>107</v>
       </c>
-      <c r="C37" t="s">
+      <c r="E37">
+        <v>1</v>
+      </c>
+      <c r="F37" t="s">
+        <v>21</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>1</v>
+      </c>
+      <c r="I37" t="s">
+        <v>22</v>
+      </c>
+      <c r="J37" t="s">
+        <v>90</v>
+      </c>
+      <c r="K37" t="s">
         <v>108</v>
       </c>
-      <c r="D37" t="s">
-        <v>21</v>
-      </c>
-      <c r="E37">
-        <v>180</v>
-      </c>
-      <c r="F37" t="s">
-        <v>21</v>
-      </c>
-      <c r="G37">
-        <v>0</v>
-      </c>
-      <c r="H37">
-        <v>180</v>
-      </c>
-      <c r="I37" t="s">
-        <v>22</v>
-      </c>
-      <c r="J37" t="s">
-        <v>93</v>
-      </c>
-      <c r="K37" t="s">
-        <v>24</v>
-      </c>
       <c r="L37" t="s">
         <v>25</v>
       </c>
       <c r="M37" t="s">
-        <v>50</v>
+        <v>109</v>
       </c>
       <c r="N37" t="s">
         <v>21</v>
@@ -2791,174 +2773,6 @@
         <v>21</v>
       </c>
       <c r="R37" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>109</v>
-      </c>
-      <c r="B38" t="s">
-        <v>110</v>
-      </c>
-      <c r="C38" t="s">
-        <v>108</v>
-      </c>
-      <c r="D38" t="s">
-        <v>21</v>
-      </c>
-      <c r="E38">
-        <v>260</v>
-      </c>
-      <c r="F38" t="s">
-        <v>21</v>
-      </c>
-      <c r="G38">
-        <v>0</v>
-      </c>
-      <c r="H38">
-        <v>260</v>
-      </c>
-      <c r="I38" t="s">
-        <v>22</v>
-      </c>
-      <c r="J38" t="s">
-        <v>93</v>
-      </c>
-      <c r="K38" t="s">
-        <v>24</v>
-      </c>
-      <c r="L38" t="s">
-        <v>25</v>
-      </c>
-      <c r="M38" t="s">
-        <v>50</v>
-      </c>
-      <c r="N38" t="s">
-        <v>21</v>
-      </c>
-      <c r="O38" t="s">
-        <v>21</v>
-      </c>
-      <c r="P38" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q38" t="s">
-        <v>21</v>
-      </c>
-      <c r="R38" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>111</v>
-      </c>
-      <c r="B39" t="s">
-        <v>112</v>
-      </c>
-      <c r="C39" t="s">
-        <v>108</v>
-      </c>
-      <c r="D39" t="s">
-        <v>21</v>
-      </c>
-      <c r="E39">
-        <v>660</v>
-      </c>
-      <c r="F39" t="s">
-        <v>21</v>
-      </c>
-      <c r="G39">
-        <v>0</v>
-      </c>
-      <c r="H39">
-        <v>660</v>
-      </c>
-      <c r="I39" t="s">
-        <v>22</v>
-      </c>
-      <c r="J39" t="s">
-        <v>93</v>
-      </c>
-      <c r="K39" t="s">
-        <v>24</v>
-      </c>
-      <c r="L39" t="s">
-        <v>25</v>
-      </c>
-      <c r="M39" t="s">
-        <v>50</v>
-      </c>
-      <c r="N39" t="s">
-        <v>21</v>
-      </c>
-      <c r="O39" t="s">
-        <v>21</v>
-      </c>
-      <c r="P39" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>21</v>
-      </c>
-      <c r="R39" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>113</v>
-      </c>
-      <c r="B40" t="s">
-        <v>114</v>
-      </c>
-      <c r="C40" t="s">
-        <v>115</v>
-      </c>
-      <c r="D40" t="s">
-        <v>21</v>
-      </c>
-      <c r="E40">
-        <v>12</v>
-      </c>
-      <c r="F40" t="s">
-        <v>21</v>
-      </c>
-      <c r="G40">
-        <v>0</v>
-      </c>
-      <c r="H40">
-        <v>12</v>
-      </c>
-      <c r="I40" t="s">
-        <v>22</v>
-      </c>
-      <c r="J40" t="s">
-        <v>93</v>
-      </c>
-      <c r="K40" t="s">
-        <v>24</v>
-      </c>
-      <c r="L40" t="s">
-        <v>25</v>
-      </c>
-      <c r="M40" t="s">
-        <v>50</v>
-      </c>
-      <c r="N40" t="s">
-        <v>21</v>
-      </c>
-      <c r="O40" t="s">
-        <v>21</v>
-      </c>
-      <c r="P40" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>21</v>
-      </c>
-      <c r="R40" t="s">
         <v>27</v>
       </c>
     </row>

--- a/pc.xlsx
+++ b/pc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FFBB936C-775F-4998-8C51-BB0EBC58EB72}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D7E5BFF1-3B26-45C7-80F1-37133539566E}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="106">
   <si>
     <t>Cod. producto</t>
   </si>
@@ -76,78 +76,78 @@
     <t>Situacion</t>
   </si>
   <si>
+    <t>CABEZAL-ACEITE-JIT</t>
+  </si>
+  <si>
+    <t>CABEZAL NEUMATICO DE ACEITE-200LTS</t>
+  </si>
+  <si>
+    <t>SOL - 2027</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Unidades</t>
+  </si>
+  <si>
+    <t>2026-04</t>
+  </si>
+  <si>
+    <t>BUENOS AIRES</t>
+  </si>
+  <si>
+    <t>Activa</t>
+  </si>
+  <si>
+    <t>Javier Aguero</t>
+  </si>
+  <si>
+    <t>Pendiente</t>
+  </si>
+  <si>
+    <t>CABEZAL-GRASERA-JIT</t>
+  </si>
+  <si>
+    <t>CABEZAL NEUMATICO DE GRASA - 200LTS</t>
+  </si>
+  <si>
     <t>MANG.SILICONADA 2.1/4"</t>
   </si>
   <si>
     <t>MANGUERA SILICONA EXPELENTE AIRE CALIENTE 2.1/4"</t>
   </si>
   <si>
-    <t>SOL - 2027</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Unidades</t>
-  </si>
-  <si>
-    <t>2026-04</t>
-  </si>
-  <si>
-    <t>BUENOS AIRES</t>
-  </si>
-  <si>
-    <t>Activa</t>
-  </si>
-  <si>
-    <t>Javier Aguero</t>
-  </si>
-  <si>
-    <t>Pendiente</t>
-  </si>
-  <si>
     <t>MANG.SILICONADA 2.1/2"</t>
   </si>
   <si>
     <t>MANG SILIC. EXPEL. silicona / Ø int. 63mm / PT: 5BAR /</t>
   </si>
   <si>
-    <t>CABEZAL-ACEITE-JIT</t>
-  </si>
-  <si>
-    <t>CABEZAL NEUMATICO DE ACEITE-200LTS</t>
-  </si>
-  <si>
-    <t>CABEZAL-GRASERA-JIT</t>
-  </si>
-  <si>
-    <t>CABEZAL NEUMATICO DE GRASA - 200LTS</t>
-  </si>
-  <si>
     <t>PUMP-200LTS</t>
   </si>
   <si>
     <t>Bomba P50 Engranaje 2.1/2" Eje Z14 Trompa 5"x4" Giro Derecho S1.1/2"-P1.1/4" 200L</t>
   </si>
   <si>
+    <t>RETEN-6002</t>
+  </si>
+  <si>
+    <t>SOL - 2030</t>
+  </si>
+  <si>
     <t>FILT-10MZ10</t>
   </si>
   <si>
     <t>ELEMENTO FILTRO HIDRAULICO 10MIC SPIN-ON LARGO 10"</t>
   </si>
   <si>
-    <t>SOL - 2030</t>
-  </si>
-  <si>
     <t>FILT-MZ10</t>
   </si>
   <si>
     <t>ELEMENTO FILTRO HIDRAULICO 10MIC SPIN-ON LARGO 7"</t>
   </si>
   <si>
-    <t>RETEN-6002</t>
-  </si>
-  <si>
     <t>HTX-24-20P</t>
   </si>
   <si>
@@ -157,18 +157,24 @@
     <t>SOL - 2032</t>
   </si>
   <si>
+    <t>JK-06P</t>
+  </si>
+  <si>
+    <t>MANGUERA JACK HOSE 3/8</t>
+  </si>
+  <si>
+    <t>SOL - 2033</t>
+  </si>
+  <si>
+    <t>CD Buenos Aires</t>
+  </si>
+  <si>
     <t>10643-16-12P</t>
   </si>
   <si>
     <t>TERMINAL HG JIC 1 5/16"  X MANGUERA 3/4"</t>
   </si>
   <si>
-    <t>SOL - 2033</t>
-  </si>
-  <si>
-    <t>CD Buenos Aires</t>
-  </si>
-  <si>
     <t>1JC77-16-16P</t>
   </si>
   <si>
@@ -181,12 +187,6 @@
     <t>TERMINAL RECTO HG 1.11/16" AS PLANO X MANGUERA R15 1.1/4"</t>
   </si>
   <si>
-    <t>JK-06P</t>
-  </si>
-  <si>
-    <t>MANGUERA JACK HOSE 3/8</t>
-  </si>
-  <si>
     <t>ANV 38 NPT F</t>
   </si>
   <si>
@@ -307,18 +307,6 @@
     <t>00905</t>
   </si>
   <si>
-    <t>FILTRO HIDRAULICO</t>
-  </si>
-  <si>
-    <t>FILTRO HIDRAULICO - GENERICO</t>
-  </si>
-  <si>
-    <t>SOL - 2142</t>
-  </si>
-  <si>
-    <t>00906</t>
-  </si>
-  <si>
     <t>76581002</t>
   </si>
   <si>
@@ -334,22 +322,22 @@
     <t>TERMINAL RECTO HG JIC 9/16" UNF X MANGUERA 1/4" G25170-0406 4G-6FJX</t>
   </si>
   <si>
-    <t>FT 257/5-14</t>
-  </si>
-  <si>
-    <t>VALVULA AGUJA UNIDIRECCIONAL 1/4" - 350 BAR 15 LT</t>
-  </si>
-  <si>
-    <t>SOL - 2145</t>
-  </si>
-  <si>
-    <t>00816</t>
-  </si>
-  <si>
-    <t>HIDROIL SRL</t>
-  </si>
-  <si>
-    <t>Deposito</t>
+    <t>6NH3-20-16P</t>
+  </si>
+  <si>
+    <t>ADAPTADOR CODO 90° BRIDA DE 2.1/8" X MF JIC 1.5/16" UNF SAE62 5000 PSI</t>
+  </si>
+  <si>
+    <t>SOL - 2147</t>
+  </si>
+  <si>
+    <t>00908</t>
+  </si>
+  <si>
+    <t>ACCESORIOS A.CARB O BCE</t>
+  </si>
+  <si>
+    <t>ACCESORIOS DE ACERO AL CARBONO O BRONCE - GENERICO</t>
   </si>
 </sst>
 </file>
@@ -774,7 +762,7 @@
         <v>21</v>
       </c>
       <c r="E2">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
         <v>21</v>
@@ -783,7 +771,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="I2" t="s">
         <v>22</v>
@@ -886,7 +874,7 @@
         <v>21</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="F4" t="s">
         <v>21</v>
@@ -895,7 +883,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="I4" t="s">
         <v>22</v>
@@ -1045,16 +1033,16 @@
         <v>36</v>
       </c>
       <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" t="s">
         <v>37</v>
       </c>
-      <c r="C7" t="s">
-        <v>38</v>
-      </c>
       <c r="D7" t="s">
         <v>21</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F7" t="s">
         <v>21</v>
@@ -1063,7 +1051,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="I7" t="s">
         <v>22</v>
@@ -1098,19 +1086,19 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" t="s">
         <v>39</v>
       </c>
-      <c r="B8" t="s">
-        <v>40</v>
-      </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
         <v>21</v>
       </c>
       <c r="E8">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
         <v>21</v>
@@ -1119,7 +1107,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="I8" t="s">
         <v>22</v>
@@ -1154,19 +1142,19 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B9" t="s">
         <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
         <v>21</v>
       </c>
       <c r="E9">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F9" t="s">
         <v>21</v>
@@ -1175,7 +1163,7 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I9" t="s">
         <v>22</v>
@@ -1278,7 +1266,7 @@
         <v>21</v>
       </c>
       <c r="E11">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="F11" t="s">
         <v>21</v>
@@ -1287,7 +1275,7 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="I11" t="s">
         <v>22</v>
@@ -1334,7 +1322,7 @@
         <v>21</v>
       </c>
       <c r="E12">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="F12" t="s">
         <v>21</v>
@@ -1343,7 +1331,7 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="I12" t="s">
         <v>22</v>
@@ -1390,7 +1378,7 @@
         <v>21</v>
       </c>
       <c r="E13">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F13" t="s">
         <v>21</v>
@@ -1399,7 +1387,7 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I13" t="s">
         <v>22</v>
@@ -1446,7 +1434,7 @@
         <v>21</v>
       </c>
       <c r="E14">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="F14" t="s">
         <v>21</v>
@@ -1455,7 +1443,7 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="I14" t="s">
         <v>22</v>
@@ -2507,10 +2495,10 @@
         <v>97</v>
       </c>
       <c r="D33" t="s">
-        <v>98</v>
+        <v>21</v>
       </c>
       <c r="E33">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="F33" t="s">
         <v>21</v>
@@ -2519,7 +2507,7 @@
         <v>0</v>
       </c>
       <c r="H33">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="I33" t="s">
         <v>22</v>
@@ -2528,13 +2516,13 @@
         <v>90</v>
       </c>
       <c r="K33" t="s">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="L33" t="s">
         <v>25</v>
       </c>
       <c r="M33" t="s">
-        <v>81</v>
+        <v>48</v>
       </c>
       <c r="N33" t="s">
         <v>21</v>
@@ -2554,19 +2542,19 @@
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>98</v>
+      </c>
+      <c r="B34" t="s">
         <v>99</v>
       </c>
-      <c r="B34" t="s">
-        <v>100</v>
-      </c>
       <c r="C34" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D34" t="s">
         <v>21</v>
       </c>
       <c r="E34">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="F34" t="s">
         <v>21</v>
@@ -2575,7 +2563,7 @@
         <v>0</v>
       </c>
       <c r="H34">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="I34" t="s">
         <v>22</v>
@@ -2610,19 +2598,19 @@
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>102</v>
+        <v>49</v>
       </c>
       <c r="B35" t="s">
-        <v>103</v>
+        <v>50</v>
       </c>
       <c r="C35" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D35" t="s">
         <v>21</v>
       </c>
       <c r="E35">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="F35" t="s">
         <v>21</v>
@@ -2631,7 +2619,7 @@
         <v>0</v>
       </c>
       <c r="H35">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="I35" t="s">
         <v>22</v>
@@ -2666,19 +2654,19 @@
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="B36" t="s">
-        <v>46</v>
+        <v>101</v>
       </c>
       <c r="C36" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D36" t="s">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="E36">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F36" t="s">
         <v>21</v>
@@ -2687,7 +2675,7 @@
         <v>0</v>
       </c>
       <c r="H36">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="I36" t="s">
         <v>22</v>
@@ -2696,13 +2684,13 @@
         <v>90</v>
       </c>
       <c r="K36" t="s">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="L36" t="s">
         <v>25</v>
       </c>
       <c r="M36" t="s">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="N36" t="s">
         <v>21</v>
@@ -2728,13 +2716,13 @@
         <v>105</v>
       </c>
       <c r="C37" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D37" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E37">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F37" t="s">
         <v>21</v>
@@ -2743,7 +2731,7 @@
         <v>0</v>
       </c>
       <c r="H37">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I37" t="s">
         <v>22</v>
@@ -2752,13 +2740,13 @@
         <v>90</v>
       </c>
       <c r="K37" t="s">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="L37" t="s">
         <v>25</v>
       </c>
       <c r="M37" t="s">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="N37" t="s">
         <v>21</v>

--- a/pc.xlsx
+++ b/pc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D7E5BFF1-3B26-45C7-80F1-37133539566E}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E6DB6E1-8F1D-44D4-BF50-E6BEF88FAE24}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="110">
   <si>
     <t>Cod. producto</t>
   </si>
@@ -76,54 +76,54 @@
     <t>Situacion</t>
   </si>
   <si>
+    <t>MANG.SILICONADA 2.1/4"</t>
+  </si>
+  <si>
+    <t>MANGUERA SILICONA EXPELENTE AIRE CALIENTE 2.1/4"</t>
+  </si>
+  <si>
+    <t>SOL - 2027</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Unidades</t>
+  </si>
+  <si>
+    <t>2026-04</t>
+  </si>
+  <si>
+    <t>BUENOS AIRES</t>
+  </si>
+  <si>
+    <t>Activa</t>
+  </si>
+  <si>
+    <t>Javier Aguero</t>
+  </si>
+  <si>
+    <t>Pendiente</t>
+  </si>
+  <si>
+    <t>MANG.SILICONADA 2.1/2"</t>
+  </si>
+  <si>
+    <t>MANG SILIC. EXPEL. silicona / Ø int. 63mm / PT: 5BAR /</t>
+  </si>
+  <si>
     <t>CABEZAL-ACEITE-JIT</t>
   </si>
   <si>
     <t>CABEZAL NEUMATICO DE ACEITE-200LTS</t>
   </si>
   <si>
-    <t>SOL - 2027</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Unidades</t>
-  </si>
-  <si>
-    <t>2026-04</t>
-  </si>
-  <si>
-    <t>BUENOS AIRES</t>
-  </si>
-  <si>
-    <t>Activa</t>
-  </si>
-  <si>
-    <t>Javier Aguero</t>
-  </si>
-  <si>
-    <t>Pendiente</t>
-  </si>
-  <si>
     <t>CABEZAL-GRASERA-JIT</t>
   </si>
   <si>
     <t>CABEZAL NEUMATICO DE GRASA - 200LTS</t>
   </si>
   <si>
-    <t>MANG.SILICONADA 2.1/4"</t>
-  </si>
-  <si>
-    <t>MANGUERA SILICONA EXPELENTE AIRE CALIENTE 2.1/4"</t>
-  </si>
-  <si>
-    <t>MANG.SILICONADA 2.1/2"</t>
-  </si>
-  <si>
-    <t>MANG SILIC. EXPEL. silicona / Ø int. 63mm / PT: 5BAR /</t>
-  </si>
-  <si>
     <t>PUMP-200LTS</t>
   </si>
   <si>
@@ -169,12 +169,6 @@
     <t>CD Buenos Aires</t>
   </si>
   <si>
-    <t>10643-16-12P</t>
-  </si>
-  <si>
-    <t>TERMINAL HG JIC 1 5/16"  X MANGUERA 3/4"</t>
-  </si>
-  <si>
     <t>1JC77-16-16P</t>
   </si>
   <si>
@@ -187,21 +181,33 @@
     <t>TERMINAL RECTO HG 1.11/16" AS PLANO X MANGUERA R15 1.1/4"</t>
   </si>
   <si>
+    <t>2TM2</t>
+  </si>
+  <si>
+    <t>ACOPLE RAPIDO CUPLA 1/4" X MACHO 1/4" NPT 10.000PSI</t>
+  </si>
+  <si>
+    <t>SOL - 2034</t>
+  </si>
+  <si>
     <t>ANV 38 NPT F</t>
   </si>
   <si>
     <t>ACOPLE RAPIDO HEMBRA C/ROSCA HEMBRA DE 3/8" NPT FASTER</t>
   </si>
   <si>
-    <t>SOL - 2034</t>
-  </si>
-  <si>
     <t>ANV 38 NPT M</t>
   </si>
   <si>
     <t>ACOPLE RAPIDO MACHO C/ROSCA HEMBRA DE 3/8" NPT FASTER</t>
   </si>
   <si>
+    <t>T2F2</t>
+  </si>
+  <si>
+    <t>ACOPLE RAPIDO NIPLE 1/4" X HEMBRA 1/4" NPT 10.000PSI</t>
+  </si>
+  <si>
     <t>FFH20 114NPT F</t>
   </si>
   <si>
@@ -214,18 +220,6 @@
     <t>ACOPLE FRENTE PLANO 1.1/4" MACHO CON ROSCA HEMBRA DE 1.1/4" NPT</t>
   </si>
   <si>
-    <t>T2F2</t>
-  </si>
-  <si>
-    <t>ACOPLE RAPIDO NIPLE 1/4" X HEMBRA 1/4" NPT 10.000PSI</t>
-  </si>
-  <si>
-    <t>2TM2</t>
-  </si>
-  <si>
-    <t>ACOPLE RAPIDO CUPLA 1/4" X MACHO 1/4" NPT 10.000PSI</t>
-  </si>
-  <si>
     <t>F5OG-10-1/2P</t>
   </si>
   <si>
@@ -307,37 +301,55 @@
     <t>00905</t>
   </si>
   <si>
-    <t>76581002</t>
-  </si>
-  <si>
-    <t>MANG. DE PVC CON ESPIRAL DE ACERO ASP/EXP GRADO ALIMENT.RAUSPIRAFLEX M 50 MM</t>
-  </si>
-  <si>
-    <t>SOL - 2143</t>
-  </si>
-  <si>
-    <t>710308065</t>
-  </si>
-  <si>
-    <t>TERMINAL RECTO HG JIC 9/16" UNF X MANGUERA 1/4" G25170-0406 4G-6FJX</t>
-  </si>
-  <si>
-    <t>6NH3-20-16P</t>
-  </si>
-  <si>
-    <t>ADAPTADOR CODO 90° BRIDA DE 2.1/8" X MF JIC 1.5/16" UNF SAE62 5000 PSI</t>
-  </si>
-  <si>
-    <t>SOL - 2147</t>
-  </si>
-  <si>
-    <t>00908</t>
+    <t>ACCESORIOS ACERO INOX</t>
+  </si>
+  <si>
+    <t>ACCESORIOS DE ACERO INOXIDABLE - GENERICO</t>
+  </si>
+  <si>
+    <t>SOL - 2157</t>
+  </si>
+  <si>
+    <t>0007-00000140</t>
+  </si>
+  <si>
+    <t>SAN JULIAN</t>
+  </si>
+  <si>
+    <t>OPERACIONES SAN JULIAN</t>
   </si>
   <si>
     <t>ACCESORIOS A.CARB O BCE</t>
   </si>
   <si>
     <t>ACCESORIOS DE ACERO AL CARBONO O BRONCE - GENERICO</t>
+  </si>
+  <si>
+    <t>SOL - 2158</t>
+  </si>
+  <si>
+    <t>0007-00000141</t>
+  </si>
+  <si>
+    <t>4657-4583</t>
+  </si>
+  <si>
+    <t>MANGUERA R2 DE 1/4" 5800 PSI, 4AGR2 GATES</t>
+  </si>
+  <si>
+    <t>SOL - 2155</t>
+  </si>
+  <si>
+    <t>VALVULA HIDRAULICA</t>
+  </si>
+  <si>
+    <t>VALVULA HIDRAULICA - GENERICO</t>
+  </si>
+  <si>
+    <t>SOL - 2159</t>
+  </si>
+  <si>
+    <t>00916</t>
   </si>
 </sst>
 </file>
@@ -689,7 +701,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R37"/>
+  <dimension ref="A1:R35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
@@ -762,7 +774,7 @@
         <v>21</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="F2" t="s">
         <v>21</v>
@@ -771,7 +783,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="I2" t="s">
         <v>22</v>
@@ -874,7 +886,7 @@
         <v>21</v>
       </c>
       <c r="E4">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
         <v>21</v>
@@ -883,7 +895,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="I4" t="s">
         <v>22</v>
@@ -1322,7 +1334,7 @@
         <v>21</v>
       </c>
       <c r="E12">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F12" t="s">
         <v>21</v>
@@ -1331,7 +1343,7 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="I12" t="s">
         <v>22</v>
@@ -1378,7 +1390,7 @@
         <v>21</v>
       </c>
       <c r="E13">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F13" t="s">
         <v>21</v>
@@ -1387,7 +1399,7 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I13" t="s">
         <v>22</v>
@@ -1428,13 +1440,13 @@
         <v>54</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D14" t="s">
         <v>21</v>
       </c>
       <c r="E14">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F14" t="s">
         <v>21</v>
@@ -1443,7 +1455,7 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I14" t="s">
         <v>22</v>
@@ -1478,13 +1490,13 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" t="s">
         <v>55</v>
-      </c>
-      <c r="B15" t="s">
-        <v>56</v>
-      </c>
-      <c r="C15" t="s">
-        <v>57</v>
       </c>
       <c r="D15" t="s">
         <v>21</v>
@@ -1540,7 +1552,7 @@
         <v>59</v>
       </c>
       <c r="C16" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D16" t="s">
         <v>21</v>
@@ -1596,13 +1608,13 @@
         <v>61</v>
       </c>
       <c r="C17" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D17" t="s">
         <v>21</v>
       </c>
       <c r="E17">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="F17" t="s">
         <v>21</v>
@@ -1611,7 +1623,7 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="I17" t="s">
         <v>22</v>
@@ -1652,7 +1664,7 @@
         <v>63</v>
       </c>
       <c r="C18" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D18" t="s">
         <v>21</v>
@@ -1708,13 +1720,13 @@
         <v>65</v>
       </c>
       <c r="C19" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D19" t="s">
         <v>21</v>
       </c>
       <c r="E19">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="F19" t="s">
         <v>21</v>
@@ -1723,7 +1735,7 @@
         <v>0</v>
       </c>
       <c r="H19">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="I19" t="s">
         <v>22</v>
@@ -1764,13 +1776,13 @@
         <v>67</v>
       </c>
       <c r="C20" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="D20" t="s">
         <v>21</v>
       </c>
       <c r="E20">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="F20" t="s">
         <v>21</v>
@@ -1779,7 +1791,7 @@
         <v>0</v>
       </c>
       <c r="H20">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="I20" t="s">
         <v>22</v>
@@ -1814,19 +1826,19 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>69</v>
+      </c>
+      <c r="B21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21" t="s">
         <v>68</v>
       </c>
-      <c r="B21" t="s">
-        <v>69</v>
-      </c>
-      <c r="C21" t="s">
-        <v>70</v>
-      </c>
       <c r="D21" t="s">
         <v>21</v>
       </c>
       <c r="E21">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F21" t="s">
         <v>21</v>
@@ -1835,7 +1847,7 @@
         <v>0</v>
       </c>
       <c r="H21">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I21" t="s">
         <v>22</v>
@@ -1876,13 +1888,13 @@
         <v>72</v>
       </c>
       <c r="C22" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D22" t="s">
         <v>21</v>
       </c>
       <c r="E22">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F22" t="s">
         <v>21</v>
@@ -1891,7 +1903,7 @@
         <v>0</v>
       </c>
       <c r="H22">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="I22" t="s">
         <v>22</v>
@@ -1926,13 +1938,13 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>71</v>
+      </c>
+      <c r="B23" t="s">
+        <v>72</v>
+      </c>
+      <c r="C23" t="s">
         <v>73</v>
-      </c>
-      <c r="B23" t="s">
-        <v>74</v>
-      </c>
-      <c r="C23" t="s">
-        <v>75</v>
       </c>
       <c r="D23" t="s">
         <v>21</v>
@@ -1982,13 +1994,13 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>71</v>
+      </c>
+      <c r="B24" t="s">
+        <v>72</v>
+      </c>
+      <c r="C24" t="s">
         <v>73</v>
-      </c>
-      <c r="B24" t="s">
-        <v>74</v>
-      </c>
-      <c r="C24" t="s">
-        <v>75</v>
       </c>
       <c r="D24" t="s">
         <v>21</v>
@@ -2038,19 +2050,19 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>71</v>
+      </c>
+      <c r="B25" t="s">
+        <v>72</v>
+      </c>
+      <c r="C25" t="s">
         <v>73</v>
       </c>
-      <c r="B25" t="s">
-        <v>74</v>
-      </c>
-      <c r="C25" t="s">
-        <v>75</v>
-      </c>
       <c r="D25" t="s">
         <v>21</v>
       </c>
       <c r="E25">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F25" t="s">
         <v>21</v>
@@ -2059,7 +2071,7 @@
         <v>0</v>
       </c>
       <c r="H25">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I25" t="s">
         <v>22</v>
@@ -2094,13 +2106,13 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>71</v>
+      </c>
+      <c r="B26" t="s">
+        <v>72</v>
+      </c>
+      <c r="C26" t="s">
         <v>73</v>
-      </c>
-      <c r="B26" t="s">
-        <v>74</v>
-      </c>
-      <c r="C26" t="s">
-        <v>75</v>
       </c>
       <c r="D26" t="s">
         <v>21</v>
@@ -2150,19 +2162,19 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B27" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C27" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D27" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="E27">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="F27" t="s">
         <v>21</v>
@@ -2171,7 +2183,7 @@
         <v>0</v>
       </c>
       <c r="H27">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I27" t="s">
         <v>22</v>
@@ -2180,13 +2192,13 @@
         <v>23</v>
       </c>
       <c r="K27" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="L27" t="s">
         <v>25</v>
       </c>
       <c r="M27" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="N27" t="s">
         <v>21</v>
@@ -2206,16 +2218,16 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B28" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C28" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D28" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E28">
         <v>90</v>
@@ -2236,13 +2248,13 @@
         <v>23</v>
       </c>
       <c r="K28" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L28" t="s">
         <v>25</v>
       </c>
       <c r="M28" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="N28" t="s">
         <v>21</v>
@@ -2262,19 +2274,19 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B29" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C29" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D29" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E29">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="F29" t="s">
         <v>21</v>
@@ -2283,22 +2295,22 @@
         <v>0</v>
       </c>
       <c r="H29">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="I29" t="s">
         <v>22</v>
       </c>
       <c r="J29" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="K29" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L29" t="s">
         <v>25</v>
       </c>
       <c r="M29" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="N29" t="s">
         <v>21</v>
@@ -2318,16 +2330,16 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B30" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C30" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D30" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E30">
         <v>1</v>
@@ -2345,16 +2357,16 @@
         <v>22</v>
       </c>
       <c r="J30" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K30" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L30" t="s">
         <v>25</v>
       </c>
       <c r="M30" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="N30" t="s">
         <v>21</v>
@@ -2374,10 +2386,10 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B31" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C31" t="s">
         <v>91</v>
@@ -2401,16 +2413,16 @@
         <v>22</v>
       </c>
       <c r="J31" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K31" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L31" t="s">
         <v>25</v>
       </c>
       <c r="M31" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="N31" t="s">
         <v>21</v>
@@ -2430,19 +2442,19 @@
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="B32" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C32" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D32" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="F32" t="s">
         <v>21</v>
@@ -2451,22 +2463,22 @@
         <v>0</v>
       </c>
       <c r="H32">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="I32" t="s">
         <v>22</v>
       </c>
       <c r="J32" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K32" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="L32" t="s">
         <v>25</v>
       </c>
       <c r="M32" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="N32" t="s">
         <v>21</v>
@@ -2486,43 +2498,43 @@
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B33" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C33" t="s">
+        <v>101</v>
+      </c>
+      <c r="D33" t="s">
+        <v>102</v>
+      </c>
+      <c r="E33">
+        <v>8</v>
+      </c>
+      <c r="F33" t="s">
+        <v>21</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>8</v>
+      </c>
+      <c r="I33" t="s">
+        <v>22</v>
+      </c>
+      <c r="J33" t="s">
+        <v>88</v>
+      </c>
+      <c r="K33" t="s">
         <v>97</v>
       </c>
-      <c r="D33" t="s">
-        <v>21</v>
-      </c>
-      <c r="E33">
-        <v>50</v>
-      </c>
-      <c r="F33" t="s">
-        <v>21</v>
-      </c>
-      <c r="G33">
-        <v>0</v>
-      </c>
-      <c r="H33">
-        <v>50</v>
-      </c>
-      <c r="I33" t="s">
-        <v>22</v>
-      </c>
-      <c r="J33" t="s">
-        <v>90</v>
-      </c>
-      <c r="K33" t="s">
-        <v>24</v>
-      </c>
       <c r="L33" t="s">
         <v>25</v>
       </c>
       <c r="M33" t="s">
-        <v>48</v>
+        <v>98</v>
       </c>
       <c r="N33" t="s">
         <v>21</v>
@@ -2542,19 +2554,19 @@
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B34" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C34" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="D34" t="s">
         <v>21</v>
       </c>
       <c r="E34">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="F34" t="s">
         <v>21</v>
@@ -2563,13 +2575,13 @@
         <v>0</v>
       </c>
       <c r="H34">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="I34" t="s">
         <v>22</v>
       </c>
       <c r="J34" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K34" t="s">
         <v>24</v>
@@ -2598,19 +2610,19 @@
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>49</v>
+        <v>106</v>
       </c>
       <c r="B35" t="s">
-        <v>50</v>
+        <v>107</v>
       </c>
       <c r="C35" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="D35" t="s">
-        <v>21</v>
+        <v>109</v>
       </c>
       <c r="E35">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="F35" t="s">
         <v>21</v>
@@ -2619,22 +2631,22 @@
         <v>0</v>
       </c>
       <c r="H35">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="I35" t="s">
         <v>22</v>
       </c>
       <c r="J35" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K35" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="L35" t="s">
         <v>25</v>
       </c>
       <c r="M35" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="N35" t="s">
         <v>21</v>
@@ -2649,118 +2661,6 @@
         <v>21</v>
       </c>
       <c r="R35" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>100</v>
-      </c>
-      <c r="B36" t="s">
-        <v>101</v>
-      </c>
-      <c r="C36" t="s">
-        <v>102</v>
-      </c>
-      <c r="D36" t="s">
-        <v>103</v>
-      </c>
-      <c r="E36">
-        <v>10</v>
-      </c>
-      <c r="F36" t="s">
-        <v>21</v>
-      </c>
-      <c r="G36">
-        <v>0</v>
-      </c>
-      <c r="H36">
-        <v>10</v>
-      </c>
-      <c r="I36" t="s">
-        <v>22</v>
-      </c>
-      <c r="J36" t="s">
-        <v>90</v>
-      </c>
-      <c r="K36" t="s">
-        <v>80</v>
-      </c>
-      <c r="L36" t="s">
-        <v>25</v>
-      </c>
-      <c r="M36" t="s">
-        <v>81</v>
-      </c>
-      <c r="N36" t="s">
-        <v>21</v>
-      </c>
-      <c r="O36" t="s">
-        <v>21</v>
-      </c>
-      <c r="P36" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>21</v>
-      </c>
-      <c r="R36" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>104</v>
-      </c>
-      <c r="B37" t="s">
-        <v>105</v>
-      </c>
-      <c r="C37" t="s">
-        <v>102</v>
-      </c>
-      <c r="D37" t="s">
-        <v>103</v>
-      </c>
-      <c r="E37">
-        <v>10</v>
-      </c>
-      <c r="F37" t="s">
-        <v>21</v>
-      </c>
-      <c r="G37">
-        <v>0</v>
-      </c>
-      <c r="H37">
-        <v>10</v>
-      </c>
-      <c r="I37" t="s">
-        <v>22</v>
-      </c>
-      <c r="J37" t="s">
-        <v>90</v>
-      </c>
-      <c r="K37" t="s">
-        <v>80</v>
-      </c>
-      <c r="L37" t="s">
-        <v>25</v>
-      </c>
-      <c r="M37" t="s">
-        <v>81</v>
-      </c>
-      <c r="N37" t="s">
-        <v>21</v>
-      </c>
-      <c r="O37" t="s">
-        <v>21</v>
-      </c>
-      <c r="P37" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>21</v>
-      </c>
-      <c r="R37" t="s">
         <v>27</v>
       </c>
     </row>

--- a/pc.xlsx
+++ b/pc.xlsx
@@ -8,26 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B339491E-3859-4CEE-B73F-C518D4EEB806}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4CD0B5B2-69FF-4648-A064-8DA23617B5C0}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="56">
   <si>
     <t>Cod. producto</t>
   </si>
@@ -138,6 +131,63 @@
   </si>
   <si>
     <t>SOL - 2042</t>
+  </si>
+  <si>
+    <t>2-227-N90</t>
+  </si>
+  <si>
+    <t>ORING 2-227 D90 DI 53.57 X DE 60.63 ESP 3.53</t>
+  </si>
+  <si>
+    <t>SOL - 2200</t>
+  </si>
+  <si>
+    <t>00921</t>
+  </si>
+  <si>
+    <t>2026-05</t>
+  </si>
+  <si>
+    <t>NEUQUEN</t>
+  </si>
+  <si>
+    <t>Deposito NQN</t>
+  </si>
+  <si>
+    <t>2-222-N90</t>
+  </si>
+  <si>
+    <t>ORING 2-222 D90 DI 37.69 X DE 44.75 ESP 3.53</t>
+  </si>
+  <si>
+    <t>SOL - 2201</t>
+  </si>
+  <si>
+    <t>00922</t>
+  </si>
+  <si>
+    <t>2-016-N90</t>
+  </si>
+  <si>
+    <t>ORING 2-016 D90 DI 15.60 X DE 19.16 ESP 1.78</t>
+  </si>
+  <si>
+    <t>SOL - 2202</t>
+  </si>
+  <si>
+    <t>00923</t>
+  </si>
+  <si>
+    <t>2-121-N90</t>
+  </si>
+  <si>
+    <t>ORING 2-121 D90 DI 26.64 X DE 31.88 ESP 2.62</t>
+  </si>
+  <si>
+    <t>SOL - 2203</t>
+  </si>
+  <si>
+    <t>00924</t>
   </si>
 </sst>
 </file>
@@ -489,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
@@ -1052,6 +1102,230 @@
         <v>27</v>
       </c>
     </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11">
+        <v>800</v>
+      </c>
+      <c r="F11" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>800</v>
+      </c>
+      <c r="I11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" t="s">
+        <v>41</v>
+      </c>
+      <c r="K11" t="s">
+        <v>42</v>
+      </c>
+      <c r="L11" t="s">
+        <v>25</v>
+      </c>
+      <c r="M11" t="s">
+        <v>43</v>
+      </c>
+      <c r="N11" t="s">
+        <v>21</v>
+      </c>
+      <c r="O11" t="s">
+        <v>21</v>
+      </c>
+      <c r="P11" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>21</v>
+      </c>
+      <c r="R11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12">
+        <v>850</v>
+      </c>
+      <c r="F12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>850</v>
+      </c>
+      <c r="I12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J12" t="s">
+        <v>41</v>
+      </c>
+      <c r="K12" t="s">
+        <v>42</v>
+      </c>
+      <c r="L12" t="s">
+        <v>25</v>
+      </c>
+      <c r="M12" t="s">
+        <v>43</v>
+      </c>
+      <c r="N12" t="s">
+        <v>21</v>
+      </c>
+      <c r="O12" t="s">
+        <v>21</v>
+      </c>
+      <c r="P12" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>21</v>
+      </c>
+      <c r="R12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13">
+        <v>200</v>
+      </c>
+      <c r="F13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>200</v>
+      </c>
+      <c r="I13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J13" t="s">
+        <v>41</v>
+      </c>
+      <c r="K13" t="s">
+        <v>42</v>
+      </c>
+      <c r="L13" t="s">
+        <v>25</v>
+      </c>
+      <c r="M13" t="s">
+        <v>43</v>
+      </c>
+      <c r="N13" t="s">
+        <v>21</v>
+      </c>
+      <c r="O13" t="s">
+        <v>21</v>
+      </c>
+      <c r="P13" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>21</v>
+      </c>
+      <c r="R13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" t="s">
+        <v>55</v>
+      </c>
+      <c r="E14">
+        <v>200</v>
+      </c>
+      <c r="F14" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>200</v>
+      </c>
+      <c r="I14" t="s">
+        <v>22</v>
+      </c>
+      <c r="J14" t="s">
+        <v>41</v>
+      </c>
+      <c r="K14" t="s">
+        <v>42</v>
+      </c>
+      <c r="L14" t="s">
+        <v>25</v>
+      </c>
+      <c r="M14" t="s">
+        <v>43</v>
+      </c>
+      <c r="N14" t="s">
+        <v>21</v>
+      </c>
+      <c r="O14" t="s">
+        <v>21</v>
+      </c>
+      <c r="P14" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>21</v>
+      </c>
+      <c r="R14" t="s">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pc.xlsx
+++ b/pc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4CD0B5B2-69FF-4648-A064-8DA23617B5C0}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C071A200-B5BA-4966-B9AF-DD4E46AE01D8}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="68">
   <si>
     <t>Cod. producto</t>
   </si>
@@ -133,16 +133,16 @@
     <t>SOL - 2042</t>
   </si>
   <si>
-    <t>2-227-N90</t>
-  </si>
-  <si>
-    <t>ORING 2-227 D90 DI 53.57 X DE 60.63 ESP 3.53</t>
-  </si>
-  <si>
-    <t>SOL - 2200</t>
-  </si>
-  <si>
-    <t>00921</t>
+    <t>2-143-N90</t>
+  </si>
+  <si>
+    <t>ORING 2-143 D90 DI 61.60 X DE 66.84 ESP 2.62</t>
+  </si>
+  <si>
+    <t>SOL - 2206</t>
+  </si>
+  <si>
+    <t>00926</t>
   </si>
   <si>
     <t>2026-05</t>
@@ -154,40 +154,76 @@
     <t>Deposito NQN</t>
   </si>
   <si>
+    <t>2-112-N90</t>
+  </si>
+  <si>
+    <t>ORING 2-112 D90 DI 12.37 X DE 17.61 ESP 2.62</t>
+  </si>
+  <si>
+    <t>SOL - 2207</t>
+  </si>
+  <si>
+    <t>00927</t>
+  </si>
+  <si>
+    <t>2-220-N90</t>
+  </si>
+  <si>
+    <t>ORING 2-220 D90 DI 34.52 X DE 41.58 ESP 3.53</t>
+  </si>
+  <si>
+    <t>SOL - 2208</t>
+  </si>
+  <si>
+    <t>00928</t>
+  </si>
+  <si>
     <t>2-222-N90</t>
   </si>
   <si>
     <t>ORING 2-222 D90 DI 37.69 X DE 44.75 ESP 3.53</t>
   </si>
   <si>
-    <t>SOL - 2201</t>
-  </si>
-  <si>
-    <t>00922</t>
-  </si>
-  <si>
-    <t>2-016-N90</t>
-  </si>
-  <si>
-    <t>ORING 2-016 D90 DI 15.60 X DE 19.16 ESP 1.78</t>
-  </si>
-  <si>
-    <t>SOL - 2202</t>
-  </si>
-  <si>
-    <t>00923</t>
-  </si>
-  <si>
-    <t>2-121-N90</t>
-  </si>
-  <si>
-    <t>ORING 2-121 D90 DI 26.64 X DE 31.88 ESP 2.62</t>
-  </si>
-  <si>
-    <t>SOL - 2203</t>
-  </si>
-  <si>
-    <t>00924</t>
+    <t>SOL - 2209</t>
+  </si>
+  <si>
+    <t>00929</t>
+  </si>
+  <si>
+    <t>2-216-N90</t>
+  </si>
+  <si>
+    <t>ORING 2-216 D90 DI 28.17 X DE 35.23 ESP 3.53</t>
+  </si>
+  <si>
+    <t>SOL - 2210</t>
+  </si>
+  <si>
+    <t>00930</t>
+  </si>
+  <si>
+    <t>2-330-N90</t>
+  </si>
+  <si>
+    <t>ORING 2-330 D90 DI 53.34 X DE 64.00 ESP 5.33</t>
+  </si>
+  <si>
+    <t>SOL - 2211</t>
+  </si>
+  <si>
+    <t>00931</t>
+  </si>
+  <si>
+    <t>2-226-N90</t>
+  </si>
+  <si>
+    <t>ORING 2-226 D90 DI 50.39 X DE 57.45 ESP 3.53</t>
+  </si>
+  <si>
+    <t>SOL - 2212</t>
+  </si>
+  <si>
+    <t>00932</t>
   </si>
 </sst>
 </file>
@@ -539,7 +575,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R14"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
@@ -1116,7 +1152,7 @@
         <v>40</v>
       </c>
       <c r="E11">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="F11" t="s">
         <v>21</v>
@@ -1125,7 +1161,7 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="I11" t="s">
         <v>22</v>
@@ -1172,7 +1208,7 @@
         <v>47</v>
       </c>
       <c r="E12">
-        <v>850</v>
+        <v>400</v>
       </c>
       <c r="F12" t="s">
         <v>21</v>
@@ -1181,7 +1217,7 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>850</v>
+        <v>400</v>
       </c>
       <c r="I12" t="s">
         <v>22</v>
@@ -1228,7 +1264,7 @@
         <v>51</v>
       </c>
       <c r="E13">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="F13" t="s">
         <v>21</v>
@@ -1237,7 +1273,7 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="I13" t="s">
         <v>22</v>
@@ -1284,7 +1320,7 @@
         <v>55</v>
       </c>
       <c r="E14">
-        <v>200</v>
+        <v>950</v>
       </c>
       <c r="F14" t="s">
         <v>21</v>
@@ -1293,7 +1329,7 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>200</v>
+        <v>950</v>
       </c>
       <c r="I14" t="s">
         <v>22</v>
@@ -1323,6 +1359,174 @@
         <v>21</v>
       </c>
       <c r="R14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15">
+        <v>400</v>
+      </c>
+      <c r="F15" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>400</v>
+      </c>
+      <c r="I15" t="s">
+        <v>22</v>
+      </c>
+      <c r="J15" t="s">
+        <v>41</v>
+      </c>
+      <c r="K15" t="s">
+        <v>42</v>
+      </c>
+      <c r="L15" t="s">
+        <v>25</v>
+      </c>
+      <c r="M15" t="s">
+        <v>43</v>
+      </c>
+      <c r="N15" t="s">
+        <v>21</v>
+      </c>
+      <c r="O15" t="s">
+        <v>21</v>
+      </c>
+      <c r="P15" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>21</v>
+      </c>
+      <c r="R15" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" t="s">
+        <v>62</v>
+      </c>
+      <c r="D16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E16">
+        <v>400</v>
+      </c>
+      <c r="F16" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>400</v>
+      </c>
+      <c r="I16" t="s">
+        <v>22</v>
+      </c>
+      <c r="J16" t="s">
+        <v>41</v>
+      </c>
+      <c r="K16" t="s">
+        <v>42</v>
+      </c>
+      <c r="L16" t="s">
+        <v>25</v>
+      </c>
+      <c r="M16" t="s">
+        <v>43</v>
+      </c>
+      <c r="N16" t="s">
+        <v>21</v>
+      </c>
+      <c r="O16" t="s">
+        <v>21</v>
+      </c>
+      <c r="P16" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>21</v>
+      </c>
+      <c r="R16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" t="s">
+        <v>67</v>
+      </c>
+      <c r="E17">
+        <v>800</v>
+      </c>
+      <c r="F17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>800</v>
+      </c>
+      <c r="I17" t="s">
+        <v>22</v>
+      </c>
+      <c r="J17" t="s">
+        <v>41</v>
+      </c>
+      <c r="K17" t="s">
+        <v>42</v>
+      </c>
+      <c r="L17" t="s">
+        <v>25</v>
+      </c>
+      <c r="M17" t="s">
+        <v>43</v>
+      </c>
+      <c r="N17" t="s">
+        <v>21</v>
+      </c>
+      <c r="O17" t="s">
+        <v>21</v>
+      </c>
+      <c r="P17" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>21</v>
+      </c>
+      <c r="R17" t="s">
         <v>27</v>
       </c>
     </row>

--- a/pc.xlsx
+++ b/pc.xlsx
@@ -8,19 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D10E6799-4FA4-4EA8-8C5F-46EF7D20DDEC}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9BCC3F26-D2BE-4014-818B-03DCC35A62D2}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1248" uniqueCount="184">
   <si>
     <t>Cod. producto</t>
   </si>
@@ -104,6 +111,474 @@
   </si>
   <si>
     <t>Pendiente</t>
+  </si>
+  <si>
+    <t>46512208</t>
+  </si>
+  <si>
+    <t>MANGUERA HIDRAU. ESPIRALADA GATES (SAE100 R13) 24EFG5K X LL</t>
+  </si>
+  <si>
+    <t>SOL - 2307</t>
+  </si>
+  <si>
+    <t>2026-06</t>
+  </si>
+  <si>
+    <t>C5OX-24-20F</t>
+  </si>
+  <si>
+    <t>ADAP CODO 90° MF 1.7/8" AS JIC 37° X MF 1.5/8" AS ORING</t>
+  </si>
+  <si>
+    <t>CODO 90-1/4" S3000</t>
+  </si>
+  <si>
+    <t>CODO 90° 1/4" H-H NPT SERIE 3000</t>
+  </si>
+  <si>
+    <t>BUJE RED-2"x1.1/2" S3000</t>
+  </si>
+  <si>
+    <t>BUJE DE RED 2" NPT x 1.1/2" NPT SERIE 3000</t>
+  </si>
+  <si>
+    <t>BUJE RED-3/4"x1/2" S3000</t>
+  </si>
+  <si>
+    <t>BUJE DE RED 3/4" NPT x 1/2" NPT SERIE 3000</t>
+  </si>
+  <si>
+    <t>XHX6-12-16N</t>
+  </si>
+  <si>
+    <t>ADAP RECTO HG JIC 1.1/16" x MF JIC 1 1/16" UNF</t>
+  </si>
+  <si>
+    <t>4AH3-16-16P</t>
+  </si>
+  <si>
+    <t>ADAPTADOR RECTO BRIDA DE 1.3/4" X MF JIC 1.5/16" UNF SAE61 5000 PSI</t>
+  </si>
+  <si>
+    <t>6AH3-20-20P</t>
+  </si>
+  <si>
+    <t>ADAPTADOR RECTO BRIDA DE 2.1/8" X MF JIC 1.5/8" UNF SAE62 5000 PSI</t>
+  </si>
+  <si>
+    <t>313213001</t>
+  </si>
+  <si>
+    <t>MANG. DE POLIURETANO PARA NEUMÁTICA. RAUPURAM 10 MM</t>
+  </si>
+  <si>
+    <t>1250-0625-250B</t>
+  </si>
+  <si>
+    <t>POLYPAK 15.88 x 22.22 x 6.35</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>WIPER 50.80 x 63.50 x 9.52/6.35</t>
+  </si>
+  <si>
+    <t>0K-89-N90</t>
+  </si>
+  <si>
+    <t>KIT DE ORING EN PULGADAS N90</t>
+  </si>
+  <si>
+    <t>0K-89T</t>
+  </si>
+  <si>
+    <t>KIT DE ORING EN PULGADAS N70</t>
+  </si>
+  <si>
+    <t>0PHB408T N70</t>
+  </si>
+  <si>
+    <t>KIT DE ORING MILIMETRICOS N70</t>
+  </si>
+  <si>
+    <t>2-250-N90</t>
+  </si>
+  <si>
+    <t>ORING 2-250 D90 DI 126.59 X DE 133.65 ESP 3.53</t>
+  </si>
+  <si>
+    <t>2-332-N70</t>
+  </si>
+  <si>
+    <t>ORING 2-332 D70 DI 59.69 X DE 70.35 ESP 5.33</t>
+  </si>
+  <si>
+    <t>2-250N90V</t>
+  </si>
+  <si>
+    <t>ORING 2-250 V70 DI 126.59 X ESP 3.53</t>
+  </si>
+  <si>
+    <t>FT 221/1-100</t>
+  </si>
+  <si>
+    <t>VALVULA ESFERICA DE 2 VIAS, ALTA PRESION 1"</t>
+  </si>
+  <si>
+    <t>FT 257/5-14</t>
+  </si>
+  <si>
+    <t>VALVULA AGUJA UNIDIRECCIONAL 1/4" - 350 BAR 15 LT</t>
+  </si>
+  <si>
+    <t>FT 257/6-100</t>
+  </si>
+  <si>
+    <t>VALVULA DE RETENCION EN LINEA RECTA 1" 160LPM - 350 BAR</t>
+  </si>
+  <si>
+    <t>LG-3T</t>
+  </si>
+  <si>
+    <t>INDICADOR DE NIVEL Y TEMPERATURA DE 254MM - M12 METALICO</t>
+  </si>
+  <si>
+    <t>25UC</t>
+  </si>
+  <si>
+    <t>BRIDA EN U (PESTAÑA) PARA MANÓMETROS SERIE PFQ Y PFP 2,5"</t>
+  </si>
+  <si>
+    <t>PFQ806R3R1</t>
+  </si>
+  <si>
+    <t>MANOMETRO 2,5" INFERIOR 1/4 NPT 0-14 BAR</t>
+  </si>
+  <si>
+    <t>PFQ905R3R1</t>
+  </si>
+  <si>
+    <t>MANOMETRO 2,5" ROSCA POSTERIOR 1/4 NPT 0-10 BAR C/GLICERINA</t>
+  </si>
+  <si>
+    <t>PFQ915R3R1</t>
+  </si>
+  <si>
+    <t>MANOMETRO 2,5" ROSCA POSTERIOR 1/4 NPT 0-400 BAR C/GLICERINA</t>
+  </si>
+  <si>
+    <t>PFQ918R3R1</t>
+  </si>
+  <si>
+    <t>MANOMETRO 2,5" ROSCA POSTERIOR 1/4 NPT 0-600 BAR C/GLICERINA</t>
+  </si>
+  <si>
+    <t>FB-2</t>
+  </si>
+  <si>
+    <t>BOCA DE CARGA GRANDE BRIDADA 40 MIC.</t>
+  </si>
+  <si>
+    <t>FK-12</t>
+  </si>
+  <si>
+    <t>OJO DE BUEY NIVEL PLASTICO DE 1/2" BSP</t>
+  </si>
+  <si>
+    <t>PFP835ZRR1R11</t>
+  </si>
+  <si>
+    <t>MANOMETRO SERIE PFQ-ZR 2,5", 0/15.000 PSI - 0/1.000 bar, 1/4" NPT INFERIOR</t>
+  </si>
+  <si>
+    <t>934331T</t>
+  </si>
+  <si>
+    <t>FILTRO TRICEPTOR SILICA GEL 8"</t>
+  </si>
+  <si>
+    <t>313-2825-000</t>
+  </si>
+  <si>
+    <t>ENGRANAJE P50 DE 2 1/2"</t>
+  </si>
+  <si>
+    <t>391-0381-905</t>
+  </si>
+  <si>
+    <t>TORRINGTON P50</t>
+  </si>
+  <si>
+    <t>391-2185-912</t>
+  </si>
+  <si>
+    <t>PLACA AXIAL DE BRONCE P50</t>
+  </si>
+  <si>
+    <t>391-2882-051</t>
+  </si>
+  <si>
+    <t>CUERDA P30 Y P50</t>
+  </si>
+  <si>
+    <t>391-2883-119P</t>
+  </si>
+  <si>
+    <t>RETEN M-30 P/EJE ENTERIZO</t>
+  </si>
+  <si>
+    <t>391-2884-021P</t>
+  </si>
+  <si>
+    <t>SELLO GOMA SQUARE GASKET 50-25</t>
+  </si>
+  <si>
+    <t>10677-16-16P</t>
+  </si>
+  <si>
+    <t>TERMINAL RECTO HG JIC 1.5/16" UNF x MANGUERA R15 1"</t>
+  </si>
+  <si>
+    <t>SOL - 2308</t>
+  </si>
+  <si>
+    <t>10677-20-20P</t>
+  </si>
+  <si>
+    <t>TERMINAL RECTO HG JIC 1.5/8" UNF x MANGUERA R15 1.1/4"</t>
+  </si>
+  <si>
+    <t>10677-24-24P</t>
+  </si>
+  <si>
+    <t>TERMINAL RECTO HG JIC 1.7/8" UNF x MANGUERA R15 1.1/2"</t>
+  </si>
+  <si>
+    <t>11543-12-12P</t>
+  </si>
+  <si>
+    <t>TERMINAL BRIDA 1 1/2" SAE3000 X MANGUERA 3/4"</t>
+  </si>
+  <si>
+    <t>13943-20-20P</t>
+  </si>
+  <si>
+    <t>TERMINAL 90° HG JIC 1 5/8" X MANGUERA 1 1/4"</t>
+  </si>
+  <si>
+    <t>16A77-16-16P</t>
+  </si>
+  <si>
+    <t>TERMINAL BRIDA RECTA SERIE 6000 SAE62 1" X MANGUERA R15 1"</t>
+  </si>
+  <si>
+    <t>16N77-24-24P</t>
+  </si>
+  <si>
+    <t>TERMINAL BRIDA SERIE 6000 SAE 62 CODO 90º 1.1/2" X MANGUERA 1.1/2" R15</t>
+  </si>
+  <si>
+    <t>301-04P</t>
+  </si>
+  <si>
+    <t>MANG.SAE 100 R2 1/4"</t>
+  </si>
+  <si>
+    <t>301-06P</t>
+  </si>
+  <si>
+    <t>MANG.SAE 100 R2 3/8"</t>
+  </si>
+  <si>
+    <t>301-08P</t>
+  </si>
+  <si>
+    <t>MANG.SAE 100 R2 1/2"</t>
+  </si>
+  <si>
+    <t>301-12P</t>
+  </si>
+  <si>
+    <t>MANG.SAE 100 R2 3/4"</t>
+  </si>
+  <si>
+    <t>301-16P</t>
+  </si>
+  <si>
+    <t>MANG.SAE 100 R2 1"</t>
+  </si>
+  <si>
+    <t>301-20P</t>
+  </si>
+  <si>
+    <t>MANG.SAE 100 R2 1.1/4"</t>
+  </si>
+  <si>
+    <t>301-24P</t>
+  </si>
+  <si>
+    <t>MANG.SAE 100 R2 1.1/2"</t>
+  </si>
+  <si>
+    <t>301-32P</t>
+  </si>
+  <si>
+    <t>MANG.SAE 100 R2 2"</t>
+  </si>
+  <si>
+    <t>797TC-08P</t>
+  </si>
+  <si>
+    <t>MANGUERA R15 GLOBALCORE 1/2" 6000PSI</t>
+  </si>
+  <si>
+    <t>797TC-16P</t>
+  </si>
+  <si>
+    <t>MANGUERA R15 GLOBALCORE 1" 6000PSI</t>
+  </si>
+  <si>
+    <t>722TC-16</t>
+  </si>
+  <si>
+    <t>MANGUERA SAE 100 R12 1" 4000PSI</t>
+  </si>
+  <si>
+    <t>722TC-12</t>
+  </si>
+  <si>
+    <t>MANGUERA SAE 100 R12 3/4" 4000PSI</t>
+  </si>
+  <si>
+    <t>HG-100N</t>
+  </si>
+  <si>
+    <t>PROTECTOR P/MANGUERA ESPIRALADO DI 25 mm</t>
+  </si>
+  <si>
+    <t>SOL - 2309</t>
+  </si>
+  <si>
+    <t>HG-250N</t>
+  </si>
+  <si>
+    <t>PROTECTOR P/MANGUERA ESPIRALADO DI 65 mm</t>
+  </si>
+  <si>
+    <t>10643-04-04P</t>
+  </si>
+  <si>
+    <t>TERMINAL HG JIC 7/16" X MANGUERA 1/4"</t>
+  </si>
+  <si>
+    <t>10643-06-06P</t>
+  </si>
+  <si>
+    <t>TERMINAL HG JIC 9/16" X MANGUERA 3/8"</t>
+  </si>
+  <si>
+    <t>10643-08-08P</t>
+  </si>
+  <si>
+    <t>TERMINAL HG JIC 3/4" X MANGUERA 1/2"</t>
+  </si>
+  <si>
+    <t>10643-12-12P</t>
+  </si>
+  <si>
+    <t>TERMINAL HG JIC 1 1/16" X MANGUERA 3/4"</t>
+  </si>
+  <si>
+    <t>10643-16-16P</t>
+  </si>
+  <si>
+    <t>TERMINAL HG JIC 1 5/16"  X MANGUERA 1"</t>
+  </si>
+  <si>
+    <t>10643-20-20P</t>
+  </si>
+  <si>
+    <t>TERMINAL HG JIC 1 5/8"  X MANGUERA 1 1/4"</t>
+  </si>
+  <si>
+    <t>10643-24-24P</t>
+  </si>
+  <si>
+    <t>TERMINAL HG JIC 1.7/8" X MANGUERA 1 1/2"</t>
+  </si>
+  <si>
+    <t>10643-32-32P</t>
+  </si>
+  <si>
+    <t>TERMINAL HG JIC 2 1/2"  X MANGUERA 2"</t>
+  </si>
+  <si>
+    <t>30182-04-06P</t>
+  </si>
+  <si>
+    <t>TERMINAL MF 1/4" NPT X MANGUERA 3/8" PUSH LOOK</t>
+  </si>
+  <si>
+    <t>30682-06-04P</t>
+  </si>
+  <si>
+    <t>TERMINAL HG 9/16" X MANGUERA 1/4" PUSH LOOK</t>
+  </si>
+  <si>
+    <t>30682-06-06P</t>
+  </si>
+  <si>
+    <t>TERMINAL HG 9/16" X MANGUERA 3/8" PUSH LOOK</t>
+  </si>
+  <si>
+    <t>C5OX-24F</t>
+  </si>
+  <si>
+    <t>ADAP CODO 90° MF 1.7/8" AS JIC 37° X MF 1.7/8" AS ORING</t>
+  </si>
+  <si>
+    <t>C6X-24F</t>
+  </si>
+  <si>
+    <t>ADAPTADOR CODO 90° HG X MF JIC 1.7/8" UNF</t>
+  </si>
+  <si>
+    <t>C6X-32F</t>
+  </si>
+  <si>
+    <t>ADAPTADOR CODO 90° HG X MF JIC 2.1/2" UNF</t>
+  </si>
+  <si>
+    <t>FTX-32P</t>
+  </si>
+  <si>
+    <t>ADAP RECTO 2 1/2 UNF JIC X 2 NPT</t>
+  </si>
+  <si>
+    <t>HTX-32P</t>
+  </si>
+  <si>
+    <t>ADAP RECTO DOBLE MF JIC 2.1/2" UNF</t>
+  </si>
+  <si>
+    <t>S6X-24F</t>
+  </si>
+  <si>
+    <t>TEE MF X HG X MF JIC 1 7/8 UNF JIC</t>
+  </si>
+  <si>
+    <t>V6X-20F</t>
+  </si>
+  <si>
+    <t>ADAP CODO 45° MF x HG JIC 1.5/8" UNF</t>
+  </si>
+  <si>
+    <t>V6X-24F</t>
+  </si>
+  <si>
+    <t>ADAP CODO 45° MF x HG JIC 1.7/8" UNF</t>
   </si>
 </sst>
 </file>
@@ -455,7 +930,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R83"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
@@ -794,6 +1269,4318 @@
         <v>27</v>
       </c>
     </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7">
+        <v>61</v>
+      </c>
+      <c r="F7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>61</v>
+      </c>
+      <c r="I7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" t="s">
+        <v>31</v>
+      </c>
+      <c r="K7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" t="s">
+        <v>25</v>
+      </c>
+      <c r="M7" t="s">
+        <v>26</v>
+      </c>
+      <c r="N7" t="s">
+        <v>21</v>
+      </c>
+      <c r="O7" t="s">
+        <v>21</v>
+      </c>
+      <c r="P7" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>21</v>
+      </c>
+      <c r="R7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8">
+        <v>10</v>
+      </c>
+      <c r="F8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>10</v>
+      </c>
+      <c r="I8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M8" t="s">
+        <v>26</v>
+      </c>
+      <c r="N8" t="s">
+        <v>21</v>
+      </c>
+      <c r="O8" t="s">
+        <v>21</v>
+      </c>
+      <c r="P8" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>21</v>
+      </c>
+      <c r="R8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9">
+        <v>20</v>
+      </c>
+      <c r="F9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>20</v>
+      </c>
+      <c r="I9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" t="s">
+        <v>31</v>
+      </c>
+      <c r="K9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" t="s">
+        <v>25</v>
+      </c>
+      <c r="M9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N9" t="s">
+        <v>21</v>
+      </c>
+      <c r="O9" t="s">
+        <v>21</v>
+      </c>
+      <c r="P9" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>21</v>
+      </c>
+      <c r="R9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10">
+        <v>5</v>
+      </c>
+      <c r="F10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>5</v>
+      </c>
+      <c r="I10" t="s">
+        <v>22</v>
+      </c>
+      <c r="J10" t="s">
+        <v>31</v>
+      </c>
+      <c r="K10" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" t="s">
+        <v>25</v>
+      </c>
+      <c r="M10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N10" t="s">
+        <v>21</v>
+      </c>
+      <c r="O10" t="s">
+        <v>21</v>
+      </c>
+      <c r="P10" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>21</v>
+      </c>
+      <c r="R10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11">
+        <v>50</v>
+      </c>
+      <c r="F11" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>50</v>
+      </c>
+      <c r="I11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" t="s">
+        <v>31</v>
+      </c>
+      <c r="K11" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" t="s">
+        <v>25</v>
+      </c>
+      <c r="M11" t="s">
+        <v>26</v>
+      </c>
+      <c r="N11" t="s">
+        <v>21</v>
+      </c>
+      <c r="O11" t="s">
+        <v>21</v>
+      </c>
+      <c r="P11" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>21</v>
+      </c>
+      <c r="R11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>10</v>
+      </c>
+      <c r="I12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K12" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" t="s">
+        <v>25</v>
+      </c>
+      <c r="M12" t="s">
+        <v>26</v>
+      </c>
+      <c r="N12" t="s">
+        <v>21</v>
+      </c>
+      <c r="O12" t="s">
+        <v>21</v>
+      </c>
+      <c r="P12" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>21</v>
+      </c>
+      <c r="R12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>10</v>
+      </c>
+      <c r="I13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K13" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" t="s">
+        <v>25</v>
+      </c>
+      <c r="M13" t="s">
+        <v>26</v>
+      </c>
+      <c r="N13" t="s">
+        <v>21</v>
+      </c>
+      <c r="O13" t="s">
+        <v>21</v>
+      </c>
+      <c r="P13" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>21</v>
+      </c>
+      <c r="R13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14">
+        <v>10</v>
+      </c>
+      <c r="F14" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>10</v>
+      </c>
+      <c r="I14" t="s">
+        <v>22</v>
+      </c>
+      <c r="J14" t="s">
+        <v>31</v>
+      </c>
+      <c r="K14" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" t="s">
+        <v>25</v>
+      </c>
+      <c r="M14" t="s">
+        <v>26</v>
+      </c>
+      <c r="N14" t="s">
+        <v>21</v>
+      </c>
+      <c r="O14" t="s">
+        <v>21</v>
+      </c>
+      <c r="P14" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>21</v>
+      </c>
+      <c r="R14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15">
+        <v>100</v>
+      </c>
+      <c r="F15" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>100</v>
+      </c>
+      <c r="I15" t="s">
+        <v>22</v>
+      </c>
+      <c r="J15" t="s">
+        <v>31</v>
+      </c>
+      <c r="K15" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" t="s">
+        <v>25</v>
+      </c>
+      <c r="M15" t="s">
+        <v>26</v>
+      </c>
+      <c r="N15" t="s">
+        <v>21</v>
+      </c>
+      <c r="O15" t="s">
+        <v>21</v>
+      </c>
+      <c r="P15" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>21</v>
+      </c>
+      <c r="R15" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16">
+        <v>50</v>
+      </c>
+      <c r="F16" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>50</v>
+      </c>
+      <c r="I16" t="s">
+        <v>22</v>
+      </c>
+      <c r="J16" t="s">
+        <v>31</v>
+      </c>
+      <c r="K16" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" t="s">
+        <v>25</v>
+      </c>
+      <c r="M16" t="s">
+        <v>26</v>
+      </c>
+      <c r="N16" t="s">
+        <v>21</v>
+      </c>
+      <c r="O16" t="s">
+        <v>21</v>
+      </c>
+      <c r="P16" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>21</v>
+      </c>
+      <c r="R16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17">
+        <v>20</v>
+      </c>
+      <c r="F17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>20</v>
+      </c>
+      <c r="I17" t="s">
+        <v>22</v>
+      </c>
+      <c r="J17" t="s">
+        <v>31</v>
+      </c>
+      <c r="K17" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" t="s">
+        <v>25</v>
+      </c>
+      <c r="M17" t="s">
+        <v>26</v>
+      </c>
+      <c r="N17" t="s">
+        <v>21</v>
+      </c>
+      <c r="O17" t="s">
+        <v>21</v>
+      </c>
+      <c r="P17" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>21</v>
+      </c>
+      <c r="R17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18">
+        <v>5</v>
+      </c>
+      <c r="F18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>5</v>
+      </c>
+      <c r="I18" t="s">
+        <v>22</v>
+      </c>
+      <c r="J18" t="s">
+        <v>31</v>
+      </c>
+      <c r="K18" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18" t="s">
+        <v>25</v>
+      </c>
+      <c r="M18" t="s">
+        <v>26</v>
+      </c>
+      <c r="N18" t="s">
+        <v>21</v>
+      </c>
+      <c r="O18" t="s">
+        <v>21</v>
+      </c>
+      <c r="P18" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>21</v>
+      </c>
+      <c r="R18" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19">
+        <v>6</v>
+      </c>
+      <c r="F19" t="s">
+        <v>21</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>6</v>
+      </c>
+      <c r="I19" t="s">
+        <v>22</v>
+      </c>
+      <c r="J19" t="s">
+        <v>31</v>
+      </c>
+      <c r="K19" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" t="s">
+        <v>25</v>
+      </c>
+      <c r="M19" t="s">
+        <v>26</v>
+      </c>
+      <c r="N19" t="s">
+        <v>21</v>
+      </c>
+      <c r="O19" t="s">
+        <v>21</v>
+      </c>
+      <c r="P19" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>21</v>
+      </c>
+      <c r="R19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20">
+        <v>4</v>
+      </c>
+      <c r="F20" t="s">
+        <v>21</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>4</v>
+      </c>
+      <c r="I20" t="s">
+        <v>22</v>
+      </c>
+      <c r="J20" t="s">
+        <v>31</v>
+      </c>
+      <c r="K20" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20" t="s">
+        <v>25</v>
+      </c>
+      <c r="M20" t="s">
+        <v>26</v>
+      </c>
+      <c r="N20" t="s">
+        <v>21</v>
+      </c>
+      <c r="O20" t="s">
+        <v>21</v>
+      </c>
+      <c r="P20" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>21</v>
+      </c>
+      <c r="R20" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21">
+        <v>300</v>
+      </c>
+      <c r="F21" t="s">
+        <v>21</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>300</v>
+      </c>
+      <c r="I21" t="s">
+        <v>22</v>
+      </c>
+      <c r="J21" t="s">
+        <v>31</v>
+      </c>
+      <c r="K21" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21" t="s">
+        <v>25</v>
+      </c>
+      <c r="M21" t="s">
+        <v>26</v>
+      </c>
+      <c r="N21" t="s">
+        <v>21</v>
+      </c>
+      <c r="O21" t="s">
+        <v>21</v>
+      </c>
+      <c r="P21" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>21</v>
+      </c>
+      <c r="R21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>60</v>
+      </c>
+      <c r="B22" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" t="s">
+        <v>21</v>
+      </c>
+      <c r="E22">
+        <v>100</v>
+      </c>
+      <c r="F22" t="s">
+        <v>21</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>100</v>
+      </c>
+      <c r="I22" t="s">
+        <v>22</v>
+      </c>
+      <c r="J22" t="s">
+        <v>31</v>
+      </c>
+      <c r="K22" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" t="s">
+        <v>25</v>
+      </c>
+      <c r="M22" t="s">
+        <v>26</v>
+      </c>
+      <c r="N22" t="s">
+        <v>21</v>
+      </c>
+      <c r="O22" t="s">
+        <v>21</v>
+      </c>
+      <c r="P22" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>21</v>
+      </c>
+      <c r="R22" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>62</v>
+      </c>
+      <c r="B23" t="s">
+        <v>63</v>
+      </c>
+      <c r="C23" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23" t="s">
+        <v>21</v>
+      </c>
+      <c r="E23">
+        <v>200</v>
+      </c>
+      <c r="F23" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>200</v>
+      </c>
+      <c r="I23" t="s">
+        <v>22</v>
+      </c>
+      <c r="J23" t="s">
+        <v>31</v>
+      </c>
+      <c r="K23" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23" t="s">
+        <v>25</v>
+      </c>
+      <c r="M23" t="s">
+        <v>26</v>
+      </c>
+      <c r="N23" t="s">
+        <v>21</v>
+      </c>
+      <c r="O23" t="s">
+        <v>21</v>
+      </c>
+      <c r="P23" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>21</v>
+      </c>
+      <c r="R23" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>64</v>
+      </c>
+      <c r="B24" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D24" t="s">
+        <v>21</v>
+      </c>
+      <c r="E24">
+        <v>20</v>
+      </c>
+      <c r="F24" t="s">
+        <v>21</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>20</v>
+      </c>
+      <c r="I24" t="s">
+        <v>22</v>
+      </c>
+      <c r="J24" t="s">
+        <v>31</v>
+      </c>
+      <c r="K24" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" t="s">
+        <v>25</v>
+      </c>
+      <c r="M24" t="s">
+        <v>26</v>
+      </c>
+      <c r="N24" t="s">
+        <v>21</v>
+      </c>
+      <c r="O24" t="s">
+        <v>21</v>
+      </c>
+      <c r="P24" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>21</v>
+      </c>
+      <c r="R24" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>66</v>
+      </c>
+      <c r="B25" t="s">
+        <v>67</v>
+      </c>
+      <c r="C25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D25" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25">
+        <v>6</v>
+      </c>
+      <c r="F25" t="s">
+        <v>21</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>6</v>
+      </c>
+      <c r="I25" t="s">
+        <v>22</v>
+      </c>
+      <c r="J25" t="s">
+        <v>31</v>
+      </c>
+      <c r="K25" t="s">
+        <v>24</v>
+      </c>
+      <c r="L25" t="s">
+        <v>25</v>
+      </c>
+      <c r="M25" t="s">
+        <v>26</v>
+      </c>
+      <c r="N25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O25" t="s">
+        <v>21</v>
+      </c>
+      <c r="P25" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>21</v>
+      </c>
+      <c r="R25" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>68</v>
+      </c>
+      <c r="B26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C26" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26" t="s">
+        <v>21</v>
+      </c>
+      <c r="E26">
+        <v>6</v>
+      </c>
+      <c r="F26" t="s">
+        <v>21</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>6</v>
+      </c>
+      <c r="I26" t="s">
+        <v>22</v>
+      </c>
+      <c r="J26" t="s">
+        <v>31</v>
+      </c>
+      <c r="K26" t="s">
+        <v>24</v>
+      </c>
+      <c r="L26" t="s">
+        <v>25</v>
+      </c>
+      <c r="M26" t="s">
+        <v>26</v>
+      </c>
+      <c r="N26" t="s">
+        <v>21</v>
+      </c>
+      <c r="O26" t="s">
+        <v>21</v>
+      </c>
+      <c r="P26" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>21</v>
+      </c>
+      <c r="R26" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>70</v>
+      </c>
+      <c r="B27" t="s">
+        <v>71</v>
+      </c>
+      <c r="C27" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27">
+        <v>16</v>
+      </c>
+      <c r="F27" t="s">
+        <v>21</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>16</v>
+      </c>
+      <c r="I27" t="s">
+        <v>22</v>
+      </c>
+      <c r="J27" t="s">
+        <v>31</v>
+      </c>
+      <c r="K27" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27" t="s">
+        <v>25</v>
+      </c>
+      <c r="M27" t="s">
+        <v>26</v>
+      </c>
+      <c r="N27" t="s">
+        <v>21</v>
+      </c>
+      <c r="O27" t="s">
+        <v>21</v>
+      </c>
+      <c r="P27" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>21</v>
+      </c>
+      <c r="R27" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>72</v>
+      </c>
+      <c r="B28" t="s">
+        <v>73</v>
+      </c>
+      <c r="C28" t="s">
+        <v>30</v>
+      </c>
+      <c r="D28" t="s">
+        <v>21</v>
+      </c>
+      <c r="E28">
+        <v>20</v>
+      </c>
+      <c r="F28" t="s">
+        <v>21</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>20</v>
+      </c>
+      <c r="I28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J28" t="s">
+        <v>31</v>
+      </c>
+      <c r="K28" t="s">
+        <v>24</v>
+      </c>
+      <c r="L28" t="s">
+        <v>25</v>
+      </c>
+      <c r="M28" t="s">
+        <v>26</v>
+      </c>
+      <c r="N28" t="s">
+        <v>21</v>
+      </c>
+      <c r="O28" t="s">
+        <v>21</v>
+      </c>
+      <c r="P28" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>21</v>
+      </c>
+      <c r="R28" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>74</v>
+      </c>
+      <c r="B29" t="s">
+        <v>75</v>
+      </c>
+      <c r="C29" t="s">
+        <v>30</v>
+      </c>
+      <c r="D29" t="s">
+        <v>21</v>
+      </c>
+      <c r="E29">
+        <v>30</v>
+      </c>
+      <c r="F29" t="s">
+        <v>21</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>30</v>
+      </c>
+      <c r="I29" t="s">
+        <v>22</v>
+      </c>
+      <c r="J29" t="s">
+        <v>31</v>
+      </c>
+      <c r="K29" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29" t="s">
+        <v>25</v>
+      </c>
+      <c r="M29" t="s">
+        <v>26</v>
+      </c>
+      <c r="N29" t="s">
+        <v>21</v>
+      </c>
+      <c r="O29" t="s">
+        <v>21</v>
+      </c>
+      <c r="P29" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>21</v>
+      </c>
+      <c r="R29" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>76</v>
+      </c>
+      <c r="B30" t="s">
+        <v>77</v>
+      </c>
+      <c r="C30" t="s">
+        <v>30</v>
+      </c>
+      <c r="D30" t="s">
+        <v>21</v>
+      </c>
+      <c r="E30">
+        <v>8</v>
+      </c>
+      <c r="F30" t="s">
+        <v>21</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>8</v>
+      </c>
+      <c r="I30" t="s">
+        <v>22</v>
+      </c>
+      <c r="J30" t="s">
+        <v>31</v>
+      </c>
+      <c r="K30" t="s">
+        <v>24</v>
+      </c>
+      <c r="L30" t="s">
+        <v>25</v>
+      </c>
+      <c r="M30" t="s">
+        <v>26</v>
+      </c>
+      <c r="N30" t="s">
+        <v>21</v>
+      </c>
+      <c r="O30" t="s">
+        <v>21</v>
+      </c>
+      <c r="P30" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>21</v>
+      </c>
+      <c r="R30" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>78</v>
+      </c>
+      <c r="B31" t="s">
+        <v>79</v>
+      </c>
+      <c r="C31" t="s">
+        <v>30</v>
+      </c>
+      <c r="D31" t="s">
+        <v>21</v>
+      </c>
+      <c r="E31">
+        <v>25</v>
+      </c>
+      <c r="F31" t="s">
+        <v>21</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>25</v>
+      </c>
+      <c r="I31" t="s">
+        <v>22</v>
+      </c>
+      <c r="J31" t="s">
+        <v>31</v>
+      </c>
+      <c r="K31" t="s">
+        <v>24</v>
+      </c>
+      <c r="L31" t="s">
+        <v>25</v>
+      </c>
+      <c r="M31" t="s">
+        <v>26</v>
+      </c>
+      <c r="N31" t="s">
+        <v>21</v>
+      </c>
+      <c r="O31" t="s">
+        <v>21</v>
+      </c>
+      <c r="P31" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>21</v>
+      </c>
+      <c r="R31" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>80</v>
+      </c>
+      <c r="B32" t="s">
+        <v>81</v>
+      </c>
+      <c r="C32" t="s">
+        <v>30</v>
+      </c>
+      <c r="D32" t="s">
+        <v>21</v>
+      </c>
+      <c r="E32">
+        <v>8</v>
+      </c>
+      <c r="F32" t="s">
+        <v>21</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>8</v>
+      </c>
+      <c r="I32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J32" t="s">
+        <v>31</v>
+      </c>
+      <c r="K32" t="s">
+        <v>24</v>
+      </c>
+      <c r="L32" t="s">
+        <v>25</v>
+      </c>
+      <c r="M32" t="s">
+        <v>26</v>
+      </c>
+      <c r="N32" t="s">
+        <v>21</v>
+      </c>
+      <c r="O32" t="s">
+        <v>21</v>
+      </c>
+      <c r="P32" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>21</v>
+      </c>
+      <c r="R32" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>82</v>
+      </c>
+      <c r="B33" t="s">
+        <v>83</v>
+      </c>
+      <c r="C33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D33" t="s">
+        <v>21</v>
+      </c>
+      <c r="E33">
+        <v>40</v>
+      </c>
+      <c r="F33" t="s">
+        <v>21</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>40</v>
+      </c>
+      <c r="I33" t="s">
+        <v>22</v>
+      </c>
+      <c r="J33" t="s">
+        <v>31</v>
+      </c>
+      <c r="K33" t="s">
+        <v>24</v>
+      </c>
+      <c r="L33" t="s">
+        <v>25</v>
+      </c>
+      <c r="M33" t="s">
+        <v>26</v>
+      </c>
+      <c r="N33" t="s">
+        <v>21</v>
+      </c>
+      <c r="O33" t="s">
+        <v>21</v>
+      </c>
+      <c r="P33" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>21</v>
+      </c>
+      <c r="R33" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>84</v>
+      </c>
+      <c r="B34" t="s">
+        <v>85</v>
+      </c>
+      <c r="C34" t="s">
+        <v>30</v>
+      </c>
+      <c r="D34" t="s">
+        <v>21</v>
+      </c>
+      <c r="E34">
+        <v>5</v>
+      </c>
+      <c r="F34" t="s">
+        <v>21</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>5</v>
+      </c>
+      <c r="I34" t="s">
+        <v>22</v>
+      </c>
+      <c r="J34" t="s">
+        <v>31</v>
+      </c>
+      <c r="K34" t="s">
+        <v>24</v>
+      </c>
+      <c r="L34" t="s">
+        <v>25</v>
+      </c>
+      <c r="M34" t="s">
+        <v>26</v>
+      </c>
+      <c r="N34" t="s">
+        <v>21</v>
+      </c>
+      <c r="O34" t="s">
+        <v>21</v>
+      </c>
+      <c r="P34" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>21</v>
+      </c>
+      <c r="R34" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>86</v>
+      </c>
+      <c r="B35" t="s">
+        <v>87</v>
+      </c>
+      <c r="C35" t="s">
+        <v>30</v>
+      </c>
+      <c r="D35" t="s">
+        <v>21</v>
+      </c>
+      <c r="E35">
+        <v>2</v>
+      </c>
+      <c r="F35" t="s">
+        <v>21</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>2</v>
+      </c>
+      <c r="I35" t="s">
+        <v>22</v>
+      </c>
+      <c r="J35" t="s">
+        <v>31</v>
+      </c>
+      <c r="K35" t="s">
+        <v>24</v>
+      </c>
+      <c r="L35" t="s">
+        <v>25</v>
+      </c>
+      <c r="M35" t="s">
+        <v>26</v>
+      </c>
+      <c r="N35" t="s">
+        <v>21</v>
+      </c>
+      <c r="O35" t="s">
+        <v>21</v>
+      </c>
+      <c r="P35" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>21</v>
+      </c>
+      <c r="R35" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>88</v>
+      </c>
+      <c r="B36" t="s">
+        <v>89</v>
+      </c>
+      <c r="C36" t="s">
+        <v>30</v>
+      </c>
+      <c r="D36" t="s">
+        <v>21</v>
+      </c>
+      <c r="E36">
+        <v>20</v>
+      </c>
+      <c r="F36" t="s">
+        <v>21</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>20</v>
+      </c>
+      <c r="I36" t="s">
+        <v>22</v>
+      </c>
+      <c r="J36" t="s">
+        <v>31</v>
+      </c>
+      <c r="K36" t="s">
+        <v>24</v>
+      </c>
+      <c r="L36" t="s">
+        <v>25</v>
+      </c>
+      <c r="M36" t="s">
+        <v>26</v>
+      </c>
+      <c r="N36" t="s">
+        <v>21</v>
+      </c>
+      <c r="O36" t="s">
+        <v>21</v>
+      </c>
+      <c r="P36" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>21</v>
+      </c>
+      <c r="R36" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>90</v>
+      </c>
+      <c r="B37" t="s">
+        <v>91</v>
+      </c>
+      <c r="C37" t="s">
+        <v>30</v>
+      </c>
+      <c r="D37" t="s">
+        <v>21</v>
+      </c>
+      <c r="E37">
+        <v>15</v>
+      </c>
+      <c r="F37" t="s">
+        <v>21</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>15</v>
+      </c>
+      <c r="I37" t="s">
+        <v>22</v>
+      </c>
+      <c r="J37" t="s">
+        <v>31</v>
+      </c>
+      <c r="K37" t="s">
+        <v>24</v>
+      </c>
+      <c r="L37" t="s">
+        <v>25</v>
+      </c>
+      <c r="M37" t="s">
+        <v>26</v>
+      </c>
+      <c r="N37" t="s">
+        <v>21</v>
+      </c>
+      <c r="O37" t="s">
+        <v>21</v>
+      </c>
+      <c r="P37" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>21</v>
+      </c>
+      <c r="R37" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>92</v>
+      </c>
+      <c r="B38" t="s">
+        <v>93</v>
+      </c>
+      <c r="C38" t="s">
+        <v>30</v>
+      </c>
+      <c r="D38" t="s">
+        <v>21</v>
+      </c>
+      <c r="E38">
+        <v>30</v>
+      </c>
+      <c r="F38" t="s">
+        <v>21</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>30</v>
+      </c>
+      <c r="I38" t="s">
+        <v>22</v>
+      </c>
+      <c r="J38" t="s">
+        <v>31</v>
+      </c>
+      <c r="K38" t="s">
+        <v>24</v>
+      </c>
+      <c r="L38" t="s">
+        <v>25</v>
+      </c>
+      <c r="M38" t="s">
+        <v>26</v>
+      </c>
+      <c r="N38" t="s">
+        <v>21</v>
+      </c>
+      <c r="O38" t="s">
+        <v>21</v>
+      </c>
+      <c r="P38" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>21</v>
+      </c>
+      <c r="R38" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>94</v>
+      </c>
+      <c r="B39" t="s">
+        <v>95</v>
+      </c>
+      <c r="C39" t="s">
+        <v>30</v>
+      </c>
+      <c r="D39" t="s">
+        <v>21</v>
+      </c>
+      <c r="E39">
+        <v>100</v>
+      </c>
+      <c r="F39" t="s">
+        <v>21</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>100</v>
+      </c>
+      <c r="I39" t="s">
+        <v>22</v>
+      </c>
+      <c r="J39" t="s">
+        <v>31</v>
+      </c>
+      <c r="K39" t="s">
+        <v>24</v>
+      </c>
+      <c r="L39" t="s">
+        <v>25</v>
+      </c>
+      <c r="M39" t="s">
+        <v>26</v>
+      </c>
+      <c r="N39" t="s">
+        <v>21</v>
+      </c>
+      <c r="O39" t="s">
+        <v>21</v>
+      </c>
+      <c r="P39" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>21</v>
+      </c>
+      <c r="R39" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>96</v>
+      </c>
+      <c r="B40" t="s">
+        <v>97</v>
+      </c>
+      <c r="C40" t="s">
+        <v>30</v>
+      </c>
+      <c r="D40" t="s">
+        <v>21</v>
+      </c>
+      <c r="E40">
+        <v>50</v>
+      </c>
+      <c r="F40" t="s">
+        <v>21</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>50</v>
+      </c>
+      <c r="I40" t="s">
+        <v>22</v>
+      </c>
+      <c r="J40" t="s">
+        <v>31</v>
+      </c>
+      <c r="K40" t="s">
+        <v>24</v>
+      </c>
+      <c r="L40" t="s">
+        <v>25</v>
+      </c>
+      <c r="M40" t="s">
+        <v>26</v>
+      </c>
+      <c r="N40" t="s">
+        <v>21</v>
+      </c>
+      <c r="O40" t="s">
+        <v>21</v>
+      </c>
+      <c r="P40" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>21</v>
+      </c>
+      <c r="R40" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>98</v>
+      </c>
+      <c r="B41" t="s">
+        <v>99</v>
+      </c>
+      <c r="C41" t="s">
+        <v>30</v>
+      </c>
+      <c r="D41" t="s">
+        <v>21</v>
+      </c>
+      <c r="E41">
+        <v>20</v>
+      </c>
+      <c r="F41" t="s">
+        <v>21</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>20</v>
+      </c>
+      <c r="I41" t="s">
+        <v>22</v>
+      </c>
+      <c r="J41" t="s">
+        <v>31</v>
+      </c>
+      <c r="K41" t="s">
+        <v>24</v>
+      </c>
+      <c r="L41" t="s">
+        <v>25</v>
+      </c>
+      <c r="M41" t="s">
+        <v>26</v>
+      </c>
+      <c r="N41" t="s">
+        <v>21</v>
+      </c>
+      <c r="O41" t="s">
+        <v>21</v>
+      </c>
+      <c r="P41" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>21</v>
+      </c>
+      <c r="R41" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>100</v>
+      </c>
+      <c r="B42" t="s">
+        <v>101</v>
+      </c>
+      <c r="C42" t="s">
+        <v>30</v>
+      </c>
+      <c r="D42" t="s">
+        <v>21</v>
+      </c>
+      <c r="E42">
+        <v>100</v>
+      </c>
+      <c r="F42" t="s">
+        <v>21</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>100</v>
+      </c>
+      <c r="I42" t="s">
+        <v>22</v>
+      </c>
+      <c r="J42" t="s">
+        <v>31</v>
+      </c>
+      <c r="K42" t="s">
+        <v>24</v>
+      </c>
+      <c r="L42" t="s">
+        <v>25</v>
+      </c>
+      <c r="M42" t="s">
+        <v>26</v>
+      </c>
+      <c r="N42" t="s">
+        <v>21</v>
+      </c>
+      <c r="O42" t="s">
+        <v>21</v>
+      </c>
+      <c r="P42" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>21</v>
+      </c>
+      <c r="R42" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>102</v>
+      </c>
+      <c r="B43" t="s">
+        <v>103</v>
+      </c>
+      <c r="C43" t="s">
+        <v>104</v>
+      </c>
+      <c r="D43" t="s">
+        <v>21</v>
+      </c>
+      <c r="E43">
+        <v>200</v>
+      </c>
+      <c r="F43" t="s">
+        <v>21</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>200</v>
+      </c>
+      <c r="I43" t="s">
+        <v>22</v>
+      </c>
+      <c r="J43" t="s">
+        <v>31</v>
+      </c>
+      <c r="K43" t="s">
+        <v>24</v>
+      </c>
+      <c r="L43" t="s">
+        <v>25</v>
+      </c>
+      <c r="M43" t="s">
+        <v>26</v>
+      </c>
+      <c r="N43" t="s">
+        <v>21</v>
+      </c>
+      <c r="O43" t="s">
+        <v>21</v>
+      </c>
+      <c r="P43" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>21</v>
+      </c>
+      <c r="R43" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>105</v>
+      </c>
+      <c r="B44" t="s">
+        <v>106</v>
+      </c>
+      <c r="C44" t="s">
+        <v>104</v>
+      </c>
+      <c r="D44" t="s">
+        <v>21</v>
+      </c>
+      <c r="E44">
+        <v>100</v>
+      </c>
+      <c r="F44" t="s">
+        <v>21</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>100</v>
+      </c>
+      <c r="I44" t="s">
+        <v>22</v>
+      </c>
+      <c r="J44" t="s">
+        <v>31</v>
+      </c>
+      <c r="K44" t="s">
+        <v>24</v>
+      </c>
+      <c r="L44" t="s">
+        <v>25</v>
+      </c>
+      <c r="M44" t="s">
+        <v>26</v>
+      </c>
+      <c r="N44" t="s">
+        <v>21</v>
+      </c>
+      <c r="O44" t="s">
+        <v>21</v>
+      </c>
+      <c r="P44" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>21</v>
+      </c>
+      <c r="R44" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>107</v>
+      </c>
+      <c r="B45" t="s">
+        <v>108</v>
+      </c>
+      <c r="C45" t="s">
+        <v>104</v>
+      </c>
+      <c r="D45" t="s">
+        <v>21</v>
+      </c>
+      <c r="E45">
+        <v>30</v>
+      </c>
+      <c r="F45" t="s">
+        <v>21</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>30</v>
+      </c>
+      <c r="I45" t="s">
+        <v>22</v>
+      </c>
+      <c r="J45" t="s">
+        <v>31</v>
+      </c>
+      <c r="K45" t="s">
+        <v>24</v>
+      </c>
+      <c r="L45" t="s">
+        <v>25</v>
+      </c>
+      <c r="M45" t="s">
+        <v>26</v>
+      </c>
+      <c r="N45" t="s">
+        <v>21</v>
+      </c>
+      <c r="O45" t="s">
+        <v>21</v>
+      </c>
+      <c r="P45" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>21</v>
+      </c>
+      <c r="R45" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>109</v>
+      </c>
+      <c r="B46" t="s">
+        <v>110</v>
+      </c>
+      <c r="C46" t="s">
+        <v>104</v>
+      </c>
+      <c r="D46" t="s">
+        <v>21</v>
+      </c>
+      <c r="E46">
+        <v>10</v>
+      </c>
+      <c r="F46" t="s">
+        <v>21</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>10</v>
+      </c>
+      <c r="I46" t="s">
+        <v>22</v>
+      </c>
+      <c r="J46" t="s">
+        <v>31</v>
+      </c>
+      <c r="K46" t="s">
+        <v>24</v>
+      </c>
+      <c r="L46" t="s">
+        <v>25</v>
+      </c>
+      <c r="M46" t="s">
+        <v>26</v>
+      </c>
+      <c r="N46" t="s">
+        <v>21</v>
+      </c>
+      <c r="O46" t="s">
+        <v>21</v>
+      </c>
+      <c r="P46" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>21</v>
+      </c>
+      <c r="R46" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>111</v>
+      </c>
+      <c r="B47" t="s">
+        <v>112</v>
+      </c>
+      <c r="C47" t="s">
+        <v>104</v>
+      </c>
+      <c r="D47" t="s">
+        <v>21</v>
+      </c>
+      <c r="E47">
+        <v>90</v>
+      </c>
+      <c r="F47" t="s">
+        <v>21</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>90</v>
+      </c>
+      <c r="I47" t="s">
+        <v>22</v>
+      </c>
+      <c r="J47" t="s">
+        <v>31</v>
+      </c>
+      <c r="K47" t="s">
+        <v>24</v>
+      </c>
+      <c r="L47" t="s">
+        <v>25</v>
+      </c>
+      <c r="M47" t="s">
+        <v>26</v>
+      </c>
+      <c r="N47" t="s">
+        <v>21</v>
+      </c>
+      <c r="O47" t="s">
+        <v>21</v>
+      </c>
+      <c r="P47" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>21</v>
+      </c>
+      <c r="R47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>113</v>
+      </c>
+      <c r="B48" t="s">
+        <v>114</v>
+      </c>
+      <c r="C48" t="s">
+        <v>104</v>
+      </c>
+      <c r="D48" t="s">
+        <v>21</v>
+      </c>
+      <c r="E48">
+        <v>20</v>
+      </c>
+      <c r="F48" t="s">
+        <v>21</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>20</v>
+      </c>
+      <c r="I48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J48" t="s">
+        <v>31</v>
+      </c>
+      <c r="K48" t="s">
+        <v>24</v>
+      </c>
+      <c r="L48" t="s">
+        <v>25</v>
+      </c>
+      <c r="M48" t="s">
+        <v>26</v>
+      </c>
+      <c r="N48" t="s">
+        <v>21</v>
+      </c>
+      <c r="O48" t="s">
+        <v>21</v>
+      </c>
+      <c r="P48" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>21</v>
+      </c>
+      <c r="R48" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>115</v>
+      </c>
+      <c r="B49" t="s">
+        <v>116</v>
+      </c>
+      <c r="C49" t="s">
+        <v>104</v>
+      </c>
+      <c r="D49" t="s">
+        <v>21</v>
+      </c>
+      <c r="E49">
+        <v>10</v>
+      </c>
+      <c r="F49" t="s">
+        <v>21</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>10</v>
+      </c>
+      <c r="I49" t="s">
+        <v>22</v>
+      </c>
+      <c r="J49" t="s">
+        <v>31</v>
+      </c>
+      <c r="K49" t="s">
+        <v>24</v>
+      </c>
+      <c r="L49" t="s">
+        <v>25</v>
+      </c>
+      <c r="M49" t="s">
+        <v>26</v>
+      </c>
+      <c r="N49" t="s">
+        <v>21</v>
+      </c>
+      <c r="O49" t="s">
+        <v>21</v>
+      </c>
+      <c r="P49" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>21</v>
+      </c>
+      <c r="R49" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>117</v>
+      </c>
+      <c r="B50" t="s">
+        <v>118</v>
+      </c>
+      <c r="C50" t="s">
+        <v>104</v>
+      </c>
+      <c r="D50" t="s">
+        <v>21</v>
+      </c>
+      <c r="E50">
+        <v>3600</v>
+      </c>
+      <c r="F50" t="s">
+        <v>21</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>3600</v>
+      </c>
+      <c r="I50" t="s">
+        <v>22</v>
+      </c>
+      <c r="J50" t="s">
+        <v>31</v>
+      </c>
+      <c r="K50" t="s">
+        <v>24</v>
+      </c>
+      <c r="L50" t="s">
+        <v>25</v>
+      </c>
+      <c r="M50" t="s">
+        <v>26</v>
+      </c>
+      <c r="N50" t="s">
+        <v>21</v>
+      </c>
+      <c r="O50" t="s">
+        <v>21</v>
+      </c>
+      <c r="P50" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>21</v>
+      </c>
+      <c r="R50" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>119</v>
+      </c>
+      <c r="B51" t="s">
+        <v>120</v>
+      </c>
+      <c r="C51" t="s">
+        <v>104</v>
+      </c>
+      <c r="D51" t="s">
+        <v>21</v>
+      </c>
+      <c r="E51">
+        <v>6500</v>
+      </c>
+      <c r="F51" t="s">
+        <v>21</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>6500</v>
+      </c>
+      <c r="I51" t="s">
+        <v>22</v>
+      </c>
+      <c r="J51" t="s">
+        <v>31</v>
+      </c>
+      <c r="K51" t="s">
+        <v>24</v>
+      </c>
+      <c r="L51" t="s">
+        <v>25</v>
+      </c>
+      <c r="M51" t="s">
+        <v>26</v>
+      </c>
+      <c r="N51" t="s">
+        <v>21</v>
+      </c>
+      <c r="O51" t="s">
+        <v>21</v>
+      </c>
+      <c r="P51" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>21</v>
+      </c>
+      <c r="R51" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>121</v>
+      </c>
+      <c r="B52" t="s">
+        <v>122</v>
+      </c>
+      <c r="C52" t="s">
+        <v>104</v>
+      </c>
+      <c r="D52" t="s">
+        <v>21</v>
+      </c>
+      <c r="E52">
+        <v>3800</v>
+      </c>
+      <c r="F52" t="s">
+        <v>21</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>3800</v>
+      </c>
+      <c r="I52" t="s">
+        <v>22</v>
+      </c>
+      <c r="J52" t="s">
+        <v>31</v>
+      </c>
+      <c r="K52" t="s">
+        <v>24</v>
+      </c>
+      <c r="L52" t="s">
+        <v>25</v>
+      </c>
+      <c r="M52" t="s">
+        <v>26</v>
+      </c>
+      <c r="N52" t="s">
+        <v>21</v>
+      </c>
+      <c r="O52" t="s">
+        <v>21</v>
+      </c>
+      <c r="P52" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>21</v>
+      </c>
+      <c r="R52" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>123</v>
+      </c>
+      <c r="B53" t="s">
+        <v>124</v>
+      </c>
+      <c r="C53" t="s">
+        <v>104</v>
+      </c>
+      <c r="D53" t="s">
+        <v>21</v>
+      </c>
+      <c r="E53">
+        <v>1300</v>
+      </c>
+      <c r="F53" t="s">
+        <v>21</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>1300</v>
+      </c>
+      <c r="I53" t="s">
+        <v>22</v>
+      </c>
+      <c r="J53" t="s">
+        <v>31</v>
+      </c>
+      <c r="K53" t="s">
+        <v>24</v>
+      </c>
+      <c r="L53" t="s">
+        <v>25</v>
+      </c>
+      <c r="M53" t="s">
+        <v>26</v>
+      </c>
+      <c r="N53" t="s">
+        <v>21</v>
+      </c>
+      <c r="O53" t="s">
+        <v>21</v>
+      </c>
+      <c r="P53" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>21</v>
+      </c>
+      <c r="R53" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>125</v>
+      </c>
+      <c r="B54" t="s">
+        <v>126</v>
+      </c>
+      <c r="C54" t="s">
+        <v>104</v>
+      </c>
+      <c r="D54" t="s">
+        <v>21</v>
+      </c>
+      <c r="E54">
+        <v>2000</v>
+      </c>
+      <c r="F54" t="s">
+        <v>21</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>2000</v>
+      </c>
+      <c r="I54" t="s">
+        <v>22</v>
+      </c>
+      <c r="J54" t="s">
+        <v>31</v>
+      </c>
+      <c r="K54" t="s">
+        <v>24</v>
+      </c>
+      <c r="L54" t="s">
+        <v>25</v>
+      </c>
+      <c r="M54" t="s">
+        <v>26</v>
+      </c>
+      <c r="N54" t="s">
+        <v>21</v>
+      </c>
+      <c r="O54" t="s">
+        <v>21</v>
+      </c>
+      <c r="P54" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>21</v>
+      </c>
+      <c r="R54" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>127</v>
+      </c>
+      <c r="B55" t="s">
+        <v>128</v>
+      </c>
+      <c r="C55" t="s">
+        <v>104</v>
+      </c>
+      <c r="D55" t="s">
+        <v>21</v>
+      </c>
+      <c r="E55">
+        <v>1200</v>
+      </c>
+      <c r="F55" t="s">
+        <v>21</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>1200</v>
+      </c>
+      <c r="I55" t="s">
+        <v>22</v>
+      </c>
+      <c r="J55" t="s">
+        <v>31</v>
+      </c>
+      <c r="K55" t="s">
+        <v>24</v>
+      </c>
+      <c r="L55" t="s">
+        <v>25</v>
+      </c>
+      <c r="M55" t="s">
+        <v>26</v>
+      </c>
+      <c r="N55" t="s">
+        <v>21</v>
+      </c>
+      <c r="O55" t="s">
+        <v>21</v>
+      </c>
+      <c r="P55" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>21</v>
+      </c>
+      <c r="R55" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>129</v>
+      </c>
+      <c r="B56" t="s">
+        <v>130</v>
+      </c>
+      <c r="C56" t="s">
+        <v>104</v>
+      </c>
+      <c r="D56" t="s">
+        <v>21</v>
+      </c>
+      <c r="E56">
+        <v>1500</v>
+      </c>
+      <c r="F56" t="s">
+        <v>21</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>1500</v>
+      </c>
+      <c r="I56" t="s">
+        <v>22</v>
+      </c>
+      <c r="J56" t="s">
+        <v>31</v>
+      </c>
+      <c r="K56" t="s">
+        <v>24</v>
+      </c>
+      <c r="L56" t="s">
+        <v>25</v>
+      </c>
+      <c r="M56" t="s">
+        <v>26</v>
+      </c>
+      <c r="N56" t="s">
+        <v>21</v>
+      </c>
+      <c r="O56" t="s">
+        <v>21</v>
+      </c>
+      <c r="P56" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>21</v>
+      </c>
+      <c r="R56" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>131</v>
+      </c>
+      <c r="B57" t="s">
+        <v>132</v>
+      </c>
+      <c r="C57" t="s">
+        <v>104</v>
+      </c>
+      <c r="D57" t="s">
+        <v>21</v>
+      </c>
+      <c r="E57">
+        <v>200</v>
+      </c>
+      <c r="F57" t="s">
+        <v>21</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>200</v>
+      </c>
+      <c r="I57" t="s">
+        <v>22</v>
+      </c>
+      <c r="J57" t="s">
+        <v>31</v>
+      </c>
+      <c r="K57" t="s">
+        <v>24</v>
+      </c>
+      <c r="L57" t="s">
+        <v>25</v>
+      </c>
+      <c r="M57" t="s">
+        <v>26</v>
+      </c>
+      <c r="N57" t="s">
+        <v>21</v>
+      </c>
+      <c r="O57" t="s">
+        <v>21</v>
+      </c>
+      <c r="P57" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>21</v>
+      </c>
+      <c r="R57" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>133</v>
+      </c>
+      <c r="B58" t="s">
+        <v>134</v>
+      </c>
+      <c r="C58" t="s">
+        <v>104</v>
+      </c>
+      <c r="D58" t="s">
+        <v>21</v>
+      </c>
+      <c r="E58">
+        <v>100</v>
+      </c>
+      <c r="F58" t="s">
+        <v>21</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>100</v>
+      </c>
+      <c r="I58" t="s">
+        <v>22</v>
+      </c>
+      <c r="J58" t="s">
+        <v>31</v>
+      </c>
+      <c r="K58" t="s">
+        <v>24</v>
+      </c>
+      <c r="L58" t="s">
+        <v>25</v>
+      </c>
+      <c r="M58" t="s">
+        <v>26</v>
+      </c>
+      <c r="N58" t="s">
+        <v>21</v>
+      </c>
+      <c r="O58" t="s">
+        <v>21</v>
+      </c>
+      <c r="P58" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>21</v>
+      </c>
+      <c r="R58" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>135</v>
+      </c>
+      <c r="B59" t="s">
+        <v>136</v>
+      </c>
+      <c r="C59" t="s">
+        <v>104</v>
+      </c>
+      <c r="D59" t="s">
+        <v>21</v>
+      </c>
+      <c r="E59">
+        <v>100</v>
+      </c>
+      <c r="F59" t="s">
+        <v>21</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>100</v>
+      </c>
+      <c r="I59" t="s">
+        <v>22</v>
+      </c>
+      <c r="J59" t="s">
+        <v>31</v>
+      </c>
+      <c r="K59" t="s">
+        <v>24</v>
+      </c>
+      <c r="L59" t="s">
+        <v>25</v>
+      </c>
+      <c r="M59" t="s">
+        <v>26</v>
+      </c>
+      <c r="N59" t="s">
+        <v>21</v>
+      </c>
+      <c r="O59" t="s">
+        <v>21</v>
+      </c>
+      <c r="P59" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>21</v>
+      </c>
+      <c r="R59" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>137</v>
+      </c>
+      <c r="B60" t="s">
+        <v>138</v>
+      </c>
+      <c r="C60" t="s">
+        <v>104</v>
+      </c>
+      <c r="D60" t="s">
+        <v>21</v>
+      </c>
+      <c r="E60">
+        <v>550</v>
+      </c>
+      <c r="F60" t="s">
+        <v>21</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>550</v>
+      </c>
+      <c r="I60" t="s">
+        <v>22</v>
+      </c>
+      <c r="J60" t="s">
+        <v>31</v>
+      </c>
+      <c r="K60" t="s">
+        <v>24</v>
+      </c>
+      <c r="L60" t="s">
+        <v>25</v>
+      </c>
+      <c r="M60" t="s">
+        <v>26</v>
+      </c>
+      <c r="N60" t="s">
+        <v>21</v>
+      </c>
+      <c r="O60" t="s">
+        <v>21</v>
+      </c>
+      <c r="P60" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>21</v>
+      </c>
+      <c r="R60" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>139</v>
+      </c>
+      <c r="B61" t="s">
+        <v>140</v>
+      </c>
+      <c r="C61" t="s">
+        <v>104</v>
+      </c>
+      <c r="D61" t="s">
+        <v>21</v>
+      </c>
+      <c r="E61">
+        <v>500</v>
+      </c>
+      <c r="F61" t="s">
+        <v>21</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>500</v>
+      </c>
+      <c r="I61" t="s">
+        <v>22</v>
+      </c>
+      <c r="J61" t="s">
+        <v>31</v>
+      </c>
+      <c r="K61" t="s">
+        <v>24</v>
+      </c>
+      <c r="L61" t="s">
+        <v>25</v>
+      </c>
+      <c r="M61" t="s">
+        <v>26</v>
+      </c>
+      <c r="N61" t="s">
+        <v>21</v>
+      </c>
+      <c r="O61" t="s">
+        <v>21</v>
+      </c>
+      <c r="P61" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>21</v>
+      </c>
+      <c r="R61" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>141</v>
+      </c>
+      <c r="B62" t="s">
+        <v>142</v>
+      </c>
+      <c r="C62" t="s">
+        <v>143</v>
+      </c>
+      <c r="D62" t="s">
+        <v>21</v>
+      </c>
+      <c r="E62">
+        <v>2500</v>
+      </c>
+      <c r="F62" t="s">
+        <v>21</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>2500</v>
+      </c>
+      <c r="I62" t="s">
+        <v>22</v>
+      </c>
+      <c r="J62" t="s">
+        <v>31</v>
+      </c>
+      <c r="K62" t="s">
+        <v>24</v>
+      </c>
+      <c r="L62" t="s">
+        <v>25</v>
+      </c>
+      <c r="M62" t="s">
+        <v>26</v>
+      </c>
+      <c r="N62" t="s">
+        <v>21</v>
+      </c>
+      <c r="O62" t="s">
+        <v>21</v>
+      </c>
+      <c r="P62" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>21</v>
+      </c>
+      <c r="R62" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>144</v>
+      </c>
+      <c r="B63" t="s">
+        <v>145</v>
+      </c>
+      <c r="C63" t="s">
+        <v>143</v>
+      </c>
+      <c r="D63" t="s">
+        <v>21</v>
+      </c>
+      <c r="E63">
+        <v>500</v>
+      </c>
+      <c r="F63" t="s">
+        <v>21</v>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>500</v>
+      </c>
+      <c r="I63" t="s">
+        <v>22</v>
+      </c>
+      <c r="J63" t="s">
+        <v>31</v>
+      </c>
+      <c r="K63" t="s">
+        <v>24</v>
+      </c>
+      <c r="L63" t="s">
+        <v>25</v>
+      </c>
+      <c r="M63" t="s">
+        <v>26</v>
+      </c>
+      <c r="N63" t="s">
+        <v>21</v>
+      </c>
+      <c r="O63" t="s">
+        <v>21</v>
+      </c>
+      <c r="P63" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>21</v>
+      </c>
+      <c r="R63" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>146</v>
+      </c>
+      <c r="B64" t="s">
+        <v>147</v>
+      </c>
+      <c r="C64" t="s">
+        <v>143</v>
+      </c>
+      <c r="D64" t="s">
+        <v>21</v>
+      </c>
+      <c r="E64">
+        <v>2200</v>
+      </c>
+      <c r="F64" t="s">
+        <v>21</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>2200</v>
+      </c>
+      <c r="I64" t="s">
+        <v>22</v>
+      </c>
+      <c r="J64" t="s">
+        <v>31</v>
+      </c>
+      <c r="K64" t="s">
+        <v>24</v>
+      </c>
+      <c r="L64" t="s">
+        <v>25</v>
+      </c>
+      <c r="M64" t="s">
+        <v>26</v>
+      </c>
+      <c r="N64" t="s">
+        <v>21</v>
+      </c>
+      <c r="O64" t="s">
+        <v>21</v>
+      </c>
+      <c r="P64" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>21</v>
+      </c>
+      <c r="R64" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>148</v>
+      </c>
+      <c r="B65" t="s">
+        <v>149</v>
+      </c>
+      <c r="C65" t="s">
+        <v>143</v>
+      </c>
+      <c r="D65" t="s">
+        <v>21</v>
+      </c>
+      <c r="E65">
+        <v>2600</v>
+      </c>
+      <c r="F65" t="s">
+        <v>21</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>2600</v>
+      </c>
+      <c r="I65" t="s">
+        <v>22</v>
+      </c>
+      <c r="J65" t="s">
+        <v>31</v>
+      </c>
+      <c r="K65" t="s">
+        <v>24</v>
+      </c>
+      <c r="L65" t="s">
+        <v>25</v>
+      </c>
+      <c r="M65" t="s">
+        <v>26</v>
+      </c>
+      <c r="N65" t="s">
+        <v>21</v>
+      </c>
+      <c r="O65" t="s">
+        <v>21</v>
+      </c>
+      <c r="P65" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>21</v>
+      </c>
+      <c r="R65" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>150</v>
+      </c>
+      <c r="B66" t="s">
+        <v>151</v>
+      </c>
+      <c r="C66" t="s">
+        <v>143</v>
+      </c>
+      <c r="D66" t="s">
+        <v>21</v>
+      </c>
+      <c r="E66">
+        <v>2400</v>
+      </c>
+      <c r="F66" t="s">
+        <v>21</v>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>2400</v>
+      </c>
+      <c r="I66" t="s">
+        <v>22</v>
+      </c>
+      <c r="J66" t="s">
+        <v>31</v>
+      </c>
+      <c r="K66" t="s">
+        <v>24</v>
+      </c>
+      <c r="L66" t="s">
+        <v>25</v>
+      </c>
+      <c r="M66" t="s">
+        <v>26</v>
+      </c>
+      <c r="N66" t="s">
+        <v>21</v>
+      </c>
+      <c r="O66" t="s">
+        <v>21</v>
+      </c>
+      <c r="P66" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>21</v>
+      </c>
+      <c r="R66" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>152</v>
+      </c>
+      <c r="B67" t="s">
+        <v>153</v>
+      </c>
+      <c r="C67" t="s">
+        <v>143</v>
+      </c>
+      <c r="D67" t="s">
+        <v>21</v>
+      </c>
+      <c r="E67">
+        <v>2400</v>
+      </c>
+      <c r="F67" t="s">
+        <v>21</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>2400</v>
+      </c>
+      <c r="I67" t="s">
+        <v>22</v>
+      </c>
+      <c r="J67" t="s">
+        <v>31</v>
+      </c>
+      <c r="K67" t="s">
+        <v>24</v>
+      </c>
+      <c r="L67" t="s">
+        <v>25</v>
+      </c>
+      <c r="M67" t="s">
+        <v>26</v>
+      </c>
+      <c r="N67" t="s">
+        <v>21</v>
+      </c>
+      <c r="O67" t="s">
+        <v>21</v>
+      </c>
+      <c r="P67" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>21</v>
+      </c>
+      <c r="R67" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>154</v>
+      </c>
+      <c r="B68" t="s">
+        <v>155</v>
+      </c>
+      <c r="C68" t="s">
+        <v>143</v>
+      </c>
+      <c r="D68" t="s">
+        <v>21</v>
+      </c>
+      <c r="E68">
+        <v>2000</v>
+      </c>
+      <c r="F68" t="s">
+        <v>21</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>2000</v>
+      </c>
+      <c r="I68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J68" t="s">
+        <v>31</v>
+      </c>
+      <c r="K68" t="s">
+        <v>24</v>
+      </c>
+      <c r="L68" t="s">
+        <v>25</v>
+      </c>
+      <c r="M68" t="s">
+        <v>26</v>
+      </c>
+      <c r="N68" t="s">
+        <v>21</v>
+      </c>
+      <c r="O68" t="s">
+        <v>21</v>
+      </c>
+      <c r="P68" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>21</v>
+      </c>
+      <c r="R68" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>156</v>
+      </c>
+      <c r="B69" t="s">
+        <v>157</v>
+      </c>
+      <c r="C69" t="s">
+        <v>143</v>
+      </c>
+      <c r="D69" t="s">
+        <v>21</v>
+      </c>
+      <c r="E69">
+        <v>1200</v>
+      </c>
+      <c r="F69" t="s">
+        <v>21</v>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>1200</v>
+      </c>
+      <c r="I69" t="s">
+        <v>22</v>
+      </c>
+      <c r="J69" t="s">
+        <v>31</v>
+      </c>
+      <c r="K69" t="s">
+        <v>24</v>
+      </c>
+      <c r="L69" t="s">
+        <v>25</v>
+      </c>
+      <c r="M69" t="s">
+        <v>26</v>
+      </c>
+      <c r="N69" t="s">
+        <v>21</v>
+      </c>
+      <c r="O69" t="s">
+        <v>21</v>
+      </c>
+      <c r="P69" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>21</v>
+      </c>
+      <c r="R69" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>158</v>
+      </c>
+      <c r="B70" t="s">
+        <v>159</v>
+      </c>
+      <c r="C70" t="s">
+        <v>143</v>
+      </c>
+      <c r="D70" t="s">
+        <v>21</v>
+      </c>
+      <c r="E70">
+        <v>1200</v>
+      </c>
+      <c r="F70" t="s">
+        <v>21</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>1200</v>
+      </c>
+      <c r="I70" t="s">
+        <v>22</v>
+      </c>
+      <c r="J70" t="s">
+        <v>31</v>
+      </c>
+      <c r="K70" t="s">
+        <v>24</v>
+      </c>
+      <c r="L70" t="s">
+        <v>25</v>
+      </c>
+      <c r="M70" t="s">
+        <v>26</v>
+      </c>
+      <c r="N70" t="s">
+        <v>21</v>
+      </c>
+      <c r="O70" t="s">
+        <v>21</v>
+      </c>
+      <c r="P70" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>21</v>
+      </c>
+      <c r="R70" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>160</v>
+      </c>
+      <c r="B71" t="s">
+        <v>161</v>
+      </c>
+      <c r="C71" t="s">
+        <v>143</v>
+      </c>
+      <c r="D71" t="s">
+        <v>21</v>
+      </c>
+      <c r="E71">
+        <v>750</v>
+      </c>
+      <c r="F71" t="s">
+        <v>21</v>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>750</v>
+      </c>
+      <c r="I71" t="s">
+        <v>22</v>
+      </c>
+      <c r="J71" t="s">
+        <v>31</v>
+      </c>
+      <c r="K71" t="s">
+        <v>24</v>
+      </c>
+      <c r="L71" t="s">
+        <v>25</v>
+      </c>
+      <c r="M71" t="s">
+        <v>26</v>
+      </c>
+      <c r="N71" t="s">
+        <v>21</v>
+      </c>
+      <c r="O71" t="s">
+        <v>21</v>
+      </c>
+      <c r="P71" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>21</v>
+      </c>
+      <c r="R71" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>162</v>
+      </c>
+      <c r="B72" t="s">
+        <v>163</v>
+      </c>
+      <c r="C72" t="s">
+        <v>143</v>
+      </c>
+      <c r="D72" t="s">
+        <v>21</v>
+      </c>
+      <c r="E72">
+        <v>450</v>
+      </c>
+      <c r="F72" t="s">
+        <v>21</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>450</v>
+      </c>
+      <c r="I72" t="s">
+        <v>22</v>
+      </c>
+      <c r="J72" t="s">
+        <v>31</v>
+      </c>
+      <c r="K72" t="s">
+        <v>24</v>
+      </c>
+      <c r="L72" t="s">
+        <v>25</v>
+      </c>
+      <c r="M72" t="s">
+        <v>26</v>
+      </c>
+      <c r="N72" t="s">
+        <v>21</v>
+      </c>
+      <c r="O72" t="s">
+        <v>21</v>
+      </c>
+      <c r="P72" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>21</v>
+      </c>
+      <c r="R72" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>164</v>
+      </c>
+      <c r="B73" t="s">
+        <v>165</v>
+      </c>
+      <c r="C73" t="s">
+        <v>143</v>
+      </c>
+      <c r="D73" t="s">
+        <v>21</v>
+      </c>
+      <c r="E73">
+        <v>200</v>
+      </c>
+      <c r="F73" t="s">
+        <v>21</v>
+      </c>
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
+        <v>200</v>
+      </c>
+      <c r="I73" t="s">
+        <v>22</v>
+      </c>
+      <c r="J73" t="s">
+        <v>31</v>
+      </c>
+      <c r="K73" t="s">
+        <v>24</v>
+      </c>
+      <c r="L73" t="s">
+        <v>25</v>
+      </c>
+      <c r="M73" t="s">
+        <v>26</v>
+      </c>
+      <c r="N73" t="s">
+        <v>21</v>
+      </c>
+      <c r="O73" t="s">
+        <v>21</v>
+      </c>
+      <c r="P73" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>21</v>
+      </c>
+      <c r="R73" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>166</v>
+      </c>
+      <c r="B74" t="s">
+        <v>167</v>
+      </c>
+      <c r="C74" t="s">
+        <v>143</v>
+      </c>
+      <c r="D74" t="s">
+        <v>21</v>
+      </c>
+      <c r="E74">
+        <v>500</v>
+      </c>
+      <c r="F74" t="s">
+        <v>21</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
+        <v>500</v>
+      </c>
+      <c r="I74" t="s">
+        <v>22</v>
+      </c>
+      <c r="J74" t="s">
+        <v>31</v>
+      </c>
+      <c r="K74" t="s">
+        <v>24</v>
+      </c>
+      <c r="L74" t="s">
+        <v>25</v>
+      </c>
+      <c r="M74" t="s">
+        <v>26</v>
+      </c>
+      <c r="N74" t="s">
+        <v>21</v>
+      </c>
+      <c r="O74" t="s">
+        <v>21</v>
+      </c>
+      <c r="P74" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>21</v>
+      </c>
+      <c r="R74" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>32</v>
+      </c>
+      <c r="B75" t="s">
+        <v>33</v>
+      </c>
+      <c r="C75" t="s">
+        <v>143</v>
+      </c>
+      <c r="D75" t="s">
+        <v>21</v>
+      </c>
+      <c r="E75">
+        <v>20</v>
+      </c>
+      <c r="F75" t="s">
+        <v>21</v>
+      </c>
+      <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="H75">
+        <v>20</v>
+      </c>
+      <c r="I75" t="s">
+        <v>22</v>
+      </c>
+      <c r="J75" t="s">
+        <v>31</v>
+      </c>
+      <c r="K75" t="s">
+        <v>24</v>
+      </c>
+      <c r="L75" t="s">
+        <v>25</v>
+      </c>
+      <c r="M75" t="s">
+        <v>26</v>
+      </c>
+      <c r="N75" t="s">
+        <v>21</v>
+      </c>
+      <c r="O75" t="s">
+        <v>21</v>
+      </c>
+      <c r="P75" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>21</v>
+      </c>
+      <c r="R75" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>168</v>
+      </c>
+      <c r="B76" t="s">
+        <v>169</v>
+      </c>
+      <c r="C76" t="s">
+        <v>143</v>
+      </c>
+      <c r="D76" t="s">
+        <v>21</v>
+      </c>
+      <c r="E76">
+        <v>70</v>
+      </c>
+      <c r="F76" t="s">
+        <v>21</v>
+      </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <v>70</v>
+      </c>
+      <c r="I76" t="s">
+        <v>22</v>
+      </c>
+      <c r="J76" t="s">
+        <v>31</v>
+      </c>
+      <c r="K76" t="s">
+        <v>24</v>
+      </c>
+      <c r="L76" t="s">
+        <v>25</v>
+      </c>
+      <c r="M76" t="s">
+        <v>26</v>
+      </c>
+      <c r="N76" t="s">
+        <v>21</v>
+      </c>
+      <c r="O76" t="s">
+        <v>21</v>
+      </c>
+      <c r="P76" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>21</v>
+      </c>
+      <c r="R76" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>170</v>
+      </c>
+      <c r="B77" t="s">
+        <v>171</v>
+      </c>
+      <c r="C77" t="s">
+        <v>143</v>
+      </c>
+      <c r="D77" t="s">
+        <v>21</v>
+      </c>
+      <c r="E77">
+        <v>300</v>
+      </c>
+      <c r="F77" t="s">
+        <v>21</v>
+      </c>
+      <c r="G77">
+        <v>0</v>
+      </c>
+      <c r="H77">
+        <v>300</v>
+      </c>
+      <c r="I77" t="s">
+        <v>22</v>
+      </c>
+      <c r="J77" t="s">
+        <v>31</v>
+      </c>
+      <c r="K77" t="s">
+        <v>24</v>
+      </c>
+      <c r="L77" t="s">
+        <v>25</v>
+      </c>
+      <c r="M77" t="s">
+        <v>26</v>
+      </c>
+      <c r="N77" t="s">
+        <v>21</v>
+      </c>
+      <c r="O77" t="s">
+        <v>21</v>
+      </c>
+      <c r="P77" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>21</v>
+      </c>
+      <c r="R77" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>172</v>
+      </c>
+      <c r="B78" t="s">
+        <v>173</v>
+      </c>
+      <c r="C78" t="s">
+        <v>143</v>
+      </c>
+      <c r="D78" t="s">
+        <v>21</v>
+      </c>
+      <c r="E78">
+        <v>30</v>
+      </c>
+      <c r="F78" t="s">
+        <v>21</v>
+      </c>
+      <c r="G78">
+        <v>0</v>
+      </c>
+      <c r="H78">
+        <v>30</v>
+      </c>
+      <c r="I78" t="s">
+        <v>22</v>
+      </c>
+      <c r="J78" t="s">
+        <v>31</v>
+      </c>
+      <c r="K78" t="s">
+        <v>24</v>
+      </c>
+      <c r="L78" t="s">
+        <v>25</v>
+      </c>
+      <c r="M78" t="s">
+        <v>26</v>
+      </c>
+      <c r="N78" t="s">
+        <v>21</v>
+      </c>
+      <c r="O78" t="s">
+        <v>21</v>
+      </c>
+      <c r="P78" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>21</v>
+      </c>
+      <c r="R78" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>174</v>
+      </c>
+      <c r="B79" t="s">
+        <v>175</v>
+      </c>
+      <c r="C79" t="s">
+        <v>143</v>
+      </c>
+      <c r="D79" t="s">
+        <v>21</v>
+      </c>
+      <c r="E79">
+        <v>150</v>
+      </c>
+      <c r="F79" t="s">
+        <v>21</v>
+      </c>
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
+        <v>150</v>
+      </c>
+      <c r="I79" t="s">
+        <v>22</v>
+      </c>
+      <c r="J79" t="s">
+        <v>31</v>
+      </c>
+      <c r="K79" t="s">
+        <v>24</v>
+      </c>
+      <c r="L79" t="s">
+        <v>25</v>
+      </c>
+      <c r="M79" t="s">
+        <v>26</v>
+      </c>
+      <c r="N79" t="s">
+        <v>21</v>
+      </c>
+      <c r="O79" t="s">
+        <v>21</v>
+      </c>
+      <c r="P79" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>21</v>
+      </c>
+      <c r="R79" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>176</v>
+      </c>
+      <c r="B80" t="s">
+        <v>177</v>
+      </c>
+      <c r="C80" t="s">
+        <v>143</v>
+      </c>
+      <c r="D80" t="s">
+        <v>21</v>
+      </c>
+      <c r="E80">
+        <v>20</v>
+      </c>
+      <c r="F80" t="s">
+        <v>21</v>
+      </c>
+      <c r="G80">
+        <v>0</v>
+      </c>
+      <c r="H80">
+        <v>20</v>
+      </c>
+      <c r="I80" t="s">
+        <v>22</v>
+      </c>
+      <c r="J80" t="s">
+        <v>31</v>
+      </c>
+      <c r="K80" t="s">
+        <v>24</v>
+      </c>
+      <c r="L80" t="s">
+        <v>25</v>
+      </c>
+      <c r="M80" t="s">
+        <v>26</v>
+      </c>
+      <c r="N80" t="s">
+        <v>21</v>
+      </c>
+      <c r="O80" t="s">
+        <v>21</v>
+      </c>
+      <c r="P80" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>21</v>
+      </c>
+      <c r="R80" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>178</v>
+      </c>
+      <c r="B81" t="s">
+        <v>179</v>
+      </c>
+      <c r="C81" t="s">
+        <v>143</v>
+      </c>
+      <c r="D81" t="s">
+        <v>21</v>
+      </c>
+      <c r="E81">
+        <v>30</v>
+      </c>
+      <c r="F81" t="s">
+        <v>21</v>
+      </c>
+      <c r="G81">
+        <v>0</v>
+      </c>
+      <c r="H81">
+        <v>30</v>
+      </c>
+      <c r="I81" t="s">
+        <v>22</v>
+      </c>
+      <c r="J81" t="s">
+        <v>31</v>
+      </c>
+      <c r="K81" t="s">
+        <v>24</v>
+      </c>
+      <c r="L81" t="s">
+        <v>25</v>
+      </c>
+      <c r="M81" t="s">
+        <v>26</v>
+      </c>
+      <c r="N81" t="s">
+        <v>21</v>
+      </c>
+      <c r="O81" t="s">
+        <v>21</v>
+      </c>
+      <c r="P81" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>21</v>
+      </c>
+      <c r="R81" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>180</v>
+      </c>
+      <c r="B82" t="s">
+        <v>181</v>
+      </c>
+      <c r="C82" t="s">
+        <v>143</v>
+      </c>
+      <c r="D82" t="s">
+        <v>21</v>
+      </c>
+      <c r="E82">
+        <v>50</v>
+      </c>
+      <c r="F82" t="s">
+        <v>21</v>
+      </c>
+      <c r="G82">
+        <v>0</v>
+      </c>
+      <c r="H82">
+        <v>50</v>
+      </c>
+      <c r="I82" t="s">
+        <v>22</v>
+      </c>
+      <c r="J82" t="s">
+        <v>31</v>
+      </c>
+      <c r="K82" t="s">
+        <v>24</v>
+      </c>
+      <c r="L82" t="s">
+        <v>25</v>
+      </c>
+      <c r="M82" t="s">
+        <v>26</v>
+      </c>
+      <c r="N82" t="s">
+        <v>21</v>
+      </c>
+      <c r="O82" t="s">
+        <v>21</v>
+      </c>
+      <c r="P82" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>21</v>
+      </c>
+      <c r="R82" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>182</v>
+      </c>
+      <c r="B83" t="s">
+        <v>183</v>
+      </c>
+      <c r="C83" t="s">
+        <v>143</v>
+      </c>
+      <c r="D83" t="s">
+        <v>21</v>
+      </c>
+      <c r="E83">
+        <v>60</v>
+      </c>
+      <c r="F83" t="s">
+        <v>21</v>
+      </c>
+      <c r="G83">
+        <v>0</v>
+      </c>
+      <c r="H83">
+        <v>60</v>
+      </c>
+      <c r="I83" t="s">
+        <v>22</v>
+      </c>
+      <c r="J83" t="s">
+        <v>31</v>
+      </c>
+      <c r="K83" t="s">
+        <v>24</v>
+      </c>
+      <c r="L83" t="s">
+        <v>25</v>
+      </c>
+      <c r="M83" t="s">
+        <v>26</v>
+      </c>
+      <c r="N83" t="s">
+        <v>21</v>
+      </c>
+      <c r="O83" t="s">
+        <v>21</v>
+      </c>
+      <c r="P83" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>21</v>
+      </c>
+      <c r="R83" t="s">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pc.xlsx
+++ b/pc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9BCC3F26-D2BE-4014-818B-03DCC35A62D2}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7A379679-DF4B-4B8D-BD86-2E7EBEB1164B}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -113,64 +113,208 @@
     <t>Pendiente</t>
   </si>
   <si>
+    <t>C5OX-24-20F</t>
+  </si>
+  <si>
+    <t>ADAP CODO 90° MF 1.7/8" AS JIC 37° X MF 1.5/8" AS ORING</t>
+  </si>
+  <si>
+    <t>SOL - 2307</t>
+  </si>
+  <si>
+    <t>2026-06</t>
+  </si>
+  <si>
+    <t>934331T</t>
+  </si>
+  <si>
+    <t>FILTRO TRICEPTOR SILICA GEL 8"</t>
+  </si>
+  <si>
+    <t>XHX6-12-16N</t>
+  </si>
+  <si>
+    <t>ADAP RECTO HG JIC 1.1/16" x MF JIC 1 1/16" UNF</t>
+  </si>
+  <si>
+    <t>FT 221/1-100</t>
+  </si>
+  <si>
+    <t>VALVULA ESFERICA DE 2 VIAS, ALTA PRESION 1"</t>
+  </si>
+  <si>
+    <t>FT 257/5-14</t>
+  </si>
+  <si>
+    <t>VALVULA AGUJA UNIDIRECCIONAL 1/4" - 350 BAR 15 LT</t>
+  </si>
+  <si>
+    <t>FT 257/6-100</t>
+  </si>
+  <si>
+    <t>VALVULA DE RETENCION EN LINEA RECTA 1" 160LPM - 350 BAR</t>
+  </si>
+  <si>
+    <t>0PHB408T N70</t>
+  </si>
+  <si>
+    <t>KIT DE ORING MILIMETRICOS N70</t>
+  </si>
+  <si>
+    <t>BUJE RED-2"x1.1/2" S3000</t>
+  </si>
+  <si>
+    <t>BUJE DE RED 2" NPT x 1.1/2" NPT SERIE 3000</t>
+  </si>
+  <si>
+    <t>BUJE RED-3/4"x1/2" S3000</t>
+  </si>
+  <si>
+    <t>BUJE DE RED 3/4" NPT x 1/2" NPT SERIE 3000</t>
+  </si>
+  <si>
+    <t>LG-3T</t>
+  </si>
+  <si>
+    <t>INDICADOR DE NIVEL Y TEMPERATURA DE 254MM - M12 METALICO</t>
+  </si>
+  <si>
+    <t>313-2825-000</t>
+  </si>
+  <si>
+    <t>ENGRANAJE P50 DE 2 1/2"</t>
+  </si>
+  <si>
+    <t>391-0381-905</t>
+  </si>
+  <si>
+    <t>TORRINGTON P50</t>
+  </si>
+  <si>
+    <t>391-2185-912</t>
+  </si>
+  <si>
+    <t>PLACA AXIAL DE BRONCE P50</t>
+  </si>
+  <si>
+    <t>391-2882-051</t>
+  </si>
+  <si>
+    <t>CUERDA P30 Y P50</t>
+  </si>
+  <si>
+    <t>391-2883-119P</t>
+  </si>
+  <si>
+    <t>RETEN M-30 P/EJE ENTERIZO</t>
+  </si>
+  <si>
+    <t>391-2884-021P</t>
+  </si>
+  <si>
+    <t>SELLO GOMA SQUARE GASKET 50-25</t>
+  </si>
+  <si>
+    <t>25UC</t>
+  </si>
+  <si>
+    <t>BRIDA EN U (PESTAÑA) PARA MANÓMETROS SERIE PFQ Y PFP 2,5"</t>
+  </si>
+  <si>
+    <t>PFQ806R3R1</t>
+  </si>
+  <si>
+    <t>MANOMETRO 2,5" INFERIOR 1/4 NPT 0-14 BAR</t>
+  </si>
+  <si>
+    <t>PFQ905R3R1</t>
+  </si>
+  <si>
+    <t>MANOMETRO 2,5" ROSCA POSTERIOR 1/4 NPT 0-10 BAR C/GLICERINA</t>
+  </si>
+  <si>
+    <t>PFQ915R3R1</t>
+  </si>
+  <si>
+    <t>MANOMETRO 2,5" ROSCA POSTERIOR 1/4 NPT 0-400 BAR C/GLICERINA</t>
+  </si>
+  <si>
+    <t>PFQ918R3R1</t>
+  </si>
+  <si>
+    <t>MANOMETRO 2,5" ROSCA POSTERIOR 1/4 NPT 0-600 BAR C/GLICERINA</t>
+  </si>
+  <si>
+    <t>FB-2</t>
+  </si>
+  <si>
+    <t>BOCA DE CARGA GRANDE BRIDADA 40 MIC.</t>
+  </si>
+  <si>
+    <t>FK-12</t>
+  </si>
+  <si>
+    <t>OJO DE BUEY NIVEL PLASTICO DE 1/2" BSP</t>
+  </si>
+  <si>
+    <t>4AH3-16-16P</t>
+  </si>
+  <si>
+    <t>ADAPTADOR RECTO BRIDA DE 1.3/4" X MF JIC 1.5/16" UNF SAE61 5000 PSI</t>
+  </si>
+  <si>
+    <t>6AH3-20-20P</t>
+  </si>
+  <si>
+    <t>ADAPTADOR RECTO BRIDA DE 2.1/8" X MF JIC 1.5/8" UNF SAE62 5000 PSI</t>
+  </si>
+  <si>
+    <t>PFP835ZRR1R11</t>
+  </si>
+  <si>
+    <t>MANOMETRO SERIE PFQ-ZR 2,5", 0/15.000 PSI - 0/1.000 bar, 1/4" NPT INFERIOR</t>
+  </si>
+  <si>
+    <t>CODO 90-1/4" S3000</t>
+  </si>
+  <si>
+    <t>CODO 90° 1/4" H-H NPT SERIE 3000</t>
+  </si>
+  <si>
+    <t>2-250N90V</t>
+  </si>
+  <si>
+    <t>ORING 2-250 V70 DI 126.59 X ESP 3.53</t>
+  </si>
+  <si>
+    <t>313213001</t>
+  </si>
+  <si>
+    <t>MANG. DE POLIURETANO PARA NEUMÁTICA. RAUPURAM 10 MM</t>
+  </si>
+  <si>
     <t>46512208</t>
   </si>
   <si>
     <t>MANGUERA HIDRAU. ESPIRALADA GATES (SAE100 R13) 24EFG5K X LL</t>
   </si>
   <si>
-    <t>SOL - 2307</t>
-  </si>
-  <si>
-    <t>2026-06</t>
-  </si>
-  <si>
-    <t>C5OX-24-20F</t>
-  </si>
-  <si>
-    <t>ADAP CODO 90° MF 1.7/8" AS JIC 37° X MF 1.5/8" AS ORING</t>
-  </si>
-  <si>
-    <t>CODO 90-1/4" S3000</t>
-  </si>
-  <si>
-    <t>CODO 90° 1/4" H-H NPT SERIE 3000</t>
-  </si>
-  <si>
-    <t>BUJE RED-2"x1.1/2" S3000</t>
-  </si>
-  <si>
-    <t>BUJE DE RED 2" NPT x 1.1/2" NPT SERIE 3000</t>
-  </si>
-  <si>
-    <t>BUJE RED-3/4"x1/2" S3000</t>
-  </si>
-  <si>
-    <t>BUJE DE RED 3/4" NPT x 1/2" NPT SERIE 3000</t>
-  </si>
-  <si>
-    <t>XHX6-12-16N</t>
-  </si>
-  <si>
-    <t>ADAP RECTO HG JIC 1.1/16" x MF JIC 1 1/16" UNF</t>
-  </si>
-  <si>
-    <t>4AH3-16-16P</t>
-  </si>
-  <si>
-    <t>ADAPTADOR RECTO BRIDA DE 1.3/4" X MF JIC 1.5/16" UNF SAE61 5000 PSI</t>
-  </si>
-  <si>
-    <t>6AH3-20-20P</t>
-  </si>
-  <si>
-    <t>ADAPTADOR RECTO BRIDA DE 2.1/8" X MF JIC 1.5/8" UNF SAE62 5000 PSI</t>
-  </si>
-  <si>
-    <t>313213001</t>
-  </si>
-  <si>
-    <t>MANG. DE POLIURETANO PARA NEUMÁTICA. RAUPURAM 10 MM</t>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>WIPER 50.80 x 63.50 x 9.52/6.35</t>
+  </si>
+  <si>
+    <t>0K-89-N90</t>
+  </si>
+  <si>
+    <t>KIT DE ORING EN PULGADAS N90</t>
+  </si>
+  <si>
+    <t>0K-89T</t>
+  </si>
+  <si>
+    <t>KIT DE ORING EN PULGADAS N70</t>
   </si>
   <si>
     <t>1250-0625-250B</t>
@@ -179,30 +323,6 @@
     <t>POLYPAK 15.88 x 22.22 x 6.35</t>
   </si>
   <si>
-    <t>2000</t>
-  </si>
-  <si>
-    <t>WIPER 50.80 x 63.50 x 9.52/6.35</t>
-  </si>
-  <si>
-    <t>0K-89-N90</t>
-  </si>
-  <si>
-    <t>KIT DE ORING EN PULGADAS N90</t>
-  </si>
-  <si>
-    <t>0K-89T</t>
-  </si>
-  <si>
-    <t>KIT DE ORING EN PULGADAS N70</t>
-  </si>
-  <si>
-    <t>0PHB408T N70</t>
-  </si>
-  <si>
-    <t>KIT DE ORING MILIMETRICOS N70</t>
-  </si>
-  <si>
     <t>2-250-N90</t>
   </si>
   <si>
@@ -215,124 +335,79 @@
     <t>ORING 2-332 D70 DI 59.69 X DE 70.35 ESP 5.33</t>
   </si>
   <si>
-    <t>2-250N90V</t>
-  </si>
-  <si>
-    <t>ORING 2-250 V70 DI 126.59 X ESP 3.53</t>
-  </si>
-  <si>
-    <t>FT 221/1-100</t>
-  </si>
-  <si>
-    <t>VALVULA ESFERICA DE 2 VIAS, ALTA PRESION 1"</t>
-  </si>
-  <si>
-    <t>FT 257/5-14</t>
-  </si>
-  <si>
-    <t>VALVULA AGUJA UNIDIRECCIONAL 1/4" - 350 BAR 15 LT</t>
-  </si>
-  <si>
-    <t>FT 257/6-100</t>
-  </si>
-  <si>
-    <t>VALVULA DE RETENCION EN LINEA RECTA 1" 160LPM - 350 BAR</t>
-  </si>
-  <si>
-    <t>LG-3T</t>
-  </si>
-  <si>
-    <t>INDICADOR DE NIVEL Y TEMPERATURA DE 254MM - M12 METALICO</t>
-  </si>
-  <si>
-    <t>25UC</t>
-  </si>
-  <si>
-    <t>BRIDA EN U (PESTAÑA) PARA MANÓMETROS SERIE PFQ Y PFP 2,5"</t>
-  </si>
-  <si>
-    <t>PFQ806R3R1</t>
-  </si>
-  <si>
-    <t>MANOMETRO 2,5" INFERIOR 1/4 NPT 0-14 BAR</t>
-  </si>
-  <si>
-    <t>PFQ905R3R1</t>
-  </si>
-  <si>
-    <t>MANOMETRO 2,5" ROSCA POSTERIOR 1/4 NPT 0-10 BAR C/GLICERINA</t>
-  </si>
-  <si>
-    <t>PFQ915R3R1</t>
-  </si>
-  <si>
-    <t>MANOMETRO 2,5" ROSCA POSTERIOR 1/4 NPT 0-400 BAR C/GLICERINA</t>
-  </si>
-  <si>
-    <t>PFQ918R3R1</t>
-  </si>
-  <si>
-    <t>MANOMETRO 2,5" ROSCA POSTERIOR 1/4 NPT 0-600 BAR C/GLICERINA</t>
-  </si>
-  <si>
-    <t>FB-2</t>
-  </si>
-  <si>
-    <t>BOCA DE CARGA GRANDE BRIDADA 40 MIC.</t>
-  </si>
-  <si>
-    <t>FK-12</t>
-  </si>
-  <si>
-    <t>OJO DE BUEY NIVEL PLASTICO DE 1/2" BSP</t>
-  </si>
-  <si>
-    <t>PFP835ZRR1R11</t>
-  </si>
-  <si>
-    <t>MANOMETRO SERIE PFQ-ZR 2,5", 0/15.000 PSI - 0/1.000 bar, 1/4" NPT INFERIOR</t>
-  </si>
-  <si>
-    <t>934331T</t>
-  </si>
-  <si>
-    <t>FILTRO TRICEPTOR SILICA GEL 8"</t>
-  </si>
-  <si>
-    <t>313-2825-000</t>
-  </si>
-  <si>
-    <t>ENGRANAJE P50 DE 2 1/2"</t>
-  </si>
-  <si>
-    <t>391-0381-905</t>
-  </si>
-  <si>
-    <t>TORRINGTON P50</t>
-  </si>
-  <si>
-    <t>391-2185-912</t>
-  </si>
-  <si>
-    <t>PLACA AXIAL DE BRONCE P50</t>
-  </si>
-  <si>
-    <t>391-2882-051</t>
-  </si>
-  <si>
-    <t>CUERDA P30 Y P50</t>
-  </si>
-  <si>
-    <t>391-2883-119P</t>
-  </si>
-  <si>
-    <t>RETEN M-30 P/EJE ENTERIZO</t>
-  </si>
-  <si>
-    <t>391-2884-021P</t>
-  </si>
-  <si>
-    <t>SELLO GOMA SQUARE GASKET 50-25</t>
+    <t>301-04P</t>
+  </si>
+  <si>
+    <t>MANG.SAE 100 R2 1/4"</t>
+  </si>
+  <si>
+    <t>SOL - 2308</t>
+  </si>
+  <si>
+    <t>301-06P</t>
+  </si>
+  <si>
+    <t>MANG.SAE 100 R2 3/8"</t>
+  </si>
+  <si>
+    <t>301-08P</t>
+  </si>
+  <si>
+    <t>MANG.SAE 100 R2 1/2"</t>
+  </si>
+  <si>
+    <t>301-12P</t>
+  </si>
+  <si>
+    <t>MANG.SAE 100 R2 3/4"</t>
+  </si>
+  <si>
+    <t>301-16P</t>
+  </si>
+  <si>
+    <t>MANG.SAE 100 R2 1"</t>
+  </si>
+  <si>
+    <t>301-20P</t>
+  </si>
+  <si>
+    <t>MANG.SAE 100 R2 1.1/4"</t>
+  </si>
+  <si>
+    <t>301-24P</t>
+  </si>
+  <si>
+    <t>MANG.SAE 100 R2 1.1/2"</t>
+  </si>
+  <si>
+    <t>301-32P</t>
+  </si>
+  <si>
+    <t>MANG.SAE 100 R2 2"</t>
+  </si>
+  <si>
+    <t>797TC-08P</t>
+  </si>
+  <si>
+    <t>MANGUERA R15 GLOBALCORE 1/2" 6000PSI</t>
+  </si>
+  <si>
+    <t>797TC-16P</t>
+  </si>
+  <si>
+    <t>MANGUERA R15 GLOBALCORE 1" 6000PSI</t>
+  </si>
+  <si>
+    <t>722TC-16</t>
+  </si>
+  <si>
+    <t>MANGUERA SAE 100 R12 1" 4000PSI</t>
+  </si>
+  <si>
+    <t>722TC-12</t>
+  </si>
+  <si>
+    <t>MANGUERA SAE 100 R12 3/4" 4000PSI</t>
   </si>
   <si>
     <t>10677-16-16P</t>
@@ -341,9 +416,6 @@
     <t>TERMINAL RECTO HG JIC 1.5/16" UNF x MANGUERA R15 1"</t>
   </si>
   <si>
-    <t>SOL - 2308</t>
-  </si>
-  <si>
     <t>10677-20-20P</t>
   </si>
   <si>
@@ -380,76 +452,25 @@
     <t>TERMINAL BRIDA SERIE 6000 SAE 62 CODO 90º 1.1/2" X MANGUERA 1.1/2" R15</t>
   </si>
   <si>
-    <t>301-04P</t>
-  </si>
-  <si>
-    <t>MANG.SAE 100 R2 1/4"</t>
-  </si>
-  <si>
-    <t>301-06P</t>
-  </si>
-  <si>
-    <t>MANG.SAE 100 R2 3/8"</t>
-  </si>
-  <si>
-    <t>301-08P</t>
-  </si>
-  <si>
-    <t>MANG.SAE 100 R2 1/2"</t>
-  </si>
-  <si>
-    <t>301-12P</t>
-  </si>
-  <si>
-    <t>MANG.SAE 100 R2 3/4"</t>
-  </si>
-  <si>
-    <t>301-16P</t>
-  </si>
-  <si>
-    <t>MANG.SAE 100 R2 1"</t>
-  </si>
-  <si>
-    <t>301-20P</t>
-  </si>
-  <si>
-    <t>MANG.SAE 100 R2 1.1/4"</t>
-  </si>
-  <si>
-    <t>301-24P</t>
-  </si>
-  <si>
-    <t>MANG.SAE 100 R2 1.1/2"</t>
-  </si>
-  <si>
-    <t>301-32P</t>
-  </si>
-  <si>
-    <t>MANG.SAE 100 R2 2"</t>
-  </si>
-  <si>
-    <t>797TC-08P</t>
-  </si>
-  <si>
-    <t>MANGUERA R15 GLOBALCORE 1/2" 6000PSI</t>
-  </si>
-  <si>
-    <t>797TC-16P</t>
-  </si>
-  <si>
-    <t>MANGUERA R15 GLOBALCORE 1" 6000PSI</t>
-  </si>
-  <si>
-    <t>722TC-16</t>
-  </si>
-  <si>
-    <t>MANGUERA SAE 100 R12 1" 4000PSI</t>
-  </si>
-  <si>
-    <t>722TC-12</t>
-  </si>
-  <si>
-    <t>MANGUERA SAE 100 R12 3/4" 4000PSI</t>
+    <t>30182-04-06P</t>
+  </si>
+  <si>
+    <t>TERMINAL MF 1/4" NPT X MANGUERA 3/8" PUSH LOOK</t>
+  </si>
+  <si>
+    <t>SOL - 2309</t>
+  </si>
+  <si>
+    <t>30682-06-04P</t>
+  </si>
+  <si>
+    <t>TERMINAL HG 9/16" X MANGUERA 1/4" PUSH LOOK</t>
+  </si>
+  <si>
+    <t>30682-06-06P</t>
+  </si>
+  <si>
+    <t>TERMINAL HG 9/16" X MANGUERA 3/8" PUSH LOOK</t>
   </si>
   <si>
     <t>HG-100N</t>
@@ -458,9 +479,6 @@
     <t>PROTECTOR P/MANGUERA ESPIRALADO DI 25 mm</t>
   </si>
   <si>
-    <t>SOL - 2309</t>
-  </si>
-  <si>
     <t>HG-250N</t>
   </si>
   <si>
@@ -513,24 +531,6 @@
   </si>
   <si>
     <t>TERMINAL HG JIC 2 1/2"  X MANGUERA 2"</t>
-  </si>
-  <si>
-    <t>30182-04-06P</t>
-  </si>
-  <si>
-    <t>TERMINAL MF 1/4" NPT X MANGUERA 3/8" PUSH LOOK</t>
-  </si>
-  <si>
-    <t>30682-06-04P</t>
-  </si>
-  <si>
-    <t>TERMINAL HG 9/16" X MANGUERA 1/4" PUSH LOOK</t>
-  </si>
-  <si>
-    <t>30682-06-06P</t>
-  </si>
-  <si>
-    <t>TERMINAL HG 9/16" X MANGUERA 3/8" PUSH LOOK</t>
   </si>
   <si>
     <t>C5OX-24F</t>
@@ -1283,7 +1283,7 @@
         <v>21</v>
       </c>
       <c r="E7">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
         <v>21</v>
@@ -1292,7 +1292,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="I7" t="s">
         <v>22</v>
@@ -1339,7 +1339,7 @@
         <v>21</v>
       </c>
       <c r="E8">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F8" t="s">
         <v>21</v>
@@ -1348,7 +1348,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I8" t="s">
         <v>22</v>
@@ -1395,7 +1395,7 @@
         <v>21</v>
       </c>
       <c r="E9">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
         <v>21</v>
@@ -1404,7 +1404,7 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I9" t="s">
         <v>22</v>
@@ -1451,7 +1451,7 @@
         <v>21</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F10" t="s">
         <v>21</v>
@@ -1460,7 +1460,7 @@
         <v>0</v>
       </c>
       <c r="H10">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="I10" t="s">
         <v>22</v>
@@ -1507,7 +1507,7 @@
         <v>21</v>
       </c>
       <c r="E11">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
         <v>21</v>
@@ -1516,7 +1516,7 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="I11" t="s">
         <v>22</v>
@@ -1563,7 +1563,7 @@
         <v>21</v>
       </c>
       <c r="E12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
         <v>21</v>
@@ -1572,7 +1572,7 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I12" t="s">
         <v>22</v>
@@ -1619,7 +1619,7 @@
         <v>21</v>
       </c>
       <c r="E13">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F13" t="s">
         <v>21</v>
@@ -1628,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I13" t="s">
         <v>22</v>
@@ -1675,7 +1675,7 @@
         <v>21</v>
       </c>
       <c r="E14">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
         <v>21</v>
@@ -1684,7 +1684,7 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I14" t="s">
         <v>22</v>
@@ -1731,7 +1731,7 @@
         <v>21</v>
       </c>
       <c r="E15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F15" t="s">
         <v>21</v>
@@ -1740,7 +1740,7 @@
         <v>0</v>
       </c>
       <c r="H15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I15" t="s">
         <v>22</v>
@@ -1787,7 +1787,7 @@
         <v>21</v>
       </c>
       <c r="E16">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="F16" t="s">
         <v>21</v>
@@ -1796,7 +1796,7 @@
         <v>0</v>
       </c>
       <c r="H16">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="I16" t="s">
         <v>22</v>
@@ -1843,7 +1843,7 @@
         <v>21</v>
       </c>
       <c r="E17">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F17" t="s">
         <v>21</v>
@@ -1852,7 +1852,7 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I17" t="s">
         <v>22</v>
@@ -1899,7 +1899,7 @@
         <v>21</v>
       </c>
       <c r="E18">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="F18" t="s">
         <v>21</v>
@@ -1908,7 +1908,7 @@
         <v>0</v>
       </c>
       <c r="H18">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="I18" t="s">
         <v>22</v>
@@ -1955,7 +1955,7 @@
         <v>21</v>
       </c>
       <c r="E19">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="F19" t="s">
         <v>21</v>
@@ -1964,7 +1964,7 @@
         <v>0</v>
       </c>
       <c r="H19">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="I19" t="s">
         <v>22</v>
@@ -2011,7 +2011,7 @@
         <v>21</v>
       </c>
       <c r="E20">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="F20" t="s">
         <v>21</v>
@@ -2020,7 +2020,7 @@
         <v>0</v>
       </c>
       <c r="H20">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="I20" t="s">
         <v>22</v>
@@ -2067,7 +2067,7 @@
         <v>21</v>
       </c>
       <c r="E21">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="F21" t="s">
         <v>21</v>
@@ -2076,7 +2076,7 @@
         <v>0</v>
       </c>
       <c r="H21">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="I21" t="s">
         <v>22</v>
@@ -2179,7 +2179,7 @@
         <v>21</v>
       </c>
       <c r="E23">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="F23" t="s">
         <v>21</v>
@@ -2188,7 +2188,7 @@
         <v>0</v>
       </c>
       <c r="H23">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="I23" t="s">
         <v>22</v>
@@ -2235,7 +2235,7 @@
         <v>21</v>
       </c>
       <c r="E24">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F24" t="s">
         <v>21</v>
@@ -2244,7 +2244,7 @@
         <v>0</v>
       </c>
       <c r="H24">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I24" t="s">
         <v>22</v>
@@ -2291,7 +2291,7 @@
         <v>21</v>
       </c>
       <c r="E25">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F25" t="s">
         <v>21</v>
@@ -2300,7 +2300,7 @@
         <v>0</v>
       </c>
       <c r="H25">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I25" t="s">
         <v>22</v>
@@ -2347,7 +2347,7 @@
         <v>21</v>
       </c>
       <c r="E26">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="F26" t="s">
         <v>21</v>
@@ -2356,7 +2356,7 @@
         <v>0</v>
       </c>
       <c r="H26">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="I26" t="s">
         <v>22</v>
@@ -2403,7 +2403,7 @@
         <v>21</v>
       </c>
       <c r="E27">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F27" t="s">
         <v>21</v>
@@ -2412,7 +2412,7 @@
         <v>0</v>
       </c>
       <c r="H27">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I27" t="s">
         <v>22</v>
@@ -2459,7 +2459,7 @@
         <v>21</v>
       </c>
       <c r="E28">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F28" t="s">
         <v>21</v>
@@ -2468,7 +2468,7 @@
         <v>0</v>
       </c>
       <c r="H28">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="I28" t="s">
         <v>22</v>
@@ -2515,7 +2515,7 @@
         <v>21</v>
       </c>
       <c r="E29">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F29" t="s">
         <v>21</v>
@@ -2524,7 +2524,7 @@
         <v>0</v>
       </c>
       <c r="H29">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="I29" t="s">
         <v>22</v>
@@ -2571,7 +2571,7 @@
         <v>21</v>
       </c>
       <c r="E30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F30" t="s">
         <v>21</v>
@@ -2580,7 +2580,7 @@
         <v>0</v>
       </c>
       <c r="H30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I30" t="s">
         <v>22</v>
@@ -2627,7 +2627,7 @@
         <v>21</v>
       </c>
       <c r="E31">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F31" t="s">
         <v>21</v>
@@ -2636,7 +2636,7 @@
         <v>0</v>
       </c>
       <c r="H31">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="I31" t="s">
         <v>22</v>
@@ -2683,7 +2683,7 @@
         <v>21</v>
       </c>
       <c r="E32">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F32" t="s">
         <v>21</v>
@@ -2692,7 +2692,7 @@
         <v>0</v>
       </c>
       <c r="H32">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I32" t="s">
         <v>22</v>
@@ -2739,7 +2739,7 @@
         <v>21</v>
       </c>
       <c r="E33">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F33" t="s">
         <v>21</v>
@@ -2748,7 +2748,7 @@
         <v>0</v>
       </c>
       <c r="H33">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="I33" t="s">
         <v>22</v>
@@ -2795,7 +2795,7 @@
         <v>21</v>
       </c>
       <c r="E34">
-        <v>5</v>
+        <v>200</v>
       </c>
       <c r="F34" t="s">
         <v>21</v>
@@ -2804,7 +2804,7 @@
         <v>0</v>
       </c>
       <c r="H34">
-        <v>5</v>
+        <v>200</v>
       </c>
       <c r="I34" t="s">
         <v>22</v>
@@ -2851,7 +2851,7 @@
         <v>21</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="F35" t="s">
         <v>21</v>
@@ -2860,7 +2860,7 @@
         <v>0</v>
       </c>
       <c r="H35">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="I35" t="s">
         <v>22</v>
@@ -2907,7 +2907,7 @@
         <v>21</v>
       </c>
       <c r="E36">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="F36" t="s">
         <v>21</v>
@@ -2916,7 +2916,7 @@
         <v>0</v>
       </c>
       <c r="H36">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="I36" t="s">
         <v>22</v>
@@ -2963,7 +2963,7 @@
         <v>21</v>
       </c>
       <c r="E37">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F37" t="s">
         <v>21</v>
@@ -2972,7 +2972,7 @@
         <v>0</v>
       </c>
       <c r="H37">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I37" t="s">
         <v>22</v>
@@ -3019,7 +3019,7 @@
         <v>21</v>
       </c>
       <c r="E38">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F38" t="s">
         <v>21</v>
@@ -3028,7 +3028,7 @@
         <v>0</v>
       </c>
       <c r="H38">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="I38" t="s">
         <v>22</v>
@@ -3075,7 +3075,7 @@
         <v>21</v>
       </c>
       <c r="E39">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="F39" t="s">
         <v>21</v>
@@ -3084,7 +3084,7 @@
         <v>0</v>
       </c>
       <c r="H39">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="I39" t="s">
         <v>22</v>
@@ -3187,7 +3187,7 @@
         <v>21</v>
       </c>
       <c r="E41">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="F41" t="s">
         <v>21</v>
@@ -3196,7 +3196,7 @@
         <v>0</v>
       </c>
       <c r="H41">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="I41" t="s">
         <v>22</v>
@@ -3299,7 +3299,7 @@
         <v>21</v>
       </c>
       <c r="E43">
-        <v>200</v>
+        <v>3600</v>
       </c>
       <c r="F43" t="s">
         <v>21</v>
@@ -3308,7 +3308,7 @@
         <v>0</v>
       </c>
       <c r="H43">
-        <v>200</v>
+        <v>3600</v>
       </c>
       <c r="I43" t="s">
         <v>22</v>
@@ -3355,7 +3355,7 @@
         <v>21</v>
       </c>
       <c r="E44">
-        <v>100</v>
+        <v>6500</v>
       </c>
       <c r="F44" t="s">
         <v>21</v>
@@ -3364,7 +3364,7 @@
         <v>0</v>
       </c>
       <c r="H44">
-        <v>100</v>
+        <v>6500</v>
       </c>
       <c r="I44" t="s">
         <v>22</v>
@@ -3411,7 +3411,7 @@
         <v>21</v>
       </c>
       <c r="E45">
-        <v>30</v>
+        <v>3800</v>
       </c>
       <c r="F45" t="s">
         <v>21</v>
@@ -3420,7 +3420,7 @@
         <v>0</v>
       </c>
       <c r="H45">
-        <v>30</v>
+        <v>3800</v>
       </c>
       <c r="I45" t="s">
         <v>22</v>
@@ -3467,7 +3467,7 @@
         <v>21</v>
       </c>
       <c r="E46">
-        <v>10</v>
+        <v>1300</v>
       </c>
       <c r="F46" t="s">
         <v>21</v>
@@ -3476,7 +3476,7 @@
         <v>0</v>
       </c>
       <c r="H46">
-        <v>10</v>
+        <v>1300</v>
       </c>
       <c r="I46" t="s">
         <v>22</v>
@@ -3523,7 +3523,7 @@
         <v>21</v>
       </c>
       <c r="E47">
-        <v>90</v>
+        <v>2000</v>
       </c>
       <c r="F47" t="s">
         <v>21</v>
@@ -3532,7 +3532,7 @@
         <v>0</v>
       </c>
       <c r="H47">
-        <v>90</v>
+        <v>2000</v>
       </c>
       <c r="I47" t="s">
         <v>22</v>
@@ -3579,7 +3579,7 @@
         <v>21</v>
       </c>
       <c r="E48">
-        <v>20</v>
+        <v>1200</v>
       </c>
       <c r="F48" t="s">
         <v>21</v>
@@ -3588,7 +3588,7 @@
         <v>0</v>
       </c>
       <c r="H48">
-        <v>20</v>
+        <v>1200</v>
       </c>
       <c r="I48" t="s">
         <v>22</v>
@@ -3635,7 +3635,7 @@
         <v>21</v>
       </c>
       <c r="E49">
-        <v>10</v>
+        <v>1500</v>
       </c>
       <c r="F49" t="s">
         <v>21</v>
@@ -3644,7 +3644,7 @@
         <v>0</v>
       </c>
       <c r="H49">
-        <v>10</v>
+        <v>1500</v>
       </c>
       <c r="I49" t="s">
         <v>22</v>
@@ -3691,7 +3691,7 @@
         <v>21</v>
       </c>
       <c r="E50">
-        <v>3600</v>
+        <v>200</v>
       </c>
       <c r="F50" t="s">
         <v>21</v>
@@ -3700,7 +3700,7 @@
         <v>0</v>
       </c>
       <c r="H50">
-        <v>3600</v>
+        <v>200</v>
       </c>
       <c r="I50" t="s">
         <v>22</v>
@@ -3747,7 +3747,7 @@
         <v>21</v>
       </c>
       <c r="E51">
-        <v>6500</v>
+        <v>100</v>
       </c>
       <c r="F51" t="s">
         <v>21</v>
@@ -3756,7 +3756,7 @@
         <v>0</v>
       </c>
       <c r="H51">
-        <v>6500</v>
+        <v>100</v>
       </c>
       <c r="I51" t="s">
         <v>22</v>
@@ -3803,7 +3803,7 @@
         <v>21</v>
       </c>
       <c r="E52">
-        <v>3800</v>
+        <v>100</v>
       </c>
       <c r="F52" t="s">
         <v>21</v>
@@ -3812,7 +3812,7 @@
         <v>0</v>
       </c>
       <c r="H52">
-        <v>3800</v>
+        <v>100</v>
       </c>
       <c r="I52" t="s">
         <v>22</v>
@@ -3859,7 +3859,7 @@
         <v>21</v>
       </c>
       <c r="E53">
-        <v>1300</v>
+        <v>550</v>
       </c>
       <c r="F53" t="s">
         <v>21</v>
@@ -3868,7 +3868,7 @@
         <v>0</v>
       </c>
       <c r="H53">
-        <v>1300</v>
+        <v>550</v>
       </c>
       <c r="I53" t="s">
         <v>22</v>
@@ -3915,7 +3915,7 @@
         <v>21</v>
       </c>
       <c r="E54">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="F54" t="s">
         <v>21</v>
@@ -3924,7 +3924,7 @@
         <v>0</v>
       </c>
       <c r="H54">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="I54" t="s">
         <v>22</v>
@@ -3971,7 +3971,7 @@
         <v>21</v>
       </c>
       <c r="E55">
-        <v>1200</v>
+        <v>200</v>
       </c>
       <c r="F55" t="s">
         <v>21</v>
@@ -3980,7 +3980,7 @@
         <v>0</v>
       </c>
       <c r="H55">
-        <v>1200</v>
+        <v>200</v>
       </c>
       <c r="I55" t="s">
         <v>22</v>
@@ -4027,7 +4027,7 @@
         <v>21</v>
       </c>
       <c r="E56">
-        <v>1500</v>
+        <v>100</v>
       </c>
       <c r="F56" t="s">
         <v>21</v>
@@ -4036,7 +4036,7 @@
         <v>0</v>
       </c>
       <c r="H56">
-        <v>1500</v>
+        <v>100</v>
       </c>
       <c r="I56" t="s">
         <v>22</v>
@@ -4083,7 +4083,7 @@
         <v>21</v>
       </c>
       <c r="E57">
-        <v>200</v>
+        <v>30</v>
       </c>
       <c r="F57" t="s">
         <v>21</v>
@@ -4092,7 +4092,7 @@
         <v>0</v>
       </c>
       <c r="H57">
-        <v>200</v>
+        <v>30</v>
       </c>
       <c r="I57" t="s">
         <v>22</v>
@@ -4139,7 +4139,7 @@
         <v>21</v>
       </c>
       <c r="E58">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F58" t="s">
         <v>21</v>
@@ -4148,7 +4148,7 @@
         <v>0</v>
       </c>
       <c r="H58">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="I58" t="s">
         <v>22</v>
@@ -4195,7 +4195,7 @@
         <v>21</v>
       </c>
       <c r="E59">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F59" t="s">
         <v>21</v>
@@ -4204,7 +4204,7 @@
         <v>0</v>
       </c>
       <c r="H59">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I59" t="s">
         <v>22</v>
@@ -4251,7 +4251,7 @@
         <v>21</v>
       </c>
       <c r="E60">
-        <v>550</v>
+        <v>20</v>
       </c>
       <c r="F60" t="s">
         <v>21</v>
@@ -4260,7 +4260,7 @@
         <v>0</v>
       </c>
       <c r="H60">
-        <v>550</v>
+        <v>20</v>
       </c>
       <c r="I60" t="s">
         <v>22</v>
@@ -4307,7 +4307,7 @@
         <v>21</v>
       </c>
       <c r="E61">
-        <v>500</v>
+        <v>10</v>
       </c>
       <c r="F61" t="s">
         <v>21</v>
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="H61">
-        <v>500</v>
+        <v>10</v>
       </c>
       <c r="I61" t="s">
         <v>22</v>
@@ -4363,7 +4363,7 @@
         <v>21</v>
       </c>
       <c r="E62">
-        <v>2500</v>
+        <v>450</v>
       </c>
       <c r="F62" t="s">
         <v>21</v>
@@ -4372,7 +4372,7 @@
         <v>0</v>
       </c>
       <c r="H62">
-        <v>2500</v>
+        <v>450</v>
       </c>
       <c r="I62" t="s">
         <v>22</v>
@@ -4419,7 +4419,7 @@
         <v>21</v>
       </c>
       <c r="E63">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F63" t="s">
         <v>21</v>
@@ -4428,7 +4428,7 @@
         <v>0</v>
       </c>
       <c r="H63">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="I63" t="s">
         <v>22</v>
@@ -4475,7 +4475,7 @@
         <v>21</v>
       </c>
       <c r="E64">
-        <v>2200</v>
+        <v>500</v>
       </c>
       <c r="F64" t="s">
         <v>21</v>
@@ -4484,7 +4484,7 @@
         <v>0</v>
       </c>
       <c r="H64">
-        <v>2200</v>
+        <v>500</v>
       </c>
       <c r="I64" t="s">
         <v>22</v>
@@ -4531,7 +4531,7 @@
         <v>21</v>
       </c>
       <c r="E65">
-        <v>2600</v>
+        <v>2500</v>
       </c>
       <c r="F65" t="s">
         <v>21</v>
@@ -4540,7 +4540,7 @@
         <v>0</v>
       </c>
       <c r="H65">
-        <v>2600</v>
+        <v>2500</v>
       </c>
       <c r="I65" t="s">
         <v>22</v>
@@ -4587,7 +4587,7 @@
         <v>21</v>
       </c>
       <c r="E66">
-        <v>2400</v>
+        <v>500</v>
       </c>
       <c r="F66" t="s">
         <v>21</v>
@@ -4596,7 +4596,7 @@
         <v>0</v>
       </c>
       <c r="H66">
-        <v>2400</v>
+        <v>500</v>
       </c>
       <c r="I66" t="s">
         <v>22</v>
@@ -4643,7 +4643,7 @@
         <v>21</v>
       </c>
       <c r="E67">
-        <v>2400</v>
+        <v>2200</v>
       </c>
       <c r="F67" t="s">
         <v>21</v>
@@ -4652,7 +4652,7 @@
         <v>0</v>
       </c>
       <c r="H67">
-        <v>2400</v>
+        <v>2200</v>
       </c>
       <c r="I67" t="s">
         <v>22</v>
@@ -4699,7 +4699,7 @@
         <v>21</v>
       </c>
       <c r="E68">
-        <v>2000</v>
+        <v>2600</v>
       </c>
       <c r="F68" t="s">
         <v>21</v>
@@ -4708,7 +4708,7 @@
         <v>0</v>
       </c>
       <c r="H68">
-        <v>2000</v>
+        <v>2600</v>
       </c>
       <c r="I68" t="s">
         <v>22</v>
@@ -4755,7 +4755,7 @@
         <v>21</v>
       </c>
       <c r="E69">
-        <v>1200</v>
+        <v>2400</v>
       </c>
       <c r="F69" t="s">
         <v>21</v>
@@ -4764,7 +4764,7 @@
         <v>0</v>
       </c>
       <c r="H69">
-        <v>1200</v>
+        <v>2400</v>
       </c>
       <c r="I69" t="s">
         <v>22</v>
@@ -4811,7 +4811,7 @@
         <v>21</v>
       </c>
       <c r="E70">
-        <v>1200</v>
+        <v>2400</v>
       </c>
       <c r="F70" t="s">
         <v>21</v>
@@ -4820,7 +4820,7 @@
         <v>0</v>
       </c>
       <c r="H70">
-        <v>1200</v>
+        <v>2400</v>
       </c>
       <c r="I70" t="s">
         <v>22</v>
@@ -4867,7 +4867,7 @@
         <v>21</v>
       </c>
       <c r="E71">
-        <v>750</v>
+        <v>2000</v>
       </c>
       <c r="F71" t="s">
         <v>21</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="H71">
-        <v>750</v>
+        <v>2000</v>
       </c>
       <c r="I71" t="s">
         <v>22</v>
@@ -4923,7 +4923,7 @@
         <v>21</v>
       </c>
       <c r="E72">
-        <v>450</v>
+        <v>1200</v>
       </c>
       <c r="F72" t="s">
         <v>21</v>
@@ -4932,7 +4932,7 @@
         <v>0</v>
       </c>
       <c r="H72">
-        <v>450</v>
+        <v>1200</v>
       </c>
       <c r="I72" t="s">
         <v>22</v>
@@ -4979,7 +4979,7 @@
         <v>21</v>
       </c>
       <c r="E73">
-        <v>200</v>
+        <v>1200</v>
       </c>
       <c r="F73" t="s">
         <v>21</v>
@@ -4988,7 +4988,7 @@
         <v>0</v>
       </c>
       <c r="H73">
-        <v>200</v>
+        <v>1200</v>
       </c>
       <c r="I73" t="s">
         <v>22</v>
@@ -5035,7 +5035,7 @@
         <v>21</v>
       </c>
       <c r="E74">
-        <v>500</v>
+        <v>750</v>
       </c>
       <c r="F74" t="s">
         <v>21</v>
@@ -5044,7 +5044,7 @@
         <v>0</v>
       </c>
       <c r="H74">
-        <v>500</v>
+        <v>750</v>
       </c>
       <c r="I74" t="s">
         <v>22</v>
@@ -5079,10 +5079,10 @@
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B75" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C75" t="s">
         <v>143</v>

--- a/pc.xlsx
+++ b/pc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Claude\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F475467-836C-4497-826C-9E3405879208}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8AEFBED3-B9C4-46EA-A46F-10381AC96828}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="28">
   <si>
     <t>Cod. producto</t>
   </si>
@@ -111,54 +111,6 @@
   </si>
   <si>
     <t>Pendiente</t>
-  </si>
-  <si>
-    <t>C5OX-24-20F</t>
-  </si>
-  <si>
-    <t>ADAP CODO 90° MF 1.7/8" AS JIC 37° X MF 1.5/8" AS ORING</t>
-  </si>
-  <si>
-    <t>SOL - 2307</t>
-  </si>
-  <si>
-    <t>2026-06</t>
-  </si>
-  <si>
-    <t>391-2882-051</t>
-  </si>
-  <si>
-    <t>CUERDA P30 Y P50</t>
-  </si>
-  <si>
-    <t>391-2884-021P</t>
-  </si>
-  <si>
-    <t>SELLO GOMA SQUARE GASKET 50-25</t>
-  </si>
-  <si>
-    <t>2000</t>
-  </si>
-  <si>
-    <t>WIPER 50.80 x 63.50 x 9.52/6.35</t>
-  </si>
-  <si>
-    <t>1250-0625-250B</t>
-  </si>
-  <si>
-    <t>POLYPAK 15.88 x 22.22 x 6.35</t>
-  </si>
-  <si>
-    <t>313213001</t>
-  </si>
-  <si>
-    <t>MANG. DE POLIURETANO PARA NEUMÁTICA. RAUPURAM 10 MM</t>
-  </si>
-  <si>
-    <t>934331T</t>
-  </si>
-  <si>
-    <t>FILTRO TRICEPTOR SILICA GEL 8"</t>
   </si>
 </sst>
 </file>
@@ -510,8 +462,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:R6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="47.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -846,398 +802,6 @@
         <v>21</v>
       </c>
       <c r="R6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>10</v>
-      </c>
-      <c r="I7" t="s">
-        <v>22</v>
-      </c>
-      <c r="J7" t="s">
-        <v>31</v>
-      </c>
-      <c r="K7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L7" t="s">
-        <v>25</v>
-      </c>
-      <c r="M7" t="s">
-        <v>26</v>
-      </c>
-      <c r="N7" t="s">
-        <v>21</v>
-      </c>
-      <c r="O7" t="s">
-        <v>21</v>
-      </c>
-      <c r="P7" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>21</v>
-      </c>
-      <c r="R7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8">
-        <v>50</v>
-      </c>
-      <c r="F8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>50</v>
-      </c>
-      <c r="I8" t="s">
-        <v>22</v>
-      </c>
-      <c r="J8" t="s">
-        <v>31</v>
-      </c>
-      <c r="K8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L8" t="s">
-        <v>25</v>
-      </c>
-      <c r="M8" t="s">
-        <v>26</v>
-      </c>
-      <c r="N8" t="s">
-        <v>21</v>
-      </c>
-      <c r="O8" t="s">
-        <v>21</v>
-      </c>
-      <c r="P8" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>21</v>
-      </c>
-      <c r="R8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9">
-        <v>100</v>
-      </c>
-      <c r="F9" t="s">
-        <v>21</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>100</v>
-      </c>
-      <c r="I9" t="s">
-        <v>22</v>
-      </c>
-      <c r="J9" t="s">
-        <v>31</v>
-      </c>
-      <c r="K9" t="s">
-        <v>24</v>
-      </c>
-      <c r="L9" t="s">
-        <v>25</v>
-      </c>
-      <c r="M9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N9" t="s">
-        <v>21</v>
-      </c>
-      <c r="O9" t="s">
-        <v>21</v>
-      </c>
-      <c r="P9" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>21</v>
-      </c>
-      <c r="R9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10">
-        <v>20</v>
-      </c>
-      <c r="F10" t="s">
-        <v>21</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>20</v>
-      </c>
-      <c r="I10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K10" t="s">
-        <v>24</v>
-      </c>
-      <c r="L10" t="s">
-        <v>25</v>
-      </c>
-      <c r="M10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N10" t="s">
-        <v>21</v>
-      </c>
-      <c r="O10" t="s">
-        <v>21</v>
-      </c>
-      <c r="P10" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>21</v>
-      </c>
-      <c r="R10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11">
-        <v>50</v>
-      </c>
-      <c r="F11" t="s">
-        <v>21</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>50</v>
-      </c>
-      <c r="I11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J11" t="s">
-        <v>31</v>
-      </c>
-      <c r="K11" t="s">
-        <v>24</v>
-      </c>
-      <c r="L11" t="s">
-        <v>25</v>
-      </c>
-      <c r="M11" t="s">
-        <v>26</v>
-      </c>
-      <c r="N11" t="s">
-        <v>21</v>
-      </c>
-      <c r="O11" t="s">
-        <v>21</v>
-      </c>
-      <c r="P11" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>21</v>
-      </c>
-      <c r="R11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12">
-        <v>100</v>
-      </c>
-      <c r="F12" t="s">
-        <v>21</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>100</v>
-      </c>
-      <c r="I12" t="s">
-        <v>22</v>
-      </c>
-      <c r="J12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K12" t="s">
-        <v>24</v>
-      </c>
-      <c r="L12" t="s">
-        <v>25</v>
-      </c>
-      <c r="M12" t="s">
-        <v>26</v>
-      </c>
-      <c r="N12" t="s">
-        <v>21</v>
-      </c>
-      <c r="O12" t="s">
-        <v>21</v>
-      </c>
-      <c r="P12" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>21</v>
-      </c>
-      <c r="R12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>42</v>
-      </c>
-      <c r="B13" t="s">
-        <v>43</v>
-      </c>
-      <c r="C13" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13">
-        <v>20</v>
-      </c>
-      <c r="F13" t="s">
-        <v>21</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>17</v>
-      </c>
-      <c r="I13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J13" t="s">
-        <v>31</v>
-      </c>
-      <c r="K13" t="s">
-        <v>24</v>
-      </c>
-      <c r="L13" t="s">
-        <v>25</v>
-      </c>
-      <c r="M13" t="s">
-        <v>26</v>
-      </c>
-      <c r="N13" t="s">
-        <v>21</v>
-      </c>
-      <c r="O13" t="s">
-        <v>21</v>
-      </c>
-      <c r="P13" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>21</v>
-      </c>
-      <c r="R13" t="s">
         <v>27</v>
       </c>
     </row>

--- a/pc.xlsx
+++ b/pc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Claude\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8AEFBED3-B9C4-46EA-A46F-10381AC96828}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E350A6FC-F67C-4F8D-9653-8D22CB4642A2}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="51">
   <si>
     <t>Cod. producto</t>
   </si>
@@ -111,6 +111,75 @@
   </si>
   <si>
     <t>Pendiente</t>
+  </si>
+  <si>
+    <t>C5OX-24-20F</t>
+  </si>
+  <si>
+    <t>ADAP CODO 90° MF 1.7/8" AS JIC 37° X MF 1.5/8" AS ORING</t>
+  </si>
+  <si>
+    <t>SOL - 2384</t>
+  </si>
+  <si>
+    <t>2026-07</t>
+  </si>
+  <si>
+    <t>391-2882-051</t>
+  </si>
+  <si>
+    <t>CUERDA P30 Y P50</t>
+  </si>
+  <si>
+    <t>391-2884-021P</t>
+  </si>
+  <si>
+    <t>SELLO GOMA SQUARE GASKET 50-25</t>
+  </si>
+  <si>
+    <t>1870-1000-312B</t>
+  </si>
+  <si>
+    <t>POLYPAK 25.40 x 34.92 x 7.94</t>
+  </si>
+  <si>
+    <t>SOL - 2401</t>
+  </si>
+  <si>
+    <t>FT 257/6-14</t>
+  </si>
+  <si>
+    <t>VALVULA DE RETENCION EN LINEA RECTA 1/4" 30LPM - 500 BAR</t>
+  </si>
+  <si>
+    <t>FTX-06P</t>
+  </si>
+  <si>
+    <t>ADAP RECTO 9/16 UNF JIC X 1/4 NPT</t>
+  </si>
+  <si>
+    <t>FTX-08-12P</t>
+  </si>
+  <si>
+    <t>ADAP RECTO 3/4 UNF JIC X 3/4 NPT</t>
+  </si>
+  <si>
+    <t>FTX-12-08P</t>
+  </si>
+  <si>
+    <t>ADAP RECTO 1 1/6 UNF JIC X 1/2 NPT</t>
+  </si>
+  <si>
+    <t>TX-16P</t>
+  </si>
+  <si>
+    <t>VIROLA AS. JIC 37º P/TUERCA 1.5/16 UNF - PARA CAÑO DE 1"</t>
+  </si>
+  <si>
+    <t>BTX-12P</t>
+  </si>
+  <si>
+    <t>TUERCA HG JIC ROSCA 1.1/16" UNF - PARA CAÑO DE 3/4"</t>
   </si>
 </sst>
 </file>
@@ -462,12 +531,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="47.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.109375" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -802,6 +867,566 @@
         <v>21</v>
       </c>
       <c r="R6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>10</v>
+      </c>
+      <c r="I7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" t="s">
+        <v>31</v>
+      </c>
+      <c r="K7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" t="s">
+        <v>25</v>
+      </c>
+      <c r="M7" t="s">
+        <v>26</v>
+      </c>
+      <c r="N7" t="s">
+        <v>21</v>
+      </c>
+      <c r="O7" t="s">
+        <v>21</v>
+      </c>
+      <c r="P7" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>21</v>
+      </c>
+      <c r="R7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8">
+        <v>50</v>
+      </c>
+      <c r="F8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>50</v>
+      </c>
+      <c r="I8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M8" t="s">
+        <v>26</v>
+      </c>
+      <c r="N8" t="s">
+        <v>21</v>
+      </c>
+      <c r="O8" t="s">
+        <v>21</v>
+      </c>
+      <c r="P8" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>21</v>
+      </c>
+      <c r="R8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9">
+        <v>100</v>
+      </c>
+      <c r="F9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>100</v>
+      </c>
+      <c r="I9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" t="s">
+        <v>31</v>
+      </c>
+      <c r="K9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" t="s">
+        <v>25</v>
+      </c>
+      <c r="M9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N9" t="s">
+        <v>21</v>
+      </c>
+      <c r="O9" t="s">
+        <v>21</v>
+      </c>
+      <c r="P9" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>21</v>
+      </c>
+      <c r="R9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10">
+        <v>20</v>
+      </c>
+      <c r="F10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>20</v>
+      </c>
+      <c r="I10" t="s">
+        <v>22</v>
+      </c>
+      <c r="J10" t="s">
+        <v>31</v>
+      </c>
+      <c r="K10" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" t="s">
+        <v>25</v>
+      </c>
+      <c r="M10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N10" t="s">
+        <v>21</v>
+      </c>
+      <c r="O10" t="s">
+        <v>21</v>
+      </c>
+      <c r="P10" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>21</v>
+      </c>
+      <c r="R10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11">
+        <v>4</v>
+      </c>
+      <c r="F11" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>4</v>
+      </c>
+      <c r="I11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" t="s">
+        <v>31</v>
+      </c>
+      <c r="K11" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" t="s">
+        <v>25</v>
+      </c>
+      <c r="M11" t="s">
+        <v>26</v>
+      </c>
+      <c r="N11" t="s">
+        <v>21</v>
+      </c>
+      <c r="O11" t="s">
+        <v>21</v>
+      </c>
+      <c r="P11" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>21</v>
+      </c>
+      <c r="R11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12">
+        <v>50</v>
+      </c>
+      <c r="F12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>50</v>
+      </c>
+      <c r="I12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K12" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" t="s">
+        <v>25</v>
+      </c>
+      <c r="M12" t="s">
+        <v>26</v>
+      </c>
+      <c r="N12" t="s">
+        <v>21</v>
+      </c>
+      <c r="O12" t="s">
+        <v>21</v>
+      </c>
+      <c r="P12" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>21</v>
+      </c>
+      <c r="R12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13">
+        <v>20</v>
+      </c>
+      <c r="F13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>20</v>
+      </c>
+      <c r="I13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K13" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" t="s">
+        <v>25</v>
+      </c>
+      <c r="M13" t="s">
+        <v>26</v>
+      </c>
+      <c r="N13" t="s">
+        <v>21</v>
+      </c>
+      <c r="O13" t="s">
+        <v>21</v>
+      </c>
+      <c r="P13" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>21</v>
+      </c>
+      <c r="R13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14">
+        <v>20</v>
+      </c>
+      <c r="F14" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>20</v>
+      </c>
+      <c r="I14" t="s">
+        <v>22</v>
+      </c>
+      <c r="J14" t="s">
+        <v>31</v>
+      </c>
+      <c r="K14" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" t="s">
+        <v>25</v>
+      </c>
+      <c r="M14" t="s">
+        <v>26</v>
+      </c>
+      <c r="N14" t="s">
+        <v>21</v>
+      </c>
+      <c r="O14" t="s">
+        <v>21</v>
+      </c>
+      <c r="P14" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>21</v>
+      </c>
+      <c r="R14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15">
+        <v>20</v>
+      </c>
+      <c r="F15" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>20</v>
+      </c>
+      <c r="I15" t="s">
+        <v>22</v>
+      </c>
+      <c r="J15" t="s">
+        <v>31</v>
+      </c>
+      <c r="K15" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" t="s">
+        <v>25</v>
+      </c>
+      <c r="M15" t="s">
+        <v>26</v>
+      </c>
+      <c r="N15" t="s">
+        <v>21</v>
+      </c>
+      <c r="O15" t="s">
+        <v>21</v>
+      </c>
+      <c r="P15" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>21</v>
+      </c>
+      <c r="R15" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16">
+        <v>20</v>
+      </c>
+      <c r="F16" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>20</v>
+      </c>
+      <c r="I16" t="s">
+        <v>22</v>
+      </c>
+      <c r="J16" t="s">
+        <v>31</v>
+      </c>
+      <c r="K16" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" t="s">
+        <v>25</v>
+      </c>
+      <c r="M16" t="s">
+        <v>26</v>
+      </c>
+      <c r="N16" t="s">
+        <v>21</v>
+      </c>
+      <c r="O16" t="s">
+        <v>21</v>
+      </c>
+      <c r="P16" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>21</v>
+      </c>
+      <c r="R16" t="s">
         <v>27</v>
       </c>
     </row>

--- a/pc.xlsx
+++ b/pc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Claude\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E350A6FC-F67C-4F8D-9653-8D22CB4642A2}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4C42B354-6BD4-4698-BC37-79BFB6614FCB}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="49">
   <si>
     <t>Cod. producto</t>
   </si>
@@ -146,16 +146,10 @@
     <t>SOL - 2401</t>
   </si>
   <si>
-    <t>FT 257/6-14</t>
-  </si>
-  <si>
-    <t>VALVULA DE RETENCION EN LINEA RECTA 1/4" 30LPM - 500 BAR</t>
-  </si>
-  <si>
-    <t>FTX-06P</t>
-  </si>
-  <si>
-    <t>ADAP RECTO 9/16 UNF JIC X 1/4 NPT</t>
+    <t>BTX-12P</t>
+  </si>
+  <si>
+    <t>TUERCA HG JIC ROSCA 1.1/16" UNF - PARA CAÑO DE 3/4"</t>
   </si>
   <si>
     <t>FTX-08-12P</t>
@@ -170,16 +164,16 @@
     <t>ADAP RECTO 1 1/6 UNF JIC X 1/2 NPT</t>
   </si>
   <si>
+    <t>TX-06P</t>
+  </si>
+  <si>
+    <t>VIROLA AS. JIC 37º P/TUERCA 9/16 UNF - PARA CAÑO DE 3/8"</t>
+  </si>
+  <si>
     <t>TX-16P</t>
   </si>
   <si>
     <t>VIROLA AS. JIC 37º P/TUERCA 1.5/16 UNF - PARA CAÑO DE 1"</t>
-  </si>
-  <si>
-    <t>BTX-12P</t>
-  </si>
-  <si>
-    <t>TUERCA HG JIC ROSCA 1.1/16" UNF - PARA CAÑO DE 3/4"</t>
   </si>
 </sst>
 </file>
@@ -531,7 +525,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
@@ -1108,7 +1102,7 @@
         <v>21</v>
       </c>
       <c r="E11">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F11" t="s">
         <v>21</v>
@@ -1117,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="I11" t="s">
         <v>22</v>
@@ -1164,7 +1158,7 @@
         <v>21</v>
       </c>
       <c r="E12">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F12" t="s">
         <v>21</v>
@@ -1173,7 +1167,7 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="I12" t="s">
         <v>22</v>
@@ -1276,7 +1270,7 @@
         <v>21</v>
       </c>
       <c r="E14">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F14" t="s">
         <v>21</v>
@@ -1285,7 +1279,7 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="I14" t="s">
         <v>22</v>
@@ -1371,62 +1365,6 @@
         <v>21</v>
       </c>
       <c r="R15" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>49</v>
-      </c>
-      <c r="B16" t="s">
-        <v>50</v>
-      </c>
-      <c r="C16" t="s">
-        <v>38</v>
-      </c>
-      <c r="D16" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16">
-        <v>20</v>
-      </c>
-      <c r="F16" t="s">
-        <v>21</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>20</v>
-      </c>
-      <c r="I16" t="s">
-        <v>22</v>
-      </c>
-      <c r="J16" t="s">
-        <v>31</v>
-      </c>
-      <c r="K16" t="s">
-        <v>24</v>
-      </c>
-      <c r="L16" t="s">
-        <v>25</v>
-      </c>
-      <c r="M16" t="s">
-        <v>26</v>
-      </c>
-      <c r="N16" t="s">
-        <v>21</v>
-      </c>
-      <c r="O16" t="s">
-        <v>21</v>
-      </c>
-      <c r="P16" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>21</v>
-      </c>
-      <c r="R16" t="s">
         <v>27</v>
       </c>
     </row>

--- a/pc.xlsx
+++ b/pc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Claude\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4C42B354-6BD4-4698-BC37-79BFB6614FCB}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{26290C7F-3D5A-4B05-B934-E4FDAC3A3927}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/pc.xlsx
+++ b/pc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Claude\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{26290C7F-3D5A-4B05-B934-E4FDAC3A3927}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C1D41B81-897C-4815-9039-271DC75B0FF2}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="36">
   <si>
     <t>Cod. producto</t>
   </si>
@@ -135,45 +135,6 @@
   </si>
   <si>
     <t>SELLO GOMA SQUARE GASKET 50-25</t>
-  </si>
-  <si>
-    <t>1870-1000-312B</t>
-  </si>
-  <si>
-    <t>POLYPAK 25.40 x 34.92 x 7.94</t>
-  </si>
-  <si>
-    <t>SOL - 2401</t>
-  </si>
-  <si>
-    <t>BTX-12P</t>
-  </si>
-  <si>
-    <t>TUERCA HG JIC ROSCA 1.1/16" UNF - PARA CAÑO DE 3/4"</t>
-  </si>
-  <si>
-    <t>FTX-08-12P</t>
-  </si>
-  <si>
-    <t>ADAP RECTO 3/4 UNF JIC X 3/4 NPT</t>
-  </si>
-  <si>
-    <t>FTX-12-08P</t>
-  </si>
-  <si>
-    <t>ADAP RECTO 1 1/6 UNF JIC X 1/2 NPT</t>
-  </si>
-  <si>
-    <t>TX-06P</t>
-  </si>
-  <si>
-    <t>VIROLA AS. JIC 37º P/TUERCA 9/16 UNF - PARA CAÑO DE 3/8"</t>
-  </si>
-  <si>
-    <t>TX-16P</t>
-  </si>
-  <si>
-    <t>VIROLA AS. JIC 37º P/TUERCA 1.5/16 UNF - PARA CAÑO DE 1"</t>
   </si>
 </sst>
 </file>
@@ -525,7 +486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
@@ -1032,342 +993,6 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10">
-        <v>20</v>
-      </c>
-      <c r="F10" t="s">
-        <v>21</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>20</v>
-      </c>
-      <c r="I10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J10" t="s">
-        <v>31</v>
-      </c>
-      <c r="K10" t="s">
-        <v>24</v>
-      </c>
-      <c r="L10" t="s">
-        <v>25</v>
-      </c>
-      <c r="M10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N10" t="s">
-        <v>21</v>
-      </c>
-      <c r="O10" t="s">
-        <v>21</v>
-      </c>
-      <c r="P10" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>21</v>
-      </c>
-      <c r="R10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" t="s">
-        <v>40</v>
-      </c>
-      <c r="C11" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11">
-        <v>20</v>
-      </c>
-      <c r="F11" t="s">
-        <v>21</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>20</v>
-      </c>
-      <c r="I11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J11" t="s">
-        <v>31</v>
-      </c>
-      <c r="K11" t="s">
-        <v>24</v>
-      </c>
-      <c r="L11" t="s">
-        <v>25</v>
-      </c>
-      <c r="M11" t="s">
-        <v>26</v>
-      </c>
-      <c r="N11" t="s">
-        <v>21</v>
-      </c>
-      <c r="O11" t="s">
-        <v>21</v>
-      </c>
-      <c r="P11" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>21</v>
-      </c>
-      <c r="R11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12">
-        <v>20</v>
-      </c>
-      <c r="F12" t="s">
-        <v>21</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>20</v>
-      </c>
-      <c r="I12" t="s">
-        <v>22</v>
-      </c>
-      <c r="J12" t="s">
-        <v>31</v>
-      </c>
-      <c r="K12" t="s">
-        <v>24</v>
-      </c>
-      <c r="L12" t="s">
-        <v>25</v>
-      </c>
-      <c r="M12" t="s">
-        <v>26</v>
-      </c>
-      <c r="N12" t="s">
-        <v>21</v>
-      </c>
-      <c r="O12" t="s">
-        <v>21</v>
-      </c>
-      <c r="P12" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>21</v>
-      </c>
-      <c r="R12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B13" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13">
-        <v>20</v>
-      </c>
-      <c r="F13" t="s">
-        <v>21</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>20</v>
-      </c>
-      <c r="I13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J13" t="s">
-        <v>31</v>
-      </c>
-      <c r="K13" t="s">
-        <v>24</v>
-      </c>
-      <c r="L13" t="s">
-        <v>25</v>
-      </c>
-      <c r="M13" t="s">
-        <v>26</v>
-      </c>
-      <c r="N13" t="s">
-        <v>21</v>
-      </c>
-      <c r="O13" t="s">
-        <v>21</v>
-      </c>
-      <c r="P13" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>21</v>
-      </c>
-      <c r="R13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>45</v>
-      </c>
-      <c r="B14" t="s">
-        <v>46</v>
-      </c>
-      <c r="C14" t="s">
-        <v>38</v>
-      </c>
-      <c r="D14" t="s">
-        <v>21</v>
-      </c>
-      <c r="E14">
-        <v>50</v>
-      </c>
-      <c r="F14" t="s">
-        <v>21</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>50</v>
-      </c>
-      <c r="I14" t="s">
-        <v>22</v>
-      </c>
-      <c r="J14" t="s">
-        <v>31</v>
-      </c>
-      <c r="K14" t="s">
-        <v>24</v>
-      </c>
-      <c r="L14" t="s">
-        <v>25</v>
-      </c>
-      <c r="M14" t="s">
-        <v>26</v>
-      </c>
-      <c r="N14" t="s">
-        <v>21</v>
-      </c>
-      <c r="O14" t="s">
-        <v>21</v>
-      </c>
-      <c r="P14" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>21</v>
-      </c>
-      <c r="R14" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>47</v>
-      </c>
-      <c r="B15" t="s">
-        <v>48</v>
-      </c>
-      <c r="C15" t="s">
-        <v>38</v>
-      </c>
-      <c r="D15" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15">
-        <v>20</v>
-      </c>
-      <c r="F15" t="s">
-        <v>21</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>20</v>
-      </c>
-      <c r="I15" t="s">
-        <v>22</v>
-      </c>
-      <c r="J15" t="s">
-        <v>31</v>
-      </c>
-      <c r="K15" t="s">
-        <v>24</v>
-      </c>
-      <c r="L15" t="s">
-        <v>25</v>
-      </c>
-      <c r="M15" t="s">
-        <v>26</v>
-      </c>
-      <c r="N15" t="s">
-        <v>21</v>
-      </c>
-      <c r="O15" t="s">
-        <v>21</v>
-      </c>
-      <c r="P15" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>21</v>
-      </c>
-      <c r="R15" t="s">
-        <v>27</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pc.xlsx
+++ b/pc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Claude\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C1D41B81-897C-4815-9039-271DC75B0FF2}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{607B9CC7-5FCF-49BF-B23E-0802365FC79A}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/pc.xlsx
+++ b/pc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Claude\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{607B9CC7-5FCF-49BF-B23E-0802365FC79A}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{78156416-2C69-4F03-94E0-ADD2180268B5}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="57">
   <si>
     <t>Cod. producto</t>
   </si>
@@ -113,6 +113,27 @@
     <t>Pendiente</t>
   </si>
   <si>
+    <t>509-548-2300</t>
+  </si>
+  <si>
+    <t>Motor hidráulico de engranajes aplicación para cooler</t>
+  </si>
+  <si>
+    <t>SOL - 2273</t>
+  </si>
+  <si>
+    <t>00948</t>
+  </si>
+  <si>
+    <t>2026-06</t>
+  </si>
+  <si>
+    <t>NEUQUEN</t>
+  </si>
+  <si>
+    <t>Deposito NQN</t>
+  </si>
+  <si>
     <t>C5OX-24-20F</t>
   </si>
   <si>
@@ -135,6 +156,48 @@
   </si>
   <si>
     <t>SELLO GOMA SQUARE GASKET 50-25</t>
+  </si>
+  <si>
+    <t>CV FLETES AEREOS</t>
+  </si>
+  <si>
+    <t>Flete Aereo</t>
+  </si>
+  <si>
+    <t>SOL - 2420</t>
+  </si>
+  <si>
+    <t>0007-00000150</t>
+  </si>
+  <si>
+    <t>SAN JULIAN</t>
+  </si>
+  <si>
+    <t>OPERACIONES SAN JULIAN</t>
+  </si>
+  <si>
+    <t>0914180C</t>
+  </si>
+  <si>
+    <t>CONECTOR MINIMES 1/4" NPTF TAPA METALICA</t>
+  </si>
+  <si>
+    <t>SOL - 2430</t>
+  </si>
+  <si>
+    <t>2026-08</t>
+  </si>
+  <si>
+    <t>934332T</t>
+  </si>
+  <si>
+    <t>FILTRO TRICEPTOR SILICA GEL 10"</t>
+  </si>
+  <si>
+    <t>SOL - 2431</t>
+  </si>
+  <si>
+    <t>0007-00000152</t>
   </si>
 </sst>
 </file>
@@ -486,7 +549,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
@@ -559,7 +622,7 @@
         <v>21</v>
       </c>
       <c r="E2">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F2" t="s">
         <v>21</v>
@@ -568,7 +631,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I2" t="s">
         <v>22</v>
@@ -615,7 +678,7 @@
         <v>21</v>
       </c>
       <c r="E3">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F3" t="s">
         <v>21</v>
@@ -624,7 +687,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I3" t="s">
         <v>22</v>
@@ -727,7 +790,7 @@
         <v>21</v>
       </c>
       <c r="E5">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F5" t="s">
         <v>21</v>
@@ -736,7 +799,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="I5" t="s">
         <v>22</v>
@@ -783,7 +846,7 @@
         <v>21</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F6" t="s">
         <v>21</v>
@@ -792,7 +855,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="I6" t="s">
         <v>22</v>
@@ -836,10 +899,10 @@
         <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F7" t="s">
         <v>21</v>
@@ -848,22 +911,22 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I7" t="s">
         <v>22</v>
       </c>
       <c r="J7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K7" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L7" t="s">
         <v>25</v>
       </c>
       <c r="M7" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="N7" t="s">
         <v>21</v>
@@ -883,19 +946,19 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
         <v>21</v>
       </c>
       <c r="E8">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
         <v>21</v>
@@ -904,13 +967,13 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="I8" t="s">
         <v>22</v>
       </c>
       <c r="J8" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="K8" t="s">
         <v>24</v>
@@ -939,19 +1002,19 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
         <v>21</v>
       </c>
       <c r="E9">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F9" t="s">
         <v>21</v>
@@ -960,13 +1023,13 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I9" t="s">
         <v>22</v>
       </c>
       <c r="J9" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="K9" t="s">
         <v>24</v>
@@ -990,6 +1053,230 @@
         <v>21</v>
       </c>
       <c r="R9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10">
+        <v>100</v>
+      </c>
+      <c r="F10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>100</v>
+      </c>
+      <c r="I10" t="s">
+        <v>22</v>
+      </c>
+      <c r="J10" t="s">
+        <v>38</v>
+      </c>
+      <c r="K10" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" t="s">
+        <v>25</v>
+      </c>
+      <c r="M10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N10" t="s">
+        <v>21</v>
+      </c>
+      <c r="O10" t="s">
+        <v>21</v>
+      </c>
+      <c r="P10" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>21</v>
+      </c>
+      <c r="R10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" t="s">
+        <v>38</v>
+      </c>
+      <c r="K11" t="s">
+        <v>47</v>
+      </c>
+      <c r="L11" t="s">
+        <v>25</v>
+      </c>
+      <c r="M11" t="s">
+        <v>48</v>
+      </c>
+      <c r="N11" t="s">
+        <v>21</v>
+      </c>
+      <c r="O11" t="s">
+        <v>21</v>
+      </c>
+      <c r="P11" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>21</v>
+      </c>
+      <c r="R11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>10</v>
+      </c>
+      <c r="I12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J12" t="s">
+        <v>52</v>
+      </c>
+      <c r="K12" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" t="s">
+        <v>25</v>
+      </c>
+      <c r="M12" t="s">
+        <v>26</v>
+      </c>
+      <c r="N12" t="s">
+        <v>21</v>
+      </c>
+      <c r="O12" t="s">
+        <v>21</v>
+      </c>
+      <c r="P12" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>21</v>
+      </c>
+      <c r="R12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13">
+        <v>12</v>
+      </c>
+      <c r="F13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>12</v>
+      </c>
+      <c r="I13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J13" t="s">
+        <v>52</v>
+      </c>
+      <c r="K13" t="s">
+        <v>47</v>
+      </c>
+      <c r="L13" t="s">
+        <v>25</v>
+      </c>
+      <c r="M13" t="s">
+        <v>48</v>
+      </c>
+      <c r="N13" t="s">
+        <v>21</v>
+      </c>
+      <c r="O13" t="s">
+        <v>21</v>
+      </c>
+      <c r="P13" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>21</v>
+      </c>
+      <c r="R13" t="s">
         <v>27</v>
       </c>
     </row>

--- a/pc.xlsx
+++ b/pc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Claude\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{78156416-2C69-4F03-94E0-ADD2180268B5}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7598A86-B6E7-4A86-BB3D-298ECC9C7F9E}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -158,24 +158,6 @@
     <t>SELLO GOMA SQUARE GASKET 50-25</t>
   </si>
   <si>
-    <t>CV FLETES AEREOS</t>
-  </si>
-  <si>
-    <t>Flete Aereo</t>
-  </si>
-  <si>
-    <t>SOL - 2420</t>
-  </si>
-  <si>
-    <t>0007-00000150</t>
-  </si>
-  <si>
-    <t>SAN JULIAN</t>
-  </si>
-  <si>
-    <t>OPERACIONES SAN JULIAN</t>
-  </si>
-  <si>
     <t>0914180C</t>
   </si>
   <si>
@@ -188,16 +170,34 @@
     <t>2026-08</t>
   </si>
   <si>
-    <t>934332T</t>
-  </si>
-  <si>
-    <t>FILTRO TRICEPTOR SILICA GEL 10"</t>
-  </si>
-  <si>
-    <t>SOL - 2431</t>
-  </si>
-  <si>
-    <t>0007-00000152</t>
+    <t>BOMBA HCA A ENGRANAJES</t>
+  </si>
+  <si>
+    <t>BOMBA HIDRAULICA A ENGRANAJES - GENERICO</t>
+  </si>
+  <si>
+    <t>SOL - 2436</t>
+  </si>
+  <si>
+    <t>00953</t>
+  </si>
+  <si>
+    <t>HIDROIL SRL</t>
+  </si>
+  <si>
+    <t>Deposito</t>
+  </si>
+  <si>
+    <t>VRL25-I</t>
+  </si>
+  <si>
+    <t>VÁLVULA RETENCIÓN DE 1/4" INOX. 5000 PSI</t>
+  </si>
+  <si>
+    <t>SOL - 2437</t>
+  </si>
+  <si>
+    <t>01022</t>
   </si>
 </sst>
 </file>
@@ -622,7 +622,7 @@
         <v>21</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F2" t="s">
         <v>21</v>
@@ -631,7 +631,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="I2" t="s">
         <v>22</v>
@@ -678,7 +678,7 @@
         <v>21</v>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F3" t="s">
         <v>21</v>
@@ -687,7 +687,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="I3" t="s">
         <v>22</v>
@@ -790,7 +790,7 @@
         <v>21</v>
       </c>
       <c r="E5">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F5" t="s">
         <v>21</v>
@@ -799,7 +799,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I5" t="s">
         <v>22</v>
@@ -846,7 +846,7 @@
         <v>21</v>
       </c>
       <c r="E6">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F6" t="s">
         <v>21</v>
@@ -855,7 +855,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I6" t="s">
         <v>22</v>
@@ -1123,10 +1123,10 @@
         <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
         <v>21</v>
@@ -1135,22 +1135,22 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I11" t="s">
         <v>22</v>
       </c>
       <c r="J11" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="K11" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="L11" t="s">
         <v>25</v>
       </c>
       <c r="M11" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="N11" t="s">
         <v>21</v>
@@ -1170,16 +1170,16 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" t="s">
         <v>49</v>
       </c>
-      <c r="B12" t="s">
+      <c r="D12" t="s">
         <v>50</v>
-      </c>
-      <c r="C12" t="s">
-        <v>51</v>
-      </c>
-      <c r="D12" t="s">
-        <v>21</v>
       </c>
       <c r="E12">
         <v>10</v>
@@ -1197,16 +1197,16 @@
         <v>22</v>
       </c>
       <c r="J12" t="s">
+        <v>46</v>
+      </c>
+      <c r="K12" t="s">
+        <v>51</v>
+      </c>
+      <c r="L12" t="s">
+        <v>25</v>
+      </c>
+      <c r="M12" t="s">
         <v>52</v>
-      </c>
-      <c r="K12" t="s">
-        <v>24</v>
-      </c>
-      <c r="L12" t="s">
-        <v>25</v>
-      </c>
-      <c r="M12" t="s">
-        <v>26</v>
       </c>
       <c r="N12" t="s">
         <v>21</v>
@@ -1238,7 +1238,7 @@
         <v>56</v>
       </c>
       <c r="E13">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="F13" t="s">
         <v>21</v>
@@ -1247,22 +1247,22 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="I13" t="s">
         <v>22</v>
       </c>
       <c r="J13" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="K13" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="L13" t="s">
         <v>25</v>
       </c>
       <c r="M13" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="N13" t="s">
         <v>21</v>

--- a/pc.xlsx
+++ b/pc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Claude\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7598A86-B6E7-4A86-BB3D-298ECC9C7F9E}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{914768A6-A3A9-4D84-A00E-83B0BFB5CBC9}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="56">
   <si>
     <t>Cod. producto</t>
   </si>
@@ -158,46 +158,43 @@
     <t>SELLO GOMA SQUARE GASKET 50-25</t>
   </si>
   <si>
-    <t>0914180C</t>
-  </si>
-  <si>
-    <t>CONECTOR MINIMES 1/4" NPTF TAPA METALICA</t>
-  </si>
-  <si>
-    <t>SOL - 2430</t>
+    <t>BOMBA HCA A ENGRANAJES</t>
+  </si>
+  <si>
+    <t>BOMBA HIDRAULICA A ENGRANAJES - GENERICO</t>
+  </si>
+  <si>
+    <t>SOL - 2439</t>
+  </si>
+  <si>
+    <t>00955</t>
   </si>
   <si>
     <t>2026-08</t>
   </si>
   <si>
-    <t>BOMBA HCA A ENGRANAJES</t>
-  </si>
-  <si>
-    <t>BOMBA HIDRAULICA A ENGRANAJES - GENERICO</t>
-  </si>
-  <si>
-    <t>SOL - 2436</t>
-  </si>
-  <si>
-    <t>00953</t>
-  </si>
-  <si>
     <t>HIDROIL SRL</t>
   </si>
   <si>
     <t>Deposito</t>
   </si>
   <si>
-    <t>VRL25-I</t>
-  </si>
-  <si>
-    <t>VÁLVULA RETENCIÓN DE 1/4" INOX. 5000 PSI</t>
-  </si>
-  <si>
-    <t>SOL - 2437</t>
-  </si>
-  <si>
-    <t>01022</t>
+    <t>ACCESORIOS A.CARB O BCE</t>
+  </si>
+  <si>
+    <t>ACCESORIOS DE ACERO AL CARBONO O BRONCE - GENERICO</t>
+  </si>
+  <si>
+    <t>SOL - 2442</t>
+  </si>
+  <si>
+    <t>0007-00000153</t>
+  </si>
+  <si>
+    <t>SAN JULIAN</t>
+  </si>
+  <si>
+    <t>OPERACIONES SAN JULIAN</t>
   </si>
 </sst>
 </file>
@@ -1123,7 +1120,7 @@
         <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1141,16 +1138,16 @@
         <v>22</v>
       </c>
       <c r="J11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K11" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L11" t="s">
         <v>25</v>
       </c>
       <c r="M11" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="N11" t="s">
         <v>21</v>
@@ -1170,16 +1167,16 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B12" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D12" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E12">
         <v>10</v>
@@ -1197,16 +1194,16 @@
         <v>22</v>
       </c>
       <c r="J12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K12" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L12" t="s">
         <v>25</v>
       </c>
       <c r="M12" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="N12" t="s">
         <v>21</v>
@@ -1226,19 +1223,19 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" t="s">
         <v>53</v>
       </c>
-      <c r="B13" t="s">
-        <v>54</v>
-      </c>
-      <c r="C13" t="s">
-        <v>55</v>
-      </c>
-      <c r="D13" t="s">
-        <v>56</v>
-      </c>
       <c r="E13">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
         <v>21</v>
@@ -1247,22 +1244,22 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="I13" t="s">
         <v>22</v>
       </c>
       <c r="J13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K13" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="L13" t="s">
         <v>25</v>
       </c>
       <c r="M13" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="N13" t="s">
         <v>21</v>

--- a/pc.xlsx
+++ b/pc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Claude\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{914768A6-A3A9-4D84-A00E-83B0BFB5CBC9}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{023D9ED3-98BC-4B13-8E0F-CE3E77A5F3B4}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="49">
   <si>
     <t>Cod. producto</t>
   </si>
@@ -158,43 +158,22 @@
     <t>SELLO GOMA SQUARE GASKET 50-25</t>
   </si>
   <si>
-    <t>BOMBA HCA A ENGRANAJES</t>
-  </si>
-  <si>
-    <t>BOMBA HIDRAULICA A ENGRANAJES - GENERICO</t>
-  </si>
-  <si>
-    <t>SOL - 2439</t>
-  </si>
-  <si>
-    <t>00955</t>
+    <t>10643-20-20N</t>
+  </si>
+  <si>
+    <t>TERMINAL RECTO HG JIC 1.5/8" x MANGUERA 1.1/4"</t>
+  </si>
+  <si>
+    <t>SOL - 2443</t>
+  </si>
+  <si>
+    <t>01023</t>
   </si>
   <si>
     <t>2026-08</t>
   </si>
   <si>
-    <t>HIDROIL SRL</t>
-  </si>
-  <si>
-    <t>Deposito</t>
-  </si>
-  <si>
-    <t>ACCESORIOS A.CARB O BCE</t>
-  </si>
-  <si>
-    <t>ACCESORIOS DE ACERO AL CARBONO O BRONCE - GENERICO</t>
-  </si>
-  <si>
-    <t>SOL - 2442</t>
-  </si>
-  <si>
-    <t>0007-00000153</t>
-  </si>
-  <si>
-    <t>SAN JULIAN</t>
-  </si>
-  <si>
-    <t>OPERACIONES SAN JULIAN</t>
+    <t>Deposito Nqn 2</t>
   </si>
 </sst>
 </file>
@@ -546,7 +525,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:R11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
@@ -1123,7 +1102,7 @@
         <v>46</v>
       </c>
       <c r="E11">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="F11" t="s">
         <v>21</v>
@@ -1132,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>10</v>
+        <v>130</v>
       </c>
       <c r="I11" t="s">
         <v>22</v>
@@ -1141,14 +1120,14 @@
         <v>47</v>
       </c>
       <c r="K11" t="s">
+        <v>33</v>
+      </c>
+      <c r="L11" t="s">
+        <v>25</v>
+      </c>
+      <c r="M11" t="s">
         <v>48</v>
       </c>
-      <c r="L11" t="s">
-        <v>25</v>
-      </c>
-      <c r="M11" t="s">
-        <v>49</v>
-      </c>
       <c r="N11" t="s">
         <v>21</v>
       </c>
@@ -1162,118 +1141,6 @@
         <v>21</v>
       </c>
       <c r="R11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>50</v>
-      </c>
-      <c r="B12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C12" t="s">
-        <v>52</v>
-      </c>
-      <c r="D12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E12">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>21</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>10</v>
-      </c>
-      <c r="I12" t="s">
-        <v>22</v>
-      </c>
-      <c r="J12" t="s">
-        <v>47</v>
-      </c>
-      <c r="K12" t="s">
-        <v>54</v>
-      </c>
-      <c r="L12" t="s">
-        <v>25</v>
-      </c>
-      <c r="M12" t="s">
-        <v>55</v>
-      </c>
-      <c r="N12" t="s">
-        <v>21</v>
-      </c>
-      <c r="O12" t="s">
-        <v>21</v>
-      </c>
-      <c r="P12" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>21</v>
-      </c>
-      <c r="R12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>50</v>
-      </c>
-      <c r="B13" t="s">
-        <v>51</v>
-      </c>
-      <c r="C13" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" t="s">
-        <v>53</v>
-      </c>
-      <c r="E13">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>21</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>10</v>
-      </c>
-      <c r="I13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J13" t="s">
-        <v>47</v>
-      </c>
-      <c r="K13" t="s">
-        <v>54</v>
-      </c>
-      <c r="L13" t="s">
-        <v>25</v>
-      </c>
-      <c r="M13" t="s">
-        <v>55</v>
-      </c>
-      <c r="N13" t="s">
-        <v>21</v>
-      </c>
-      <c r="O13" t="s">
-        <v>21</v>
-      </c>
-      <c r="P13" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>21</v>
-      </c>
-      <c r="R13" t="s">
         <v>27</v>
       </c>
     </row>

--- a/pc.xlsx
+++ b/pc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Claude\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{023D9ED3-98BC-4B13-8E0F-CE3E77A5F3B4}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B724C46B-E297-43C7-B970-8C7C07EF44D9}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="57">
   <si>
     <t>Cod. producto</t>
   </si>
@@ -158,22 +158,46 @@
     <t>SELLO GOMA SQUARE GASKET 50-25</t>
   </si>
   <si>
-    <t>10643-20-20N</t>
-  </si>
-  <si>
-    <t>TERMINAL RECTO HG JIC 1.5/8" x MANGUERA 1.1/4"</t>
-  </si>
-  <si>
-    <t>SOL - 2443</t>
-  </si>
-  <si>
-    <t>01023</t>
+    <t>BUJE RED-1/4"x1/8" S3000</t>
+  </si>
+  <si>
+    <t>BUJE DE RED 1/4" NPT x 1/8" NPT SERIE 3000</t>
+  </si>
+  <si>
+    <t>SOL - 2445</t>
+  </si>
+  <si>
+    <t>01024</t>
   </si>
   <si>
     <t>2026-08</t>
   </si>
   <si>
     <t>Deposito Nqn 2</t>
+  </si>
+  <si>
+    <t>BUJE RED-3/8"x1/4" S3000</t>
+  </si>
+  <si>
+    <t>BUJE DE RED 3/8" NPT x 1/4" NPT SERIE 3000</t>
+  </si>
+  <si>
+    <t>ENTRER-3/8" S3000</t>
+  </si>
+  <si>
+    <t>ENTRERROSCA 3/8" NPT SERIE 3000</t>
+  </si>
+  <si>
+    <t>TAPON-1/8" S3000</t>
+  </si>
+  <si>
+    <t>TAPON MACHO 1/8" NPT SERIE 3000</t>
+  </si>
+  <si>
+    <t>BUJE RED-1.1/2"x1" S3000</t>
+  </si>
+  <si>
+    <t>BUJE DE RED 1.1/2" NPT x 1" NPT SERIE 3000</t>
   </si>
 </sst>
 </file>
@@ -525,7 +549,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
@@ -1102,7 +1126,7 @@
         <v>46</v>
       </c>
       <c r="E11">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F11" t="s">
         <v>21</v>
@@ -1111,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>130</v>
+        <v>300</v>
       </c>
       <c r="I11" t="s">
         <v>22</v>
@@ -1141,6 +1165,230 @@
         <v>21</v>
       </c>
       <c r="R11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12">
+        <v>300</v>
+      </c>
+      <c r="F12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>300</v>
+      </c>
+      <c r="I12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J12" t="s">
+        <v>47</v>
+      </c>
+      <c r="K12" t="s">
+        <v>33</v>
+      </c>
+      <c r="L12" t="s">
+        <v>25</v>
+      </c>
+      <c r="M12" t="s">
+        <v>48</v>
+      </c>
+      <c r="N12" t="s">
+        <v>21</v>
+      </c>
+      <c r="O12" t="s">
+        <v>21</v>
+      </c>
+      <c r="P12" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>21</v>
+      </c>
+      <c r="R12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13">
+        <v>250</v>
+      </c>
+      <c r="F13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>250</v>
+      </c>
+      <c r="I13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J13" t="s">
+        <v>47</v>
+      </c>
+      <c r="K13" t="s">
+        <v>33</v>
+      </c>
+      <c r="L13" t="s">
+        <v>25</v>
+      </c>
+      <c r="M13" t="s">
+        <v>48</v>
+      </c>
+      <c r="N13" t="s">
+        <v>21</v>
+      </c>
+      <c r="O13" t="s">
+        <v>21</v>
+      </c>
+      <c r="P13" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>21</v>
+      </c>
+      <c r="R13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14">
+        <v>250</v>
+      </c>
+      <c r="F14" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>250</v>
+      </c>
+      <c r="I14" t="s">
+        <v>22</v>
+      </c>
+      <c r="J14" t="s">
+        <v>47</v>
+      </c>
+      <c r="K14" t="s">
+        <v>33</v>
+      </c>
+      <c r="L14" t="s">
+        <v>25</v>
+      </c>
+      <c r="M14" t="s">
+        <v>48</v>
+      </c>
+      <c r="N14" t="s">
+        <v>21</v>
+      </c>
+      <c r="O14" t="s">
+        <v>21</v>
+      </c>
+      <c r="P14" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>21</v>
+      </c>
+      <c r="R14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15">
+        <v>60</v>
+      </c>
+      <c r="F15" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>60</v>
+      </c>
+      <c r="I15" t="s">
+        <v>22</v>
+      </c>
+      <c r="J15" t="s">
+        <v>47</v>
+      </c>
+      <c r="K15" t="s">
+        <v>33</v>
+      </c>
+      <c r="L15" t="s">
+        <v>25</v>
+      </c>
+      <c r="M15" t="s">
+        <v>48</v>
+      </c>
+      <c r="N15" t="s">
+        <v>21</v>
+      </c>
+      <c r="O15" t="s">
+        <v>21</v>
+      </c>
+      <c r="P15" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>21</v>
+      </c>
+      <c r="R15" t="s">
         <v>27</v>
       </c>
     </row>

--- a/pc.xlsx
+++ b/pc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Claude\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B724C46B-E297-43C7-B970-8C7C07EF44D9}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F4F67182-9160-47FF-BA3E-B52579F9725B}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="67">
   <si>
     <t>Cod. producto</t>
   </si>
@@ -198,6 +198,36 @@
   </si>
   <si>
     <t>BUJE DE RED 1.1/2" NPT x 1" NPT SERIE 3000</t>
+  </si>
+  <si>
+    <t>PFQ915R3R1</t>
+  </si>
+  <si>
+    <t>MANOMETRO 2,5" ROSCA POSTERIOR 1/4 NPT 0-400 BAR C/GLICERINA</t>
+  </si>
+  <si>
+    <t>SOL - 2451</t>
+  </si>
+  <si>
+    <t>00960</t>
+  </si>
+  <si>
+    <t>HIDROIL SRL</t>
+  </si>
+  <si>
+    <t>Deposito</t>
+  </si>
+  <si>
+    <t>CV MAT MOST</t>
+  </si>
+  <si>
+    <t>MATERIALES MOSTRADOR</t>
+  </si>
+  <si>
+    <t>SOL - 2454</t>
+  </si>
+  <si>
+    <t>01029</t>
   </si>
 </sst>
 </file>
@@ -549,7 +579,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
@@ -1392,6 +1422,118 @@
         <v>27</v>
       </c>
     </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>8</v>
+      </c>
+      <c r="I16" t="s">
+        <v>22</v>
+      </c>
+      <c r="J16" t="s">
+        <v>47</v>
+      </c>
+      <c r="K16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L16" t="s">
+        <v>25</v>
+      </c>
+      <c r="M16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N16" t="s">
+        <v>21</v>
+      </c>
+      <c r="O16" t="s">
+        <v>21</v>
+      </c>
+      <c r="P16" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>21</v>
+      </c>
+      <c r="R16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" t="s">
+        <v>66</v>
+      </c>
+      <c r="E17">
+        <v>20</v>
+      </c>
+      <c r="F17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>20</v>
+      </c>
+      <c r="I17" t="s">
+        <v>22</v>
+      </c>
+      <c r="J17" t="s">
+        <v>47</v>
+      </c>
+      <c r="K17" t="s">
+        <v>33</v>
+      </c>
+      <c r="L17" t="s">
+        <v>25</v>
+      </c>
+      <c r="M17" t="s">
+        <v>34</v>
+      </c>
+      <c r="N17" t="s">
+        <v>21</v>
+      </c>
+      <c r="O17" t="s">
+        <v>21</v>
+      </c>
+      <c r="P17" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>21</v>
+      </c>
+      <c r="R17" t="s">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pc.xlsx
+++ b/pc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Claude\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F4F67182-9160-47FF-BA3E-B52579F9725B}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{60C853F6-EDC4-4F9B-BA17-B8AD541B7657}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="43">
   <si>
     <t>Cod. producto</t>
   </si>
@@ -156,78 +156,6 @@
   </si>
   <si>
     <t>SELLO GOMA SQUARE GASKET 50-25</t>
-  </si>
-  <si>
-    <t>BUJE RED-1/4"x1/8" S3000</t>
-  </si>
-  <si>
-    <t>BUJE DE RED 1/4" NPT x 1/8" NPT SERIE 3000</t>
-  </si>
-  <si>
-    <t>SOL - 2445</t>
-  </si>
-  <si>
-    <t>01024</t>
-  </si>
-  <si>
-    <t>2026-08</t>
-  </si>
-  <si>
-    <t>Deposito Nqn 2</t>
-  </si>
-  <si>
-    <t>BUJE RED-3/8"x1/4" S3000</t>
-  </si>
-  <si>
-    <t>BUJE DE RED 3/8" NPT x 1/4" NPT SERIE 3000</t>
-  </si>
-  <si>
-    <t>ENTRER-3/8" S3000</t>
-  </si>
-  <si>
-    <t>ENTRERROSCA 3/8" NPT SERIE 3000</t>
-  </si>
-  <si>
-    <t>TAPON-1/8" S3000</t>
-  </si>
-  <si>
-    <t>TAPON MACHO 1/8" NPT SERIE 3000</t>
-  </si>
-  <si>
-    <t>BUJE RED-1.1/2"x1" S3000</t>
-  </si>
-  <si>
-    <t>BUJE DE RED 1.1/2" NPT x 1" NPT SERIE 3000</t>
-  </si>
-  <si>
-    <t>PFQ915R3R1</t>
-  </si>
-  <si>
-    <t>MANOMETRO 2,5" ROSCA POSTERIOR 1/4 NPT 0-400 BAR C/GLICERINA</t>
-  </si>
-  <si>
-    <t>SOL - 2451</t>
-  </si>
-  <si>
-    <t>00960</t>
-  </si>
-  <si>
-    <t>HIDROIL SRL</t>
-  </si>
-  <si>
-    <t>Deposito</t>
-  </si>
-  <si>
-    <t>CV MAT MOST</t>
-  </si>
-  <si>
-    <t>MATERIALES MOSTRADOR</t>
-  </si>
-  <si>
-    <t>SOL - 2454</t>
-  </si>
-  <si>
-    <t>01029</t>
   </si>
 </sst>
 </file>
@@ -579,7 +507,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R17"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
@@ -1142,398 +1070,6 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>43</v>
-      </c>
-      <c r="B11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C11" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" t="s">
-        <v>46</v>
-      </c>
-      <c r="E11">
-        <v>300</v>
-      </c>
-      <c r="F11" t="s">
-        <v>21</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>300</v>
-      </c>
-      <c r="I11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J11" t="s">
-        <v>47</v>
-      </c>
-      <c r="K11" t="s">
-        <v>33</v>
-      </c>
-      <c r="L11" t="s">
-        <v>25</v>
-      </c>
-      <c r="M11" t="s">
-        <v>48</v>
-      </c>
-      <c r="N11" t="s">
-        <v>21</v>
-      </c>
-      <c r="O11" t="s">
-        <v>21</v>
-      </c>
-      <c r="P11" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>21</v>
-      </c>
-      <c r="R11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>49</v>
-      </c>
-      <c r="B12" t="s">
-        <v>50</v>
-      </c>
-      <c r="C12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" t="s">
-        <v>46</v>
-      </c>
-      <c r="E12">
-        <v>300</v>
-      </c>
-      <c r="F12" t="s">
-        <v>21</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>300</v>
-      </c>
-      <c r="I12" t="s">
-        <v>22</v>
-      </c>
-      <c r="J12" t="s">
-        <v>47</v>
-      </c>
-      <c r="K12" t="s">
-        <v>33</v>
-      </c>
-      <c r="L12" t="s">
-        <v>25</v>
-      </c>
-      <c r="M12" t="s">
-        <v>48</v>
-      </c>
-      <c r="N12" t="s">
-        <v>21</v>
-      </c>
-      <c r="O12" t="s">
-        <v>21</v>
-      </c>
-      <c r="P12" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>21</v>
-      </c>
-      <c r="R12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>51</v>
-      </c>
-      <c r="B13" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" t="s">
-        <v>46</v>
-      </c>
-      <c r="E13">
-        <v>250</v>
-      </c>
-      <c r="F13" t="s">
-        <v>21</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>250</v>
-      </c>
-      <c r="I13" t="s">
-        <v>22</v>
-      </c>
-      <c r="J13" t="s">
-        <v>47</v>
-      </c>
-      <c r="K13" t="s">
-        <v>33</v>
-      </c>
-      <c r="L13" t="s">
-        <v>25</v>
-      </c>
-      <c r="M13" t="s">
-        <v>48</v>
-      </c>
-      <c r="N13" t="s">
-        <v>21</v>
-      </c>
-      <c r="O13" t="s">
-        <v>21</v>
-      </c>
-      <c r="P13" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>21</v>
-      </c>
-      <c r="R13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>53</v>
-      </c>
-      <c r="B14" t="s">
-        <v>54</v>
-      </c>
-      <c r="C14" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" t="s">
-        <v>46</v>
-      </c>
-      <c r="E14">
-        <v>250</v>
-      </c>
-      <c r="F14" t="s">
-        <v>21</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>250</v>
-      </c>
-      <c r="I14" t="s">
-        <v>22</v>
-      </c>
-      <c r="J14" t="s">
-        <v>47</v>
-      </c>
-      <c r="K14" t="s">
-        <v>33</v>
-      </c>
-      <c r="L14" t="s">
-        <v>25</v>
-      </c>
-      <c r="M14" t="s">
-        <v>48</v>
-      </c>
-      <c r="N14" t="s">
-        <v>21</v>
-      </c>
-      <c r="O14" t="s">
-        <v>21</v>
-      </c>
-      <c r="P14" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>21</v>
-      </c>
-      <c r="R14" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>55</v>
-      </c>
-      <c r="B15" t="s">
-        <v>56</v>
-      </c>
-      <c r="C15" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" t="s">
-        <v>46</v>
-      </c>
-      <c r="E15">
-        <v>60</v>
-      </c>
-      <c r="F15" t="s">
-        <v>21</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>60</v>
-      </c>
-      <c r="I15" t="s">
-        <v>22</v>
-      </c>
-      <c r="J15" t="s">
-        <v>47</v>
-      </c>
-      <c r="K15" t="s">
-        <v>33</v>
-      </c>
-      <c r="L15" t="s">
-        <v>25</v>
-      </c>
-      <c r="M15" t="s">
-        <v>48</v>
-      </c>
-      <c r="N15" t="s">
-        <v>21</v>
-      </c>
-      <c r="O15" t="s">
-        <v>21</v>
-      </c>
-      <c r="P15" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>21</v>
-      </c>
-      <c r="R15" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>57</v>
-      </c>
-      <c r="B16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C16" t="s">
-        <v>59</v>
-      </c>
-      <c r="D16" t="s">
-        <v>60</v>
-      </c>
-      <c r="E16">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>21</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>8</v>
-      </c>
-      <c r="I16" t="s">
-        <v>22</v>
-      </c>
-      <c r="J16" t="s">
-        <v>47</v>
-      </c>
-      <c r="K16" t="s">
-        <v>61</v>
-      </c>
-      <c r="L16" t="s">
-        <v>25</v>
-      </c>
-      <c r="M16" t="s">
-        <v>62</v>
-      </c>
-      <c r="N16" t="s">
-        <v>21</v>
-      </c>
-      <c r="O16" t="s">
-        <v>21</v>
-      </c>
-      <c r="P16" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>21</v>
-      </c>
-      <c r="R16" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>63</v>
-      </c>
-      <c r="B17" t="s">
-        <v>64</v>
-      </c>
-      <c r="C17" t="s">
-        <v>65</v>
-      </c>
-      <c r="D17" t="s">
-        <v>66</v>
-      </c>
-      <c r="E17">
-        <v>20</v>
-      </c>
-      <c r="F17" t="s">
-        <v>21</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <v>20</v>
-      </c>
-      <c r="I17" t="s">
-        <v>22</v>
-      </c>
-      <c r="J17" t="s">
-        <v>47</v>
-      </c>
-      <c r="K17" t="s">
-        <v>33</v>
-      </c>
-      <c r="L17" t="s">
-        <v>25</v>
-      </c>
-      <c r="M17" t="s">
-        <v>34</v>
-      </c>
-      <c r="N17" t="s">
-        <v>21</v>
-      </c>
-      <c r="O17" t="s">
-        <v>21</v>
-      </c>
-      <c r="P17" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>21</v>
-      </c>
-      <c r="R17" t="s">
-        <v>27</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pc.xlsx
+++ b/pc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Claude\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{60C853F6-EDC4-4F9B-BA17-B8AD541B7657}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{56AFBDBC-D605-4FC7-ACB0-B2536CF671D7}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="50">
   <si>
     <t>Cod. producto</t>
   </si>
@@ -156,6 +156,27 @@
   </si>
   <si>
     <t>SELLO GOMA SQUARE GASKET 50-25</t>
+  </si>
+  <si>
+    <t>RACORDS Y CAMISAS</t>
+  </si>
+  <si>
+    <t>RACORDS Y CAMISAS ALTA/BAJA PRESION - GENERICO</t>
+  </si>
+  <si>
+    <t>SOL - 2465</t>
+  </si>
+  <si>
+    <t>0007-00000158</t>
+  </si>
+  <si>
+    <t>2026-08</t>
+  </si>
+  <si>
+    <t>SAN JULIAN</t>
+  </si>
+  <si>
+    <t>OPERACIONES SAN JULIAN</t>
   </si>
 </sst>
 </file>
@@ -507,7 +528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:R11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
@@ -692,7 +713,7 @@
         <v>21</v>
       </c>
       <c r="E4">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F4" t="s">
         <v>21</v>
@@ -701,7 +722,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I4" t="s">
         <v>22</v>
@@ -804,7 +825,7 @@
         <v>21</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F6" t="s">
         <v>21</v>
@@ -813,7 +834,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="I6" t="s">
         <v>22</v>
@@ -1067,6 +1088,62 @@
         <v>21</v>
       </c>
       <c r="R10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11">
+        <v>6</v>
+      </c>
+      <c r="F11" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>6</v>
+      </c>
+      <c r="I11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" t="s">
+        <v>47</v>
+      </c>
+      <c r="K11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L11" t="s">
+        <v>25</v>
+      </c>
+      <c r="M11" t="s">
+        <v>49</v>
+      </c>
+      <c r="N11" t="s">
+        <v>21</v>
+      </c>
+      <c r="O11" t="s">
+        <v>21</v>
+      </c>
+      <c r="P11" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>21</v>
+      </c>
+      <c r="R11" t="s">
         <v>27</v>
       </c>
     </row>

--- a/pc.xlsx
+++ b/pc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Claude\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{56AFBDBC-D605-4FC7-ACB0-B2536CF671D7}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DEF8ED45-00AF-4054-A30D-B2BE2AE52300}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="106">
   <si>
     <t>Cod. producto</t>
   </si>
@@ -177,6 +177,174 @@
   </si>
   <si>
     <t>OPERACIONES SAN JULIAN</t>
+  </si>
+  <si>
+    <t>SA-634-1100C</t>
+  </si>
+  <si>
+    <t>BLOCK CILINDROS SAUER SERIE 90-130</t>
+  </si>
+  <si>
+    <t>SOL - 2488</t>
+  </si>
+  <si>
+    <t>01036</t>
+  </si>
+  <si>
+    <t>Deposito Nqn 2</t>
+  </si>
+  <si>
+    <t>SA-634-3201M</t>
+  </si>
+  <si>
+    <t>EJE TRANSMISION MOTOR SAUER 90-130 - Z23 - CHALLENGER</t>
+  </si>
+  <si>
+    <t>SA-634-2200</t>
+  </si>
+  <si>
+    <t>PISTON SAUER SERIE 90-130</t>
+  </si>
+  <si>
+    <t>SA-634-4701</t>
+  </si>
+  <si>
+    <t>PLACA FRICCION SAUER SERIE 90-130</t>
+  </si>
+  <si>
+    <t>SA-634-4401</t>
+  </si>
+  <si>
+    <t>PLACA VALV. LH/RH SAUER SERIE 90-130</t>
+  </si>
+  <si>
+    <t>SA-633-1100C</t>
+  </si>
+  <si>
+    <t>BLOCK CILINDROS SAUER SERIE 90-100</t>
+  </si>
+  <si>
+    <t>SA-640-3201A</t>
+  </si>
+  <si>
+    <t>EJE TRANSMISION MOTOR SAUER SERIE 90-100 Z21</t>
+  </si>
+  <si>
+    <t>SA-640-3306F</t>
+  </si>
+  <si>
+    <t>KIT SELLOS MOTOR SAUER 90-100 M.F.</t>
+  </si>
+  <si>
+    <t>SA-633-2100</t>
+  </si>
+  <si>
+    <t>PISTON SAUER SERIE 90-100</t>
+  </si>
+  <si>
+    <t>SA-640-4701</t>
+  </si>
+  <si>
+    <t>PLACA FRICCION SAUER 90-100 - 505350</t>
+  </si>
+  <si>
+    <t>SA-633-4501</t>
+  </si>
+  <si>
+    <t>PLACA VALV. LH/RH SAUER SERIE 90-100</t>
+  </si>
+  <si>
+    <t>SA-632-1100C</t>
+  </si>
+  <si>
+    <t>BLOCK CILINDROS SAUER SERIE 90-75</t>
+  </si>
+  <si>
+    <t>SA-632-3201A</t>
+  </si>
+  <si>
+    <t>EJE TRANSMISION SAUER SERIE 90-75 - Z21M</t>
+  </si>
+  <si>
+    <t>SA-632-2100C</t>
+  </si>
+  <si>
+    <t>PISTON SAUER SERIE 90-75</t>
+  </si>
+  <si>
+    <t>SA-639-4701</t>
+  </si>
+  <si>
+    <t>PLACA FRICCION SAUER 90-75</t>
+  </si>
+  <si>
+    <t>SA-632-4501</t>
+  </si>
+  <si>
+    <t>PLACA VALV. LH/RH SAUER SERIE 90-75 - 518805</t>
+  </si>
+  <si>
+    <t>SA-WLA632-3306F</t>
+  </si>
+  <si>
+    <t>KIT SELLOS BOMBA SAUER SERIE 90-75</t>
+  </si>
+  <si>
+    <t>SA-323766</t>
+  </si>
+  <si>
+    <t>PLACA VALV. MOTOR SAUER SERIE 90-75</t>
+  </si>
+  <si>
+    <t>SA-634-7800A</t>
+  </si>
+  <si>
+    <t>BOMBA PRECARGA SAUER SERIE 90-130/180 26CC</t>
+  </si>
+  <si>
+    <t>SA-633-7800C</t>
+  </si>
+  <si>
+    <t>BOMBA PRECARGA SAUER SERIE 90-100 - 26cc -8200240</t>
+  </si>
+  <si>
+    <t>SA-632-7800A</t>
+  </si>
+  <si>
+    <t>BOMBA PRECARGA SAUER SERIE 90-75 - 14cc</t>
+  </si>
+  <si>
+    <t>SA-631-7800A</t>
+  </si>
+  <si>
+    <t>BOMBA PRECARGA SAUER 90-55 - 11cc - ALTURA</t>
+  </si>
+  <si>
+    <t>SA-640-5221</t>
+  </si>
+  <si>
+    <t>BASCULANTE SAUER SERIE 90-100-SIMPLE ROSCA - C/ SALTO- 82000232 - MV</t>
+  </si>
+  <si>
+    <t>SA-638-5221</t>
+  </si>
+  <si>
+    <t>BASCULANTE SAUER SERIE 90-55</t>
+  </si>
+  <si>
+    <t>SA-639-5221</t>
+  </si>
+  <si>
+    <t>BASCULANTE SAUER SERIE 90-75 - SIMPLE ROSCA</t>
+  </si>
+  <si>
+    <t>RD200EZ</t>
+  </si>
+  <si>
+    <t>ACOPLE TIPO CAMLOCK 2" EZ CUERPO X HEMBRA AISI 316 DIXON</t>
+  </si>
+  <si>
+    <t>SOL - 2489</t>
   </si>
 </sst>
 </file>
@@ -528,8 +696,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:R37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="65.21875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -713,7 +884,7 @@
         <v>21</v>
       </c>
       <c r="E4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F4" t="s">
         <v>21</v>
@@ -722,7 +893,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="I4" t="s">
         <v>22</v>
@@ -825,7 +996,7 @@
         <v>21</v>
       </c>
       <c r="E6">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F6" t="s">
         <v>21</v>
@@ -834,7 +1005,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I6" t="s">
         <v>22</v>
@@ -1144,6 +1315,1462 @@
         <v>21</v>
       </c>
       <c r="R11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>2</v>
+      </c>
+      <c r="I12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J12" t="s">
+        <v>47</v>
+      </c>
+      <c r="K12" t="s">
+        <v>33</v>
+      </c>
+      <c r="L12" t="s">
+        <v>25</v>
+      </c>
+      <c r="M12" t="s">
+        <v>54</v>
+      </c>
+      <c r="N12" t="s">
+        <v>21</v>
+      </c>
+      <c r="O12" t="s">
+        <v>21</v>
+      </c>
+      <c r="P12" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>21</v>
+      </c>
+      <c r="R12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13" t="s">
+        <v>22</v>
+      </c>
+      <c r="J13" t="s">
+        <v>47</v>
+      </c>
+      <c r="K13" t="s">
+        <v>33</v>
+      </c>
+      <c r="L13" t="s">
+        <v>25</v>
+      </c>
+      <c r="M13" t="s">
+        <v>54</v>
+      </c>
+      <c r="N13" t="s">
+        <v>21</v>
+      </c>
+      <c r="O13" t="s">
+        <v>21</v>
+      </c>
+      <c r="P13" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>21</v>
+      </c>
+      <c r="R13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14">
+        <v>9</v>
+      </c>
+      <c r="F14" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>9</v>
+      </c>
+      <c r="I14" t="s">
+        <v>22</v>
+      </c>
+      <c r="J14" t="s">
+        <v>47</v>
+      </c>
+      <c r="K14" t="s">
+        <v>33</v>
+      </c>
+      <c r="L14" t="s">
+        <v>25</v>
+      </c>
+      <c r="M14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N14" t="s">
+        <v>21</v>
+      </c>
+      <c r="O14" t="s">
+        <v>21</v>
+      </c>
+      <c r="P14" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>21</v>
+      </c>
+      <c r="R14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15">
+        <v>2</v>
+      </c>
+      <c r="F15" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>2</v>
+      </c>
+      <c r="I15" t="s">
+        <v>22</v>
+      </c>
+      <c r="J15" t="s">
+        <v>47</v>
+      </c>
+      <c r="K15" t="s">
+        <v>33</v>
+      </c>
+      <c r="L15" t="s">
+        <v>25</v>
+      </c>
+      <c r="M15" t="s">
+        <v>54</v>
+      </c>
+      <c r="N15" t="s">
+        <v>21</v>
+      </c>
+      <c r="O15" t="s">
+        <v>21</v>
+      </c>
+      <c r="P15" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>21</v>
+      </c>
+      <c r="R15" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16">
+        <v>2</v>
+      </c>
+      <c r="F16" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>2</v>
+      </c>
+      <c r="I16" t="s">
+        <v>22</v>
+      </c>
+      <c r="J16" t="s">
+        <v>47</v>
+      </c>
+      <c r="K16" t="s">
+        <v>33</v>
+      </c>
+      <c r="L16" t="s">
+        <v>25</v>
+      </c>
+      <c r="M16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N16" t="s">
+        <v>21</v>
+      </c>
+      <c r="O16" t="s">
+        <v>21</v>
+      </c>
+      <c r="P16" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>21</v>
+      </c>
+      <c r="R16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" t="s">
+        <v>53</v>
+      </c>
+      <c r="E17">
+        <v>2</v>
+      </c>
+      <c r="F17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>2</v>
+      </c>
+      <c r="I17" t="s">
+        <v>22</v>
+      </c>
+      <c r="J17" t="s">
+        <v>47</v>
+      </c>
+      <c r="K17" t="s">
+        <v>33</v>
+      </c>
+      <c r="L17" t="s">
+        <v>25</v>
+      </c>
+      <c r="M17" t="s">
+        <v>54</v>
+      </c>
+      <c r="N17" t="s">
+        <v>21</v>
+      </c>
+      <c r="O17" t="s">
+        <v>21</v>
+      </c>
+      <c r="P17" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>21</v>
+      </c>
+      <c r="R17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>65</v>
+      </c>
+      <c r="B18" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18" t="s">
+        <v>22</v>
+      </c>
+      <c r="J18" t="s">
+        <v>47</v>
+      </c>
+      <c r="K18" t="s">
+        <v>33</v>
+      </c>
+      <c r="L18" t="s">
+        <v>25</v>
+      </c>
+      <c r="M18" t="s">
+        <v>54</v>
+      </c>
+      <c r="N18" t="s">
+        <v>21</v>
+      </c>
+      <c r="O18" t="s">
+        <v>21</v>
+      </c>
+      <c r="P18" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>21</v>
+      </c>
+      <c r="R18" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" t="s">
+        <v>53</v>
+      </c>
+      <c r="E19">
+        <v>5</v>
+      </c>
+      <c r="F19" t="s">
+        <v>21</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>5</v>
+      </c>
+      <c r="I19" t="s">
+        <v>22</v>
+      </c>
+      <c r="J19" t="s">
+        <v>47</v>
+      </c>
+      <c r="K19" t="s">
+        <v>33</v>
+      </c>
+      <c r="L19" t="s">
+        <v>25</v>
+      </c>
+      <c r="M19" t="s">
+        <v>54</v>
+      </c>
+      <c r="N19" t="s">
+        <v>21</v>
+      </c>
+      <c r="O19" t="s">
+        <v>21</v>
+      </c>
+      <c r="P19" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>21</v>
+      </c>
+      <c r="R19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" t="s">
+        <v>70</v>
+      </c>
+      <c r="C20" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" t="s">
+        <v>53</v>
+      </c>
+      <c r="E20">
+        <v>18</v>
+      </c>
+      <c r="F20" t="s">
+        <v>21</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>18</v>
+      </c>
+      <c r="I20" t="s">
+        <v>22</v>
+      </c>
+      <c r="J20" t="s">
+        <v>47</v>
+      </c>
+      <c r="K20" t="s">
+        <v>33</v>
+      </c>
+      <c r="L20" t="s">
+        <v>25</v>
+      </c>
+      <c r="M20" t="s">
+        <v>54</v>
+      </c>
+      <c r="N20" t="s">
+        <v>21</v>
+      </c>
+      <c r="O20" t="s">
+        <v>21</v>
+      </c>
+      <c r="P20" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>21</v>
+      </c>
+      <c r="R20" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>71</v>
+      </c>
+      <c r="B21" t="s">
+        <v>72</v>
+      </c>
+      <c r="C21" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" t="s">
+        <v>53</v>
+      </c>
+      <c r="E21">
+        <v>2</v>
+      </c>
+      <c r="F21" t="s">
+        <v>21</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>2</v>
+      </c>
+      <c r="I21" t="s">
+        <v>22</v>
+      </c>
+      <c r="J21" t="s">
+        <v>47</v>
+      </c>
+      <c r="K21" t="s">
+        <v>33</v>
+      </c>
+      <c r="L21" t="s">
+        <v>25</v>
+      </c>
+      <c r="M21" t="s">
+        <v>54</v>
+      </c>
+      <c r="N21" t="s">
+        <v>21</v>
+      </c>
+      <c r="O21" t="s">
+        <v>21</v>
+      </c>
+      <c r="P21" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>21</v>
+      </c>
+      <c r="R21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" t="s">
+        <v>52</v>
+      </c>
+      <c r="D22" t="s">
+        <v>53</v>
+      </c>
+      <c r="E22">
+        <v>2</v>
+      </c>
+      <c r="F22" t="s">
+        <v>21</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>2</v>
+      </c>
+      <c r="I22" t="s">
+        <v>22</v>
+      </c>
+      <c r="J22" t="s">
+        <v>47</v>
+      </c>
+      <c r="K22" t="s">
+        <v>33</v>
+      </c>
+      <c r="L22" t="s">
+        <v>25</v>
+      </c>
+      <c r="M22" t="s">
+        <v>54</v>
+      </c>
+      <c r="N22" t="s">
+        <v>21</v>
+      </c>
+      <c r="O22" t="s">
+        <v>21</v>
+      </c>
+      <c r="P22" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>21</v>
+      </c>
+      <c r="R22" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>75</v>
+      </c>
+      <c r="B23" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" t="s">
+        <v>52</v>
+      </c>
+      <c r="D23" t="s">
+        <v>53</v>
+      </c>
+      <c r="E23">
+        <v>2</v>
+      </c>
+      <c r="F23" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>2</v>
+      </c>
+      <c r="I23" t="s">
+        <v>22</v>
+      </c>
+      <c r="J23" t="s">
+        <v>47</v>
+      </c>
+      <c r="K23" t="s">
+        <v>33</v>
+      </c>
+      <c r="L23" t="s">
+        <v>25</v>
+      </c>
+      <c r="M23" t="s">
+        <v>54</v>
+      </c>
+      <c r="N23" t="s">
+        <v>21</v>
+      </c>
+      <c r="O23" t="s">
+        <v>21</v>
+      </c>
+      <c r="P23" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>21</v>
+      </c>
+      <c r="R23" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>77</v>
+      </c>
+      <c r="B24" t="s">
+        <v>78</v>
+      </c>
+      <c r="C24" t="s">
+        <v>52</v>
+      </c>
+      <c r="D24" t="s">
+        <v>53</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24" t="s">
+        <v>21</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24" t="s">
+        <v>22</v>
+      </c>
+      <c r="J24" t="s">
+        <v>47</v>
+      </c>
+      <c r="K24" t="s">
+        <v>33</v>
+      </c>
+      <c r="L24" t="s">
+        <v>25</v>
+      </c>
+      <c r="M24" t="s">
+        <v>54</v>
+      </c>
+      <c r="N24" t="s">
+        <v>21</v>
+      </c>
+      <c r="O24" t="s">
+        <v>21</v>
+      </c>
+      <c r="P24" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>21</v>
+      </c>
+      <c r="R24" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>79</v>
+      </c>
+      <c r="B25" t="s">
+        <v>80</v>
+      </c>
+      <c r="C25" t="s">
+        <v>52</v>
+      </c>
+      <c r="D25" t="s">
+        <v>53</v>
+      </c>
+      <c r="E25">
+        <v>18</v>
+      </c>
+      <c r="F25" t="s">
+        <v>21</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>18</v>
+      </c>
+      <c r="I25" t="s">
+        <v>22</v>
+      </c>
+      <c r="J25" t="s">
+        <v>47</v>
+      </c>
+      <c r="K25" t="s">
+        <v>33</v>
+      </c>
+      <c r="L25" t="s">
+        <v>25</v>
+      </c>
+      <c r="M25" t="s">
+        <v>54</v>
+      </c>
+      <c r="N25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O25" t="s">
+        <v>21</v>
+      </c>
+      <c r="P25" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>21</v>
+      </c>
+      <c r="R25" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>81</v>
+      </c>
+      <c r="B26" t="s">
+        <v>82</v>
+      </c>
+      <c r="C26" t="s">
+        <v>52</v>
+      </c>
+      <c r="D26" t="s">
+        <v>53</v>
+      </c>
+      <c r="E26">
+        <v>2</v>
+      </c>
+      <c r="F26" t="s">
+        <v>21</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>2</v>
+      </c>
+      <c r="I26" t="s">
+        <v>22</v>
+      </c>
+      <c r="J26" t="s">
+        <v>47</v>
+      </c>
+      <c r="K26" t="s">
+        <v>33</v>
+      </c>
+      <c r="L26" t="s">
+        <v>25</v>
+      </c>
+      <c r="M26" t="s">
+        <v>54</v>
+      </c>
+      <c r="N26" t="s">
+        <v>21</v>
+      </c>
+      <c r="O26" t="s">
+        <v>21</v>
+      </c>
+      <c r="P26" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>21</v>
+      </c>
+      <c r="R26" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>83</v>
+      </c>
+      <c r="B27" t="s">
+        <v>84</v>
+      </c>
+      <c r="C27" t="s">
+        <v>52</v>
+      </c>
+      <c r="D27" t="s">
+        <v>53</v>
+      </c>
+      <c r="E27">
+        <v>2</v>
+      </c>
+      <c r="F27" t="s">
+        <v>21</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>2</v>
+      </c>
+      <c r="I27" t="s">
+        <v>22</v>
+      </c>
+      <c r="J27" t="s">
+        <v>47</v>
+      </c>
+      <c r="K27" t="s">
+        <v>33</v>
+      </c>
+      <c r="L27" t="s">
+        <v>25</v>
+      </c>
+      <c r="M27" t="s">
+        <v>54</v>
+      </c>
+      <c r="N27" t="s">
+        <v>21</v>
+      </c>
+      <c r="O27" t="s">
+        <v>21</v>
+      </c>
+      <c r="P27" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>21</v>
+      </c>
+      <c r="R27" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>85</v>
+      </c>
+      <c r="B28" t="s">
+        <v>86</v>
+      </c>
+      <c r="C28" t="s">
+        <v>52</v>
+      </c>
+      <c r="D28" t="s">
+        <v>53</v>
+      </c>
+      <c r="E28">
+        <v>6</v>
+      </c>
+      <c r="F28" t="s">
+        <v>21</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>6</v>
+      </c>
+      <c r="I28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J28" t="s">
+        <v>47</v>
+      </c>
+      <c r="K28" t="s">
+        <v>33</v>
+      </c>
+      <c r="L28" t="s">
+        <v>25</v>
+      </c>
+      <c r="M28" t="s">
+        <v>54</v>
+      </c>
+      <c r="N28" t="s">
+        <v>21</v>
+      </c>
+      <c r="O28" t="s">
+        <v>21</v>
+      </c>
+      <c r="P28" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>21</v>
+      </c>
+      <c r="R28" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>87</v>
+      </c>
+      <c r="B29" t="s">
+        <v>88</v>
+      </c>
+      <c r="C29" t="s">
+        <v>52</v>
+      </c>
+      <c r="D29" t="s">
+        <v>53</v>
+      </c>
+      <c r="E29">
+        <v>2</v>
+      </c>
+      <c r="F29" t="s">
+        <v>21</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>2</v>
+      </c>
+      <c r="I29" t="s">
+        <v>22</v>
+      </c>
+      <c r="J29" t="s">
+        <v>47</v>
+      </c>
+      <c r="K29" t="s">
+        <v>33</v>
+      </c>
+      <c r="L29" t="s">
+        <v>25</v>
+      </c>
+      <c r="M29" t="s">
+        <v>54</v>
+      </c>
+      <c r="N29" t="s">
+        <v>21</v>
+      </c>
+      <c r="O29" t="s">
+        <v>21</v>
+      </c>
+      <c r="P29" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>21</v>
+      </c>
+      <c r="R29" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>89</v>
+      </c>
+      <c r="B30" t="s">
+        <v>90</v>
+      </c>
+      <c r="C30" t="s">
+        <v>52</v>
+      </c>
+      <c r="D30" t="s">
+        <v>53</v>
+      </c>
+      <c r="E30">
+        <v>3</v>
+      </c>
+      <c r="F30" t="s">
+        <v>21</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>3</v>
+      </c>
+      <c r="I30" t="s">
+        <v>22</v>
+      </c>
+      <c r="J30" t="s">
+        <v>47</v>
+      </c>
+      <c r="K30" t="s">
+        <v>33</v>
+      </c>
+      <c r="L30" t="s">
+        <v>25</v>
+      </c>
+      <c r="M30" t="s">
+        <v>54</v>
+      </c>
+      <c r="N30" t="s">
+        <v>21</v>
+      </c>
+      <c r="O30" t="s">
+        <v>21</v>
+      </c>
+      <c r="P30" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>21</v>
+      </c>
+      <c r="R30" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>91</v>
+      </c>
+      <c r="B31" t="s">
+        <v>92</v>
+      </c>
+      <c r="C31" t="s">
+        <v>52</v>
+      </c>
+      <c r="D31" t="s">
+        <v>53</v>
+      </c>
+      <c r="E31">
+        <v>3</v>
+      </c>
+      <c r="F31" t="s">
+        <v>21</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>3</v>
+      </c>
+      <c r="I31" t="s">
+        <v>22</v>
+      </c>
+      <c r="J31" t="s">
+        <v>47</v>
+      </c>
+      <c r="K31" t="s">
+        <v>33</v>
+      </c>
+      <c r="L31" t="s">
+        <v>25</v>
+      </c>
+      <c r="M31" t="s">
+        <v>54</v>
+      </c>
+      <c r="N31" t="s">
+        <v>21</v>
+      </c>
+      <c r="O31" t="s">
+        <v>21</v>
+      </c>
+      <c r="P31" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>21</v>
+      </c>
+      <c r="R31" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>93</v>
+      </c>
+      <c r="B32" t="s">
+        <v>94</v>
+      </c>
+      <c r="C32" t="s">
+        <v>52</v>
+      </c>
+      <c r="D32" t="s">
+        <v>53</v>
+      </c>
+      <c r="E32">
+        <v>3</v>
+      </c>
+      <c r="F32" t="s">
+        <v>21</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>3</v>
+      </c>
+      <c r="I32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J32" t="s">
+        <v>47</v>
+      </c>
+      <c r="K32" t="s">
+        <v>33</v>
+      </c>
+      <c r="L32" t="s">
+        <v>25</v>
+      </c>
+      <c r="M32" t="s">
+        <v>54</v>
+      </c>
+      <c r="N32" t="s">
+        <v>21</v>
+      </c>
+      <c r="O32" t="s">
+        <v>21</v>
+      </c>
+      <c r="P32" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>21</v>
+      </c>
+      <c r="R32" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>95</v>
+      </c>
+      <c r="B33" t="s">
+        <v>96</v>
+      </c>
+      <c r="C33" t="s">
+        <v>52</v>
+      </c>
+      <c r="D33" t="s">
+        <v>53</v>
+      </c>
+      <c r="E33">
+        <v>3</v>
+      </c>
+      <c r="F33" t="s">
+        <v>21</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>3</v>
+      </c>
+      <c r="I33" t="s">
+        <v>22</v>
+      </c>
+      <c r="J33" t="s">
+        <v>47</v>
+      </c>
+      <c r="K33" t="s">
+        <v>33</v>
+      </c>
+      <c r="L33" t="s">
+        <v>25</v>
+      </c>
+      <c r="M33" t="s">
+        <v>54</v>
+      </c>
+      <c r="N33" t="s">
+        <v>21</v>
+      </c>
+      <c r="O33" t="s">
+        <v>21</v>
+      </c>
+      <c r="P33" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>21</v>
+      </c>
+      <c r="R33" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>97</v>
+      </c>
+      <c r="B34" t="s">
+        <v>98</v>
+      </c>
+      <c r="C34" t="s">
+        <v>52</v>
+      </c>
+      <c r="D34" t="s">
+        <v>53</v>
+      </c>
+      <c r="E34">
+        <v>2</v>
+      </c>
+      <c r="F34" t="s">
+        <v>21</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>2</v>
+      </c>
+      <c r="I34" t="s">
+        <v>22</v>
+      </c>
+      <c r="J34" t="s">
+        <v>47</v>
+      </c>
+      <c r="K34" t="s">
+        <v>33</v>
+      </c>
+      <c r="L34" t="s">
+        <v>25</v>
+      </c>
+      <c r="M34" t="s">
+        <v>54</v>
+      </c>
+      <c r="N34" t="s">
+        <v>21</v>
+      </c>
+      <c r="O34" t="s">
+        <v>21</v>
+      </c>
+      <c r="P34" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>21</v>
+      </c>
+      <c r="R34" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>99</v>
+      </c>
+      <c r="B35" t="s">
+        <v>100</v>
+      </c>
+      <c r="C35" t="s">
+        <v>52</v>
+      </c>
+      <c r="D35" t="s">
+        <v>53</v>
+      </c>
+      <c r="E35">
+        <v>2</v>
+      </c>
+      <c r="F35" t="s">
+        <v>21</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>2</v>
+      </c>
+      <c r="I35" t="s">
+        <v>22</v>
+      </c>
+      <c r="J35" t="s">
+        <v>47</v>
+      </c>
+      <c r="K35" t="s">
+        <v>33</v>
+      </c>
+      <c r="L35" t="s">
+        <v>25</v>
+      </c>
+      <c r="M35" t="s">
+        <v>54</v>
+      </c>
+      <c r="N35" t="s">
+        <v>21</v>
+      </c>
+      <c r="O35" t="s">
+        <v>21</v>
+      </c>
+      <c r="P35" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>21</v>
+      </c>
+      <c r="R35" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>101</v>
+      </c>
+      <c r="B36" t="s">
+        <v>102</v>
+      </c>
+      <c r="C36" t="s">
+        <v>52</v>
+      </c>
+      <c r="D36" t="s">
+        <v>53</v>
+      </c>
+      <c r="E36">
+        <v>2</v>
+      </c>
+      <c r="F36" t="s">
+        <v>21</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>2</v>
+      </c>
+      <c r="I36" t="s">
+        <v>22</v>
+      </c>
+      <c r="J36" t="s">
+        <v>47</v>
+      </c>
+      <c r="K36" t="s">
+        <v>33</v>
+      </c>
+      <c r="L36" t="s">
+        <v>25</v>
+      </c>
+      <c r="M36" t="s">
+        <v>54</v>
+      </c>
+      <c r="N36" t="s">
+        <v>21</v>
+      </c>
+      <c r="O36" t="s">
+        <v>21</v>
+      </c>
+      <c r="P36" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>21</v>
+      </c>
+      <c r="R36" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>103</v>
+      </c>
+      <c r="B37" t="s">
+        <v>104</v>
+      </c>
+      <c r="C37" t="s">
+        <v>105</v>
+      </c>
+      <c r="D37" t="s">
+        <v>21</v>
+      </c>
+      <c r="E37">
+        <v>10</v>
+      </c>
+      <c r="F37" t="s">
+        <v>21</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>10</v>
+      </c>
+      <c r="I37" t="s">
+        <v>22</v>
+      </c>
+      <c r="J37" t="s">
+        <v>47</v>
+      </c>
+      <c r="K37" t="s">
+        <v>24</v>
+      </c>
+      <c r="L37" t="s">
+        <v>25</v>
+      </c>
+      <c r="M37" t="s">
+        <v>26</v>
+      </c>
+      <c r="N37" t="s">
+        <v>21</v>
+      </c>
+      <c r="O37" t="s">
+        <v>21</v>
+      </c>
+      <c r="P37" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>21</v>
+      </c>
+      <c r="R37" t="s">
         <v>27</v>
       </c>
     </row>

--- a/pc.xlsx
+++ b/pc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Claude\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DEF8ED45-00AF-4054-A30D-B2BE2AE52300}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FBE9DE1B-653D-40F9-9742-3AF03751960C}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1083" uniqueCount="177">
   <si>
     <t>Cod. producto</t>
   </si>
@@ -224,6 +224,84 @@
     <t>BLOCK CILINDROS SAUER SERIE 90-100</t>
   </si>
   <si>
+    <t>SA-639-5221</t>
+  </si>
+  <si>
+    <t>BASCULANTE SAUER SERIE 90-75 - SIMPLE ROSCA</t>
+  </si>
+  <si>
+    <t>SA-634-7800A</t>
+  </si>
+  <si>
+    <t>BOMBA PRECARGA SAUER SERIE 90-130/180 26CC</t>
+  </si>
+  <si>
+    <t>SA-633-7800C</t>
+  </si>
+  <si>
+    <t>BOMBA PRECARGA SAUER SERIE 90-100 - 26cc -8200240</t>
+  </si>
+  <si>
+    <t>SA-632-7800A</t>
+  </si>
+  <si>
+    <t>BOMBA PRECARGA SAUER SERIE 90-75 - 14cc</t>
+  </si>
+  <si>
+    <t>SA-631-7800A</t>
+  </si>
+  <si>
+    <t>BOMBA PRECARGA SAUER 90-55 - 11cc - ALTURA</t>
+  </si>
+  <si>
+    <t>SA-640-5221</t>
+  </si>
+  <si>
+    <t>BASCULANTE SAUER SERIE 90-100-SIMPLE ROSCA - C/ SALTO- 82000232 - MV</t>
+  </si>
+  <si>
+    <t>SA-638-5221</t>
+  </si>
+  <si>
+    <t>BASCULANTE SAUER SERIE 90-55</t>
+  </si>
+  <si>
+    <t>SA-632-3201A</t>
+  </si>
+  <si>
+    <t>EJE TRANSMISION SAUER SERIE 90-75 - Z21M</t>
+  </si>
+  <si>
+    <t>SA-632-2100C</t>
+  </si>
+  <si>
+    <t>PISTON SAUER SERIE 90-75</t>
+  </si>
+  <si>
+    <t>SA-639-4701</t>
+  </si>
+  <si>
+    <t>PLACA FRICCION SAUER 90-75</t>
+  </si>
+  <si>
+    <t>SA-632-4501</t>
+  </si>
+  <si>
+    <t>PLACA VALV. LH/RH SAUER SERIE 90-75 - 518805</t>
+  </si>
+  <si>
+    <t>SA-WLA632-3306F</t>
+  </si>
+  <si>
+    <t>KIT SELLOS BOMBA SAUER SERIE 90-75</t>
+  </si>
+  <si>
+    <t>SA-323766</t>
+  </si>
+  <si>
+    <t>PLACA VALV. MOTOR SAUER SERIE 90-75</t>
+  </si>
+  <si>
     <t>SA-640-3201A</t>
   </si>
   <si>
@@ -260,84 +338,6 @@
     <t>BLOCK CILINDROS SAUER SERIE 90-75</t>
   </si>
   <si>
-    <t>SA-632-3201A</t>
-  </si>
-  <si>
-    <t>EJE TRANSMISION SAUER SERIE 90-75 - Z21M</t>
-  </si>
-  <si>
-    <t>SA-632-2100C</t>
-  </si>
-  <si>
-    <t>PISTON SAUER SERIE 90-75</t>
-  </si>
-  <si>
-    <t>SA-639-4701</t>
-  </si>
-  <si>
-    <t>PLACA FRICCION SAUER 90-75</t>
-  </si>
-  <si>
-    <t>SA-632-4501</t>
-  </si>
-  <si>
-    <t>PLACA VALV. LH/RH SAUER SERIE 90-75 - 518805</t>
-  </si>
-  <si>
-    <t>SA-WLA632-3306F</t>
-  </si>
-  <si>
-    <t>KIT SELLOS BOMBA SAUER SERIE 90-75</t>
-  </si>
-  <si>
-    <t>SA-323766</t>
-  </si>
-  <si>
-    <t>PLACA VALV. MOTOR SAUER SERIE 90-75</t>
-  </si>
-  <si>
-    <t>SA-634-7800A</t>
-  </si>
-  <si>
-    <t>BOMBA PRECARGA SAUER SERIE 90-130/180 26CC</t>
-  </si>
-  <si>
-    <t>SA-633-7800C</t>
-  </si>
-  <si>
-    <t>BOMBA PRECARGA SAUER SERIE 90-100 - 26cc -8200240</t>
-  </si>
-  <si>
-    <t>SA-632-7800A</t>
-  </si>
-  <si>
-    <t>BOMBA PRECARGA SAUER SERIE 90-75 - 14cc</t>
-  </si>
-  <si>
-    <t>SA-631-7800A</t>
-  </si>
-  <si>
-    <t>BOMBA PRECARGA SAUER 90-55 - 11cc - ALTURA</t>
-  </si>
-  <si>
-    <t>SA-640-5221</t>
-  </si>
-  <si>
-    <t>BASCULANTE SAUER SERIE 90-100-SIMPLE ROSCA - C/ SALTO- 82000232 - MV</t>
-  </si>
-  <si>
-    <t>SA-638-5221</t>
-  </si>
-  <si>
-    <t>BASCULANTE SAUER SERIE 90-55</t>
-  </si>
-  <si>
-    <t>SA-639-5221</t>
-  </si>
-  <si>
-    <t>BASCULANTE SAUER SERIE 90-75 - SIMPLE ROSCA</t>
-  </si>
-  <si>
     <t>RD200EZ</t>
   </si>
   <si>
@@ -345,6 +345,219 @@
   </si>
   <si>
     <t>SOL - 2489</t>
+  </si>
+  <si>
+    <t>AR02G</t>
+  </si>
+  <si>
+    <t>ALEMITE RECTO DE 1/8" GAS</t>
+  </si>
+  <si>
+    <t>SOL - 2493</t>
+  </si>
+  <si>
+    <t>BUJE RED-2"x1.1/2" S3000</t>
+  </si>
+  <si>
+    <t>BUJE DE RED 2" NPT x 1.1/2" NPT SERIE 3000</t>
+  </si>
+  <si>
+    <t>CUPLA-1/2" S3000</t>
+  </si>
+  <si>
+    <t>CUPLA 1/2" NPT SERIE 3000</t>
+  </si>
+  <si>
+    <t>2500-3500-375B</t>
+  </si>
+  <si>
+    <t>POLYPAK 88.90 x 101.60 x 9.52</t>
+  </si>
+  <si>
+    <t>313-1135-194</t>
+  </si>
+  <si>
+    <t>EJE POSTIZO P50 Z14</t>
+  </si>
+  <si>
+    <t>313-5037-202</t>
+  </si>
+  <si>
+    <t>TROMPA P50 DE 5" X 4</t>
+  </si>
+  <si>
+    <t>391-0381-905</t>
+  </si>
+  <si>
+    <t>TORRINGTON P50</t>
+  </si>
+  <si>
+    <t>391-2883-119P</t>
+  </si>
+  <si>
+    <t>RETEN M-30 P/EJE ENTERIZO</t>
+  </si>
+  <si>
+    <t>46511385</t>
+  </si>
+  <si>
+    <t>MANGUERA GATES SAE100 R12 3/4"  12EFG4K X LL</t>
+  </si>
+  <si>
+    <t>TAPON-1" S3000</t>
+  </si>
+  <si>
+    <t>TAPON MACHO 1" NPT SERIE 3000</t>
+  </si>
+  <si>
+    <t>TAPON-1/4" S3000</t>
+  </si>
+  <si>
+    <t>TAPON MACHO 1/4" NPT SERIE 3000</t>
+  </si>
+  <si>
+    <t>TAPON-3/4" S3000</t>
+  </si>
+  <si>
+    <t>TAPON MACHO 3/4" NPT SERIE 3000</t>
+  </si>
+  <si>
+    <t>TAPON-3/8" S3000</t>
+  </si>
+  <si>
+    <t>TAPON MACHO 3/8" NPT SERIE 3000</t>
+  </si>
+  <si>
+    <t>TEE-1/2" S3000</t>
+  </si>
+  <si>
+    <t>TEE H x H x H 1/2" NPT SERIE 3000</t>
+  </si>
+  <si>
+    <t>PFQ723ZRR1R11</t>
+  </si>
+  <si>
+    <t>MANOMETRO SERIE PFQ-ZR 4", 0/15.000 PSI - 0/1.000 bar, 1/2" NPT INFERIOR</t>
+  </si>
+  <si>
+    <t>PFQ905R3R1</t>
+  </si>
+  <si>
+    <t>MANOMETRO 2,5" ROSCA POSTERIOR 1/4 NPT 0-10 BAR C/GLICERINA</t>
+  </si>
+  <si>
+    <t>PFQ908R3R1</t>
+  </si>
+  <si>
+    <t>MANOMETRO 2,5" ROSCA POSTERIOR 1/4 NPT 0-40 BAR C/GLICERINA</t>
+  </si>
+  <si>
+    <t>PFQ918R3R1</t>
+  </si>
+  <si>
+    <t>MANOMETRO 2,5" ROSCA POSTERIOR 1/4 NPT 0-600 BAR C/GLICERINA</t>
+  </si>
+  <si>
+    <t>SA-519021</t>
+  </si>
+  <si>
+    <t>RETEN EJE MOTOR 51V060 / EJE BOMBA S90/100 A 250</t>
+  </si>
+  <si>
+    <t>TAPA-3/4" S3000</t>
+  </si>
+  <si>
+    <t>TAPA HEMBRA 3/4" NPT SERIE 3000</t>
+  </si>
+  <si>
+    <t>FB-2</t>
+  </si>
+  <si>
+    <t>BOCA DE CARGA GRANDE BRIDADA 40 MIC.</t>
+  </si>
+  <si>
+    <t>FILT-D-AB-2</t>
+  </si>
+  <si>
+    <t>FILTRO AIRE RESP DESECANTE</t>
+  </si>
+  <si>
+    <t>FT 221/1-14</t>
+  </si>
+  <si>
+    <t>VALVULA ESFERICA DE 2 VIAS, ALTA PRESION 1/4"</t>
+  </si>
+  <si>
+    <t>FT 257/6-14</t>
+  </si>
+  <si>
+    <t>VALVULA DE RETENCION EN LINEA RECTA 1/4" 30LPM - 500 BAR</t>
+  </si>
+  <si>
+    <t>FTX-06P</t>
+  </si>
+  <si>
+    <t>ADAP RECTO 9/16 UNF JIC X 1/4 NPT</t>
+  </si>
+  <si>
+    <t>MA-310</t>
+  </si>
+  <si>
+    <t>PISTOLA CUENTA LTS DIGITAL VULCANO</t>
+  </si>
+  <si>
+    <t>CUPLA-1/4" S3000</t>
+  </si>
+  <si>
+    <t>CUPLA 1/4" NPT SERIE 3000</t>
+  </si>
+  <si>
+    <t>ENTRER-1" S3000</t>
+  </si>
+  <si>
+    <t>ENTRERROSCA 1" NPT SERIE 3000</t>
+  </si>
+  <si>
+    <t>ENTRER-1.1/4" S3000</t>
+  </si>
+  <si>
+    <t>ENTRERROSCA 1.1/4" NPT SERIE 3000</t>
+  </si>
+  <si>
+    <t>ENTRER-1/2" S3000</t>
+  </si>
+  <si>
+    <t>ENTRERROSCA 1/2" NPT SERIE 3000</t>
+  </si>
+  <si>
+    <t>ENTRER-1/4" S3000</t>
+  </si>
+  <si>
+    <t>ENTRERROSCA 1/4" NPT SERIE 3000</t>
+  </si>
+  <si>
+    <t>ENTRER-3/4" S3000</t>
+  </si>
+  <si>
+    <t>ENTRERROSCA 3/4" NPT SERIE 3000</t>
+  </si>
+  <si>
+    <t>AC02G-90</t>
+  </si>
+  <si>
+    <t>ALEMITE GAS 90° 1/8"</t>
+  </si>
+  <si>
+    <t>AFS-102N</t>
+  </si>
+  <si>
+    <t>BRIDA SAE 1" PARA 3000 PSI</t>
+  </si>
+  <si>
+    <t>AFS-604</t>
+  </si>
+  <si>
+    <t>JGO DE1/2 BRIDAS SAE 1.1/4" NPT P/6000 PSI</t>
   </si>
 </sst>
 </file>
@@ -696,11 +909,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R37"/>
+  <dimension ref="A1:R72"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="65.21875" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -1668,7 +1878,7 @@
         <v>53</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" t="s">
         <v>21</v>
@@ -1677,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="H18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18" t="s">
         <v>22</v>
@@ -1724,7 +1934,7 @@
         <v>53</v>
       </c>
       <c r="E19">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F19" t="s">
         <v>21</v>
@@ -1733,7 +1943,7 @@
         <v>0</v>
       </c>
       <c r="H19">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I19" t="s">
         <v>22</v>
@@ -1780,7 +1990,7 @@
         <v>53</v>
       </c>
       <c r="E20">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="F20" t="s">
         <v>21</v>
@@ -1789,7 +1999,7 @@
         <v>0</v>
       </c>
       <c r="H20">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="I20" t="s">
         <v>22</v>
@@ -1836,7 +2046,7 @@
         <v>53</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F21" t="s">
         <v>21</v>
@@ -1845,7 +2055,7 @@
         <v>0</v>
       </c>
       <c r="H21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I21" t="s">
         <v>22</v>
@@ -1892,7 +2102,7 @@
         <v>53</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F22" t="s">
         <v>21</v>
@@ -1901,7 +2111,7 @@
         <v>0</v>
       </c>
       <c r="H22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I22" t="s">
         <v>22</v>
@@ -2004,7 +2214,7 @@
         <v>53</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24" t="s">
         <v>21</v>
@@ -2013,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="H24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I24" t="s">
         <v>22</v>
@@ -2060,7 +2270,7 @@
         <v>53</v>
       </c>
       <c r="E25">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="F25" t="s">
         <v>21</v>
@@ -2069,7 +2279,7 @@
         <v>0</v>
       </c>
       <c r="H25">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="I25" t="s">
         <v>22</v>
@@ -2116,7 +2326,7 @@
         <v>53</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="F26" t="s">
         <v>21</v>
@@ -2125,7 +2335,7 @@
         <v>0</v>
       </c>
       <c r="H26">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="I26" t="s">
         <v>22</v>
@@ -2228,7 +2438,7 @@
         <v>53</v>
       </c>
       <c r="E28">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F28" t="s">
         <v>21</v>
@@ -2237,7 +2447,7 @@
         <v>0</v>
       </c>
       <c r="H28">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I28" t="s">
         <v>22</v>
@@ -2284,7 +2494,7 @@
         <v>53</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F29" t="s">
         <v>21</v>
@@ -2293,7 +2503,7 @@
         <v>0</v>
       </c>
       <c r="H29">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I29" t="s">
         <v>22</v>
@@ -2340,7 +2550,7 @@
         <v>53</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F30" t="s">
         <v>21</v>
@@ -2349,7 +2559,7 @@
         <v>0</v>
       </c>
       <c r="H30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I30" t="s">
         <v>22</v>
@@ -2396,7 +2606,7 @@
         <v>53</v>
       </c>
       <c r="E31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F31" t="s">
         <v>21</v>
@@ -2405,7 +2615,7 @@
         <v>0</v>
       </c>
       <c r="H31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I31" t="s">
         <v>22</v>
@@ -2452,7 +2662,7 @@
         <v>53</v>
       </c>
       <c r="E32">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F32" t="s">
         <v>21</v>
@@ -2461,7 +2671,7 @@
         <v>0</v>
       </c>
       <c r="H32">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I32" t="s">
         <v>22</v>
@@ -2508,7 +2718,7 @@
         <v>53</v>
       </c>
       <c r="E33">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="F33" t="s">
         <v>21</v>
@@ -2517,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="H33">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="I33" t="s">
         <v>22</v>
@@ -2771,6 +2981,1966 @@
         <v>21</v>
       </c>
       <c r="R37" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>106</v>
+      </c>
+      <c r="B38" t="s">
+        <v>107</v>
+      </c>
+      <c r="C38" t="s">
+        <v>108</v>
+      </c>
+      <c r="D38" t="s">
+        <v>21</v>
+      </c>
+      <c r="E38">
+        <v>300</v>
+      </c>
+      <c r="F38" t="s">
+        <v>21</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>300</v>
+      </c>
+      <c r="I38" t="s">
+        <v>22</v>
+      </c>
+      <c r="J38" t="s">
+        <v>47</v>
+      </c>
+      <c r="K38" t="s">
+        <v>24</v>
+      </c>
+      <c r="L38" t="s">
+        <v>25</v>
+      </c>
+      <c r="M38" t="s">
+        <v>26</v>
+      </c>
+      <c r="N38" t="s">
+        <v>21</v>
+      </c>
+      <c r="O38" t="s">
+        <v>21</v>
+      </c>
+      <c r="P38" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>21</v>
+      </c>
+      <c r="R38" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>109</v>
+      </c>
+      <c r="B39" t="s">
+        <v>110</v>
+      </c>
+      <c r="C39" t="s">
+        <v>108</v>
+      </c>
+      <c r="D39" t="s">
+        <v>21</v>
+      </c>
+      <c r="E39">
+        <v>10</v>
+      </c>
+      <c r="F39" t="s">
+        <v>21</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>10</v>
+      </c>
+      <c r="I39" t="s">
+        <v>22</v>
+      </c>
+      <c r="J39" t="s">
+        <v>47</v>
+      </c>
+      <c r="K39" t="s">
+        <v>24</v>
+      </c>
+      <c r="L39" t="s">
+        <v>25</v>
+      </c>
+      <c r="M39" t="s">
+        <v>26</v>
+      </c>
+      <c r="N39" t="s">
+        <v>21</v>
+      </c>
+      <c r="O39" t="s">
+        <v>21</v>
+      </c>
+      <c r="P39" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>21</v>
+      </c>
+      <c r="R39" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>111</v>
+      </c>
+      <c r="B40" t="s">
+        <v>112</v>
+      </c>
+      <c r="C40" t="s">
+        <v>108</v>
+      </c>
+      <c r="D40" t="s">
+        <v>21</v>
+      </c>
+      <c r="E40">
+        <v>150</v>
+      </c>
+      <c r="F40" t="s">
+        <v>21</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>150</v>
+      </c>
+      <c r="I40" t="s">
+        <v>22</v>
+      </c>
+      <c r="J40" t="s">
+        <v>47</v>
+      </c>
+      <c r="K40" t="s">
+        <v>24</v>
+      </c>
+      <c r="L40" t="s">
+        <v>25</v>
+      </c>
+      <c r="M40" t="s">
+        <v>26</v>
+      </c>
+      <c r="N40" t="s">
+        <v>21</v>
+      </c>
+      <c r="O40" t="s">
+        <v>21</v>
+      </c>
+      <c r="P40" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>21</v>
+      </c>
+      <c r="R40" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>113</v>
+      </c>
+      <c r="B41" t="s">
+        <v>114</v>
+      </c>
+      <c r="C41" t="s">
+        <v>108</v>
+      </c>
+      <c r="D41" t="s">
+        <v>21</v>
+      </c>
+      <c r="E41">
+        <v>10</v>
+      </c>
+      <c r="F41" t="s">
+        <v>21</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>10</v>
+      </c>
+      <c r="I41" t="s">
+        <v>22</v>
+      </c>
+      <c r="J41" t="s">
+        <v>47</v>
+      </c>
+      <c r="K41" t="s">
+        <v>24</v>
+      </c>
+      <c r="L41" t="s">
+        <v>25</v>
+      </c>
+      <c r="M41" t="s">
+        <v>26</v>
+      </c>
+      <c r="N41" t="s">
+        <v>21</v>
+      </c>
+      <c r="O41" t="s">
+        <v>21</v>
+      </c>
+      <c r="P41" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>21</v>
+      </c>
+      <c r="R41" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>115</v>
+      </c>
+      <c r="B42" t="s">
+        <v>116</v>
+      </c>
+      <c r="C42" t="s">
+        <v>108</v>
+      </c>
+      <c r="D42" t="s">
+        <v>21</v>
+      </c>
+      <c r="E42">
+        <v>20</v>
+      </c>
+      <c r="F42" t="s">
+        <v>21</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>20</v>
+      </c>
+      <c r="I42" t="s">
+        <v>22</v>
+      </c>
+      <c r="J42" t="s">
+        <v>47</v>
+      </c>
+      <c r="K42" t="s">
+        <v>24</v>
+      </c>
+      <c r="L42" t="s">
+        <v>25</v>
+      </c>
+      <c r="M42" t="s">
+        <v>26</v>
+      </c>
+      <c r="N42" t="s">
+        <v>21</v>
+      </c>
+      <c r="O42" t="s">
+        <v>21</v>
+      </c>
+      <c r="P42" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>21</v>
+      </c>
+      <c r="R42" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>117</v>
+      </c>
+      <c r="B43" t="s">
+        <v>118</v>
+      </c>
+      <c r="C43" t="s">
+        <v>108</v>
+      </c>
+      <c r="D43" t="s">
+        <v>21</v>
+      </c>
+      <c r="E43">
+        <v>5</v>
+      </c>
+      <c r="F43" t="s">
+        <v>21</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>5</v>
+      </c>
+      <c r="I43" t="s">
+        <v>22</v>
+      </c>
+      <c r="J43" t="s">
+        <v>47</v>
+      </c>
+      <c r="K43" t="s">
+        <v>24</v>
+      </c>
+      <c r="L43" t="s">
+        <v>25</v>
+      </c>
+      <c r="M43" t="s">
+        <v>26</v>
+      </c>
+      <c r="N43" t="s">
+        <v>21</v>
+      </c>
+      <c r="O43" t="s">
+        <v>21</v>
+      </c>
+      <c r="P43" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>21</v>
+      </c>
+      <c r="R43" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>119</v>
+      </c>
+      <c r="B44" t="s">
+        <v>120</v>
+      </c>
+      <c r="C44" t="s">
+        <v>108</v>
+      </c>
+      <c r="D44" t="s">
+        <v>21</v>
+      </c>
+      <c r="E44">
+        <v>30</v>
+      </c>
+      <c r="F44" t="s">
+        <v>21</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>30</v>
+      </c>
+      <c r="I44" t="s">
+        <v>22</v>
+      </c>
+      <c r="J44" t="s">
+        <v>47</v>
+      </c>
+      <c r="K44" t="s">
+        <v>24</v>
+      </c>
+      <c r="L44" t="s">
+        <v>25</v>
+      </c>
+      <c r="M44" t="s">
+        <v>26</v>
+      </c>
+      <c r="N44" t="s">
+        <v>21</v>
+      </c>
+      <c r="O44" t="s">
+        <v>21</v>
+      </c>
+      <c r="P44" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>21</v>
+      </c>
+      <c r="R44" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>121</v>
+      </c>
+      <c r="B45" t="s">
+        <v>122</v>
+      </c>
+      <c r="C45" t="s">
+        <v>108</v>
+      </c>
+      <c r="D45" t="s">
+        <v>21</v>
+      </c>
+      <c r="E45">
+        <v>20</v>
+      </c>
+      <c r="F45" t="s">
+        <v>21</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>20</v>
+      </c>
+      <c r="I45" t="s">
+        <v>22</v>
+      </c>
+      <c r="J45" t="s">
+        <v>47</v>
+      </c>
+      <c r="K45" t="s">
+        <v>24</v>
+      </c>
+      <c r="L45" t="s">
+        <v>25</v>
+      </c>
+      <c r="M45" t="s">
+        <v>26</v>
+      </c>
+      <c r="N45" t="s">
+        <v>21</v>
+      </c>
+      <c r="O45" t="s">
+        <v>21</v>
+      </c>
+      <c r="P45" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>21</v>
+      </c>
+      <c r="R45" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>123</v>
+      </c>
+      <c r="B46" t="s">
+        <v>124</v>
+      </c>
+      <c r="C46" t="s">
+        <v>108</v>
+      </c>
+      <c r="D46" t="s">
+        <v>21</v>
+      </c>
+      <c r="E46">
+        <v>1200</v>
+      </c>
+      <c r="F46" t="s">
+        <v>21</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>1200</v>
+      </c>
+      <c r="I46" t="s">
+        <v>22</v>
+      </c>
+      <c r="J46" t="s">
+        <v>47</v>
+      </c>
+      <c r="K46" t="s">
+        <v>24</v>
+      </c>
+      <c r="L46" t="s">
+        <v>25</v>
+      </c>
+      <c r="M46" t="s">
+        <v>26</v>
+      </c>
+      <c r="N46" t="s">
+        <v>21</v>
+      </c>
+      <c r="O46" t="s">
+        <v>21</v>
+      </c>
+      <c r="P46" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>21</v>
+      </c>
+      <c r="R46" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>125</v>
+      </c>
+      <c r="B47" t="s">
+        <v>126</v>
+      </c>
+      <c r="C47" t="s">
+        <v>108</v>
+      </c>
+      <c r="D47" t="s">
+        <v>21</v>
+      </c>
+      <c r="E47">
+        <v>40</v>
+      </c>
+      <c r="F47" t="s">
+        <v>21</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>40</v>
+      </c>
+      <c r="I47" t="s">
+        <v>22</v>
+      </c>
+      <c r="J47" t="s">
+        <v>47</v>
+      </c>
+      <c r="K47" t="s">
+        <v>24</v>
+      </c>
+      <c r="L47" t="s">
+        <v>25</v>
+      </c>
+      <c r="M47" t="s">
+        <v>26</v>
+      </c>
+      <c r="N47" t="s">
+        <v>21</v>
+      </c>
+      <c r="O47" t="s">
+        <v>21</v>
+      </c>
+      <c r="P47" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>21</v>
+      </c>
+      <c r="R47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>127</v>
+      </c>
+      <c r="B48" t="s">
+        <v>128</v>
+      </c>
+      <c r="C48" t="s">
+        <v>108</v>
+      </c>
+      <c r="D48" t="s">
+        <v>21</v>
+      </c>
+      <c r="E48">
+        <v>50</v>
+      </c>
+      <c r="F48" t="s">
+        <v>21</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>50</v>
+      </c>
+      <c r="I48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J48" t="s">
+        <v>47</v>
+      </c>
+      <c r="K48" t="s">
+        <v>24</v>
+      </c>
+      <c r="L48" t="s">
+        <v>25</v>
+      </c>
+      <c r="M48" t="s">
+        <v>26</v>
+      </c>
+      <c r="N48" t="s">
+        <v>21</v>
+      </c>
+      <c r="O48" t="s">
+        <v>21</v>
+      </c>
+      <c r="P48" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>21</v>
+      </c>
+      <c r="R48" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>129</v>
+      </c>
+      <c r="B49" t="s">
+        <v>130</v>
+      </c>
+      <c r="C49" t="s">
+        <v>108</v>
+      </c>
+      <c r="D49" t="s">
+        <v>21</v>
+      </c>
+      <c r="E49">
+        <v>50</v>
+      </c>
+      <c r="F49" t="s">
+        <v>21</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>50</v>
+      </c>
+      <c r="I49" t="s">
+        <v>22</v>
+      </c>
+      <c r="J49" t="s">
+        <v>47</v>
+      </c>
+      <c r="K49" t="s">
+        <v>24</v>
+      </c>
+      <c r="L49" t="s">
+        <v>25</v>
+      </c>
+      <c r="M49" t="s">
+        <v>26</v>
+      </c>
+      <c r="N49" t="s">
+        <v>21</v>
+      </c>
+      <c r="O49" t="s">
+        <v>21</v>
+      </c>
+      <c r="P49" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>21</v>
+      </c>
+      <c r="R49" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>131</v>
+      </c>
+      <c r="B50" t="s">
+        <v>132</v>
+      </c>
+      <c r="C50" t="s">
+        <v>108</v>
+      </c>
+      <c r="D50" t="s">
+        <v>21</v>
+      </c>
+      <c r="E50">
+        <v>50</v>
+      </c>
+      <c r="F50" t="s">
+        <v>21</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>50</v>
+      </c>
+      <c r="I50" t="s">
+        <v>22</v>
+      </c>
+      <c r="J50" t="s">
+        <v>47</v>
+      </c>
+      <c r="K50" t="s">
+        <v>24</v>
+      </c>
+      <c r="L50" t="s">
+        <v>25</v>
+      </c>
+      <c r="M50" t="s">
+        <v>26</v>
+      </c>
+      <c r="N50" t="s">
+        <v>21</v>
+      </c>
+      <c r="O50" t="s">
+        <v>21</v>
+      </c>
+      <c r="P50" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>21</v>
+      </c>
+      <c r="R50" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>133</v>
+      </c>
+      <c r="B51" t="s">
+        <v>134</v>
+      </c>
+      <c r="C51" t="s">
+        <v>108</v>
+      </c>
+      <c r="D51" t="s">
+        <v>21</v>
+      </c>
+      <c r="E51">
+        <v>30</v>
+      </c>
+      <c r="F51" t="s">
+        <v>21</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>30</v>
+      </c>
+      <c r="I51" t="s">
+        <v>22</v>
+      </c>
+      <c r="J51" t="s">
+        <v>47</v>
+      </c>
+      <c r="K51" t="s">
+        <v>24</v>
+      </c>
+      <c r="L51" t="s">
+        <v>25</v>
+      </c>
+      <c r="M51" t="s">
+        <v>26</v>
+      </c>
+      <c r="N51" t="s">
+        <v>21</v>
+      </c>
+      <c r="O51" t="s">
+        <v>21</v>
+      </c>
+      <c r="P51" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>21</v>
+      </c>
+      <c r="R51" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>135</v>
+      </c>
+      <c r="B52" t="s">
+        <v>136</v>
+      </c>
+      <c r="C52" t="s">
+        <v>108</v>
+      </c>
+      <c r="D52" t="s">
+        <v>21</v>
+      </c>
+      <c r="E52">
+        <v>2</v>
+      </c>
+      <c r="F52" t="s">
+        <v>21</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>2</v>
+      </c>
+      <c r="I52" t="s">
+        <v>22</v>
+      </c>
+      <c r="J52" t="s">
+        <v>47</v>
+      </c>
+      <c r="K52" t="s">
+        <v>24</v>
+      </c>
+      <c r="L52" t="s">
+        <v>25</v>
+      </c>
+      <c r="M52" t="s">
+        <v>26</v>
+      </c>
+      <c r="N52" t="s">
+        <v>21</v>
+      </c>
+      <c r="O52" t="s">
+        <v>21</v>
+      </c>
+      <c r="P52" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>21</v>
+      </c>
+      <c r="R52" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>137</v>
+      </c>
+      <c r="B53" t="s">
+        <v>138</v>
+      </c>
+      <c r="C53" t="s">
+        <v>108</v>
+      </c>
+      <c r="D53" t="s">
+        <v>21</v>
+      </c>
+      <c r="E53">
+        <v>10</v>
+      </c>
+      <c r="F53" t="s">
+        <v>21</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>10</v>
+      </c>
+      <c r="I53" t="s">
+        <v>22</v>
+      </c>
+      <c r="J53" t="s">
+        <v>47</v>
+      </c>
+      <c r="K53" t="s">
+        <v>24</v>
+      </c>
+      <c r="L53" t="s">
+        <v>25</v>
+      </c>
+      <c r="M53" t="s">
+        <v>26</v>
+      </c>
+      <c r="N53" t="s">
+        <v>21</v>
+      </c>
+      <c r="O53" t="s">
+        <v>21</v>
+      </c>
+      <c r="P53" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>21</v>
+      </c>
+      <c r="R53" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>139</v>
+      </c>
+      <c r="B54" t="s">
+        <v>140</v>
+      </c>
+      <c r="C54" t="s">
+        <v>108</v>
+      </c>
+      <c r="D54" t="s">
+        <v>21</v>
+      </c>
+      <c r="E54">
+        <v>20</v>
+      </c>
+      <c r="F54" t="s">
+        <v>21</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>20</v>
+      </c>
+      <c r="I54" t="s">
+        <v>22</v>
+      </c>
+      <c r="J54" t="s">
+        <v>47</v>
+      </c>
+      <c r="K54" t="s">
+        <v>24</v>
+      </c>
+      <c r="L54" t="s">
+        <v>25</v>
+      </c>
+      <c r="M54" t="s">
+        <v>26</v>
+      </c>
+      <c r="N54" t="s">
+        <v>21</v>
+      </c>
+      <c r="O54" t="s">
+        <v>21</v>
+      </c>
+      <c r="P54" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>21</v>
+      </c>
+      <c r="R54" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>141</v>
+      </c>
+      <c r="B55" t="s">
+        <v>142</v>
+      </c>
+      <c r="C55" t="s">
+        <v>108</v>
+      </c>
+      <c r="D55" t="s">
+        <v>21</v>
+      </c>
+      <c r="E55">
+        <v>10</v>
+      </c>
+      <c r="F55" t="s">
+        <v>21</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>10</v>
+      </c>
+      <c r="I55" t="s">
+        <v>22</v>
+      </c>
+      <c r="J55" t="s">
+        <v>47</v>
+      </c>
+      <c r="K55" t="s">
+        <v>24</v>
+      </c>
+      <c r="L55" t="s">
+        <v>25</v>
+      </c>
+      <c r="M55" t="s">
+        <v>26</v>
+      </c>
+      <c r="N55" t="s">
+        <v>21</v>
+      </c>
+      <c r="O55" t="s">
+        <v>21</v>
+      </c>
+      <c r="P55" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>21</v>
+      </c>
+      <c r="R55" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>143</v>
+      </c>
+      <c r="B56" t="s">
+        <v>144</v>
+      </c>
+      <c r="C56" t="s">
+        <v>108</v>
+      </c>
+      <c r="D56" t="s">
+        <v>21</v>
+      </c>
+      <c r="E56">
+        <v>10</v>
+      </c>
+      <c r="F56" t="s">
+        <v>21</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>10</v>
+      </c>
+      <c r="I56" t="s">
+        <v>22</v>
+      </c>
+      <c r="J56" t="s">
+        <v>47</v>
+      </c>
+      <c r="K56" t="s">
+        <v>24</v>
+      </c>
+      <c r="L56" t="s">
+        <v>25</v>
+      </c>
+      <c r="M56" t="s">
+        <v>26</v>
+      </c>
+      <c r="N56" t="s">
+        <v>21</v>
+      </c>
+      <c r="O56" t="s">
+        <v>21</v>
+      </c>
+      <c r="P56" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>21</v>
+      </c>
+      <c r="R56" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>145</v>
+      </c>
+      <c r="B57" t="s">
+        <v>146</v>
+      </c>
+      <c r="C57" t="s">
+        <v>108</v>
+      </c>
+      <c r="D57" t="s">
+        <v>21</v>
+      </c>
+      <c r="E57">
+        <v>30</v>
+      </c>
+      <c r="F57" t="s">
+        <v>21</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>30</v>
+      </c>
+      <c r="I57" t="s">
+        <v>22</v>
+      </c>
+      <c r="J57" t="s">
+        <v>47</v>
+      </c>
+      <c r="K57" t="s">
+        <v>24</v>
+      </c>
+      <c r="L57" t="s">
+        <v>25</v>
+      </c>
+      <c r="M57" t="s">
+        <v>26</v>
+      </c>
+      <c r="N57" t="s">
+        <v>21</v>
+      </c>
+      <c r="O57" t="s">
+        <v>21</v>
+      </c>
+      <c r="P57" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>21</v>
+      </c>
+      <c r="R57" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>147</v>
+      </c>
+      <c r="B58" t="s">
+        <v>148</v>
+      </c>
+      <c r="C58" t="s">
+        <v>108</v>
+      </c>
+      <c r="D58" t="s">
+        <v>21</v>
+      </c>
+      <c r="E58">
+        <v>30</v>
+      </c>
+      <c r="F58" t="s">
+        <v>21</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>30</v>
+      </c>
+      <c r="I58" t="s">
+        <v>22</v>
+      </c>
+      <c r="J58" t="s">
+        <v>47</v>
+      </c>
+      <c r="K58" t="s">
+        <v>24</v>
+      </c>
+      <c r="L58" t="s">
+        <v>25</v>
+      </c>
+      <c r="M58" t="s">
+        <v>26</v>
+      </c>
+      <c r="N58" t="s">
+        <v>21</v>
+      </c>
+      <c r="O58" t="s">
+        <v>21</v>
+      </c>
+      <c r="P58" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>21</v>
+      </c>
+      <c r="R58" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>149</v>
+      </c>
+      <c r="B59" t="s">
+        <v>150</v>
+      </c>
+      <c r="C59" t="s">
+        <v>108</v>
+      </c>
+      <c r="D59" t="s">
+        <v>21</v>
+      </c>
+      <c r="E59">
+        <v>6</v>
+      </c>
+      <c r="F59" t="s">
+        <v>21</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>6</v>
+      </c>
+      <c r="I59" t="s">
+        <v>22</v>
+      </c>
+      <c r="J59" t="s">
+        <v>47</v>
+      </c>
+      <c r="K59" t="s">
+        <v>24</v>
+      </c>
+      <c r="L59" t="s">
+        <v>25</v>
+      </c>
+      <c r="M59" t="s">
+        <v>26</v>
+      </c>
+      <c r="N59" t="s">
+        <v>21</v>
+      </c>
+      <c r="O59" t="s">
+        <v>21</v>
+      </c>
+      <c r="P59" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>21</v>
+      </c>
+      <c r="R59" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>151</v>
+      </c>
+      <c r="B60" t="s">
+        <v>152</v>
+      </c>
+      <c r="C60" t="s">
+        <v>108</v>
+      </c>
+      <c r="D60" t="s">
+        <v>21</v>
+      </c>
+      <c r="E60">
+        <v>10</v>
+      </c>
+      <c r="F60" t="s">
+        <v>21</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>10</v>
+      </c>
+      <c r="I60" t="s">
+        <v>22</v>
+      </c>
+      <c r="J60" t="s">
+        <v>47</v>
+      </c>
+      <c r="K60" t="s">
+        <v>24</v>
+      </c>
+      <c r="L60" t="s">
+        <v>25</v>
+      </c>
+      <c r="M60" t="s">
+        <v>26</v>
+      </c>
+      <c r="N60" t="s">
+        <v>21</v>
+      </c>
+      <c r="O60" t="s">
+        <v>21</v>
+      </c>
+      <c r="P60" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>21</v>
+      </c>
+      <c r="R60" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>153</v>
+      </c>
+      <c r="B61" t="s">
+        <v>154</v>
+      </c>
+      <c r="C61" t="s">
+        <v>108</v>
+      </c>
+      <c r="D61" t="s">
+        <v>21</v>
+      </c>
+      <c r="E61">
+        <v>10</v>
+      </c>
+      <c r="F61" t="s">
+        <v>21</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>10</v>
+      </c>
+      <c r="I61" t="s">
+        <v>22</v>
+      </c>
+      <c r="J61" t="s">
+        <v>47</v>
+      </c>
+      <c r="K61" t="s">
+        <v>24</v>
+      </c>
+      <c r="L61" t="s">
+        <v>25</v>
+      </c>
+      <c r="M61" t="s">
+        <v>26</v>
+      </c>
+      <c r="N61" t="s">
+        <v>21</v>
+      </c>
+      <c r="O61" t="s">
+        <v>21</v>
+      </c>
+      <c r="P61" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>21</v>
+      </c>
+      <c r="R61" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>155</v>
+      </c>
+      <c r="B62" t="s">
+        <v>156</v>
+      </c>
+      <c r="C62" t="s">
+        <v>108</v>
+      </c>
+      <c r="D62" t="s">
+        <v>21</v>
+      </c>
+      <c r="E62">
+        <v>200</v>
+      </c>
+      <c r="F62" t="s">
+        <v>21</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>200</v>
+      </c>
+      <c r="I62" t="s">
+        <v>22</v>
+      </c>
+      <c r="J62" t="s">
+        <v>47</v>
+      </c>
+      <c r="K62" t="s">
+        <v>24</v>
+      </c>
+      <c r="L62" t="s">
+        <v>25</v>
+      </c>
+      <c r="M62" t="s">
+        <v>26</v>
+      </c>
+      <c r="N62" t="s">
+        <v>21</v>
+      </c>
+      <c r="O62" t="s">
+        <v>21</v>
+      </c>
+      <c r="P62" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>21</v>
+      </c>
+      <c r="R62" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>157</v>
+      </c>
+      <c r="B63" t="s">
+        <v>158</v>
+      </c>
+      <c r="C63" t="s">
+        <v>108</v>
+      </c>
+      <c r="D63" t="s">
+        <v>21</v>
+      </c>
+      <c r="E63">
+        <v>20</v>
+      </c>
+      <c r="F63" t="s">
+        <v>21</v>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>20</v>
+      </c>
+      <c r="I63" t="s">
+        <v>22</v>
+      </c>
+      <c r="J63" t="s">
+        <v>47</v>
+      </c>
+      <c r="K63" t="s">
+        <v>24</v>
+      </c>
+      <c r="L63" t="s">
+        <v>25</v>
+      </c>
+      <c r="M63" t="s">
+        <v>26</v>
+      </c>
+      <c r="N63" t="s">
+        <v>21</v>
+      </c>
+      <c r="O63" t="s">
+        <v>21</v>
+      </c>
+      <c r="P63" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>21</v>
+      </c>
+      <c r="R63" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>159</v>
+      </c>
+      <c r="B64" t="s">
+        <v>160</v>
+      </c>
+      <c r="C64" t="s">
+        <v>108</v>
+      </c>
+      <c r="D64" t="s">
+        <v>21</v>
+      </c>
+      <c r="E64">
+        <v>50</v>
+      </c>
+      <c r="F64" t="s">
+        <v>21</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>50</v>
+      </c>
+      <c r="I64" t="s">
+        <v>22</v>
+      </c>
+      <c r="J64" t="s">
+        <v>47</v>
+      </c>
+      <c r="K64" t="s">
+        <v>24</v>
+      </c>
+      <c r="L64" t="s">
+        <v>25</v>
+      </c>
+      <c r="M64" t="s">
+        <v>26</v>
+      </c>
+      <c r="N64" t="s">
+        <v>21</v>
+      </c>
+      <c r="O64" t="s">
+        <v>21</v>
+      </c>
+      <c r="P64" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>21</v>
+      </c>
+      <c r="R64" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>161</v>
+      </c>
+      <c r="B65" t="s">
+        <v>162</v>
+      </c>
+      <c r="C65" t="s">
+        <v>108</v>
+      </c>
+      <c r="D65" t="s">
+        <v>21</v>
+      </c>
+      <c r="E65">
+        <v>100</v>
+      </c>
+      <c r="F65" t="s">
+        <v>21</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>100</v>
+      </c>
+      <c r="I65" t="s">
+        <v>22</v>
+      </c>
+      <c r="J65" t="s">
+        <v>47</v>
+      </c>
+      <c r="K65" t="s">
+        <v>24</v>
+      </c>
+      <c r="L65" t="s">
+        <v>25</v>
+      </c>
+      <c r="M65" t="s">
+        <v>26</v>
+      </c>
+      <c r="N65" t="s">
+        <v>21</v>
+      </c>
+      <c r="O65" t="s">
+        <v>21</v>
+      </c>
+      <c r="P65" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>21</v>
+      </c>
+      <c r="R65" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>163</v>
+      </c>
+      <c r="B66" t="s">
+        <v>164</v>
+      </c>
+      <c r="C66" t="s">
+        <v>108</v>
+      </c>
+      <c r="D66" t="s">
+        <v>21</v>
+      </c>
+      <c r="E66">
+        <v>20</v>
+      </c>
+      <c r="F66" t="s">
+        <v>21</v>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>20</v>
+      </c>
+      <c r="I66" t="s">
+        <v>22</v>
+      </c>
+      <c r="J66" t="s">
+        <v>47</v>
+      </c>
+      <c r="K66" t="s">
+        <v>24</v>
+      </c>
+      <c r="L66" t="s">
+        <v>25</v>
+      </c>
+      <c r="M66" t="s">
+        <v>26</v>
+      </c>
+      <c r="N66" t="s">
+        <v>21</v>
+      </c>
+      <c r="O66" t="s">
+        <v>21</v>
+      </c>
+      <c r="P66" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>21</v>
+      </c>
+      <c r="R66" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>165</v>
+      </c>
+      <c r="B67" t="s">
+        <v>166</v>
+      </c>
+      <c r="C67" t="s">
+        <v>108</v>
+      </c>
+      <c r="D67" t="s">
+        <v>21</v>
+      </c>
+      <c r="E67">
+        <v>200</v>
+      </c>
+      <c r="F67" t="s">
+        <v>21</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>200</v>
+      </c>
+      <c r="I67" t="s">
+        <v>22</v>
+      </c>
+      <c r="J67" t="s">
+        <v>47</v>
+      </c>
+      <c r="K67" t="s">
+        <v>24</v>
+      </c>
+      <c r="L67" t="s">
+        <v>25</v>
+      </c>
+      <c r="M67" t="s">
+        <v>26</v>
+      </c>
+      <c r="N67" t="s">
+        <v>21</v>
+      </c>
+      <c r="O67" t="s">
+        <v>21</v>
+      </c>
+      <c r="P67" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>21</v>
+      </c>
+      <c r="R67" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>167</v>
+      </c>
+      <c r="B68" t="s">
+        <v>168</v>
+      </c>
+      <c r="C68" t="s">
+        <v>108</v>
+      </c>
+      <c r="D68" t="s">
+        <v>21</v>
+      </c>
+      <c r="E68">
+        <v>150</v>
+      </c>
+      <c r="F68" t="s">
+        <v>21</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>150</v>
+      </c>
+      <c r="I68" t="s">
+        <v>22</v>
+      </c>
+      <c r="J68" t="s">
+        <v>47</v>
+      </c>
+      <c r="K68" t="s">
+        <v>24</v>
+      </c>
+      <c r="L68" t="s">
+        <v>25</v>
+      </c>
+      <c r="M68" t="s">
+        <v>26</v>
+      </c>
+      <c r="N68" t="s">
+        <v>21</v>
+      </c>
+      <c r="O68" t="s">
+        <v>21</v>
+      </c>
+      <c r="P68" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>21</v>
+      </c>
+      <c r="R68" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>169</v>
+      </c>
+      <c r="B69" t="s">
+        <v>170</v>
+      </c>
+      <c r="C69" t="s">
+        <v>108</v>
+      </c>
+      <c r="D69" t="s">
+        <v>21</v>
+      </c>
+      <c r="E69">
+        <v>50</v>
+      </c>
+      <c r="F69" t="s">
+        <v>21</v>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>50</v>
+      </c>
+      <c r="I69" t="s">
+        <v>22</v>
+      </c>
+      <c r="J69" t="s">
+        <v>47</v>
+      </c>
+      <c r="K69" t="s">
+        <v>24</v>
+      </c>
+      <c r="L69" t="s">
+        <v>25</v>
+      </c>
+      <c r="M69" t="s">
+        <v>26</v>
+      </c>
+      <c r="N69" t="s">
+        <v>21</v>
+      </c>
+      <c r="O69" t="s">
+        <v>21</v>
+      </c>
+      <c r="P69" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>21</v>
+      </c>
+      <c r="R69" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>171</v>
+      </c>
+      <c r="B70" t="s">
+        <v>172</v>
+      </c>
+      <c r="C70" t="s">
+        <v>108</v>
+      </c>
+      <c r="D70" t="s">
+        <v>21</v>
+      </c>
+      <c r="E70">
+        <v>100</v>
+      </c>
+      <c r="F70" t="s">
+        <v>21</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>100</v>
+      </c>
+      <c r="I70" t="s">
+        <v>22</v>
+      </c>
+      <c r="J70" t="s">
+        <v>47</v>
+      </c>
+      <c r="K70" t="s">
+        <v>24</v>
+      </c>
+      <c r="L70" t="s">
+        <v>25</v>
+      </c>
+      <c r="M70" t="s">
+        <v>26</v>
+      </c>
+      <c r="N70" t="s">
+        <v>21</v>
+      </c>
+      <c r="O70" t="s">
+        <v>21</v>
+      </c>
+      <c r="P70" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>21</v>
+      </c>
+      <c r="R70" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>173</v>
+      </c>
+      <c r="B71" t="s">
+        <v>174</v>
+      </c>
+      <c r="C71" t="s">
+        <v>108</v>
+      </c>
+      <c r="D71" t="s">
+        <v>21</v>
+      </c>
+      <c r="E71">
+        <v>4</v>
+      </c>
+      <c r="F71" t="s">
+        <v>21</v>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>4</v>
+      </c>
+      <c r="I71" t="s">
+        <v>22</v>
+      </c>
+      <c r="J71" t="s">
+        <v>47</v>
+      </c>
+      <c r="K71" t="s">
+        <v>24</v>
+      </c>
+      <c r="L71" t="s">
+        <v>25</v>
+      </c>
+      <c r="M71" t="s">
+        <v>26</v>
+      </c>
+      <c r="N71" t="s">
+        <v>21</v>
+      </c>
+      <c r="O71" t="s">
+        <v>21</v>
+      </c>
+      <c r="P71" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>21</v>
+      </c>
+      <c r="R71" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>175</v>
+      </c>
+      <c r="B72" t="s">
+        <v>176</v>
+      </c>
+      <c r="C72" t="s">
+        <v>108</v>
+      </c>
+      <c r="D72" t="s">
+        <v>21</v>
+      </c>
+      <c r="E72">
+        <v>10</v>
+      </c>
+      <c r="F72" t="s">
+        <v>21</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>10</v>
+      </c>
+      <c r="I72" t="s">
+        <v>22</v>
+      </c>
+      <c r="J72" t="s">
+        <v>47</v>
+      </c>
+      <c r="K72" t="s">
+        <v>24</v>
+      </c>
+      <c r="L72" t="s">
+        <v>25</v>
+      </c>
+      <c r="M72" t="s">
+        <v>26</v>
+      </c>
+      <c r="N72" t="s">
+        <v>21</v>
+      </c>
+      <c r="O72" t="s">
+        <v>21</v>
+      </c>
+      <c r="P72" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>21</v>
+      </c>
+      <c r="R72" t="s">
         <v>27</v>
       </c>
     </row>

--- a/pc.xlsx
+++ b/pc.xlsx
@@ -8,26 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Claude\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FBE9DE1B-653D-40F9-9742-3AF03751960C}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA88DD15-1B2C-4F24-A479-827E9460479E}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1083" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="129">
   <si>
     <t>Cod. producto</t>
   </si>
@@ -134,24 +127,24 @@
     <t>Deposito NQN</t>
   </si>
   <si>
+    <t>391-2882-051</t>
+  </si>
+  <si>
+    <t>CUERDA P30 Y P50</t>
+  </si>
+  <si>
+    <t>SOL - 2384</t>
+  </si>
+  <si>
+    <t>2026-07</t>
+  </si>
+  <si>
     <t>C5OX-24-20F</t>
   </si>
   <si>
     <t>ADAP CODO 90° MF 1.7/8" AS JIC 37° X MF 1.5/8" AS ORING</t>
   </si>
   <si>
-    <t>SOL - 2384</t>
-  </si>
-  <si>
-    <t>2026-07</t>
-  </si>
-  <si>
-    <t>391-2882-051</t>
-  </si>
-  <si>
-    <t>CUERDA P30 Y P50</t>
-  </si>
-  <si>
     <t>391-2884-021P</t>
   </si>
   <si>
@@ -179,165 +172,6 @@
     <t>OPERACIONES SAN JULIAN</t>
   </si>
   <si>
-    <t>SA-634-1100C</t>
-  </si>
-  <si>
-    <t>BLOCK CILINDROS SAUER SERIE 90-130</t>
-  </si>
-  <si>
-    <t>SOL - 2488</t>
-  </si>
-  <si>
-    <t>01036</t>
-  </si>
-  <si>
-    <t>Deposito Nqn 2</t>
-  </si>
-  <si>
-    <t>SA-634-3201M</t>
-  </si>
-  <si>
-    <t>EJE TRANSMISION MOTOR SAUER 90-130 - Z23 - CHALLENGER</t>
-  </si>
-  <si>
-    <t>SA-634-2200</t>
-  </si>
-  <si>
-    <t>PISTON SAUER SERIE 90-130</t>
-  </si>
-  <si>
-    <t>SA-634-4701</t>
-  </si>
-  <si>
-    <t>PLACA FRICCION SAUER SERIE 90-130</t>
-  </si>
-  <si>
-    <t>SA-634-4401</t>
-  </si>
-  <si>
-    <t>PLACA VALV. LH/RH SAUER SERIE 90-130</t>
-  </si>
-  <si>
-    <t>SA-633-1100C</t>
-  </si>
-  <si>
-    <t>BLOCK CILINDROS SAUER SERIE 90-100</t>
-  </si>
-  <si>
-    <t>SA-639-5221</t>
-  </si>
-  <si>
-    <t>BASCULANTE SAUER SERIE 90-75 - SIMPLE ROSCA</t>
-  </si>
-  <si>
-    <t>SA-634-7800A</t>
-  </si>
-  <si>
-    <t>BOMBA PRECARGA SAUER SERIE 90-130/180 26CC</t>
-  </si>
-  <si>
-    <t>SA-633-7800C</t>
-  </si>
-  <si>
-    <t>BOMBA PRECARGA SAUER SERIE 90-100 - 26cc -8200240</t>
-  </si>
-  <si>
-    <t>SA-632-7800A</t>
-  </si>
-  <si>
-    <t>BOMBA PRECARGA SAUER SERIE 90-75 - 14cc</t>
-  </si>
-  <si>
-    <t>SA-631-7800A</t>
-  </si>
-  <si>
-    <t>BOMBA PRECARGA SAUER 90-55 - 11cc - ALTURA</t>
-  </si>
-  <si>
-    <t>SA-640-5221</t>
-  </si>
-  <si>
-    <t>BASCULANTE SAUER SERIE 90-100-SIMPLE ROSCA - C/ SALTO- 82000232 - MV</t>
-  </si>
-  <si>
-    <t>SA-638-5221</t>
-  </si>
-  <si>
-    <t>BASCULANTE SAUER SERIE 90-55</t>
-  </si>
-  <si>
-    <t>SA-632-3201A</t>
-  </si>
-  <si>
-    <t>EJE TRANSMISION SAUER SERIE 90-75 - Z21M</t>
-  </si>
-  <si>
-    <t>SA-632-2100C</t>
-  </si>
-  <si>
-    <t>PISTON SAUER SERIE 90-75</t>
-  </si>
-  <si>
-    <t>SA-639-4701</t>
-  </si>
-  <si>
-    <t>PLACA FRICCION SAUER 90-75</t>
-  </si>
-  <si>
-    <t>SA-632-4501</t>
-  </si>
-  <si>
-    <t>PLACA VALV. LH/RH SAUER SERIE 90-75 - 518805</t>
-  </si>
-  <si>
-    <t>SA-WLA632-3306F</t>
-  </si>
-  <si>
-    <t>KIT SELLOS BOMBA SAUER SERIE 90-75</t>
-  </si>
-  <si>
-    <t>SA-323766</t>
-  </si>
-  <si>
-    <t>PLACA VALV. MOTOR SAUER SERIE 90-75</t>
-  </si>
-  <si>
-    <t>SA-640-3201A</t>
-  </si>
-  <si>
-    <t>EJE TRANSMISION MOTOR SAUER SERIE 90-100 Z21</t>
-  </si>
-  <si>
-    <t>SA-640-3306F</t>
-  </si>
-  <si>
-    <t>KIT SELLOS MOTOR SAUER 90-100 M.F.</t>
-  </si>
-  <si>
-    <t>SA-633-2100</t>
-  </si>
-  <si>
-    <t>PISTON SAUER SERIE 90-100</t>
-  </si>
-  <si>
-    <t>SA-640-4701</t>
-  </si>
-  <si>
-    <t>PLACA FRICCION SAUER 90-100 - 505350</t>
-  </si>
-  <si>
-    <t>SA-633-4501</t>
-  </si>
-  <si>
-    <t>PLACA VALV. LH/RH SAUER SERIE 90-100</t>
-  </si>
-  <si>
-    <t>SA-632-1100C</t>
-  </si>
-  <si>
-    <t>BLOCK CILINDROS SAUER SERIE 90-75</t>
-  </si>
-  <si>
     <t>RD200EZ</t>
   </si>
   <si>
@@ -347,217 +181,232 @@
     <t>SOL - 2489</t>
   </si>
   <si>
+    <t>391-2883-119P</t>
+  </si>
+  <si>
+    <t>RETEN M-30 P/EJE ENTERIZO</t>
+  </si>
+  <si>
+    <t>SOL - 2493</t>
+  </si>
+  <si>
+    <t>PFQ723ZRR1R11</t>
+  </si>
+  <si>
+    <t>MANOMETRO SERIE PFQ-ZR 4", 0/15.000 PSI - 0/1.000 bar, 1/2" NPT INFERIOR</t>
+  </si>
+  <si>
+    <t>FTX-06P</t>
+  </si>
+  <si>
+    <t>ADAP RECTO 9/16 UNF JIC X 1/4 NPT</t>
+  </si>
+  <si>
+    <t>313-1135-194</t>
+  </si>
+  <si>
+    <t>EJE POSTIZO P50 Z14</t>
+  </si>
+  <si>
+    <t>313-5037-202</t>
+  </si>
+  <si>
+    <t>TROMPA P50 DE 5" X 4</t>
+  </si>
+  <si>
+    <t>391-0381-905</t>
+  </si>
+  <si>
+    <t>TORRINGTON P50</t>
+  </si>
+  <si>
+    <t>AFS-102N</t>
+  </si>
+  <si>
+    <t>BRIDA SAE 1" PARA 3000 PSI</t>
+  </si>
+  <si>
+    <t>AFS-604</t>
+  </si>
+  <si>
+    <t>JGO DE1/2 BRIDAS SAE 1.1/4" NPT P/6000 PSI</t>
+  </si>
+  <si>
+    <t>FB-2</t>
+  </si>
+  <si>
+    <t>BOCA DE CARGA GRANDE BRIDADA 40 MIC.</t>
+  </si>
+  <si>
+    <t>FILT-D-AB-2</t>
+  </si>
+  <si>
+    <t>FILTRO AIRE RESP DESECANTE</t>
+  </si>
+  <si>
+    <t>PFQ905R3R1</t>
+  </si>
+  <si>
+    <t>MANOMETRO 2,5" ROSCA POSTERIOR 1/4 NPT 0-10 BAR C/GLICERINA</t>
+  </si>
+  <si>
+    <t>PFQ908R3R1</t>
+  </si>
+  <si>
+    <t>MANOMETRO 2,5" ROSCA POSTERIOR 1/4 NPT 0-40 BAR C/GLICERINA</t>
+  </si>
+  <si>
+    <t>PFQ918R3R1</t>
+  </si>
+  <si>
+    <t>MANOMETRO 2,5" ROSCA POSTERIOR 1/4 NPT 0-600 BAR C/GLICERINA</t>
+  </si>
+  <si>
+    <t>2500-3500-375B</t>
+  </si>
+  <si>
+    <t>POLYPAK 88.90 x 101.60 x 9.52</t>
+  </si>
+  <si>
+    <t>FT 221/1-14</t>
+  </si>
+  <si>
+    <t>VALVULA ESFERICA DE 2 VIAS, ALTA PRESION 1/4"</t>
+  </si>
+  <si>
+    <t>FT 257/6-14</t>
+  </si>
+  <si>
+    <t>VALVULA DE RETENCION EN LINEA RECTA 1/4" 30LPM - 500 BAR</t>
+  </si>
+  <si>
+    <t>BUJE RED-2"x1.1/2" S3000</t>
+  </si>
+  <si>
+    <t>BUJE DE RED 2" NPT x 1.1/2" NPT SERIE 3000</t>
+  </si>
+  <si>
+    <t>CUPLA-1/2" S3000</t>
+  </si>
+  <si>
+    <t>CUPLA 1/2" NPT SERIE 3000</t>
+  </si>
+  <si>
+    <t>CUPLA-1/4" S3000</t>
+  </si>
+  <si>
+    <t>CUPLA 1/4" NPT SERIE 3000</t>
+  </si>
+  <si>
+    <t>ENTRER-1" S3000</t>
+  </si>
+  <si>
+    <t>ENTRERROSCA 1" NPT SERIE 3000</t>
+  </si>
+  <si>
+    <t>ENTRER-1.1/4" S3000</t>
+  </si>
+  <si>
+    <t>ENTRERROSCA 1.1/4" NPT SERIE 3000</t>
+  </si>
+  <si>
+    <t>ENTRER-1/2" S3000</t>
+  </si>
+  <si>
+    <t>ENTRERROSCA 1/2" NPT SERIE 3000</t>
+  </si>
+  <si>
+    <t>ENTRER-1/4" S3000</t>
+  </si>
+  <si>
+    <t>ENTRERROSCA 1/4" NPT SERIE 3000</t>
+  </si>
+  <si>
+    <t>ENTRER-3/4" S3000</t>
+  </si>
+  <si>
+    <t>ENTRERROSCA 3/4" NPT SERIE 3000</t>
+  </si>
+  <si>
+    <t>MA-310</t>
+  </si>
+  <si>
+    <t>PISTOLA CUENTA LTS DIGITAL VULCANO</t>
+  </si>
+  <si>
+    <t>TAPA-3/4" S3000</t>
+  </si>
+  <si>
+    <t>TAPA HEMBRA 3/4" NPT SERIE 3000</t>
+  </si>
+  <si>
+    <t>TAPON-1" S3000</t>
+  </si>
+  <si>
+    <t>TAPON MACHO 1" NPT SERIE 3000</t>
+  </si>
+  <si>
+    <t>TAPON-1/4" S3000</t>
+  </si>
+  <si>
+    <t>TAPON MACHO 1/4" NPT SERIE 3000</t>
+  </si>
+  <si>
+    <t>TAPON-3/4" S3000</t>
+  </si>
+  <si>
+    <t>TAPON MACHO 3/4" NPT SERIE 3000</t>
+  </si>
+  <si>
+    <t>TAPON-3/8" S3000</t>
+  </si>
+  <si>
+    <t>TAPON MACHO 3/8" NPT SERIE 3000</t>
+  </si>
+  <si>
+    <t>TEE-1/2" S3000</t>
+  </si>
+  <si>
+    <t>TEE H x H x H 1/2" NPT SERIE 3000</t>
+  </si>
+  <si>
+    <t>AC02G-90</t>
+  </si>
+  <si>
+    <t>ALEMITE GAS 90° 1/8"</t>
+  </si>
+  <si>
     <t>AR02G</t>
   </si>
   <si>
     <t>ALEMITE RECTO DE 1/8" GAS</t>
   </si>
   <si>
-    <t>SOL - 2493</t>
-  </si>
-  <si>
-    <t>BUJE RED-2"x1.1/2" S3000</t>
-  </si>
-  <si>
-    <t>BUJE DE RED 2" NPT x 1.1/2" NPT SERIE 3000</t>
-  </si>
-  <si>
-    <t>CUPLA-1/2" S3000</t>
-  </si>
-  <si>
-    <t>CUPLA 1/2" NPT SERIE 3000</t>
-  </si>
-  <si>
-    <t>2500-3500-375B</t>
-  </si>
-  <si>
-    <t>POLYPAK 88.90 x 101.60 x 9.52</t>
-  </si>
-  <si>
-    <t>313-1135-194</t>
-  </si>
-  <si>
-    <t>EJE POSTIZO P50 Z14</t>
-  </si>
-  <si>
-    <t>313-5037-202</t>
-  </si>
-  <si>
-    <t>TROMPA P50 DE 5" X 4</t>
-  </si>
-  <si>
-    <t>391-0381-905</t>
-  </si>
-  <si>
-    <t>TORRINGTON P50</t>
-  </si>
-  <si>
-    <t>391-2883-119P</t>
-  </si>
-  <si>
-    <t>RETEN M-30 P/EJE ENTERIZO</t>
-  </si>
-  <si>
     <t>46511385</t>
   </si>
   <si>
     <t>MANGUERA GATES SAE100 R12 3/4"  12EFG4K X LL</t>
   </si>
   <si>
-    <t>TAPON-1" S3000</t>
-  </si>
-  <si>
-    <t>TAPON MACHO 1" NPT SERIE 3000</t>
-  </si>
-  <si>
-    <t>TAPON-1/4" S3000</t>
-  </si>
-  <si>
-    <t>TAPON MACHO 1/4" NPT SERIE 3000</t>
-  </si>
-  <si>
-    <t>TAPON-3/4" S3000</t>
-  </si>
-  <si>
-    <t>TAPON MACHO 3/4" NPT SERIE 3000</t>
-  </si>
-  <si>
-    <t>TAPON-3/8" S3000</t>
-  </si>
-  <si>
-    <t>TAPON MACHO 3/8" NPT SERIE 3000</t>
-  </si>
-  <si>
-    <t>TEE-1/2" S3000</t>
-  </si>
-  <si>
-    <t>TEE H x H x H 1/2" NPT SERIE 3000</t>
-  </si>
-  <si>
-    <t>PFQ723ZRR1R11</t>
-  </si>
-  <si>
-    <t>MANOMETRO SERIE PFQ-ZR 4", 0/15.000 PSI - 0/1.000 bar, 1/2" NPT INFERIOR</t>
-  </si>
-  <si>
-    <t>PFQ905R3R1</t>
-  </si>
-  <si>
-    <t>MANOMETRO 2,5" ROSCA POSTERIOR 1/4 NPT 0-10 BAR C/GLICERINA</t>
-  </si>
-  <si>
-    <t>PFQ908R3R1</t>
-  </si>
-  <si>
-    <t>MANOMETRO 2,5" ROSCA POSTERIOR 1/4 NPT 0-40 BAR C/GLICERINA</t>
-  </si>
-  <si>
-    <t>PFQ918R3R1</t>
-  </si>
-  <si>
-    <t>MANOMETRO 2,5" ROSCA POSTERIOR 1/4 NPT 0-600 BAR C/GLICERINA</t>
-  </si>
-  <si>
-    <t>SA-519021</t>
-  </si>
-  <si>
-    <t>RETEN EJE MOTOR 51V060 / EJE BOMBA S90/100 A 250</t>
-  </si>
-  <si>
-    <t>TAPA-3/4" S3000</t>
-  </si>
-  <si>
-    <t>TAPA HEMBRA 3/4" NPT SERIE 3000</t>
-  </si>
-  <si>
-    <t>FB-2</t>
-  </si>
-  <si>
-    <t>BOCA DE CARGA GRANDE BRIDADA 40 MIC.</t>
-  </si>
-  <si>
-    <t>FILT-D-AB-2</t>
-  </si>
-  <si>
-    <t>FILTRO AIRE RESP DESECANTE</t>
-  </si>
-  <si>
-    <t>FT 221/1-14</t>
-  </si>
-  <si>
-    <t>VALVULA ESFERICA DE 2 VIAS, ALTA PRESION 1/4"</t>
-  </si>
-  <si>
-    <t>FT 257/6-14</t>
-  </si>
-  <si>
-    <t>VALVULA DE RETENCION EN LINEA RECTA 1/4" 30LPM - 500 BAR</t>
-  </si>
-  <si>
-    <t>FTX-06P</t>
-  </si>
-  <si>
-    <t>ADAP RECTO 9/16 UNF JIC X 1/4 NPT</t>
-  </si>
-  <si>
-    <t>MA-310</t>
-  </si>
-  <si>
-    <t>PISTOLA CUENTA LTS DIGITAL VULCANO</t>
-  </si>
-  <si>
-    <t>CUPLA-1/4" S3000</t>
-  </si>
-  <si>
-    <t>CUPLA 1/4" NPT SERIE 3000</t>
-  </si>
-  <si>
-    <t>ENTRER-1" S3000</t>
-  </si>
-  <si>
-    <t>ENTRERROSCA 1" NPT SERIE 3000</t>
-  </si>
-  <si>
-    <t>ENTRER-1.1/4" S3000</t>
-  </si>
-  <si>
-    <t>ENTRERROSCA 1.1/4" NPT SERIE 3000</t>
-  </si>
-  <si>
-    <t>ENTRER-1/2" S3000</t>
-  </si>
-  <si>
-    <t>ENTRERROSCA 1/2" NPT SERIE 3000</t>
-  </si>
-  <si>
-    <t>ENTRER-1/4" S3000</t>
-  </si>
-  <si>
-    <t>ENTRERROSCA 1/4" NPT SERIE 3000</t>
-  </si>
-  <si>
-    <t>ENTRER-3/4" S3000</t>
-  </si>
-  <si>
-    <t>ENTRERROSCA 3/4" NPT SERIE 3000</t>
-  </si>
-  <si>
-    <t>AC02G-90</t>
-  </si>
-  <si>
-    <t>ALEMITE GAS 90° 1/8"</t>
-  </si>
-  <si>
-    <t>AFS-102N</t>
-  </si>
-  <si>
-    <t>BRIDA SAE 1" PARA 3000 PSI</t>
-  </si>
-  <si>
-    <t>AFS-604</t>
-  </si>
-  <si>
-    <t>JGO DE1/2 BRIDAS SAE 1.1/4" NPT P/6000 PSI</t>
+    <t>BOBINAS DE ACCIONAMIENTO</t>
+  </si>
+  <si>
+    <t>BOBINAS DE ACCIONAMIENTO - GENERICO</t>
+  </si>
+  <si>
+    <t>SOL - 2501</t>
+  </si>
+  <si>
+    <t>00986</t>
+  </si>
+  <si>
+    <t>2026-09</t>
+  </si>
+  <si>
+    <t>HIDROIL SRL</t>
+  </si>
+  <si>
+    <t>Deposito</t>
   </si>
 </sst>
 </file>
@@ -909,7 +758,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R72"/>
+  <dimension ref="A1:R47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
@@ -1318,7 +1167,7 @@
         <v>21</v>
       </c>
       <c r="E8">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F8" t="s">
         <v>21</v>
@@ -1327,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="I8" t="s">
         <v>22</v>
@@ -1374,7 +1223,7 @@
         <v>21</v>
       </c>
       <c r="E9">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
         <v>21</v>
@@ -1383,7 +1232,7 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="I9" t="s">
         <v>22</v>
@@ -1539,10 +1388,10 @@
         <v>52</v>
       </c>
       <c r="D12" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
         <v>21</v>
@@ -1551,7 +1400,7 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I12" t="s">
         <v>22</v>
@@ -1560,13 +1409,13 @@
         <v>47</v>
       </c>
       <c r="K12" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="L12" t="s">
         <v>25</v>
       </c>
       <c r="M12" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="N12" t="s">
         <v>21</v>
@@ -1586,19 +1435,19 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" t="s">
         <v>55</v>
       </c>
-      <c r="B13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C13" t="s">
-        <v>52</v>
-      </c>
       <c r="D13" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F13" t="s">
         <v>21</v>
@@ -1607,7 +1456,7 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="I13" t="s">
         <v>22</v>
@@ -1616,13 +1465,13 @@
         <v>47</v>
       </c>
       <c r="K13" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="L13" t="s">
         <v>25</v>
       </c>
       <c r="M13" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="N13" t="s">
         <v>21</v>
@@ -1642,19 +1491,19 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" t="s">
         <v>57</v>
       </c>
-      <c r="B14" t="s">
-        <v>58</v>
-      </c>
       <c r="C14" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D14" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="E14">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F14" t="s">
         <v>21</v>
@@ -1663,7 +1512,7 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I14" t="s">
         <v>22</v>
@@ -1672,13 +1521,13 @@
         <v>47</v>
       </c>
       <c r="K14" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="L14" t="s">
         <v>25</v>
       </c>
       <c r="M14" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="N14" t="s">
         <v>21</v>
@@ -1698,19 +1547,19 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" t="s">
         <v>59</v>
       </c>
-      <c r="B15" t="s">
-        <v>60</v>
-      </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D15" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="F15" t="s">
         <v>21</v>
@@ -1719,7 +1568,7 @@
         <v>0</v>
       </c>
       <c r="H15">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="I15" t="s">
         <v>22</v>
@@ -1728,13 +1577,13 @@
         <v>47</v>
       </c>
       <c r="K15" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="L15" t="s">
         <v>25</v>
       </c>
       <c r="M15" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="N15" t="s">
         <v>21</v>
@@ -1754,19 +1603,19 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" t="s">
         <v>61</v>
       </c>
-      <c r="B16" t="s">
-        <v>62</v>
-      </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D16" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F16" t="s">
         <v>21</v>
@@ -1775,7 +1624,7 @@
         <v>0</v>
       </c>
       <c r="H16">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="I16" t="s">
         <v>22</v>
@@ -1784,13 +1633,13 @@
         <v>47</v>
       </c>
       <c r="K16" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="L16" t="s">
         <v>25</v>
       </c>
       <c r="M16" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="N16" t="s">
         <v>21</v>
@@ -1810,19 +1659,19 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>62</v>
+      </c>
+      <c r="B17" t="s">
         <v>63</v>
       </c>
-      <c r="B17" t="s">
-        <v>64</v>
-      </c>
       <c r="C17" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D17" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F17" t="s">
         <v>21</v>
@@ -1831,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I17" t="s">
         <v>22</v>
@@ -1840,13 +1689,13 @@
         <v>47</v>
       </c>
       <c r="K17" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="L17" t="s">
         <v>25</v>
       </c>
       <c r="M17" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="N17" t="s">
         <v>21</v>
@@ -1866,19 +1715,19 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" t="s">
         <v>65</v>
       </c>
-      <c r="B18" t="s">
-        <v>66</v>
-      </c>
       <c r="C18" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D18" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="F18" t="s">
         <v>21</v>
@@ -1887,7 +1736,7 @@
         <v>0</v>
       </c>
       <c r="H18">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="I18" t="s">
         <v>22</v>
@@ -1896,13 +1745,13 @@
         <v>47</v>
       </c>
       <c r="K18" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="L18" t="s">
         <v>25</v>
       </c>
       <c r="M18" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="N18" t="s">
         <v>21</v>
@@ -1922,19 +1771,19 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>66</v>
+      </c>
+      <c r="B19" t="s">
         <v>67</v>
       </c>
-      <c r="B19" t="s">
-        <v>68</v>
-      </c>
       <c r="C19" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D19" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F19" t="s">
         <v>21</v>
@@ -1943,7 +1792,7 @@
         <v>0</v>
       </c>
       <c r="H19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I19" t="s">
         <v>22</v>
@@ -1952,13 +1801,13 @@
         <v>47</v>
       </c>
       <c r="K19" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="L19" t="s">
         <v>25</v>
       </c>
       <c r="M19" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="N19" t="s">
         <v>21</v>
@@ -1978,19 +1827,19 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>68</v>
+      </c>
+      <c r="B20" t="s">
         <v>69</v>
       </c>
-      <c r="B20" t="s">
-        <v>70</v>
-      </c>
       <c r="C20" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D20" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F20" t="s">
         <v>21</v>
@@ -1999,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="H20">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I20" t="s">
         <v>22</v>
@@ -2008,13 +1857,13 @@
         <v>47</v>
       </c>
       <c r="K20" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="L20" t="s">
         <v>25</v>
       </c>
       <c r="M20" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="N20" t="s">
         <v>21</v>
@@ -2034,19 +1883,19 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" t="s">
         <v>71</v>
       </c>
-      <c r="B21" t="s">
-        <v>72</v>
-      </c>
       <c r="C21" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D21" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="F21" t="s">
         <v>21</v>
@@ -2055,7 +1904,7 @@
         <v>0</v>
       </c>
       <c r="H21">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="I21" t="s">
         <v>22</v>
@@ -2064,13 +1913,13 @@
         <v>47</v>
       </c>
       <c r="K21" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="L21" t="s">
         <v>25</v>
       </c>
       <c r="M21" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="N21" t="s">
         <v>21</v>
@@ -2090,19 +1939,19 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>72</v>
+      </c>
+      <c r="B22" t="s">
         <v>73</v>
       </c>
-      <c r="B22" t="s">
-        <v>74</v>
-      </c>
       <c r="C22" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D22" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F22" t="s">
         <v>21</v>
@@ -2111,7 +1960,7 @@
         <v>0</v>
       </c>
       <c r="H22">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I22" t="s">
         <v>22</v>
@@ -2120,13 +1969,13 @@
         <v>47</v>
       </c>
       <c r="K22" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="L22" t="s">
         <v>25</v>
       </c>
       <c r="M22" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="N22" t="s">
         <v>21</v>
@@ -2146,19 +1995,19 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" t="s">
         <v>75</v>
       </c>
-      <c r="B23" t="s">
-        <v>76</v>
-      </c>
       <c r="C23" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D23" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F23" t="s">
         <v>21</v>
@@ -2167,7 +2016,7 @@
         <v>0</v>
       </c>
       <c r="H23">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I23" t="s">
         <v>22</v>
@@ -2176,13 +2025,13 @@
         <v>47</v>
       </c>
       <c r="K23" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="L23" t="s">
         <v>25</v>
       </c>
       <c r="M23" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="N23" t="s">
         <v>21</v>
@@ -2202,19 +2051,19 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>76</v>
+      </c>
+      <c r="B24" t="s">
         <v>77</v>
       </c>
-      <c r="B24" t="s">
-        <v>78</v>
-      </c>
       <c r="C24" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D24" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F24" t="s">
         <v>21</v>
@@ -2223,7 +2072,7 @@
         <v>0</v>
       </c>
       <c r="H24">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="I24" t="s">
         <v>22</v>
@@ -2232,13 +2081,13 @@
         <v>47</v>
       </c>
       <c r="K24" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="L24" t="s">
         <v>25</v>
       </c>
       <c r="M24" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="N24" t="s">
         <v>21</v>
@@ -2258,19 +2107,19 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>78</v>
+      </c>
+      <c r="B25" t="s">
         <v>79</v>
       </c>
-      <c r="B25" t="s">
-        <v>80</v>
-      </c>
       <c r="C25" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D25" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F25" t="s">
         <v>21</v>
@@ -2279,7 +2128,7 @@
         <v>0</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I25" t="s">
         <v>22</v>
@@ -2288,13 +2137,13 @@
         <v>47</v>
       </c>
       <c r="K25" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="L25" t="s">
         <v>25</v>
       </c>
       <c r="M25" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="N25" t="s">
         <v>21</v>
@@ -2314,19 +2163,19 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>80</v>
+      </c>
+      <c r="B26" t="s">
         <v>81</v>
       </c>
-      <c r="B26" t="s">
-        <v>82</v>
-      </c>
       <c r="C26" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D26" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="E26">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F26" t="s">
         <v>21</v>
@@ -2335,7 +2184,7 @@
         <v>0</v>
       </c>
       <c r="H26">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="I26" t="s">
         <v>22</v>
@@ -2344,13 +2193,13 @@
         <v>47</v>
       </c>
       <c r="K26" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="L26" t="s">
         <v>25</v>
       </c>
       <c r="M26" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="N26" t="s">
         <v>21</v>
@@ -2370,19 +2219,19 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>82</v>
+      </c>
+      <c r="B27" t="s">
         <v>83</v>
       </c>
-      <c r="B27" t="s">
-        <v>84</v>
-      </c>
       <c r="C27" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D27" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F27" t="s">
         <v>21</v>
@@ -2391,7 +2240,7 @@
         <v>0</v>
       </c>
       <c r="H27">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I27" t="s">
         <v>22</v>
@@ -2400,13 +2249,13 @@
         <v>47</v>
       </c>
       <c r="K27" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="L27" t="s">
         <v>25</v>
       </c>
       <c r="M27" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="N27" t="s">
         <v>21</v>
@@ -2426,19 +2275,19 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>84</v>
+      </c>
+      <c r="B28" t="s">
         <v>85</v>
       </c>
-      <c r="B28" t="s">
-        <v>86</v>
-      </c>
       <c r="C28" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D28" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F28" t="s">
         <v>21</v>
@@ -2447,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="H28">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I28" t="s">
         <v>22</v>
@@ -2456,13 +2305,13 @@
         <v>47</v>
       </c>
       <c r="K28" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="L28" t="s">
         <v>25</v>
       </c>
       <c r="M28" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="N28" t="s">
         <v>21</v>
@@ -2482,19 +2331,19 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>86</v>
+      </c>
+      <c r="B29" t="s">
         <v>87</v>
       </c>
-      <c r="B29" t="s">
-        <v>88</v>
-      </c>
       <c r="C29" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D29" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="E29">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F29" t="s">
         <v>21</v>
@@ -2503,7 +2352,7 @@
         <v>0</v>
       </c>
       <c r="H29">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I29" t="s">
         <v>22</v>
@@ -2512,13 +2361,13 @@
         <v>47</v>
       </c>
       <c r="K29" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="L29" t="s">
         <v>25</v>
       </c>
       <c r="M29" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="N29" t="s">
         <v>21</v>
@@ -2538,19 +2387,19 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>88</v>
+      </c>
+      <c r="B30" t="s">
         <v>89</v>
       </c>
-      <c r="B30" t="s">
-        <v>90</v>
-      </c>
       <c r="C30" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D30" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>150</v>
       </c>
       <c r="F30" t="s">
         <v>21</v>
@@ -2559,7 +2408,7 @@
         <v>0</v>
       </c>
       <c r="H30">
-        <v>2</v>
+        <v>150</v>
       </c>
       <c r="I30" t="s">
         <v>22</v>
@@ -2568,13 +2417,13 @@
         <v>47</v>
       </c>
       <c r="K30" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="L30" t="s">
         <v>25</v>
       </c>
       <c r="M30" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="N30" t="s">
         <v>21</v>
@@ -2594,19 +2443,19 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>90</v>
+      </c>
+      <c r="B31" t="s">
         <v>91</v>
       </c>
-      <c r="B31" t="s">
-        <v>92</v>
-      </c>
       <c r="C31" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D31" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="F31" t="s">
         <v>21</v>
@@ -2615,7 +2464,7 @@
         <v>0</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="I31" t="s">
         <v>22</v>
@@ -2624,13 +2473,13 @@
         <v>47</v>
       </c>
       <c r="K31" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="L31" t="s">
         <v>25</v>
       </c>
       <c r="M31" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="N31" t="s">
         <v>21</v>
@@ -2650,19 +2499,19 @@
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>92</v>
+      </c>
+      <c r="B32" t="s">
         <v>93</v>
       </c>
-      <c r="B32" t="s">
-        <v>94</v>
-      </c>
       <c r="C32" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D32" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="E32">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="F32" t="s">
         <v>21</v>
@@ -2671,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="H32">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="I32" t="s">
         <v>22</v>
@@ -2680,13 +2529,13 @@
         <v>47</v>
       </c>
       <c r="K32" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="L32" t="s">
         <v>25</v>
       </c>
       <c r="M32" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="N32" t="s">
         <v>21</v>
@@ -2706,19 +2555,19 @@
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>94</v>
+      </c>
+      <c r="B33" t="s">
         <v>95</v>
       </c>
-      <c r="B33" t="s">
-        <v>96</v>
-      </c>
       <c r="C33" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D33" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="E33">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F33" t="s">
         <v>21</v>
@@ -2727,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="H33">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I33" t="s">
         <v>22</v>
@@ -2736,13 +2585,13 @@
         <v>47</v>
       </c>
       <c r="K33" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="L33" t="s">
         <v>25</v>
       </c>
       <c r="M33" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="N33" t="s">
         <v>21</v>
@@ -2762,19 +2611,19 @@
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>96</v>
+      </c>
+      <c r="B34" t="s">
         <v>97</v>
       </c>
-      <c r="B34" t="s">
-        <v>98</v>
-      </c>
       <c r="C34" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D34" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="F34" t="s">
         <v>21</v>
@@ -2783,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="H34">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="I34" t="s">
         <v>22</v>
@@ -2792,13 +2641,13 @@
         <v>47</v>
       </c>
       <c r="K34" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="L34" t="s">
         <v>25</v>
       </c>
       <c r="M34" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="N34" t="s">
         <v>21</v>
@@ -2818,19 +2667,19 @@
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>98</v>
+      </c>
+      <c r="B35" t="s">
         <v>99</v>
       </c>
-      <c r="B35" t="s">
-        <v>100</v>
-      </c>
       <c r="C35" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D35" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>150</v>
       </c>
       <c r="F35" t="s">
         <v>21</v>
@@ -2839,7 +2688,7 @@
         <v>0</v>
       </c>
       <c r="H35">
-        <v>2</v>
+        <v>150</v>
       </c>
       <c r="I35" t="s">
         <v>22</v>
@@ -2848,13 +2697,13 @@
         <v>47</v>
       </c>
       <c r="K35" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="L35" t="s">
         <v>25</v>
       </c>
       <c r="M35" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="N35" t="s">
         <v>21</v>
@@ -2874,19 +2723,19 @@
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>100</v>
+      </c>
+      <c r="B36" t="s">
         <v>101</v>
       </c>
-      <c r="B36" t="s">
-        <v>102</v>
-      </c>
       <c r="C36" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D36" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="F36" t="s">
         <v>21</v>
@@ -2895,7 +2744,7 @@
         <v>0</v>
       </c>
       <c r="H36">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="I36" t="s">
         <v>22</v>
@@ -2904,13 +2753,13 @@
         <v>47</v>
       </c>
       <c r="K36" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="L36" t="s">
         <v>25</v>
       </c>
       <c r="M36" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="N36" t="s">
         <v>21</v>
@@ -2930,19 +2779,19 @@
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>102</v>
+      </c>
+      <c r="B37" t="s">
         <v>103</v>
       </c>
-      <c r="B37" t="s">
-        <v>104</v>
-      </c>
       <c r="C37" t="s">
-        <v>105</v>
+        <v>55</v>
       </c>
       <c r="D37" t="s">
         <v>21</v>
       </c>
       <c r="E37">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F37" t="s">
         <v>21</v>
@@ -2951,7 +2800,7 @@
         <v>0</v>
       </c>
       <c r="H37">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I37" t="s">
         <v>22</v>
@@ -2986,19 +2835,19 @@
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B38" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C38" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="D38" t="s">
         <v>21</v>
       </c>
       <c r="E38">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="F38" t="s">
         <v>21</v>
@@ -3007,7 +2856,7 @@
         <v>0</v>
       </c>
       <c r="H38">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="I38" t="s">
         <v>22</v>
@@ -3042,19 +2891,19 @@
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B39" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C39" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="D39" t="s">
         <v>21</v>
       </c>
       <c r="E39">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F39" t="s">
         <v>21</v>
@@ -3063,7 +2912,7 @@
         <v>0</v>
       </c>
       <c r="H39">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="I39" t="s">
         <v>22</v>
@@ -3098,19 +2947,19 @@
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B40" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C40" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="D40" t="s">
         <v>21</v>
       </c>
       <c r="E40">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F40" t="s">
         <v>21</v>
@@ -3119,7 +2968,7 @@
         <v>0</v>
       </c>
       <c r="H40">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="I40" t="s">
         <v>22</v>
@@ -3154,19 +3003,19 @@
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B41" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C41" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="D41" t="s">
         <v>21</v>
       </c>
       <c r="E41">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F41" t="s">
         <v>21</v>
@@ -3175,7 +3024,7 @@
         <v>0</v>
       </c>
       <c r="H41">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="I41" t="s">
         <v>22</v>
@@ -3210,19 +3059,19 @@
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B42" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C42" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="D42" t="s">
         <v>21</v>
       </c>
       <c r="E42">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F42" t="s">
         <v>21</v>
@@ -3231,7 +3080,7 @@
         <v>0</v>
       </c>
       <c r="H42">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="I42" t="s">
         <v>22</v>
@@ -3266,19 +3115,19 @@
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B43" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C43" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="D43" t="s">
         <v>21</v>
       </c>
       <c r="E43">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="F43" t="s">
         <v>21</v>
@@ -3287,7 +3136,7 @@
         <v>0</v>
       </c>
       <c r="H43">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="I43" t="s">
         <v>22</v>
@@ -3322,19 +3171,19 @@
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B44" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C44" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="D44" t="s">
         <v>21</v>
       </c>
       <c r="E44">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="F44" t="s">
         <v>21</v>
@@ -3343,7 +3192,7 @@
         <v>0</v>
       </c>
       <c r="H44">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="I44" t="s">
         <v>22</v>
@@ -3378,19 +3227,19 @@
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B45" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C45" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="D45" t="s">
         <v>21</v>
       </c>
       <c r="E45">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="F45" t="s">
         <v>21</v>
@@ -3399,7 +3248,7 @@
         <v>0</v>
       </c>
       <c r="H45">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="I45" t="s">
         <v>22</v>
@@ -3434,13 +3283,13 @@
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B46" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C46" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="D46" t="s">
         <v>21</v>
@@ -3490,43 +3339,43 @@
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
+        <v>122</v>
+      </c>
+      <c r="B47" t="s">
+        <v>123</v>
+      </c>
+      <c r="C47" t="s">
+        <v>124</v>
+      </c>
+      <c r="D47" t="s">
         <v>125</v>
       </c>
-      <c r="B47" t="s">
+      <c r="E47">
+        <v>1</v>
+      </c>
+      <c r="F47" t="s">
+        <v>21</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>1</v>
+      </c>
+      <c r="I47" t="s">
+        <v>22</v>
+      </c>
+      <c r="J47" t="s">
         <v>126</v>
       </c>
-      <c r="C47" t="s">
-        <v>108</v>
-      </c>
-      <c r="D47" t="s">
-        <v>21</v>
-      </c>
-      <c r="E47">
-        <v>40</v>
-      </c>
-      <c r="F47" t="s">
-        <v>21</v>
-      </c>
-      <c r="G47">
-        <v>0</v>
-      </c>
-      <c r="H47">
-        <v>40</v>
-      </c>
-      <c r="I47" t="s">
-        <v>22</v>
-      </c>
-      <c r="J47" t="s">
-        <v>47</v>
-      </c>
       <c r="K47" t="s">
-        <v>24</v>
+        <v>127</v>
       </c>
       <c r="L47" t="s">
         <v>25</v>
       </c>
       <c r="M47" t="s">
-        <v>26</v>
+        <v>128</v>
       </c>
       <c r="N47" t="s">
         <v>21</v>
@@ -3541,1406 +3390,6 @@
         <v>21</v>
       </c>
       <c r="R47" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>127</v>
-      </c>
-      <c r="B48" t="s">
-        <v>128</v>
-      </c>
-      <c r="C48" t="s">
-        <v>108</v>
-      </c>
-      <c r="D48" t="s">
-        <v>21</v>
-      </c>
-      <c r="E48">
-        <v>50</v>
-      </c>
-      <c r="F48" t="s">
-        <v>21</v>
-      </c>
-      <c r="G48">
-        <v>0</v>
-      </c>
-      <c r="H48">
-        <v>50</v>
-      </c>
-      <c r="I48" t="s">
-        <v>22</v>
-      </c>
-      <c r="J48" t="s">
-        <v>47</v>
-      </c>
-      <c r="K48" t="s">
-        <v>24</v>
-      </c>
-      <c r="L48" t="s">
-        <v>25</v>
-      </c>
-      <c r="M48" t="s">
-        <v>26</v>
-      </c>
-      <c r="N48" t="s">
-        <v>21</v>
-      </c>
-      <c r="O48" t="s">
-        <v>21</v>
-      </c>
-      <c r="P48" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q48" t="s">
-        <v>21</v>
-      </c>
-      <c r="R48" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>129</v>
-      </c>
-      <c r="B49" t="s">
-        <v>130</v>
-      </c>
-      <c r="C49" t="s">
-        <v>108</v>
-      </c>
-      <c r="D49" t="s">
-        <v>21</v>
-      </c>
-      <c r="E49">
-        <v>50</v>
-      </c>
-      <c r="F49" t="s">
-        <v>21</v>
-      </c>
-      <c r="G49">
-        <v>0</v>
-      </c>
-      <c r="H49">
-        <v>50</v>
-      </c>
-      <c r="I49" t="s">
-        <v>22</v>
-      </c>
-      <c r="J49" t="s">
-        <v>47</v>
-      </c>
-      <c r="K49" t="s">
-        <v>24</v>
-      </c>
-      <c r="L49" t="s">
-        <v>25</v>
-      </c>
-      <c r="M49" t="s">
-        <v>26</v>
-      </c>
-      <c r="N49" t="s">
-        <v>21</v>
-      </c>
-      <c r="O49" t="s">
-        <v>21</v>
-      </c>
-      <c r="P49" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q49" t="s">
-        <v>21</v>
-      </c>
-      <c r="R49" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>131</v>
-      </c>
-      <c r="B50" t="s">
-        <v>132</v>
-      </c>
-      <c r="C50" t="s">
-        <v>108</v>
-      </c>
-      <c r="D50" t="s">
-        <v>21</v>
-      </c>
-      <c r="E50">
-        <v>50</v>
-      </c>
-      <c r="F50" t="s">
-        <v>21</v>
-      </c>
-      <c r="G50">
-        <v>0</v>
-      </c>
-      <c r="H50">
-        <v>50</v>
-      </c>
-      <c r="I50" t="s">
-        <v>22</v>
-      </c>
-      <c r="J50" t="s">
-        <v>47</v>
-      </c>
-      <c r="K50" t="s">
-        <v>24</v>
-      </c>
-      <c r="L50" t="s">
-        <v>25</v>
-      </c>
-      <c r="M50" t="s">
-        <v>26</v>
-      </c>
-      <c r="N50" t="s">
-        <v>21</v>
-      </c>
-      <c r="O50" t="s">
-        <v>21</v>
-      </c>
-      <c r="P50" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q50" t="s">
-        <v>21</v>
-      </c>
-      <c r="R50" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>133</v>
-      </c>
-      <c r="B51" t="s">
-        <v>134</v>
-      </c>
-      <c r="C51" t="s">
-        <v>108</v>
-      </c>
-      <c r="D51" t="s">
-        <v>21</v>
-      </c>
-      <c r="E51">
-        <v>30</v>
-      </c>
-      <c r="F51" t="s">
-        <v>21</v>
-      </c>
-      <c r="G51">
-        <v>0</v>
-      </c>
-      <c r="H51">
-        <v>30</v>
-      </c>
-      <c r="I51" t="s">
-        <v>22</v>
-      </c>
-      <c r="J51" t="s">
-        <v>47</v>
-      </c>
-      <c r="K51" t="s">
-        <v>24</v>
-      </c>
-      <c r="L51" t="s">
-        <v>25</v>
-      </c>
-      <c r="M51" t="s">
-        <v>26</v>
-      </c>
-      <c r="N51" t="s">
-        <v>21</v>
-      </c>
-      <c r="O51" t="s">
-        <v>21</v>
-      </c>
-      <c r="P51" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q51" t="s">
-        <v>21</v>
-      </c>
-      <c r="R51" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>135</v>
-      </c>
-      <c r="B52" t="s">
-        <v>136</v>
-      </c>
-      <c r="C52" t="s">
-        <v>108</v>
-      </c>
-      <c r="D52" t="s">
-        <v>21</v>
-      </c>
-      <c r="E52">
-        <v>2</v>
-      </c>
-      <c r="F52" t="s">
-        <v>21</v>
-      </c>
-      <c r="G52">
-        <v>0</v>
-      </c>
-      <c r="H52">
-        <v>2</v>
-      </c>
-      <c r="I52" t="s">
-        <v>22</v>
-      </c>
-      <c r="J52" t="s">
-        <v>47</v>
-      </c>
-      <c r="K52" t="s">
-        <v>24</v>
-      </c>
-      <c r="L52" t="s">
-        <v>25</v>
-      </c>
-      <c r="M52" t="s">
-        <v>26</v>
-      </c>
-      <c r="N52" t="s">
-        <v>21</v>
-      </c>
-      <c r="O52" t="s">
-        <v>21</v>
-      </c>
-      <c r="P52" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q52" t="s">
-        <v>21</v>
-      </c>
-      <c r="R52" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>137</v>
-      </c>
-      <c r="B53" t="s">
-        <v>138</v>
-      </c>
-      <c r="C53" t="s">
-        <v>108</v>
-      </c>
-      <c r="D53" t="s">
-        <v>21</v>
-      </c>
-      <c r="E53">
-        <v>10</v>
-      </c>
-      <c r="F53" t="s">
-        <v>21</v>
-      </c>
-      <c r="G53">
-        <v>0</v>
-      </c>
-      <c r="H53">
-        <v>10</v>
-      </c>
-      <c r="I53" t="s">
-        <v>22</v>
-      </c>
-      <c r="J53" t="s">
-        <v>47</v>
-      </c>
-      <c r="K53" t="s">
-        <v>24</v>
-      </c>
-      <c r="L53" t="s">
-        <v>25</v>
-      </c>
-      <c r="M53" t="s">
-        <v>26</v>
-      </c>
-      <c r="N53" t="s">
-        <v>21</v>
-      </c>
-      <c r="O53" t="s">
-        <v>21</v>
-      </c>
-      <c r="P53" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q53" t="s">
-        <v>21</v>
-      </c>
-      <c r="R53" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>139</v>
-      </c>
-      <c r="B54" t="s">
-        <v>140</v>
-      </c>
-      <c r="C54" t="s">
-        <v>108</v>
-      </c>
-      <c r="D54" t="s">
-        <v>21</v>
-      </c>
-      <c r="E54">
-        <v>20</v>
-      </c>
-      <c r="F54" t="s">
-        <v>21</v>
-      </c>
-      <c r="G54">
-        <v>0</v>
-      </c>
-      <c r="H54">
-        <v>20</v>
-      </c>
-      <c r="I54" t="s">
-        <v>22</v>
-      </c>
-      <c r="J54" t="s">
-        <v>47</v>
-      </c>
-      <c r="K54" t="s">
-        <v>24</v>
-      </c>
-      <c r="L54" t="s">
-        <v>25</v>
-      </c>
-      <c r="M54" t="s">
-        <v>26</v>
-      </c>
-      <c r="N54" t="s">
-        <v>21</v>
-      </c>
-      <c r="O54" t="s">
-        <v>21</v>
-      </c>
-      <c r="P54" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q54" t="s">
-        <v>21</v>
-      </c>
-      <c r="R54" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>141</v>
-      </c>
-      <c r="B55" t="s">
-        <v>142</v>
-      </c>
-      <c r="C55" t="s">
-        <v>108</v>
-      </c>
-      <c r="D55" t="s">
-        <v>21</v>
-      </c>
-      <c r="E55">
-        <v>10</v>
-      </c>
-      <c r="F55" t="s">
-        <v>21</v>
-      </c>
-      <c r="G55">
-        <v>0</v>
-      </c>
-      <c r="H55">
-        <v>10</v>
-      </c>
-      <c r="I55" t="s">
-        <v>22</v>
-      </c>
-      <c r="J55" t="s">
-        <v>47</v>
-      </c>
-      <c r="K55" t="s">
-        <v>24</v>
-      </c>
-      <c r="L55" t="s">
-        <v>25</v>
-      </c>
-      <c r="M55" t="s">
-        <v>26</v>
-      </c>
-      <c r="N55" t="s">
-        <v>21</v>
-      </c>
-      <c r="O55" t="s">
-        <v>21</v>
-      </c>
-      <c r="P55" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q55" t="s">
-        <v>21</v>
-      </c>
-      <c r="R55" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>143</v>
-      </c>
-      <c r="B56" t="s">
-        <v>144</v>
-      </c>
-      <c r="C56" t="s">
-        <v>108</v>
-      </c>
-      <c r="D56" t="s">
-        <v>21</v>
-      </c>
-      <c r="E56">
-        <v>10</v>
-      </c>
-      <c r="F56" t="s">
-        <v>21</v>
-      </c>
-      <c r="G56">
-        <v>0</v>
-      </c>
-      <c r="H56">
-        <v>10</v>
-      </c>
-      <c r="I56" t="s">
-        <v>22</v>
-      </c>
-      <c r="J56" t="s">
-        <v>47</v>
-      </c>
-      <c r="K56" t="s">
-        <v>24</v>
-      </c>
-      <c r="L56" t="s">
-        <v>25</v>
-      </c>
-      <c r="M56" t="s">
-        <v>26</v>
-      </c>
-      <c r="N56" t="s">
-        <v>21</v>
-      </c>
-      <c r="O56" t="s">
-        <v>21</v>
-      </c>
-      <c r="P56" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q56" t="s">
-        <v>21</v>
-      </c>
-      <c r="R56" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>145</v>
-      </c>
-      <c r="B57" t="s">
-        <v>146</v>
-      </c>
-      <c r="C57" t="s">
-        <v>108</v>
-      </c>
-      <c r="D57" t="s">
-        <v>21</v>
-      </c>
-      <c r="E57">
-        <v>30</v>
-      </c>
-      <c r="F57" t="s">
-        <v>21</v>
-      </c>
-      <c r="G57">
-        <v>0</v>
-      </c>
-      <c r="H57">
-        <v>30</v>
-      </c>
-      <c r="I57" t="s">
-        <v>22</v>
-      </c>
-      <c r="J57" t="s">
-        <v>47</v>
-      </c>
-      <c r="K57" t="s">
-        <v>24</v>
-      </c>
-      <c r="L57" t="s">
-        <v>25</v>
-      </c>
-      <c r="M57" t="s">
-        <v>26</v>
-      </c>
-      <c r="N57" t="s">
-        <v>21</v>
-      </c>
-      <c r="O57" t="s">
-        <v>21</v>
-      </c>
-      <c r="P57" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q57" t="s">
-        <v>21</v>
-      </c>
-      <c r="R57" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>147</v>
-      </c>
-      <c r="B58" t="s">
-        <v>148</v>
-      </c>
-      <c r="C58" t="s">
-        <v>108</v>
-      </c>
-      <c r="D58" t="s">
-        <v>21</v>
-      </c>
-      <c r="E58">
-        <v>30</v>
-      </c>
-      <c r="F58" t="s">
-        <v>21</v>
-      </c>
-      <c r="G58">
-        <v>0</v>
-      </c>
-      <c r="H58">
-        <v>30</v>
-      </c>
-      <c r="I58" t="s">
-        <v>22</v>
-      </c>
-      <c r="J58" t="s">
-        <v>47</v>
-      </c>
-      <c r="K58" t="s">
-        <v>24</v>
-      </c>
-      <c r="L58" t="s">
-        <v>25</v>
-      </c>
-      <c r="M58" t="s">
-        <v>26</v>
-      </c>
-      <c r="N58" t="s">
-        <v>21</v>
-      </c>
-      <c r="O58" t="s">
-        <v>21</v>
-      </c>
-      <c r="P58" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q58" t="s">
-        <v>21</v>
-      </c>
-      <c r="R58" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>149</v>
-      </c>
-      <c r="B59" t="s">
-        <v>150</v>
-      </c>
-      <c r="C59" t="s">
-        <v>108</v>
-      </c>
-      <c r="D59" t="s">
-        <v>21</v>
-      </c>
-      <c r="E59">
-        <v>6</v>
-      </c>
-      <c r="F59" t="s">
-        <v>21</v>
-      </c>
-      <c r="G59">
-        <v>0</v>
-      </c>
-      <c r="H59">
-        <v>6</v>
-      </c>
-      <c r="I59" t="s">
-        <v>22</v>
-      </c>
-      <c r="J59" t="s">
-        <v>47</v>
-      </c>
-      <c r="K59" t="s">
-        <v>24</v>
-      </c>
-      <c r="L59" t="s">
-        <v>25</v>
-      </c>
-      <c r="M59" t="s">
-        <v>26</v>
-      </c>
-      <c r="N59" t="s">
-        <v>21</v>
-      </c>
-      <c r="O59" t="s">
-        <v>21</v>
-      </c>
-      <c r="P59" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q59" t="s">
-        <v>21</v>
-      </c>
-      <c r="R59" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>151</v>
-      </c>
-      <c r="B60" t="s">
-        <v>152</v>
-      </c>
-      <c r="C60" t="s">
-        <v>108</v>
-      </c>
-      <c r="D60" t="s">
-        <v>21</v>
-      </c>
-      <c r="E60">
-        <v>10</v>
-      </c>
-      <c r="F60" t="s">
-        <v>21</v>
-      </c>
-      <c r="G60">
-        <v>0</v>
-      </c>
-      <c r="H60">
-        <v>10</v>
-      </c>
-      <c r="I60" t="s">
-        <v>22</v>
-      </c>
-      <c r="J60" t="s">
-        <v>47</v>
-      </c>
-      <c r="K60" t="s">
-        <v>24</v>
-      </c>
-      <c r="L60" t="s">
-        <v>25</v>
-      </c>
-      <c r="M60" t="s">
-        <v>26</v>
-      </c>
-      <c r="N60" t="s">
-        <v>21</v>
-      </c>
-      <c r="O60" t="s">
-        <v>21</v>
-      </c>
-      <c r="P60" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q60" t="s">
-        <v>21</v>
-      </c>
-      <c r="R60" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>153</v>
-      </c>
-      <c r="B61" t="s">
-        <v>154</v>
-      </c>
-      <c r="C61" t="s">
-        <v>108</v>
-      </c>
-      <c r="D61" t="s">
-        <v>21</v>
-      </c>
-      <c r="E61">
-        <v>10</v>
-      </c>
-      <c r="F61" t="s">
-        <v>21</v>
-      </c>
-      <c r="G61">
-        <v>0</v>
-      </c>
-      <c r="H61">
-        <v>10</v>
-      </c>
-      <c r="I61" t="s">
-        <v>22</v>
-      </c>
-      <c r="J61" t="s">
-        <v>47</v>
-      </c>
-      <c r="K61" t="s">
-        <v>24</v>
-      </c>
-      <c r="L61" t="s">
-        <v>25</v>
-      </c>
-      <c r="M61" t="s">
-        <v>26</v>
-      </c>
-      <c r="N61" t="s">
-        <v>21</v>
-      </c>
-      <c r="O61" t="s">
-        <v>21</v>
-      </c>
-      <c r="P61" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q61" t="s">
-        <v>21</v>
-      </c>
-      <c r="R61" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>155</v>
-      </c>
-      <c r="B62" t="s">
-        <v>156</v>
-      </c>
-      <c r="C62" t="s">
-        <v>108</v>
-      </c>
-      <c r="D62" t="s">
-        <v>21</v>
-      </c>
-      <c r="E62">
-        <v>200</v>
-      </c>
-      <c r="F62" t="s">
-        <v>21</v>
-      </c>
-      <c r="G62">
-        <v>0</v>
-      </c>
-      <c r="H62">
-        <v>200</v>
-      </c>
-      <c r="I62" t="s">
-        <v>22</v>
-      </c>
-      <c r="J62" t="s">
-        <v>47</v>
-      </c>
-      <c r="K62" t="s">
-        <v>24</v>
-      </c>
-      <c r="L62" t="s">
-        <v>25</v>
-      </c>
-      <c r="M62" t="s">
-        <v>26</v>
-      </c>
-      <c r="N62" t="s">
-        <v>21</v>
-      </c>
-      <c r="O62" t="s">
-        <v>21</v>
-      </c>
-      <c r="P62" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q62" t="s">
-        <v>21</v>
-      </c>
-      <c r="R62" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>157</v>
-      </c>
-      <c r="B63" t="s">
-        <v>158</v>
-      </c>
-      <c r="C63" t="s">
-        <v>108</v>
-      </c>
-      <c r="D63" t="s">
-        <v>21</v>
-      </c>
-      <c r="E63">
-        <v>20</v>
-      </c>
-      <c r="F63" t="s">
-        <v>21</v>
-      </c>
-      <c r="G63">
-        <v>0</v>
-      </c>
-      <c r="H63">
-        <v>20</v>
-      </c>
-      <c r="I63" t="s">
-        <v>22</v>
-      </c>
-      <c r="J63" t="s">
-        <v>47</v>
-      </c>
-      <c r="K63" t="s">
-        <v>24</v>
-      </c>
-      <c r="L63" t="s">
-        <v>25</v>
-      </c>
-      <c r="M63" t="s">
-        <v>26</v>
-      </c>
-      <c r="N63" t="s">
-        <v>21</v>
-      </c>
-      <c r="O63" t="s">
-        <v>21</v>
-      </c>
-      <c r="P63" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q63" t="s">
-        <v>21</v>
-      </c>
-      <c r="R63" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>159</v>
-      </c>
-      <c r="B64" t="s">
-        <v>160</v>
-      </c>
-      <c r="C64" t="s">
-        <v>108</v>
-      </c>
-      <c r="D64" t="s">
-        <v>21</v>
-      </c>
-      <c r="E64">
-        <v>50</v>
-      </c>
-      <c r="F64" t="s">
-        <v>21</v>
-      </c>
-      <c r="G64">
-        <v>0</v>
-      </c>
-      <c r="H64">
-        <v>50</v>
-      </c>
-      <c r="I64" t="s">
-        <v>22</v>
-      </c>
-      <c r="J64" t="s">
-        <v>47</v>
-      </c>
-      <c r="K64" t="s">
-        <v>24</v>
-      </c>
-      <c r="L64" t="s">
-        <v>25</v>
-      </c>
-      <c r="M64" t="s">
-        <v>26</v>
-      </c>
-      <c r="N64" t="s">
-        <v>21</v>
-      </c>
-      <c r="O64" t="s">
-        <v>21</v>
-      </c>
-      <c r="P64" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q64" t="s">
-        <v>21</v>
-      </c>
-      <c r="R64" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>161</v>
-      </c>
-      <c r="B65" t="s">
-        <v>162</v>
-      </c>
-      <c r="C65" t="s">
-        <v>108</v>
-      </c>
-      <c r="D65" t="s">
-        <v>21</v>
-      </c>
-      <c r="E65">
-        <v>100</v>
-      </c>
-      <c r="F65" t="s">
-        <v>21</v>
-      </c>
-      <c r="G65">
-        <v>0</v>
-      </c>
-      <c r="H65">
-        <v>100</v>
-      </c>
-      <c r="I65" t="s">
-        <v>22</v>
-      </c>
-      <c r="J65" t="s">
-        <v>47</v>
-      </c>
-      <c r="K65" t="s">
-        <v>24</v>
-      </c>
-      <c r="L65" t="s">
-        <v>25</v>
-      </c>
-      <c r="M65" t="s">
-        <v>26</v>
-      </c>
-      <c r="N65" t="s">
-        <v>21</v>
-      </c>
-      <c r="O65" t="s">
-        <v>21</v>
-      </c>
-      <c r="P65" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q65" t="s">
-        <v>21</v>
-      </c>
-      <c r="R65" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>163</v>
-      </c>
-      <c r="B66" t="s">
-        <v>164</v>
-      </c>
-      <c r="C66" t="s">
-        <v>108</v>
-      </c>
-      <c r="D66" t="s">
-        <v>21</v>
-      </c>
-      <c r="E66">
-        <v>20</v>
-      </c>
-      <c r="F66" t="s">
-        <v>21</v>
-      </c>
-      <c r="G66">
-        <v>0</v>
-      </c>
-      <c r="H66">
-        <v>20</v>
-      </c>
-      <c r="I66" t="s">
-        <v>22</v>
-      </c>
-      <c r="J66" t="s">
-        <v>47</v>
-      </c>
-      <c r="K66" t="s">
-        <v>24</v>
-      </c>
-      <c r="L66" t="s">
-        <v>25</v>
-      </c>
-      <c r="M66" t="s">
-        <v>26</v>
-      </c>
-      <c r="N66" t="s">
-        <v>21</v>
-      </c>
-      <c r="O66" t="s">
-        <v>21</v>
-      </c>
-      <c r="P66" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q66" t="s">
-        <v>21</v>
-      </c>
-      <c r="R66" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
-        <v>165</v>
-      </c>
-      <c r="B67" t="s">
-        <v>166</v>
-      </c>
-      <c r="C67" t="s">
-        <v>108</v>
-      </c>
-      <c r="D67" t="s">
-        <v>21</v>
-      </c>
-      <c r="E67">
-        <v>200</v>
-      </c>
-      <c r="F67" t="s">
-        <v>21</v>
-      </c>
-      <c r="G67">
-        <v>0</v>
-      </c>
-      <c r="H67">
-        <v>200</v>
-      </c>
-      <c r="I67" t="s">
-        <v>22</v>
-      </c>
-      <c r="J67" t="s">
-        <v>47</v>
-      </c>
-      <c r="K67" t="s">
-        <v>24</v>
-      </c>
-      <c r="L67" t="s">
-        <v>25</v>
-      </c>
-      <c r="M67" t="s">
-        <v>26</v>
-      </c>
-      <c r="N67" t="s">
-        <v>21</v>
-      </c>
-      <c r="O67" t="s">
-        <v>21</v>
-      </c>
-      <c r="P67" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q67" t="s">
-        <v>21</v>
-      </c>
-      <c r="R67" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
-        <v>167</v>
-      </c>
-      <c r="B68" t="s">
-        <v>168</v>
-      </c>
-      <c r="C68" t="s">
-        <v>108</v>
-      </c>
-      <c r="D68" t="s">
-        <v>21</v>
-      </c>
-      <c r="E68">
-        <v>150</v>
-      </c>
-      <c r="F68" t="s">
-        <v>21</v>
-      </c>
-      <c r="G68">
-        <v>0</v>
-      </c>
-      <c r="H68">
-        <v>150</v>
-      </c>
-      <c r="I68" t="s">
-        <v>22</v>
-      </c>
-      <c r="J68" t="s">
-        <v>47</v>
-      </c>
-      <c r="K68" t="s">
-        <v>24</v>
-      </c>
-      <c r="L68" t="s">
-        <v>25</v>
-      </c>
-      <c r="M68" t="s">
-        <v>26</v>
-      </c>
-      <c r="N68" t="s">
-        <v>21</v>
-      </c>
-      <c r="O68" t="s">
-        <v>21</v>
-      </c>
-      <c r="P68" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q68" t="s">
-        <v>21</v>
-      </c>
-      <c r="R68" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
-        <v>169</v>
-      </c>
-      <c r="B69" t="s">
-        <v>170</v>
-      </c>
-      <c r="C69" t="s">
-        <v>108</v>
-      </c>
-      <c r="D69" t="s">
-        <v>21</v>
-      </c>
-      <c r="E69">
-        <v>50</v>
-      </c>
-      <c r="F69" t="s">
-        <v>21</v>
-      </c>
-      <c r="G69">
-        <v>0</v>
-      </c>
-      <c r="H69">
-        <v>50</v>
-      </c>
-      <c r="I69" t="s">
-        <v>22</v>
-      </c>
-      <c r="J69" t="s">
-        <v>47</v>
-      </c>
-      <c r="K69" t="s">
-        <v>24</v>
-      </c>
-      <c r="L69" t="s">
-        <v>25</v>
-      </c>
-      <c r="M69" t="s">
-        <v>26</v>
-      </c>
-      <c r="N69" t="s">
-        <v>21</v>
-      </c>
-      <c r="O69" t="s">
-        <v>21</v>
-      </c>
-      <c r="P69" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q69" t="s">
-        <v>21</v>
-      </c>
-      <c r="R69" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
-        <v>171</v>
-      </c>
-      <c r="B70" t="s">
-        <v>172</v>
-      </c>
-      <c r="C70" t="s">
-        <v>108</v>
-      </c>
-      <c r="D70" t="s">
-        <v>21</v>
-      </c>
-      <c r="E70">
-        <v>100</v>
-      </c>
-      <c r="F70" t="s">
-        <v>21</v>
-      </c>
-      <c r="G70">
-        <v>0</v>
-      </c>
-      <c r="H70">
-        <v>100</v>
-      </c>
-      <c r="I70" t="s">
-        <v>22</v>
-      </c>
-      <c r="J70" t="s">
-        <v>47</v>
-      </c>
-      <c r="K70" t="s">
-        <v>24</v>
-      </c>
-      <c r="L70" t="s">
-        <v>25</v>
-      </c>
-      <c r="M70" t="s">
-        <v>26</v>
-      </c>
-      <c r="N70" t="s">
-        <v>21</v>
-      </c>
-      <c r="O70" t="s">
-        <v>21</v>
-      </c>
-      <c r="P70" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q70" t="s">
-        <v>21</v>
-      </c>
-      <c r="R70" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>173</v>
-      </c>
-      <c r="B71" t="s">
-        <v>174</v>
-      </c>
-      <c r="C71" t="s">
-        <v>108</v>
-      </c>
-      <c r="D71" t="s">
-        <v>21</v>
-      </c>
-      <c r="E71">
-        <v>4</v>
-      </c>
-      <c r="F71" t="s">
-        <v>21</v>
-      </c>
-      <c r="G71">
-        <v>0</v>
-      </c>
-      <c r="H71">
-        <v>4</v>
-      </c>
-      <c r="I71" t="s">
-        <v>22</v>
-      </c>
-      <c r="J71" t="s">
-        <v>47</v>
-      </c>
-      <c r="K71" t="s">
-        <v>24</v>
-      </c>
-      <c r="L71" t="s">
-        <v>25</v>
-      </c>
-      <c r="M71" t="s">
-        <v>26</v>
-      </c>
-      <c r="N71" t="s">
-        <v>21</v>
-      </c>
-      <c r="O71" t="s">
-        <v>21</v>
-      </c>
-      <c r="P71" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q71" t="s">
-        <v>21</v>
-      </c>
-      <c r="R71" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>175</v>
-      </c>
-      <c r="B72" t="s">
-        <v>176</v>
-      </c>
-      <c r="C72" t="s">
-        <v>108</v>
-      </c>
-      <c r="D72" t="s">
-        <v>21</v>
-      </c>
-      <c r="E72">
-        <v>10</v>
-      </c>
-      <c r="F72" t="s">
-        <v>21</v>
-      </c>
-      <c r="G72">
-        <v>0</v>
-      </c>
-      <c r="H72">
-        <v>10</v>
-      </c>
-      <c r="I72" t="s">
-        <v>22</v>
-      </c>
-      <c r="J72" t="s">
-        <v>47</v>
-      </c>
-      <c r="K72" t="s">
-        <v>24</v>
-      </c>
-      <c r="L72" t="s">
-        <v>25</v>
-      </c>
-      <c r="M72" t="s">
-        <v>26</v>
-      </c>
-      <c r="N72" t="s">
-        <v>21</v>
-      </c>
-      <c r="O72" t="s">
-        <v>21</v>
-      </c>
-      <c r="P72" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q72" t="s">
-        <v>21</v>
-      </c>
-      <c r="R72" t="s">
         <v>27</v>
       </c>
     </row>

--- a/pc.xlsx
+++ b/pc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Claude\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA88DD15-1B2C-4F24-A479-827E9460479E}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0395A9A1-F525-445A-B2E9-A15C7C00D3FD}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="112">
   <si>
     <t>Cod. producto</t>
   </si>
@@ -127,24 +127,24 @@
     <t>Deposito NQN</t>
   </si>
   <si>
+    <t>C5OX-24-20F</t>
+  </si>
+  <si>
+    <t>ADAP CODO 90° MF 1.7/8" AS JIC 37° X MF 1.5/8" AS ORING</t>
+  </si>
+  <si>
+    <t>SOL - 2384</t>
+  </si>
+  <si>
+    <t>2026-07</t>
+  </si>
+  <si>
     <t>391-2882-051</t>
   </si>
   <si>
     <t>CUERDA P30 Y P50</t>
   </si>
   <si>
-    <t>SOL - 2384</t>
-  </si>
-  <si>
-    <t>2026-07</t>
-  </si>
-  <si>
-    <t>C5OX-24-20F</t>
-  </si>
-  <si>
-    <t>ADAP CODO 90° MF 1.7/8" AS JIC 37° X MF 1.5/8" AS ORING</t>
-  </si>
-  <si>
     <t>391-2884-021P</t>
   </si>
   <si>
@@ -181,13 +181,37 @@
     <t>SOL - 2489</t>
   </si>
   <si>
+    <t>FILT-D-AB-2</t>
+  </si>
+  <si>
+    <t>FILTRO AIRE RESP DESECANTE</t>
+  </si>
+  <si>
+    <t>SOL - 2493</t>
+  </si>
+  <si>
     <t>391-2883-119P</t>
   </si>
   <si>
     <t>RETEN M-30 P/EJE ENTERIZO</t>
   </si>
   <si>
-    <t>SOL - 2493</t>
+    <t>313-1135-194</t>
+  </si>
+  <si>
+    <t>EJE POSTIZO P50 Z14</t>
+  </si>
+  <si>
+    <t>313-5037-202</t>
+  </si>
+  <si>
+    <t>TROMPA P50 DE 5" X 4</t>
+  </si>
+  <si>
+    <t>391-0381-905</t>
+  </si>
+  <si>
+    <t>TORRINGTON P50</t>
   </si>
   <si>
     <t>PFQ723ZRR1R11</t>
@@ -196,54 +220,6 @@
     <t>MANOMETRO SERIE PFQ-ZR 4", 0/15.000 PSI - 0/1.000 bar, 1/2" NPT INFERIOR</t>
   </si>
   <si>
-    <t>FTX-06P</t>
-  </si>
-  <si>
-    <t>ADAP RECTO 9/16 UNF JIC X 1/4 NPT</t>
-  </si>
-  <si>
-    <t>313-1135-194</t>
-  </si>
-  <si>
-    <t>EJE POSTIZO P50 Z14</t>
-  </si>
-  <si>
-    <t>313-5037-202</t>
-  </si>
-  <si>
-    <t>TROMPA P50 DE 5" X 4</t>
-  </si>
-  <si>
-    <t>391-0381-905</t>
-  </si>
-  <si>
-    <t>TORRINGTON P50</t>
-  </si>
-  <si>
-    <t>AFS-102N</t>
-  </si>
-  <si>
-    <t>BRIDA SAE 1" PARA 3000 PSI</t>
-  </si>
-  <si>
-    <t>AFS-604</t>
-  </si>
-  <si>
-    <t>JGO DE1/2 BRIDAS SAE 1.1/4" NPT P/6000 PSI</t>
-  </si>
-  <si>
-    <t>FB-2</t>
-  </si>
-  <si>
-    <t>BOCA DE CARGA GRANDE BRIDADA 40 MIC.</t>
-  </si>
-  <si>
-    <t>FILT-D-AB-2</t>
-  </si>
-  <si>
-    <t>FILTRO AIRE RESP DESECANTE</t>
-  </si>
-  <si>
     <t>PFQ905R3R1</t>
   </si>
   <si>
@@ -274,12 +250,6 @@
     <t>VALVULA ESFERICA DE 2 VIAS, ALTA PRESION 1/4"</t>
   </si>
   <si>
-    <t>FT 257/6-14</t>
-  </si>
-  <si>
-    <t>VALVULA DE RETENCION EN LINEA RECTA 1/4" 30LPM - 500 BAR</t>
-  </si>
-  <si>
     <t>BUJE RED-2"x1.1/2" S3000</t>
   </si>
   <si>
@@ -386,27 +356,6 @@
   </si>
   <si>
     <t>MANGUERA GATES SAE100 R12 3/4"  12EFG4K X LL</t>
-  </si>
-  <si>
-    <t>BOBINAS DE ACCIONAMIENTO</t>
-  </si>
-  <si>
-    <t>BOBINAS DE ACCIONAMIENTO - GENERICO</t>
-  </si>
-  <si>
-    <t>SOL - 2501</t>
-  </si>
-  <si>
-    <t>00986</t>
-  </si>
-  <si>
-    <t>2026-09</t>
-  </si>
-  <si>
-    <t>HIDROIL SRL</t>
-  </si>
-  <si>
-    <t>Deposito</t>
   </si>
 </sst>
 </file>
@@ -758,7 +707,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R47"/>
+  <dimension ref="A1:R41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
@@ -1167,7 +1116,7 @@
         <v>21</v>
       </c>
       <c r="E8">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
         <v>21</v>
@@ -1176,7 +1125,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="I8" t="s">
         <v>22</v>
@@ -1223,7 +1172,7 @@
         <v>21</v>
       </c>
       <c r="E9">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F9" t="s">
         <v>21</v>
@@ -1232,7 +1181,7 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="I9" t="s">
         <v>22</v>
@@ -1447,7 +1396,7 @@
         <v>21</v>
       </c>
       <c r="E13">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
         <v>21</v>
@@ -1456,7 +1405,7 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="I13" t="s">
         <v>22</v>
@@ -1503,7 +1452,7 @@
         <v>21</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F14" t="s">
         <v>21</v>
@@ -1512,7 +1461,7 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="I14" t="s">
         <v>22</v>
@@ -1559,7 +1508,7 @@
         <v>21</v>
       </c>
       <c r="E15">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="F15" t="s">
         <v>21</v>
@@ -1568,7 +1517,7 @@
         <v>0</v>
       </c>
       <c r="H15">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="I15" t="s">
         <v>22</v>
@@ -1615,7 +1564,7 @@
         <v>21</v>
       </c>
       <c r="E16">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F16" t="s">
         <v>21</v>
@@ -1624,7 +1573,7 @@
         <v>0</v>
       </c>
       <c r="H16">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="I16" t="s">
         <v>22</v>
@@ -1671,7 +1620,7 @@
         <v>21</v>
       </c>
       <c r="E17">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="F17" t="s">
         <v>21</v>
@@ -1680,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="I17" t="s">
         <v>22</v>
@@ -1727,7 +1676,7 @@
         <v>21</v>
       </c>
       <c r="E18">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="F18" t="s">
         <v>21</v>
@@ -1736,7 +1685,7 @@
         <v>0</v>
       </c>
       <c r="H18">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="I18" t="s">
         <v>22</v>
@@ -1783,7 +1732,7 @@
         <v>21</v>
       </c>
       <c r="E19">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F19" t="s">
         <v>21</v>
@@ -1792,7 +1741,7 @@
         <v>0</v>
       </c>
       <c r="H19">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I19" t="s">
         <v>22</v>
@@ -1839,7 +1788,7 @@
         <v>21</v>
       </c>
       <c r="E20">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F20" t="s">
         <v>21</v>
@@ -1848,7 +1797,7 @@
         <v>0</v>
       </c>
       <c r="H20">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I20" t="s">
         <v>22</v>
@@ -1895,7 +1844,7 @@
         <v>21</v>
       </c>
       <c r="E21">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F21" t="s">
         <v>21</v>
@@ -1904,7 +1853,7 @@
         <v>0</v>
       </c>
       <c r="H21">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="I21" t="s">
         <v>22</v>
@@ -1951,7 +1900,7 @@
         <v>21</v>
       </c>
       <c r="E22">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F22" t="s">
         <v>21</v>
@@ -1960,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="H22">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I22" t="s">
         <v>22</v>
@@ -2063,7 +2012,7 @@
         <v>21</v>
       </c>
       <c r="E24">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F24" t="s">
         <v>21</v>
@@ -2072,7 +2021,7 @@
         <v>0</v>
       </c>
       <c r="H24">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I24" t="s">
         <v>22</v>
@@ -2119,7 +2068,7 @@
         <v>21</v>
       </c>
       <c r="E25">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="F25" t="s">
         <v>21</v>
@@ -2128,7 +2077,7 @@
         <v>0</v>
       </c>
       <c r="H25">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="I25" t="s">
         <v>22</v>
@@ -2175,7 +2124,7 @@
         <v>21</v>
       </c>
       <c r="E26">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F26" t="s">
         <v>21</v>
@@ -2184,7 +2133,7 @@
         <v>0</v>
       </c>
       <c r="H26">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="I26" t="s">
         <v>22</v>
@@ -2231,7 +2180,7 @@
         <v>21</v>
       </c>
       <c r="E27">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F27" t="s">
         <v>21</v>
@@ -2240,7 +2189,7 @@
         <v>0</v>
       </c>
       <c r="H27">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="I27" t="s">
         <v>22</v>
@@ -2287,7 +2236,7 @@
         <v>21</v>
       </c>
       <c r="E28">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F28" t="s">
         <v>21</v>
@@ -2296,7 +2245,7 @@
         <v>0</v>
       </c>
       <c r="H28">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I28" t="s">
         <v>22</v>
@@ -2343,7 +2292,7 @@
         <v>21</v>
       </c>
       <c r="E29">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="F29" t="s">
         <v>21</v>
@@ -2352,7 +2301,7 @@
         <v>0</v>
       </c>
       <c r="H29">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="I29" t="s">
         <v>22</v>
@@ -2511,7 +2460,7 @@
         <v>21</v>
       </c>
       <c r="E32">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F32" t="s">
         <v>21</v>
@@ -2520,7 +2469,7 @@
         <v>0</v>
       </c>
       <c r="H32">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="I32" t="s">
         <v>22</v>
@@ -2567,7 +2516,7 @@
         <v>21</v>
       </c>
       <c r="E33">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F33" t="s">
         <v>21</v>
@@ -2576,7 +2525,7 @@
         <v>0</v>
       </c>
       <c r="H33">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I33" t="s">
         <v>22</v>
@@ -2623,7 +2572,7 @@
         <v>21</v>
       </c>
       <c r="E34">
-        <v>200</v>
+        <v>40</v>
       </c>
       <c r="F34" t="s">
         <v>21</v>
@@ -2632,7 +2581,7 @@
         <v>0</v>
       </c>
       <c r="H34">
-        <v>200</v>
+        <v>40</v>
       </c>
       <c r="I34" t="s">
         <v>22</v>
@@ -2679,7 +2628,7 @@
         <v>21</v>
       </c>
       <c r="E35">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F35" t="s">
         <v>21</v>
@@ -2688,7 +2637,7 @@
         <v>0</v>
       </c>
       <c r="H35">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="I35" t="s">
         <v>22</v>
@@ -2791,7 +2740,7 @@
         <v>21</v>
       </c>
       <c r="E37">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F37" t="s">
         <v>21</v>
@@ -2800,7 +2749,7 @@
         <v>0</v>
       </c>
       <c r="H37">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="I37" t="s">
         <v>22</v>
@@ -2903,7 +2852,7 @@
         <v>21</v>
       </c>
       <c r="E39">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="F39" t="s">
         <v>21</v>
@@ -2912,7 +2861,7 @@
         <v>0</v>
       </c>
       <c r="H39">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="I39" t="s">
         <v>22</v>
@@ -2959,7 +2908,7 @@
         <v>21</v>
       </c>
       <c r="E40">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="F40" t="s">
         <v>21</v>
@@ -2968,7 +2917,7 @@
         <v>0</v>
       </c>
       <c r="H40">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="I40" t="s">
         <v>22</v>
@@ -3015,7 +2964,7 @@
         <v>21</v>
       </c>
       <c r="E41">
-        <v>50</v>
+        <v>1200</v>
       </c>
       <c r="F41" t="s">
         <v>21</v>
@@ -3024,7 +2973,7 @@
         <v>0</v>
       </c>
       <c r="H41">
-        <v>50</v>
+        <v>1200</v>
       </c>
       <c r="I41" t="s">
         <v>22</v>
@@ -3054,342 +3003,6 @@
         <v>21</v>
       </c>
       <c r="R41" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>112</v>
-      </c>
-      <c r="B42" t="s">
-        <v>113</v>
-      </c>
-      <c r="C42" t="s">
-        <v>55</v>
-      </c>
-      <c r="D42" t="s">
-        <v>21</v>
-      </c>
-      <c r="E42">
-        <v>50</v>
-      </c>
-      <c r="F42" t="s">
-        <v>21</v>
-      </c>
-      <c r="G42">
-        <v>0</v>
-      </c>
-      <c r="H42">
-        <v>50</v>
-      </c>
-      <c r="I42" t="s">
-        <v>22</v>
-      </c>
-      <c r="J42" t="s">
-        <v>47</v>
-      </c>
-      <c r="K42" t="s">
-        <v>24</v>
-      </c>
-      <c r="L42" t="s">
-        <v>25</v>
-      </c>
-      <c r="M42" t="s">
-        <v>26</v>
-      </c>
-      <c r="N42" t="s">
-        <v>21</v>
-      </c>
-      <c r="O42" t="s">
-        <v>21</v>
-      </c>
-      <c r="P42" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q42" t="s">
-        <v>21</v>
-      </c>
-      <c r="R42" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>114</v>
-      </c>
-      <c r="B43" t="s">
-        <v>115</v>
-      </c>
-      <c r="C43" t="s">
-        <v>55</v>
-      </c>
-      <c r="D43" t="s">
-        <v>21</v>
-      </c>
-      <c r="E43">
-        <v>30</v>
-      </c>
-      <c r="F43" t="s">
-        <v>21</v>
-      </c>
-      <c r="G43">
-        <v>0</v>
-      </c>
-      <c r="H43">
-        <v>30</v>
-      </c>
-      <c r="I43" t="s">
-        <v>22</v>
-      </c>
-      <c r="J43" t="s">
-        <v>47</v>
-      </c>
-      <c r="K43" t="s">
-        <v>24</v>
-      </c>
-      <c r="L43" t="s">
-        <v>25</v>
-      </c>
-      <c r="M43" t="s">
-        <v>26</v>
-      </c>
-      <c r="N43" t="s">
-        <v>21</v>
-      </c>
-      <c r="O43" t="s">
-        <v>21</v>
-      </c>
-      <c r="P43" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q43" t="s">
-        <v>21</v>
-      </c>
-      <c r="R43" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>116</v>
-      </c>
-      <c r="B44" t="s">
-        <v>117</v>
-      </c>
-      <c r="C44" t="s">
-        <v>55</v>
-      </c>
-      <c r="D44" t="s">
-        <v>21</v>
-      </c>
-      <c r="E44">
-        <v>100</v>
-      </c>
-      <c r="F44" t="s">
-        <v>21</v>
-      </c>
-      <c r="G44">
-        <v>0</v>
-      </c>
-      <c r="H44">
-        <v>100</v>
-      </c>
-      <c r="I44" t="s">
-        <v>22</v>
-      </c>
-      <c r="J44" t="s">
-        <v>47</v>
-      </c>
-      <c r="K44" t="s">
-        <v>24</v>
-      </c>
-      <c r="L44" t="s">
-        <v>25</v>
-      </c>
-      <c r="M44" t="s">
-        <v>26</v>
-      </c>
-      <c r="N44" t="s">
-        <v>21</v>
-      </c>
-      <c r="O44" t="s">
-        <v>21</v>
-      </c>
-      <c r="P44" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q44" t="s">
-        <v>21</v>
-      </c>
-      <c r="R44" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>118</v>
-      </c>
-      <c r="B45" t="s">
-        <v>119</v>
-      </c>
-      <c r="C45" t="s">
-        <v>55</v>
-      </c>
-      <c r="D45" t="s">
-        <v>21</v>
-      </c>
-      <c r="E45">
-        <v>300</v>
-      </c>
-      <c r="F45" t="s">
-        <v>21</v>
-      </c>
-      <c r="G45">
-        <v>0</v>
-      </c>
-      <c r="H45">
-        <v>300</v>
-      </c>
-      <c r="I45" t="s">
-        <v>22</v>
-      </c>
-      <c r="J45" t="s">
-        <v>47</v>
-      </c>
-      <c r="K45" t="s">
-        <v>24</v>
-      </c>
-      <c r="L45" t="s">
-        <v>25</v>
-      </c>
-      <c r="M45" t="s">
-        <v>26</v>
-      </c>
-      <c r="N45" t="s">
-        <v>21</v>
-      </c>
-      <c r="O45" t="s">
-        <v>21</v>
-      </c>
-      <c r="P45" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q45" t="s">
-        <v>21</v>
-      </c>
-      <c r="R45" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>120</v>
-      </c>
-      <c r="B46" t="s">
-        <v>121</v>
-      </c>
-      <c r="C46" t="s">
-        <v>55</v>
-      </c>
-      <c r="D46" t="s">
-        <v>21</v>
-      </c>
-      <c r="E46">
-        <v>1200</v>
-      </c>
-      <c r="F46" t="s">
-        <v>21</v>
-      </c>
-      <c r="G46">
-        <v>0</v>
-      </c>
-      <c r="H46">
-        <v>1200</v>
-      </c>
-      <c r="I46" t="s">
-        <v>22</v>
-      </c>
-      <c r="J46" t="s">
-        <v>47</v>
-      </c>
-      <c r="K46" t="s">
-        <v>24</v>
-      </c>
-      <c r="L46" t="s">
-        <v>25</v>
-      </c>
-      <c r="M46" t="s">
-        <v>26</v>
-      </c>
-      <c r="N46" t="s">
-        <v>21</v>
-      </c>
-      <c r="O46" t="s">
-        <v>21</v>
-      </c>
-      <c r="P46" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q46" t="s">
-        <v>21</v>
-      </c>
-      <c r="R46" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>122</v>
-      </c>
-      <c r="B47" t="s">
-        <v>123</v>
-      </c>
-      <c r="C47" t="s">
-        <v>124</v>
-      </c>
-      <c r="D47" t="s">
-        <v>125</v>
-      </c>
-      <c r="E47">
-        <v>1</v>
-      </c>
-      <c r="F47" t="s">
-        <v>21</v>
-      </c>
-      <c r="G47">
-        <v>0</v>
-      </c>
-      <c r="H47">
-        <v>1</v>
-      </c>
-      <c r="I47" t="s">
-        <v>22</v>
-      </c>
-      <c r="J47" t="s">
-        <v>126</v>
-      </c>
-      <c r="K47" t="s">
-        <v>127</v>
-      </c>
-      <c r="L47" t="s">
-        <v>25</v>
-      </c>
-      <c r="M47" t="s">
-        <v>128</v>
-      </c>
-      <c r="N47" t="s">
-        <v>21</v>
-      </c>
-      <c r="O47" t="s">
-        <v>21</v>
-      </c>
-      <c r="P47" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q47" t="s">
-        <v>21</v>
-      </c>
-      <c r="R47" t="s">
         <v>27</v>
       </c>
     </row>

--- a/pc.xlsx
+++ b/pc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Claude\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0395A9A1-F525-445A-B2E9-A15C7C00D3FD}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{08C417B9-89D8-4756-9559-D237BCF6F12E}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="138">
   <si>
     <t>Cod. producto</t>
   </si>
@@ -127,30 +127,30 @@
     <t>Deposito NQN</t>
   </si>
   <si>
+    <t>391-2882-051</t>
+  </si>
+  <si>
+    <t>CUERDA P30 Y P50</t>
+  </si>
+  <si>
+    <t>SOL - 2384</t>
+  </si>
+  <si>
+    <t>2026-07</t>
+  </si>
+  <si>
+    <t>391-2884-021P</t>
+  </si>
+  <si>
+    <t>SELLO GOMA SQUARE GASKET 50-25</t>
+  </si>
+  <si>
     <t>C5OX-24-20F</t>
   </si>
   <si>
     <t>ADAP CODO 90° MF 1.7/8" AS JIC 37° X MF 1.5/8" AS ORING</t>
   </si>
   <si>
-    <t>SOL - 2384</t>
-  </si>
-  <si>
-    <t>2026-07</t>
-  </si>
-  <si>
-    <t>391-2882-051</t>
-  </si>
-  <si>
-    <t>CUERDA P30 Y P50</t>
-  </si>
-  <si>
-    <t>391-2884-021P</t>
-  </si>
-  <si>
-    <t>SELLO GOMA SQUARE GASKET 50-25</t>
-  </si>
-  <si>
     <t>RACORDS Y CAMISAS</t>
   </si>
   <si>
@@ -181,73 +181,133 @@
     <t>SOL - 2489</t>
   </si>
   <si>
+    <t>46511385</t>
+  </si>
+  <si>
+    <t>MANGUERA GATES SAE100 R12 3/4"  12EFG4K X LL</t>
+  </si>
+  <si>
+    <t>SOL - 2493</t>
+  </si>
+  <si>
+    <t>391-2883-119P</t>
+  </si>
+  <si>
+    <t>RETEN M-30 P/EJE ENTERIZO</t>
+  </si>
+  <si>
+    <t>313-1135-194</t>
+  </si>
+  <si>
+    <t>EJE POSTIZO P50 Z14</t>
+  </si>
+  <si>
+    <t>313-5037-202</t>
+  </si>
+  <si>
+    <t>TROMPA P50 DE 5" X 4</t>
+  </si>
+  <si>
+    <t>391-0381-905</t>
+  </si>
+  <si>
+    <t>TORRINGTON P50</t>
+  </si>
+  <si>
+    <t>2500-3500-375B</t>
+  </si>
+  <si>
+    <t>POLYPAK 88.90 x 101.60 x 9.52</t>
+  </si>
+  <si>
+    <t>FT 221/1-14</t>
+  </si>
+  <si>
+    <t>VALVULA ESFERICA DE 2 VIAS, ALTA PRESION 1/4"</t>
+  </si>
+  <si>
+    <t>AC02G-90</t>
+  </si>
+  <si>
+    <t>ALEMITE GAS 90° 1/8"</t>
+  </si>
+  <si>
+    <t>AR02G</t>
+  </si>
+  <si>
+    <t>ALEMITE RECTO DE 1/8" GAS</t>
+  </si>
+  <si>
+    <t>MA-310</t>
+  </si>
+  <si>
+    <t>PISTOLA CUENTA LTS DIGITAL VULCANO</t>
+  </si>
+  <si>
+    <t>PFQ723ZRR1R11</t>
+  </si>
+  <si>
+    <t>MANOMETRO SERIE PFQ-ZR 4", 0/15.000 PSI - 0/1.000 bar, 1/2" NPT INFERIOR</t>
+  </si>
+  <si>
+    <t>PFQ905R3R1</t>
+  </si>
+  <si>
+    <t>MANOMETRO 2,5" ROSCA POSTERIOR 1/4 NPT 0-10 BAR C/GLICERINA</t>
+  </si>
+  <si>
+    <t>PFQ908R3R1</t>
+  </si>
+  <si>
+    <t>MANOMETRO 2,5" ROSCA POSTERIOR 1/4 NPT 0-40 BAR C/GLICERINA</t>
+  </si>
+  <si>
+    <t>PFQ918R3R1</t>
+  </si>
+  <si>
+    <t>MANOMETRO 2,5" ROSCA POSTERIOR 1/4 NPT 0-600 BAR C/GLICERINA</t>
+  </si>
+  <si>
     <t>FILT-D-AB-2</t>
   </si>
   <si>
     <t>FILTRO AIRE RESP DESECANTE</t>
   </si>
   <si>
-    <t>SOL - 2493</t>
-  </si>
-  <si>
-    <t>391-2883-119P</t>
-  </si>
-  <si>
-    <t>RETEN M-30 P/EJE ENTERIZO</t>
-  </si>
-  <si>
-    <t>313-1135-194</t>
-  </si>
-  <si>
-    <t>EJE POSTIZO P50 Z14</t>
-  </si>
-  <si>
-    <t>313-5037-202</t>
-  </si>
-  <si>
-    <t>TROMPA P50 DE 5" X 4</t>
-  </si>
-  <si>
-    <t>391-0381-905</t>
-  </si>
-  <si>
-    <t>TORRINGTON P50</t>
-  </si>
-  <si>
-    <t>PFQ723ZRR1R11</t>
-  </si>
-  <si>
-    <t>MANOMETRO SERIE PFQ-ZR 4", 0/15.000 PSI - 0/1.000 bar, 1/2" NPT INFERIOR</t>
-  </si>
-  <si>
-    <t>PFQ905R3R1</t>
-  </si>
-  <si>
-    <t>MANOMETRO 2,5" ROSCA POSTERIOR 1/4 NPT 0-10 BAR C/GLICERINA</t>
-  </si>
-  <si>
-    <t>PFQ908R3R1</t>
-  </si>
-  <si>
-    <t>MANOMETRO 2,5" ROSCA POSTERIOR 1/4 NPT 0-40 BAR C/GLICERINA</t>
-  </si>
-  <si>
-    <t>PFQ918R3R1</t>
-  </si>
-  <si>
-    <t>MANOMETRO 2,5" ROSCA POSTERIOR 1/4 NPT 0-600 BAR C/GLICERINA</t>
-  </si>
-  <si>
-    <t>2500-3500-375B</t>
-  </si>
-  <si>
-    <t>POLYPAK 88.90 x 101.60 x 9.52</t>
-  </si>
-  <si>
-    <t>FT 221/1-14</t>
-  </si>
-  <si>
-    <t>VALVULA ESFERICA DE 2 VIAS, ALTA PRESION 1/4"</t>
+    <t>TAPA-3/4" S3000</t>
+  </si>
+  <si>
+    <t>TAPA HEMBRA 3/4" NPT SERIE 3000</t>
+  </si>
+  <si>
+    <t>TAPON-1" S3000</t>
+  </si>
+  <si>
+    <t>TAPON MACHO 1" NPT SERIE 3000</t>
+  </si>
+  <si>
+    <t>TAPON-1/4" S3000</t>
+  </si>
+  <si>
+    <t>TAPON MACHO 1/4" NPT SERIE 3000</t>
+  </si>
+  <si>
+    <t>TAPON-3/4" S3000</t>
+  </si>
+  <si>
+    <t>TAPON MACHO 3/4" NPT SERIE 3000</t>
+  </si>
+  <si>
+    <t>TAPON-3/8" S3000</t>
+  </si>
+  <si>
+    <t>TAPON MACHO 3/8" NPT SERIE 3000</t>
+  </si>
+  <si>
+    <t>TEE-1/2" S3000</t>
+  </si>
+  <si>
+    <t>TEE H x H x H 1/2" NPT SERIE 3000</t>
   </si>
   <si>
     <t>BUJE RED-2"x1.1/2" S3000</t>
@@ -298,64 +358,82 @@
     <t>ENTRERROSCA 3/4" NPT SERIE 3000</t>
   </si>
   <si>
-    <t>MA-310</t>
-  </si>
-  <si>
-    <t>PISTOLA CUENTA LTS DIGITAL VULCANO</t>
-  </si>
-  <si>
-    <t>TAPA-3/4" S3000</t>
-  </si>
-  <si>
-    <t>TAPA HEMBRA 3/4" NPT SERIE 3000</t>
-  </si>
-  <si>
-    <t>TAPON-1" S3000</t>
-  </si>
-  <si>
-    <t>TAPON MACHO 1" NPT SERIE 3000</t>
-  </si>
-  <si>
-    <t>TAPON-1/4" S3000</t>
-  </si>
-  <si>
-    <t>TAPON MACHO 1/4" NPT SERIE 3000</t>
-  </si>
-  <si>
-    <t>TAPON-3/4" S3000</t>
-  </si>
-  <si>
-    <t>TAPON MACHO 3/4" NPT SERIE 3000</t>
-  </si>
-  <si>
-    <t>TAPON-3/8" S3000</t>
-  </si>
-  <si>
-    <t>TAPON MACHO 3/8" NPT SERIE 3000</t>
-  </si>
-  <si>
-    <t>TEE-1/2" S3000</t>
-  </si>
-  <si>
-    <t>TEE H x H x H 1/2" NPT SERIE 3000</t>
-  </si>
-  <si>
-    <t>AC02G-90</t>
-  </si>
-  <si>
-    <t>ALEMITE GAS 90° 1/8"</t>
-  </si>
-  <si>
-    <t>AR02G</t>
-  </si>
-  <si>
-    <t>ALEMITE RECTO DE 1/8" GAS</t>
-  </si>
-  <si>
-    <t>46511385</t>
-  </si>
-  <si>
-    <t>MANGUERA GATES SAE100 R12 3/4"  12EFG4K X LL</t>
+    <t>AFS-102N</t>
+  </si>
+  <si>
+    <t>BRIDA SAE 1" PARA 3000 PSI</t>
+  </si>
+  <si>
+    <t>SOL - 2504</t>
+  </si>
+  <si>
+    <t>2026-09</t>
+  </si>
+  <si>
+    <t>AFS-106N</t>
+  </si>
+  <si>
+    <t>BRIDA SAE 1.1/2" NPT PARA 3000 PSI</t>
+  </si>
+  <si>
+    <t>F5OG-10-1/2P</t>
+  </si>
+  <si>
+    <t>ADAP RECTO MF 7/8" UNF AS ORING X HEMBRA FIJA 1/2" NPT</t>
+  </si>
+  <si>
+    <t>F5OG-12-3/4P</t>
+  </si>
+  <si>
+    <t>ADAP RECTO MF 1.1/16" UNF AS ORING X HEMBRA FIJA 3/4" NPT</t>
+  </si>
+  <si>
+    <t>G6X-06</t>
+  </si>
+  <si>
+    <t>ADAP RECTO HG JIC 9/16" X HF NPT 1/4"</t>
+  </si>
+  <si>
+    <t>G6X-06-06</t>
+  </si>
+  <si>
+    <t>ADAP RECTO HG JIC 9/16" X HF NPT 3/8"</t>
+  </si>
+  <si>
+    <t>G6X-08</t>
+  </si>
+  <si>
+    <t>ADAP RECTO HG JIC 3/4" X HF NPT 3/8"</t>
+  </si>
+  <si>
+    <t>G6X-08-08</t>
+  </si>
+  <si>
+    <t>ADAP RECTO HG JIC 3/4" X HF NPT 1/2"</t>
+  </si>
+  <si>
+    <t>G6X-10</t>
+  </si>
+  <si>
+    <t>ADAP RECTO HG JIC 7/8" X HF NPT 1/2"</t>
+  </si>
+  <si>
+    <t>X6EF-06F</t>
+  </si>
+  <si>
+    <t>ADAP CODO 90° FORJADO HG JIC 9/16" UNF x MF 1/4" NPT</t>
+  </si>
+  <si>
+    <t>VALVULA NEUMATICA</t>
+  </si>
+  <si>
+    <t>VALVULA NEUMATICA - GENERICO</t>
+  </si>
+  <si>
+    <t>SOL - 2506</t>
+  </si>
+  <si>
+    <t>01046</t>
   </si>
 </sst>
 </file>
@@ -707,7 +785,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R41"/>
+  <dimension ref="A1:R52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
@@ -780,7 +858,7 @@
         <v>21</v>
       </c>
       <c r="E2">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F2" t="s">
         <v>21</v>
@@ -789,7 +867,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I2" t="s">
         <v>22</v>
@@ -948,7 +1026,7 @@
         <v>21</v>
       </c>
       <c r="E5">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F5" t="s">
         <v>21</v>
@@ -957,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="I5" t="s">
         <v>22</v>
@@ -1116,7 +1194,7 @@
         <v>21</v>
       </c>
       <c r="E8">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F8" t="s">
         <v>21</v>
@@ -1125,7 +1203,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="I8" t="s">
         <v>22</v>
@@ -1172,7 +1250,7 @@
         <v>21</v>
       </c>
       <c r="E9">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F9" t="s">
         <v>21</v>
@@ -1181,7 +1259,7 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I9" t="s">
         <v>22</v>
@@ -1228,7 +1306,7 @@
         <v>21</v>
       </c>
       <c r="E10">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
         <v>21</v>
@@ -1237,7 +1315,7 @@
         <v>0</v>
       </c>
       <c r="H10">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="I10" t="s">
         <v>22</v>
@@ -1396,7 +1474,7 @@
         <v>21</v>
       </c>
       <c r="E13">
-        <v>6</v>
+        <v>1200</v>
       </c>
       <c r="F13" t="s">
         <v>21</v>
@@ -1405,7 +1483,7 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>6</v>
+        <v>1200</v>
       </c>
       <c r="I13" t="s">
         <v>22</v>
@@ -1676,7 +1754,7 @@
         <v>21</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F18" t="s">
         <v>21</v>
@@ -1685,7 +1763,7 @@
         <v>0</v>
       </c>
       <c r="H18">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I18" t="s">
         <v>22</v>
@@ -1788,7 +1866,7 @@
         <v>21</v>
       </c>
       <c r="E20">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F20" t="s">
         <v>21</v>
@@ -1797,7 +1875,7 @@
         <v>0</v>
       </c>
       <c r="H20">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="I20" t="s">
         <v>22</v>
@@ -1844,7 +1922,7 @@
         <v>21</v>
       </c>
       <c r="E21">
-        <v>10</v>
+        <v>300</v>
       </c>
       <c r="F21" t="s">
         <v>21</v>
@@ -1853,7 +1931,7 @@
         <v>0</v>
       </c>
       <c r="H21">
-        <v>10</v>
+        <v>300</v>
       </c>
       <c r="I21" t="s">
         <v>22</v>
@@ -1900,7 +1978,7 @@
         <v>21</v>
       </c>
       <c r="E22">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F22" t="s">
         <v>21</v>
@@ -1909,7 +1987,7 @@
         <v>0</v>
       </c>
       <c r="H22">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I22" t="s">
         <v>22</v>
@@ -1956,7 +2034,7 @@
         <v>21</v>
       </c>
       <c r="E23">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F23" t="s">
         <v>21</v>
@@ -1965,7 +2043,7 @@
         <v>0</v>
       </c>
       <c r="H23">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I23" t="s">
         <v>22</v>
@@ -2068,7 +2146,7 @@
         <v>21</v>
       </c>
       <c r="E25">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="F25" t="s">
         <v>21</v>
@@ -2077,7 +2155,7 @@
         <v>0</v>
       </c>
       <c r="H25">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="I25" t="s">
         <v>22</v>
@@ -2124,7 +2202,7 @@
         <v>21</v>
       </c>
       <c r="E26">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F26" t="s">
         <v>21</v>
@@ -2133,7 +2211,7 @@
         <v>0</v>
       </c>
       <c r="H26">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="I26" t="s">
         <v>22</v>
@@ -2180,7 +2258,7 @@
         <v>21</v>
       </c>
       <c r="E27">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="F27" t="s">
         <v>21</v>
@@ -2189,7 +2267,7 @@
         <v>0</v>
       </c>
       <c r="H27">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="I27" t="s">
         <v>22</v>
@@ -2236,7 +2314,7 @@
         <v>21</v>
       </c>
       <c r="E28">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F28" t="s">
         <v>21</v>
@@ -2245,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="H28">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I28" t="s">
         <v>22</v>
@@ -2292,7 +2370,7 @@
         <v>21</v>
       </c>
       <c r="E29">
-        <v>200</v>
+        <v>40</v>
       </c>
       <c r="F29" t="s">
         <v>21</v>
@@ -2301,7 +2379,7 @@
         <v>0</v>
       </c>
       <c r="H29">
-        <v>200</v>
+        <v>40</v>
       </c>
       <c r="I29" t="s">
         <v>22</v>
@@ -2348,7 +2426,7 @@
         <v>21</v>
       </c>
       <c r="E30">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F30" t="s">
         <v>21</v>
@@ -2357,7 +2435,7 @@
         <v>0</v>
       </c>
       <c r="H30">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="I30" t="s">
         <v>22</v>
@@ -2460,7 +2538,7 @@
         <v>21</v>
       </c>
       <c r="E32">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F32" t="s">
         <v>21</v>
@@ -2469,7 +2547,7 @@
         <v>0</v>
       </c>
       <c r="H32">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="I32" t="s">
         <v>22</v>
@@ -2572,7 +2650,7 @@
         <v>21</v>
       </c>
       <c r="E34">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F34" t="s">
         <v>21</v>
@@ -2581,7 +2659,7 @@
         <v>0</v>
       </c>
       <c r="H34">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="I34" t="s">
         <v>22</v>
@@ -2628,7 +2706,7 @@
         <v>21</v>
       </c>
       <c r="E35">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="F35" t="s">
         <v>21</v>
@@ -2637,7 +2715,7 @@
         <v>0</v>
       </c>
       <c r="H35">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="I35" t="s">
         <v>22</v>
@@ -2740,7 +2818,7 @@
         <v>21</v>
       </c>
       <c r="E37">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F37" t="s">
         <v>21</v>
@@ -2749,7 +2827,7 @@
         <v>0</v>
       </c>
       <c r="H37">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I37" t="s">
         <v>22</v>
@@ -2796,7 +2874,7 @@
         <v>21</v>
       </c>
       <c r="E38">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F38" t="s">
         <v>21</v>
@@ -2805,7 +2883,7 @@
         <v>0</v>
       </c>
       <c r="H38">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I38" t="s">
         <v>22</v>
@@ -2852,7 +2930,7 @@
         <v>21</v>
       </c>
       <c r="E39">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F39" t="s">
         <v>21</v>
@@ -2861,7 +2939,7 @@
         <v>0</v>
       </c>
       <c r="H39">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I39" t="s">
         <v>22</v>
@@ -2908,7 +2986,7 @@
         <v>21</v>
       </c>
       <c r="E40">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="F40" t="s">
         <v>21</v>
@@ -2917,7 +2995,7 @@
         <v>0</v>
       </c>
       <c r="H40">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="I40" t="s">
         <v>22</v>
@@ -2964,7 +3042,7 @@
         <v>21</v>
       </c>
       <c r="E41">
-        <v>1200</v>
+        <v>50</v>
       </c>
       <c r="F41" t="s">
         <v>21</v>
@@ -2973,7 +3051,7 @@
         <v>0</v>
       </c>
       <c r="H41">
-        <v>1200</v>
+        <v>50</v>
       </c>
       <c r="I41" t="s">
         <v>22</v>
@@ -3003,6 +3081,622 @@
         <v>21</v>
       </c>
       <c r="R41" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>112</v>
+      </c>
+      <c r="B42" t="s">
+        <v>113</v>
+      </c>
+      <c r="C42" t="s">
+        <v>114</v>
+      </c>
+      <c r="D42" t="s">
+        <v>21</v>
+      </c>
+      <c r="E42">
+        <v>3</v>
+      </c>
+      <c r="F42" t="s">
+        <v>21</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>3</v>
+      </c>
+      <c r="I42" t="s">
+        <v>22</v>
+      </c>
+      <c r="J42" t="s">
+        <v>115</v>
+      </c>
+      <c r="K42" t="s">
+        <v>24</v>
+      </c>
+      <c r="L42" t="s">
+        <v>25</v>
+      </c>
+      <c r="M42" t="s">
+        <v>26</v>
+      </c>
+      <c r="N42" t="s">
+        <v>21</v>
+      </c>
+      <c r="O42" t="s">
+        <v>21</v>
+      </c>
+      <c r="P42" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>21</v>
+      </c>
+      <c r="R42" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>116</v>
+      </c>
+      <c r="B43" t="s">
+        <v>117</v>
+      </c>
+      <c r="C43" t="s">
+        <v>114</v>
+      </c>
+      <c r="D43" t="s">
+        <v>21</v>
+      </c>
+      <c r="E43">
+        <v>5</v>
+      </c>
+      <c r="F43" t="s">
+        <v>21</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>5</v>
+      </c>
+      <c r="I43" t="s">
+        <v>22</v>
+      </c>
+      <c r="J43" t="s">
+        <v>115</v>
+      </c>
+      <c r="K43" t="s">
+        <v>24</v>
+      </c>
+      <c r="L43" t="s">
+        <v>25</v>
+      </c>
+      <c r="M43" t="s">
+        <v>26</v>
+      </c>
+      <c r="N43" t="s">
+        <v>21</v>
+      </c>
+      <c r="O43" t="s">
+        <v>21</v>
+      </c>
+      <c r="P43" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>21</v>
+      </c>
+      <c r="R43" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>118</v>
+      </c>
+      <c r="B44" t="s">
+        <v>119</v>
+      </c>
+      <c r="C44" t="s">
+        <v>114</v>
+      </c>
+      <c r="D44" t="s">
+        <v>21</v>
+      </c>
+      <c r="E44">
+        <v>5</v>
+      </c>
+      <c r="F44" t="s">
+        <v>21</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>5</v>
+      </c>
+      <c r="I44" t="s">
+        <v>22</v>
+      </c>
+      <c r="J44" t="s">
+        <v>115</v>
+      </c>
+      <c r="K44" t="s">
+        <v>24</v>
+      </c>
+      <c r="L44" t="s">
+        <v>25</v>
+      </c>
+      <c r="M44" t="s">
+        <v>26</v>
+      </c>
+      <c r="N44" t="s">
+        <v>21</v>
+      </c>
+      <c r="O44" t="s">
+        <v>21</v>
+      </c>
+      <c r="P44" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>21</v>
+      </c>
+      <c r="R44" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>120</v>
+      </c>
+      <c r="B45" t="s">
+        <v>121</v>
+      </c>
+      <c r="C45" t="s">
+        <v>114</v>
+      </c>
+      <c r="D45" t="s">
+        <v>21</v>
+      </c>
+      <c r="E45">
+        <v>5</v>
+      </c>
+      <c r="F45" t="s">
+        <v>21</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>5</v>
+      </c>
+      <c r="I45" t="s">
+        <v>22</v>
+      </c>
+      <c r="J45" t="s">
+        <v>115</v>
+      </c>
+      <c r="K45" t="s">
+        <v>24</v>
+      </c>
+      <c r="L45" t="s">
+        <v>25</v>
+      </c>
+      <c r="M45" t="s">
+        <v>26</v>
+      </c>
+      <c r="N45" t="s">
+        <v>21</v>
+      </c>
+      <c r="O45" t="s">
+        <v>21</v>
+      </c>
+      <c r="P45" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>21</v>
+      </c>
+      <c r="R45" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>122</v>
+      </c>
+      <c r="B46" t="s">
+        <v>123</v>
+      </c>
+      <c r="C46" t="s">
+        <v>114</v>
+      </c>
+      <c r="D46" t="s">
+        <v>21</v>
+      </c>
+      <c r="E46">
+        <v>10</v>
+      </c>
+      <c r="F46" t="s">
+        <v>21</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>10</v>
+      </c>
+      <c r="I46" t="s">
+        <v>22</v>
+      </c>
+      <c r="J46" t="s">
+        <v>115</v>
+      </c>
+      <c r="K46" t="s">
+        <v>24</v>
+      </c>
+      <c r="L46" t="s">
+        <v>25</v>
+      </c>
+      <c r="M46" t="s">
+        <v>26</v>
+      </c>
+      <c r="N46" t="s">
+        <v>21</v>
+      </c>
+      <c r="O46" t="s">
+        <v>21</v>
+      </c>
+      <c r="P46" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>21</v>
+      </c>
+      <c r="R46" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>124</v>
+      </c>
+      <c r="B47" t="s">
+        <v>125</v>
+      </c>
+      <c r="C47" t="s">
+        <v>114</v>
+      </c>
+      <c r="D47" t="s">
+        <v>21</v>
+      </c>
+      <c r="E47">
+        <v>10</v>
+      </c>
+      <c r="F47" t="s">
+        <v>21</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>10</v>
+      </c>
+      <c r="I47" t="s">
+        <v>22</v>
+      </c>
+      <c r="J47" t="s">
+        <v>115</v>
+      </c>
+      <c r="K47" t="s">
+        <v>24</v>
+      </c>
+      <c r="L47" t="s">
+        <v>25</v>
+      </c>
+      <c r="M47" t="s">
+        <v>26</v>
+      </c>
+      <c r="N47" t="s">
+        <v>21</v>
+      </c>
+      <c r="O47" t="s">
+        <v>21</v>
+      </c>
+      <c r="P47" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>21</v>
+      </c>
+      <c r="R47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>126</v>
+      </c>
+      <c r="B48" t="s">
+        <v>127</v>
+      </c>
+      <c r="C48" t="s">
+        <v>114</v>
+      </c>
+      <c r="D48" t="s">
+        <v>21</v>
+      </c>
+      <c r="E48">
+        <v>10</v>
+      </c>
+      <c r="F48" t="s">
+        <v>21</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>10</v>
+      </c>
+      <c r="I48" t="s">
+        <v>22</v>
+      </c>
+      <c r="J48" t="s">
+        <v>115</v>
+      </c>
+      <c r="K48" t="s">
+        <v>24</v>
+      </c>
+      <c r="L48" t="s">
+        <v>25</v>
+      </c>
+      <c r="M48" t="s">
+        <v>26</v>
+      </c>
+      <c r="N48" t="s">
+        <v>21</v>
+      </c>
+      <c r="O48" t="s">
+        <v>21</v>
+      </c>
+      <c r="P48" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>21</v>
+      </c>
+      <c r="R48" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>128</v>
+      </c>
+      <c r="B49" t="s">
+        <v>129</v>
+      </c>
+      <c r="C49" t="s">
+        <v>114</v>
+      </c>
+      <c r="D49" t="s">
+        <v>21</v>
+      </c>
+      <c r="E49">
+        <v>10</v>
+      </c>
+      <c r="F49" t="s">
+        <v>21</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>10</v>
+      </c>
+      <c r="I49" t="s">
+        <v>22</v>
+      </c>
+      <c r="J49" t="s">
+        <v>115</v>
+      </c>
+      <c r="K49" t="s">
+        <v>24</v>
+      </c>
+      <c r="L49" t="s">
+        <v>25</v>
+      </c>
+      <c r="M49" t="s">
+        <v>26</v>
+      </c>
+      <c r="N49" t="s">
+        <v>21</v>
+      </c>
+      <c r="O49" t="s">
+        <v>21</v>
+      </c>
+      <c r="P49" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>21</v>
+      </c>
+      <c r="R49" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>130</v>
+      </c>
+      <c r="B50" t="s">
+        <v>131</v>
+      </c>
+      <c r="C50" t="s">
+        <v>114</v>
+      </c>
+      <c r="D50" t="s">
+        <v>21</v>
+      </c>
+      <c r="E50">
+        <v>10</v>
+      </c>
+      <c r="F50" t="s">
+        <v>21</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>10</v>
+      </c>
+      <c r="I50" t="s">
+        <v>22</v>
+      </c>
+      <c r="J50" t="s">
+        <v>115</v>
+      </c>
+      <c r="K50" t="s">
+        <v>24</v>
+      </c>
+      <c r="L50" t="s">
+        <v>25</v>
+      </c>
+      <c r="M50" t="s">
+        <v>26</v>
+      </c>
+      <c r="N50" t="s">
+        <v>21</v>
+      </c>
+      <c r="O50" t="s">
+        <v>21</v>
+      </c>
+      <c r="P50" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>21</v>
+      </c>
+      <c r="R50" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>132</v>
+      </c>
+      <c r="B51" t="s">
+        <v>133</v>
+      </c>
+      <c r="C51" t="s">
+        <v>114</v>
+      </c>
+      <c r="D51" t="s">
+        <v>21</v>
+      </c>
+      <c r="E51">
+        <v>15</v>
+      </c>
+      <c r="F51" t="s">
+        <v>21</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>15</v>
+      </c>
+      <c r="I51" t="s">
+        <v>22</v>
+      </c>
+      <c r="J51" t="s">
+        <v>115</v>
+      </c>
+      <c r="K51" t="s">
+        <v>24</v>
+      </c>
+      <c r="L51" t="s">
+        <v>25</v>
+      </c>
+      <c r="M51" t="s">
+        <v>26</v>
+      </c>
+      <c r="N51" t="s">
+        <v>21</v>
+      </c>
+      <c r="O51" t="s">
+        <v>21</v>
+      </c>
+      <c r="P51" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>21</v>
+      </c>
+      <c r="R51" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>134</v>
+      </c>
+      <c r="B52" t="s">
+        <v>135</v>
+      </c>
+      <c r="C52" t="s">
+        <v>136</v>
+      </c>
+      <c r="D52" t="s">
+        <v>137</v>
+      </c>
+      <c r="E52">
+        <v>5</v>
+      </c>
+      <c r="F52" t="s">
+        <v>21</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>5</v>
+      </c>
+      <c r="I52" t="s">
+        <v>22</v>
+      </c>
+      <c r="J52" t="s">
+        <v>115</v>
+      </c>
+      <c r="K52" t="s">
+        <v>33</v>
+      </c>
+      <c r="L52" t="s">
+        <v>25</v>
+      </c>
+      <c r="M52" t="s">
+        <v>34</v>
+      </c>
+      <c r="N52" t="s">
+        <v>21</v>
+      </c>
+      <c r="O52" t="s">
+        <v>21</v>
+      </c>
+      <c r="P52" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>21</v>
+      </c>
+      <c r="R52" t="s">
         <v>27</v>
       </c>
     </row>
